--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -83,7 +83,7 @@
       <color rgb="000000FF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +115,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -142,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -292,7 +297,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -775,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M24"/>
+  <dimension ref="B1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1348,10 +1359,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>Astuce : choisir « Référence » remet tous les leviers à 0 → le modèle reproduit l'atterrissage.</t>
-        </is>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Inflation des charges externes (→ coûts)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H19" s="31">
+        <f>INDEX(D19:G19,MATCH($D$3,$D$13:$G$13,0))</f>
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
@@ -1371,18 +1403,33 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>③ Constantes de référence (scénarisables)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+    <row r="20">
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Politique salariale (→ personnel)</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H20" s="31">
+        <f>INDEX(D20:G20,MATCH($D$3,$D$13:$G$13,0))</f>
+        <v/>
+      </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
           <t>Tunon</t>
@@ -1402,135 +1449,155 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Leviers 1-5 → CA (moteur) · leviers 6-7 → coûts (P&amp;L Budget N+1). « Référence » remet tout à 0 = atterrissage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>③ Constantes de référence (scénarisables)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Paramètre</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Référence</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Cadrage</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Optimiste</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Prudent</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>ACTIF</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>Rendement d'acquisition (part payante)</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H22" s="34">
-        <f>INDEX(D22:G22,MATCH($D$3,$D$13:$G$13,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Part organique des leads (hors budget)</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G23" s="30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H23" s="31">
-        <f>INDEX(D23:G23,MATCH($D$3,$D$13:$G$13,0))</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="27" t="inlineStr">
         <is>
+          <t>Rendement d'acquisition (part payante)</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="34">
+        <f>INDEX(D24:G24,MATCH($D$3,$D$13:$G$13,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Part organique des leads (hors budget)</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H25" s="31">
+        <f>INDEX(D25:G25,MATCH($D$3,$D$13:$G$13,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="27" t="inlineStr">
+        <is>
           <t>Frais de dossier / nouvel inscrit</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D26" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="E24" s="36" t="n">
+      <c r="E26" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="F24" s="36" t="n">
+      <c r="F26" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G26" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="H24" s="37">
-        <f>INDEX(D24:G24,MATCH($D$3,$D$13:$G$13,0))</f>
+      <c r="H26" s="37">
+        <f>INDEX(D26:G26,MATCH($D$3,$D$13:$G$13,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="B22:H22"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="J5:M5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -6114,7 +6181,7 @@
         <v/>
       </c>
       <c r="E5" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F5" s="24">
@@ -6137,7 +6204,7 @@
         <v/>
       </c>
       <c r="K5" s="22">
-        <f>G5*(J5/I5)^'01_Cadrage'!$H$22</f>
+        <f>G5*(J5/I5)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L5" s="22">
@@ -6169,7 +6236,7 @@
         <v/>
       </c>
       <c r="E6" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F6" s="24">
@@ -6192,7 +6259,7 @@
         <v/>
       </c>
       <c r="K6" s="22">
-        <f>G6*(J6/I6)^'01_Cadrage'!$H$22</f>
+        <f>G6*(J6/I6)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L6" s="22">
@@ -6224,7 +6291,7 @@
         <v/>
       </c>
       <c r="E7" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F7" s="24">
@@ -6247,7 +6314,7 @@
         <v/>
       </c>
       <c r="K7" s="22">
-        <f>G7*(J7/I7)^'01_Cadrage'!$H$22</f>
+        <f>G7*(J7/I7)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L7" s="22">
@@ -6279,7 +6346,7 @@
         <v/>
       </c>
       <c r="E8" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F8" s="24">
@@ -6302,7 +6369,7 @@
         <v/>
       </c>
       <c r="K8" s="22">
-        <f>G8*(J8/I8)^'01_Cadrage'!$H$22</f>
+        <f>G8*(J8/I8)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L8" s="22">
@@ -6334,7 +6401,7 @@
         <v/>
       </c>
       <c r="E9" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F9" s="24">
@@ -6357,7 +6424,7 @@
         <v/>
       </c>
       <c r="K9" s="22">
-        <f>G9*(J9/I9)^'01_Cadrage'!$H$22</f>
+        <f>G9*(J9/I9)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L9" s="22">
@@ -6389,7 +6456,7 @@
         <v/>
       </c>
       <c r="E10" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F10" s="24">
@@ -6412,7 +6479,7 @@
         <v/>
       </c>
       <c r="K10" s="22">
-        <f>G10*(J10/I10)^'01_Cadrage'!$H$22</f>
+        <f>G10*(J10/I10)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L10" s="22">
@@ -6444,7 +6511,7 @@
         <v/>
       </c>
       <c r="E11" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F11" s="24">
@@ -6467,7 +6534,7 @@
         <v/>
       </c>
       <c r="K11" s="22">
-        <f>G11*(J11/I11)^'01_Cadrage'!$H$22</f>
+        <f>G11*(J11/I11)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L11" s="22">
@@ -6499,7 +6566,7 @@
         <v/>
       </c>
       <c r="E12" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F12" s="24">
@@ -6522,7 +6589,7 @@
         <v/>
       </c>
       <c r="K12" s="22">
-        <f>G12*(J12/I12)^'01_Cadrage'!$H$22</f>
+        <f>G12*(J12/I12)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L12" s="22">
@@ -6554,7 +6621,7 @@
         <v/>
       </c>
       <c r="E13" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F13" s="24">
@@ -6577,7 +6644,7 @@
         <v/>
       </c>
       <c r="K13" s="22">
-        <f>G13*(J13/I13)^'01_Cadrage'!$H$22</f>
+        <f>G13*(J13/I13)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L13" s="22">
@@ -6609,7 +6676,7 @@
         <v/>
       </c>
       <c r="E14" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F14" s="24">
@@ -6632,7 +6699,7 @@
         <v/>
       </c>
       <c r="K14" s="22">
-        <f>G14*(J14/I14)^'01_Cadrage'!$H$22</f>
+        <f>G14*(J14/I14)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L14" s="22">
@@ -6664,7 +6731,7 @@
         <v/>
       </c>
       <c r="E15" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F15" s="24">
@@ -6687,7 +6754,7 @@
         <v/>
       </c>
       <c r="K15" s="22">
-        <f>G15*(J15/I15)^'01_Cadrage'!$H$22</f>
+        <f>G15*(J15/I15)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L15" s="22">
@@ -6719,7 +6786,7 @@
         <v/>
       </c>
       <c r="E16" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F16" s="24">
@@ -6742,7 +6809,7 @@
         <v/>
       </c>
       <c r="K16" s="22">
-        <f>G16*(J16/I16)^'01_Cadrage'!$H$22</f>
+        <f>G16*(J16/I16)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L16" s="22">
@@ -6774,7 +6841,7 @@
         <v/>
       </c>
       <c r="E17" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F17" s="24">
@@ -6797,7 +6864,7 @@
         <v/>
       </c>
       <c r="K17" s="22">
-        <f>G17*(J17/I17)^'01_Cadrage'!$H$22</f>
+        <f>G17*(J17/I17)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L17" s="22">
@@ -6829,7 +6896,7 @@
         <v/>
       </c>
       <c r="E18" s="41">
-        <f>'01_Cadrage'!$H$23</f>
+        <f>'01_Cadrage'!$H$25</f>
         <v/>
       </c>
       <c r="F18" s="24">
@@ -6852,7 +6919,7 @@
         <v/>
       </c>
       <c r="K18" s="22">
-        <f>G18*(J18/I18)^'01_Cadrage'!$H$22</f>
+        <f>G18*(J18/I18)^'01_Cadrage'!$H$24</f>
         <v/>
       </c>
       <c r="L18" s="22">
@@ -7161,7 +7228,7 @@
         <v/>
       </c>
       <c r="AA4" s="13">
-        <f>Y4*Z4+W4*'01_Cadrage'!$H$24</f>
+        <f>Y4*Z4+W4*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7271,7 +7338,7 @@
         <v/>
       </c>
       <c r="AA5" s="13">
-        <f>Y5*Z5+W5*'01_Cadrage'!$H$24</f>
+        <f>Y5*Z5+W5*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7381,7 +7448,7 @@
         <v/>
       </c>
       <c r="AA6" s="13">
-        <f>Y6*Z6+W6*'01_Cadrage'!$H$24</f>
+        <f>Y6*Z6+W6*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7491,7 +7558,7 @@
         <v/>
       </c>
       <c r="AA7" s="13">
-        <f>Y7*Z7+W7*'01_Cadrage'!$H$24</f>
+        <f>Y7*Z7+W7*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7601,7 +7668,7 @@
         <v/>
       </c>
       <c r="AA8" s="13">
-        <f>Y8*Z8+W8*'01_Cadrage'!$H$24</f>
+        <f>Y8*Z8+W8*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7711,7 +7778,7 @@
         <v/>
       </c>
       <c r="AA9" s="13">
-        <f>Y9*Z9+W9*'01_Cadrage'!$H$24</f>
+        <f>Y9*Z9+W9*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7821,7 +7888,7 @@
         <v/>
       </c>
       <c r="AA10" s="13">
-        <f>Y10*Z10+W10*'01_Cadrage'!$H$24</f>
+        <f>Y10*Z10+W10*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -7931,7 +7998,7 @@
         <v/>
       </c>
       <c r="AA11" s="13">
-        <f>Y11*Z11+W11*'01_Cadrage'!$H$24</f>
+        <f>Y11*Z11+W11*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8041,7 +8108,7 @@
         <v/>
       </c>
       <c r="AA12" s="13">
-        <f>Y12*Z12+W12*'01_Cadrage'!$H$24</f>
+        <f>Y12*Z12+W12*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8151,7 +8218,7 @@
         <v/>
       </c>
       <c r="AA13" s="13">
-        <f>Y13*Z13+W13*'01_Cadrage'!$H$24</f>
+        <f>Y13*Z13+W13*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8261,7 +8328,7 @@
         <v/>
       </c>
       <c r="AA14" s="13">
-        <f>Y14*Z14+W14*'01_Cadrage'!$H$24</f>
+        <f>Y14*Z14+W14*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8371,7 +8438,7 @@
         <v/>
       </c>
       <c r="AA15" s="13">
-        <f>Y15*Z15+W15*'01_Cadrage'!$H$24</f>
+        <f>Y15*Z15+W15*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8481,7 +8548,7 @@
         <v/>
       </c>
       <c r="AA16" s="13">
-        <f>Y16*Z16+W16*'01_Cadrage'!$H$24</f>
+        <f>Y16*Z16+W16*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8591,7 +8658,7 @@
         <v/>
       </c>
       <c r="AA17" s="13">
-        <f>Y17*Z17+W17*'01_Cadrage'!$H$24</f>
+        <f>Y17*Z17+W17*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8701,7 +8768,7 @@
         <v/>
       </c>
       <c r="AA18" s="13">
-        <f>Y18*Z18+W18*'01_Cadrage'!$H$24</f>
+        <f>Y18*Z18+W18*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8811,7 +8878,7 @@
         <v/>
       </c>
       <c r="AA19" s="13">
-        <f>Y19*Z19+W19*'01_Cadrage'!$H$24</f>
+        <f>Y19*Z19+W19*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -8921,7 +8988,7 @@
         <v/>
       </c>
       <c r="AA20" s="13">
-        <f>Y20*Z20+W20*'01_Cadrage'!$H$24</f>
+        <f>Y20*Z20+W20*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9031,7 +9098,7 @@
         <v/>
       </c>
       <c r="AA21" s="13">
-        <f>Y21*Z21+W21*'01_Cadrage'!$H$24</f>
+        <f>Y21*Z21+W21*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9141,7 +9208,7 @@
         <v/>
       </c>
       <c r="AA22" s="13">
-        <f>Y22*Z22+W22*'01_Cadrage'!$H$24</f>
+        <f>Y22*Z22+W22*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9251,7 +9318,7 @@
         <v/>
       </c>
       <c r="AA23" s="13">
-        <f>Y23*Z23+W23*'01_Cadrage'!$H$24</f>
+        <f>Y23*Z23+W23*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9361,7 +9428,7 @@
         <v/>
       </c>
       <c r="AA24" s="13">
-        <f>Y24*Z24+W24*'01_Cadrage'!$H$24</f>
+        <f>Y24*Z24+W24*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9471,7 +9538,7 @@
         <v/>
       </c>
       <c r="AA25" s="13">
-        <f>Y25*Z25+W25*'01_Cadrage'!$H$24</f>
+        <f>Y25*Z25+W25*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9581,7 +9648,7 @@
         <v/>
       </c>
       <c r="AA26" s="13">
-        <f>Y26*Z26+W26*'01_Cadrage'!$H$24</f>
+        <f>Y26*Z26+W26*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9691,7 +9758,7 @@
         <v/>
       </c>
       <c r="AA27" s="13">
-        <f>Y27*Z27+W27*'01_Cadrage'!$H$24</f>
+        <f>Y27*Z27+W27*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9801,7 +9868,7 @@
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>Y28*Z28+W28*'01_Cadrage'!$H$24</f>
+        <f>Y28*Z28+W28*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -9911,7 +9978,7 @@
         <v/>
       </c>
       <c r="AA29" s="13">
-        <f>Y29*Z29+W29*'01_Cadrage'!$H$24</f>
+        <f>Y29*Z29+W29*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10021,7 +10088,7 @@
         <v/>
       </c>
       <c r="AA30" s="13">
-        <f>Y30*Z30+W30*'01_Cadrage'!$H$24</f>
+        <f>Y30*Z30+W30*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10131,7 +10198,7 @@
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>Y31*Z31+W31*'01_Cadrage'!$H$24</f>
+        <f>Y31*Z31+W31*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10241,7 +10308,7 @@
         <v/>
       </c>
       <c r="AA32" s="13">
-        <f>Y32*Z32+W32*'01_Cadrage'!$H$24</f>
+        <f>Y32*Z32+W32*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10351,7 +10418,7 @@
         <v/>
       </c>
       <c r="AA33" s="13">
-        <f>Y33*Z33+W33*'01_Cadrage'!$H$24</f>
+        <f>Y33*Z33+W33*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10461,7 +10528,7 @@
         <v/>
       </c>
       <c r="AA34" s="13">
-        <f>Y34*Z34+W34*'01_Cadrage'!$H$24</f>
+        <f>Y34*Z34+W34*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10571,7 +10638,7 @@
         <v/>
       </c>
       <c r="AA35" s="13">
-        <f>Y35*Z35+W35*'01_Cadrage'!$H$24</f>
+        <f>Y35*Z35+W35*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10681,7 +10748,7 @@
         <v/>
       </c>
       <c r="AA36" s="13">
-        <f>Y36*Z36+W36*'01_Cadrage'!$H$24</f>
+        <f>Y36*Z36+W36*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10791,7 +10858,7 @@
         <v/>
       </c>
       <c r="AA37" s="13">
-        <f>Y37*Z37+W37*'01_Cadrage'!$H$24</f>
+        <f>Y37*Z37+W37*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -10901,7 +10968,7 @@
         <v/>
       </c>
       <c r="AA38" s="13">
-        <f>Y38*Z38+W38*'01_Cadrage'!$H$24</f>
+        <f>Y38*Z38+W38*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11011,7 +11078,7 @@
         <v/>
       </c>
       <c r="AA39" s="13">
-        <f>Y39*Z39+W39*'01_Cadrage'!$H$24</f>
+        <f>Y39*Z39+W39*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11121,7 +11188,7 @@
         <v/>
       </c>
       <c r="AA40" s="13">
-        <f>Y40*Z40+W40*'01_Cadrage'!$H$24</f>
+        <f>Y40*Z40+W40*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11231,7 +11298,7 @@
         <v/>
       </c>
       <c r="AA41" s="13">
-        <f>Y41*Z41+W41*'01_Cadrage'!$H$24</f>
+        <f>Y41*Z41+W41*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11341,7 +11408,7 @@
         <v/>
       </c>
       <c r="AA42" s="13">
-        <f>Y42*Z42+W42*'01_Cadrage'!$H$24</f>
+        <f>Y42*Z42+W42*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11451,7 +11518,7 @@
         <v/>
       </c>
       <c r="AA43" s="13">
-        <f>Y43*Z43+W43*'01_Cadrage'!$H$24</f>
+        <f>Y43*Z43+W43*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11561,7 +11628,7 @@
         <v/>
       </c>
       <c r="AA44" s="13">
-        <f>Y44*Z44+W44*'01_Cadrage'!$H$24</f>
+        <f>Y44*Z44+W44*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11671,7 +11738,7 @@
         <v/>
       </c>
       <c r="AA45" s="13">
-        <f>Y45*Z45+W45*'01_Cadrage'!$H$24</f>
+        <f>Y45*Z45+W45*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11781,7 +11848,7 @@
         <v/>
       </c>
       <c r="AA46" s="13">
-        <f>Y46*Z46+W46*'01_Cadrage'!$H$24</f>
+        <f>Y46*Z46+W46*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -11891,7 +11958,7 @@
         <v/>
       </c>
       <c r="AA47" s="13">
-        <f>Y47*Z47+W47*'01_Cadrage'!$H$24</f>
+        <f>Y47*Z47+W47*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12001,7 +12068,7 @@
         <v/>
       </c>
       <c r="AA48" s="13">
-        <f>Y48*Z48+W48*'01_Cadrage'!$H$24</f>
+        <f>Y48*Z48+W48*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12111,7 +12178,7 @@
         <v/>
       </c>
       <c r="AA49" s="13">
-        <f>Y49*Z49+W49*'01_Cadrage'!$H$24</f>
+        <f>Y49*Z49+W49*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12221,7 +12288,7 @@
         <v/>
       </c>
       <c r="AA50" s="13">
-        <f>Y50*Z50+W50*'01_Cadrage'!$H$24</f>
+        <f>Y50*Z50+W50*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12331,7 +12398,7 @@
         <v/>
       </c>
       <c r="AA51" s="13">
-        <f>Y51*Z51+W51*'01_Cadrage'!$H$24</f>
+        <f>Y51*Z51+W51*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12441,7 +12508,7 @@
         <v/>
       </c>
       <c r="AA52" s="13">
-        <f>Y52*Z52+W52*'01_Cadrage'!$H$24</f>
+        <f>Y52*Z52+W52*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12551,7 +12618,7 @@
         <v/>
       </c>
       <c r="AA53" s="13">
-        <f>Y53*Z53+W53*'01_Cadrage'!$H$24</f>
+        <f>Y53*Z53+W53*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12661,7 +12728,7 @@
         <v/>
       </c>
       <c r="AA54" s="13">
-        <f>Y54*Z54+W54*'01_Cadrage'!$H$24</f>
+        <f>Y54*Z54+W54*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12771,7 +12838,7 @@
         <v/>
       </c>
       <c r="AA55" s="13">
-        <f>Y55*Z55+W55*'01_Cadrage'!$H$24</f>
+        <f>Y55*Z55+W55*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12881,7 +12948,7 @@
         <v/>
       </c>
       <c r="AA56" s="13">
-        <f>Y56*Z56+W56*'01_Cadrage'!$H$24</f>
+        <f>Y56*Z56+W56*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -12991,7 +13058,7 @@
         <v/>
       </c>
       <c r="AA57" s="13">
-        <f>Y57*Z57+W57*'01_Cadrage'!$H$24</f>
+        <f>Y57*Z57+W57*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -13101,7 +13168,7 @@
         <v/>
       </c>
       <c r="AA58" s="13">
-        <f>Y58*Z58+W58*'01_Cadrage'!$H$24</f>
+        <f>Y58*Z58+W58*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -13211,7 +13278,7 @@
         <v/>
       </c>
       <c r="AA59" s="13">
-        <f>Y59*Z59+W59*'01_Cadrage'!$H$24</f>
+        <f>Y59*Z59+W59*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -13321,7 +13388,7 @@
         <v/>
       </c>
       <c r="AA60" s="13">
-        <f>Y60*Z60+W60*'01_Cadrage'!$H$24</f>
+        <f>Y60*Z60+W60*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -13431,7 +13498,7 @@
         <v/>
       </c>
       <c r="AA61" s="13">
-        <f>Y61*Z61+W61*'01_Cadrage'!$H$24</f>
+        <f>Y61*Z61+W61*'01_Cadrage'!$H$26</f>
         <v/>
       </c>
     </row>
@@ -56252,7 +56319,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>COMPTE DE RÉSULTAT (SIG) — réalisé N-2 · réalisé N-1 · atterrissage N</t>
+          <t>COMPTE DE RÉSULTAT (SIG) — réalisé N-2 · N-1 · atterrissage N · BUDGET N+1 (piloté par le cadrage)</t>
         </is>
       </c>
     </row>
@@ -56284,12 +56351,12 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>Var N-1→N €</t>
+          <t>🟢 Budget N+1</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Var %</t>
+          <t>Var Bud/Att %</t>
         </is>
       </c>
     </row>
@@ -56329,12 +56396,12 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"7062",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G5" s="15">
-        <f>F5-E5</f>
+      <c r="G5" s="53">
+        <f>F5*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>IFERROR((F5-E5)/E5,0)</f>
+        <f>IFERROR(G5/F5-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56361,12 +56428,12 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"706",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G6" s="15">
-        <f>F6-E6</f>
+      <c r="G6" s="53">
+        <f>F6*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>IFERROR((F6-E6)/E6,0)</f>
+        <f>IFERROR(G6/F6-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56393,17 +56460,17 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"708",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G7" s="15">
-        <f>F7-E7</f>
+      <c r="G7" s="53">
+        <f>F7*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>IFERROR((F7-E7)/E7,0)</f>
+        <f>IFERROR(G7/F7-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="53" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t> </t>
         </is>
@@ -56425,12 +56492,12 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Produit",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G8" s="46">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="54">
-        <f>IFERROR((F8-E8)/E8,0)</f>
+      <c r="G8" s="55">
+        <f>G5+G6+G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="56">
+        <f>IFERROR(G8/F8-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56470,12 +56537,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"621",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G10" s="15">
-        <f>F10-E10</f>
+      <c r="G10" s="53">
+        <f>F10*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>IFERROR((F10-E10)/E10,0)</f>
+        <f>IFERROR(G10/F10-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56502,12 +56569,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"604",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G11" s="15">
-        <f>F11-E11</f>
+      <c r="G11" s="53">
+        <f>F11*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>IFERROR((F11-E11)/E11,0)</f>
+        <f>IFERROR(G11/F11-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56534,12 +56601,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6063",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G12" s="15">
-        <f>F12-E12</f>
+      <c r="G12" s="53">
+        <f>F12*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>IFERROR((F12-E12)/E12,0)</f>
+        <f>IFERROR(G12/F12-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56566,17 +56633,17 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6231",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G13" s="15">
-        <f>F13-E13</f>
+      <c r="G13" s="53">
+        <f>F13*('04_Moteur'!$AA$62/21936350)</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>IFERROR((F13-E13)/E13,0)</f>
+        <f>IFERROR(G13/F13-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="53" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t> </t>
         </is>
@@ -56598,12 +56665,12 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Produit",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$I$4:$I$675,"Coûts directs",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G14" s="46">
-        <f>F14-E14</f>
-        <v/>
-      </c>
-      <c r="H14" s="54">
-        <f>IFERROR((F14-E14)/E14,0)</f>
+      <c r="G14" s="55">
+        <f>G5+G6+G7+G10+G11+G12+G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="56">
+        <f>IFERROR(G14/F14-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56643,12 +56710,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6411",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G16" s="15">
-        <f>F16-E16</f>
+      <c r="G16" s="53">
+        <f>F16*(('04_Moteur'!$Y$62/2952)*(1+'01_Cadrage'!$H$20))</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>IFERROR((F16-E16)/E16,0)</f>
+        <f>IFERROR(G16/F16-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56675,12 +56742,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6413",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G17" s="15">
-        <f>F17-E17</f>
+      <c r="G17" s="53">
+        <f>F17*(('04_Moteur'!$Y$62/2952)*(1+'01_Cadrage'!$H$20))</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>IFERROR((F17-E17)/E17,0)</f>
+        <f>IFERROR(G17/F17-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56707,12 +56774,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6414",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G18" s="15">
-        <f>F18-E18</f>
+      <c r="G18" s="53">
+        <f>F18*(('04_Moteur'!$Y$62/2952)*(1+'01_Cadrage'!$H$20))</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>IFERROR((F18-E18)/E18,0)</f>
+        <f>IFERROR(G18/F18-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56739,12 +56806,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"645",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G19" s="15">
-        <f>F19-E19</f>
+      <c r="G19" s="53">
+        <f>F19*(('04_Moteur'!$Y$62/2952)*(1+'01_Cadrage'!$H$20))</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>IFERROR((F19-E19)/E19,0)</f>
+        <f>IFERROR(G19/F19-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56784,12 +56851,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"613",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G21" s="15">
-        <f>F21-E21</f>
+      <c r="G21" s="53">
+        <f>F21*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>IFERROR((F21-E21)/E21,0)</f>
+        <f>IFERROR(G21/F21-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56816,12 +56883,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"615",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G22" s="15">
-        <f>F22-E22</f>
+      <c r="G22" s="53">
+        <f>F22*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>IFERROR((F22-E22)/E22,0)</f>
+        <f>IFERROR(G22/F22-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56848,12 +56915,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"616",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G23" s="15">
-        <f>F23-E23</f>
+      <c r="G23" s="53">
+        <f>F23*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>IFERROR((F23-E23)/E23,0)</f>
+        <f>IFERROR(G23/F23-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56880,12 +56947,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6226",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G24" s="15">
-        <f>F24-E24</f>
+      <c r="G24" s="53">
+        <f>F24*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>IFERROR((F24-E24)/E24,0)</f>
+        <f>IFERROR(G24/F24-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56912,12 +56979,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6236",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G25" s="15">
-        <f>F25-E25</f>
+      <c r="G25" s="53">
+        <f>F25*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>IFERROR((F25-E25)/E25,0)</f>
+        <f>IFERROR(G25/F25-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56944,12 +57011,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"625",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G26" s="15">
-        <f>F26-E26</f>
+      <c r="G26" s="53">
+        <f>F26*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>IFERROR((F26-E26)/E26,0)</f>
+        <f>IFERROR(G26/F26-1,0)</f>
         <v/>
       </c>
     </row>
@@ -56976,12 +57043,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"626",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G27" s="15">
-        <f>F27-E27</f>
+      <c r="G27" s="53">
+        <f>F27*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>IFERROR((F27-E27)/E27,0)</f>
+        <f>IFERROR(G27/F27-1,0)</f>
         <v/>
       </c>
     </row>
@@ -57008,12 +57075,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6281",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G28" s="15">
-        <f>F28-E28</f>
+      <c r="G28" s="53">
+        <f>F28*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>IFERROR((F28-E28)/E28,0)</f>
+        <f>IFERROR(G28/F28-1,0)</f>
         <v/>
       </c>
     </row>
@@ -57053,12 +57120,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6331",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G30" s="15">
-        <f>F30-E30</f>
+      <c r="G30" s="53">
+        <f>F30*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>IFERROR((F30-E30)/E30,0)</f>
+        <f>IFERROR(G30/F30-1,0)</f>
         <v/>
       </c>
     </row>
@@ -57085,12 +57152,12 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"63511",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G31" s="15">
-        <f>F31-E31</f>
+      <c r="G31" s="53">
+        <f>F31*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>IFERROR((F31-E31)/E31,0)</f>
+        <f>IFERROR(G31/F31-1,0)</f>
         <v/>
       </c>
     </row>
@@ -57117,17 +57184,17 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6333",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G32" s="15">
-        <f>F32-E32</f>
+      <c r="G32" s="53">
+        <f>F32*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>IFERROR((F32-E32)/E32,0)</f>
+        <f>IFERROR(G32/F32-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="53" t="inlineStr">
+      <c r="B33" s="54" t="inlineStr">
         <is>
           <t> </t>
         </is>
@@ -57149,12 +57216,12 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Produit",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Charge",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")+SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$I$4:$I$675,"Dotations",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G33" s="46">
-        <f>F33-E33</f>
-        <v/>
-      </c>
-      <c r="H33" s="54">
-        <f>IFERROR((F33-E33)/E33,0)</f>
+      <c r="G33" s="55">
+        <f>G5+G6+G7+G10+G11+G12+G13+G16+G17+G18+G19+G21+G22+G23+G24+G25+G26+G27+G28+G30+G31+G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="56">
+        <f>IFERROR(G33/F33-1,0)</f>
         <v/>
       </c>
     </row>
@@ -57194,17 +57261,17 @@
         <f>-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6811",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G35" s="15">
-        <f>F35-E35</f>
+      <c r="G35" s="53">
+        <f>F35*(1+'01_Cadrage'!$H$19)</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>IFERROR((F35-E35)/E35,0)</f>
+        <f>IFERROR(G35/F35-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="53" t="inlineStr">
+      <c r="B36" s="54" t="inlineStr">
         <is>
           <t> </t>
         </is>
@@ -57226,12 +57293,12 @@
         <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Produit",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Charge",'06_Compta'!$J$4:$J$675,"2025ATT_VDEF")</f>
         <v/>
       </c>
-      <c r="G36" s="46">
-        <f>F36-E36</f>
-        <v/>
-      </c>
-      <c r="H36" s="54">
-        <f>IFERROR((F36-E36)/E36,0)</f>
+      <c r="G36" s="55">
+        <f>G5+G6+G7+G10+G11+G12+G13+G16+G17+G18+G19+G21+G22+G23+G24+G25+G26+G27+G28+G30+G31+G32+G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="56">
+        <f>IFERROR(G36/F36-1,0)</f>
         <v/>
       </c>
     </row>
@@ -57241,16 +57308,20 @@
           <t>Marge EBITDA %</t>
         </is>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="57">
         <f>IFERROR(D33/D8,0)</f>
         <v/>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="57">
         <f>IFERROR(E33/E8,0)</f>
         <v/>
       </c>
-      <c r="F37" s="55">
+      <c r="F37" s="57">
         <f>IFERROR(F33/F8,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="57">
+        <f>IFERROR(G33/G8,0)</f>
         <v/>
       </c>
     </row>
@@ -57260,16 +57331,20 @@
           <t>Marge EBIT %</t>
         </is>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="57">
         <f>IFERROR(D36/D8,0)</f>
         <v/>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="57">
         <f>IFERROR(E36/E8,0)</f>
         <v/>
       </c>
-      <c r="F38" s="55">
+      <c r="F38" s="57">
         <f>IFERROR(F36/F8,0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="57">
+        <f>IFERROR(G36/G8,0)</f>
         <v/>
       </c>
     </row>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -6227,17 +6227,17 @@
         <v>2024</v>
       </c>
       <c r="E4" s="24" t="n">
-        <v>717</v>
+        <v>645</v>
       </c>
       <c r="F4" s="24" t="n">
-        <v>1078</v>
+        <v>1158</v>
       </c>
       <c r="G4" s="27">
         <f>E4+F4</f>
         <v/>
       </c>
       <c r="H4" s="12" t="n">
-        <v>52911</v>
+        <v>56438</v>
       </c>
     </row>
     <row r="5">
@@ -6259,17 +6259,17 @@
         <v>2025</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>753</v>
+        <v>677</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>1130</v>
+        <v>1210</v>
       </c>
       <c r="G5" s="27">
         <f>E5+F5</f>
         <v/>
       </c>
       <c r="H5" s="12" t="n">
-        <v>58202</v>
+        <v>62082</v>
       </c>
     </row>
     <row r="6">
@@ -6291,17 +6291,17 @@
         <v>2026</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>790</v>
+        <v>711</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>1186</v>
+        <v>1265</v>
       </c>
       <c r="G6" s="27">
         <f>E6+F6</f>
         <v/>
       </c>
       <c r="H6" s="12" t="n">
-        <v>64022</v>
+        <v>68291</v>
       </c>
     </row>
     <row r="7">
@@ -6323,17 +6323,17 @@
         <v>2024</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>604</v>
+        <v>650</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>909</v>
+        <v>863</v>
       </c>
       <c r="G7" s="27">
         <f>E7+F7</f>
         <v/>
       </c>
       <c r="H7" s="12" t="n">
-        <v>36349</v>
+        <v>34532</v>
       </c>
     </row>
     <row r="8">
@@ -6355,17 +6355,17 @@
         <v>2025</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>953</v>
+        <v>905</v>
       </c>
       <c r="G8" s="27">
         <f>E8+F8</f>
         <v/>
       </c>
       <c r="H8" s="12" t="n">
-        <v>39984</v>
+        <v>37985</v>
       </c>
     </row>
     <row r="9">
@@ -6387,17 +6387,17 @@
         <v>2026</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="G9" s="27">
         <f>E9+F9</f>
         <v/>
       </c>
       <c r="H9" s="12" t="n">
-        <v>43982</v>
+        <v>41783</v>
       </c>
     </row>
     <row r="10">
@@ -6419,17 +6419,17 @@
         <v>2024</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>550</v>
+        <v>660</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>827</v>
+        <v>713</v>
       </c>
       <c r="G10" s="27">
         <f>E10+F10</f>
         <v/>
       </c>
       <c r="H10" s="12" t="n">
-        <v>30069</v>
+        <v>26060</v>
       </c>
     </row>
     <row r="11">
@@ -6451,17 +6451,17 @@
         <v>2025</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>578</v>
+        <v>693</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>867</v>
+        <v>749</v>
       </c>
       <c r="G11" s="27">
         <f>E11+F11</f>
         <v/>
       </c>
       <c r="H11" s="12" t="n">
-        <v>33076</v>
+        <v>28666</v>
       </c>
     </row>
     <row r="12">
@@ -6483,17 +6483,17 @@
         <v>2026</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>606</v>
+        <v>728</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>910</v>
+        <v>788</v>
       </c>
       <c r="G12" s="27">
         <f>E12+F12</f>
         <v/>
       </c>
       <c r="H12" s="12" t="n">
-        <v>36384</v>
+        <v>31533</v>
       </c>
     </row>
     <row r="13">
@@ -6515,17 +6515,17 @@
         <v>2024</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>467</v>
+        <v>572</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>701</v>
+        <v>592</v>
       </c>
       <c r="G13" s="27">
         <f>E13+F13</f>
         <v/>
       </c>
       <c r="H13" s="12" t="n">
-        <v>24232</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="14">
@@ -6547,17 +6547,17 @@
         <v>2025</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>490</v>
+        <v>600</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>736</v>
+        <v>623</v>
       </c>
       <c r="G14" s="27">
         <f>E14+F14</f>
         <v/>
       </c>
       <c r="H14" s="12" t="n">
-        <v>26655</v>
+        <v>22657</v>
       </c>
     </row>
     <row r="15">
@@ -6579,17 +6579,17 @@
         <v>2026</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>514</v>
+        <v>630</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>772</v>
+        <v>656</v>
       </c>
       <c r="G15" s="27">
         <f>E15+F15</f>
         <v/>
       </c>
       <c r="H15" s="12" t="n">
-        <v>29321</v>
+        <v>24923</v>
       </c>
     </row>
     <row r="16">
@@ -6611,17 +6611,17 @@
         <v>2024</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>991</v>
+        <v>1035</v>
       </c>
       <c r="G16" s="27">
         <f>E16+F16</f>
         <v/>
       </c>
       <c r="H16" s="12" t="n">
-        <v>48627</v>
+        <v>50248</v>
       </c>
     </row>
     <row r="17">
@@ -6643,17 +6643,17 @@
         <v>2025</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>692</v>
+        <v>657</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>1039</v>
+        <v>1080</v>
       </c>
       <c r="G17" s="27">
         <f>E17+F17</f>
         <v/>
       </c>
       <c r="H17" s="12" t="n">
-        <v>53489</v>
+        <v>55272</v>
       </c>
     </row>
     <row r="18">
@@ -6675,17 +6675,17 @@
         <v>2026</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>726</v>
+        <v>690</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>1090</v>
+        <v>1126</v>
       </c>
       <c r="G18" s="27">
         <f>E18+F18</f>
         <v/>
       </c>
       <c r="H18" s="12" t="n">
-        <v>58838</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="19">
@@ -6707,17 +6707,17 @@
         <v>2024</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>458</v>
+        <v>572</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>688</v>
+        <v>571</v>
       </c>
       <c r="G19" s="27">
         <f>E19+F19</f>
         <v/>
       </c>
       <c r="H19" s="12" t="n">
-        <v>25012</v>
+        <v>20843</v>
       </c>
     </row>
     <row r="20">
@@ -6739,17 +6739,17 @@
         <v>2025</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>721</v>
+        <v>600</v>
       </c>
       <c r="G20" s="27">
         <f>E20+F20</f>
         <v/>
       </c>
       <c r="H20" s="12" t="n">
-        <v>27513</v>
+        <v>22927</v>
       </c>
     </row>
     <row r="21">
@@ -6771,17 +6771,17 @@
         <v>2026</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>504</v>
+        <v>630</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>757</v>
+        <v>630</v>
       </c>
       <c r="G21" s="27">
         <f>E21+F21</f>
         <v/>
       </c>
       <c r="H21" s="12" t="n">
-        <v>30264</v>
+        <v>25220</v>
       </c>
     </row>
     <row r="22">
@@ -6803,17 +6803,17 @@
         <v>2024</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>430</v>
+        <v>549</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>647</v>
+        <v>526</v>
       </c>
       <c r="G22" s="27">
         <f>E22+F22</f>
         <v/>
       </c>
       <c r="H22" s="12" t="n">
-        <v>22348</v>
+        <v>18251</v>
       </c>
     </row>
     <row r="23">
@@ -6835,17 +6835,17 @@
         <v>2025</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>452</v>
+        <v>576</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>678</v>
+        <v>553</v>
       </c>
       <c r="G23" s="27">
         <f>E23+F23</f>
         <v/>
       </c>
       <c r="H23" s="12" t="n">
-        <v>24583</v>
+        <v>20076</v>
       </c>
     </row>
     <row r="24">
@@ -6867,17 +6867,17 @@
         <v>2026</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>474</v>
+        <v>605</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>712</v>
+        <v>581</v>
       </c>
       <c r="G24" s="27">
         <f>E24+F24</f>
         <v/>
       </c>
       <c r="H24" s="12" t="n">
-        <v>27041</v>
+        <v>22083</v>
       </c>
     </row>
     <row r="25">
@@ -6899,17 +6899,17 @@
         <v>2024</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="G25" s="27">
         <f>E25+F25</f>
         <v/>
       </c>
       <c r="H25" s="12" t="n">
-        <v>16860</v>
+        <v>17983</v>
       </c>
     </row>
     <row r="26">
@@ -6931,17 +6931,17 @@
         <v>2025</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="G26" s="27">
         <f>E26+F26</f>
         <v/>
       </c>
       <c r="H26" s="12" t="n">
-        <v>18545</v>
+        <v>19782</v>
       </c>
     </row>
     <row r="27">
@@ -6963,17 +6963,17 @@
         <v>2026</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="G27" s="27">
         <f>E27+F27</f>
         <v/>
       </c>
       <c r="H27" s="12" t="n">
-        <v>20400</v>
+        <v>21760</v>
       </c>
     </row>
     <row r="28">
@@ -6995,7 +6995,7 @@
         <v>2024</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F28" s="24" t="n">
         <v>371</v>
@@ -7005,7 +7005,7 @@
         <v/>
       </c>
       <c r="H28" s="12" t="n">
-        <v>12139</v>
+        <v>12341</v>
       </c>
     </row>
     <row r="29">
@@ -7027,17 +7027,17 @@
         <v>2025</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G29" s="27">
         <f>E29+F29</f>
         <v/>
       </c>
       <c r="H29" s="12" t="n">
-        <v>13353</v>
+        <v>13575</v>
       </c>
     </row>
     <row r="30">
@@ -7059,17 +7059,17 @@
         <v>2026</v>
       </c>
       <c r="E30" s="24" t="n">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G30" s="27">
         <f>E30+F30</f>
         <v/>
       </c>
       <c r="H30" s="12" t="n">
-        <v>14688</v>
+        <v>14933</v>
       </c>
     </row>
     <row r="31">
@@ -7091,17 +7091,17 @@
         <v>2024</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F31" s="24" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="G31" s="27">
         <f>E31+F31</f>
         <v/>
       </c>
       <c r="H31" s="12" t="n">
-        <v>12139</v>
+        <v>12543</v>
       </c>
     </row>
     <row r="32">
@@ -7123,17 +7123,17 @@
         <v>2025</v>
       </c>
       <c r="E32" s="24" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="G32" s="27">
         <f>E32+F32</f>
         <v/>
       </c>
       <c r="H32" s="12" t="n">
-        <v>13353</v>
+        <v>13798</v>
       </c>
     </row>
     <row r="33">
@@ -7155,17 +7155,17 @@
         <v>2026</v>
       </c>
       <c r="E33" s="24" t="n">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F33" s="24" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="G33" s="27">
         <f>E33+F33</f>
         <v/>
       </c>
       <c r="H33" s="12" t="n">
-        <v>14688</v>
+        <v>15178</v>
       </c>
     </row>
     <row r="34">
@@ -7187,17 +7187,17 @@
         <v>2024</v>
       </c>
       <c r="E34" s="24" t="n">
-        <v>570</v>
+        <v>669</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>856</v>
+        <v>765</v>
       </c>
       <c r="G34" s="27">
         <f>E34+F34</f>
         <v/>
       </c>
       <c r="H34" s="12" t="n">
-        <v>34255</v>
+        <v>30258</v>
       </c>
     </row>
     <row r="35">
@@ -7219,17 +7219,17 @@
         <v>2025</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>598</v>
+        <v>703</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>898</v>
+        <v>798</v>
       </c>
       <c r="G35" s="27">
         <f>E35+F35</f>
         <v/>
       </c>
       <c r="H35" s="12" t="n">
-        <v>37680</v>
+        <v>33284</v>
       </c>
     </row>
     <row r="36">
@@ -7251,17 +7251,17 @@
         <v>2026</v>
       </c>
       <c r="E36" s="24" t="n">
-        <v>628</v>
+        <v>738</v>
       </c>
       <c r="F36" s="24" t="n">
-        <v>942</v>
+        <v>832</v>
       </c>
       <c r="G36" s="27">
         <f>E36+F36</f>
         <v/>
       </c>
       <c r="H36" s="12" t="n">
-        <v>41448</v>
+        <v>36612</v>
       </c>
     </row>
     <row r="37">
@@ -7283,17 +7283,17 @@
         <v>2024</v>
       </c>
       <c r="E37" s="24" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="F37" s="24" t="n">
-        <v>671</v>
+        <v>528</v>
       </c>
       <c r="G37" s="27">
         <f>E37+F37</f>
         <v/>
       </c>
       <c r="H37" s="12" t="n">
-        <v>23177</v>
+        <v>18155</v>
       </c>
     </row>
     <row r="38">
@@ -7315,17 +7315,17 @@
         <v>2025</v>
       </c>
       <c r="E38" s="24" t="n">
-        <v>469</v>
+        <v>621</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>704</v>
+        <v>552</v>
       </c>
       <c r="G38" s="27">
         <f>E38+F38</f>
         <v/>
       </c>
       <c r="H38" s="12" t="n">
-        <v>25495</v>
+        <v>19971</v>
       </c>
     </row>
     <row r="39">
@@ -7347,17 +7347,17 @@
         <v>2026</v>
       </c>
       <c r="E39" s="24" t="n">
-        <v>492</v>
+        <v>652</v>
       </c>
       <c r="F39" s="24" t="n">
-        <v>738</v>
+        <v>578</v>
       </c>
       <c r="G39" s="27">
         <f>E39+F39</f>
         <v/>
       </c>
       <c r="H39" s="12" t="n">
-        <v>28044</v>
+        <v>21968</v>
       </c>
     </row>
     <row r="40">
@@ -7379,17 +7379,17 @@
         <v>2024</v>
       </c>
       <c r="E40" s="24" t="n">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>436</v>
+        <v>517</v>
       </c>
       <c r="G40" s="27">
         <f>E40+F40</f>
         <v/>
       </c>
       <c r="H40" s="12" t="n">
-        <v>21421</v>
+        <v>24992</v>
       </c>
     </row>
     <row r="41">
@@ -7411,17 +7411,17 @@
         <v>2025</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="F41" s="24" t="n">
-        <v>458</v>
+        <v>538</v>
       </c>
       <c r="G41" s="27">
         <f>E41+F41</f>
         <v/>
       </c>
       <c r="H41" s="12" t="n">
-        <v>23564</v>
+        <v>27491</v>
       </c>
     </row>
     <row r="42">
@@ -7443,17 +7443,17 @@
         <v>2026</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="F42" s="24" t="n">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="G42" s="27">
         <f>E42+F42</f>
         <v/>
       </c>
       <c r="H42" s="12" t="n">
-        <v>25920</v>
+        <v>30240</v>
       </c>
     </row>
     <row r="43">
@@ -7475,17 +7475,17 @@
         <v>2024</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="G43" s="27">
         <f>E43+F43</f>
         <v/>
       </c>
       <c r="H43" s="12" t="n">
-        <v>14836</v>
+        <v>15578</v>
       </c>
     </row>
     <row r="44">
@@ -7507,17 +7507,17 @@
         <v>2025</v>
       </c>
       <c r="E44" s="24" t="n">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="F44" s="24" t="n">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="G44" s="27">
         <f>E44+F44</f>
         <v/>
       </c>
       <c r="H44" s="12" t="n">
-        <v>16320</v>
+        <v>17136</v>
       </c>
     </row>
     <row r="45">
@@ -7539,17 +7539,17 @@
         <v>2026</v>
       </c>
       <c r="E45" s="24" t="n">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="F45" s="24" t="n">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="G45" s="27">
         <f>E45+F45</f>
         <v/>
       </c>
       <c r="H45" s="12" t="n">
-        <v>17952</v>
+        <v>18850</v>
       </c>
     </row>
   </sheetData>
@@ -7567,7 +7567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7584,6 +7584,8 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7671,6 +7673,16 @@
           <t>CPL effectif</t>
         </is>
       </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Conv. lead→inscrit</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>CAC marginal /inscrit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -7731,6 +7743,14 @@
         <f>IFERROR(K5/L5,0)</f>
         <v/>
       </c>
+      <c r="O5" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A5,'02_Base'!$B$4:$B$61,B5,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A5,'02_Base'!$B$4:$B$61,B5,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P5" s="13">
+        <f>IFERROR(I5/(J5*O5),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -7791,6 +7811,14 @@
         <f>IFERROR(K6/L6,0)</f>
         <v/>
       </c>
+      <c r="O6" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A6,'02_Base'!$B$4:$B$61,B6,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A6,'02_Base'!$B$4:$B$61,B6,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P6" s="13">
+        <f>IFERROR(I6/(J6*O6),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -7851,6 +7879,14 @@
         <f>IFERROR(K7/L7,0)</f>
         <v/>
       </c>
+      <c r="O7" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A7,'02_Base'!$B$4:$B$61,B7,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A7,'02_Base'!$B$4:$B$61,B7,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="13">
+        <f>IFERROR(I7/(J7*O7),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -7911,6 +7947,14 @@
         <f>IFERROR(K8/L8,0)</f>
         <v/>
       </c>
+      <c r="O8" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P8" s="13">
+        <f>IFERROR(I8/(J8*O8),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
@@ -7971,6 +8015,14 @@
         <f>IFERROR(K9/L9,0)</f>
         <v/>
       </c>
+      <c r="O9" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P9" s="13">
+        <f>IFERROR(I9/(J9*O9),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -8031,6 +8083,14 @@
         <f>IFERROR(K10/L10,0)</f>
         <v/>
       </c>
+      <c r="O10" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="13">
+        <f>IFERROR(I10/(J10*O10),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -8091,6 +8151,14 @@
         <f>IFERROR(K11/L11,0)</f>
         <v/>
       </c>
+      <c r="O11" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P11" s="13">
+        <f>IFERROR(I11/(J11*O11),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -8151,6 +8219,14 @@
         <f>IFERROR(K12/L12,0)</f>
         <v/>
       </c>
+      <c r="O12" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="13">
+        <f>IFERROR(I12/(J12*O12),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
@@ -8211,6 +8287,14 @@
         <f>IFERROR(K13/L13,0)</f>
         <v/>
       </c>
+      <c r="O13" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="13">
+        <f>IFERROR(I13/(J13*O13),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -8271,6 +8355,14 @@
         <f>IFERROR(K14/L14,0)</f>
         <v/>
       </c>
+      <c r="O14" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="13">
+        <f>IFERROR(I14/(J14*O14),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -8331,6 +8423,14 @@
         <f>IFERROR(K15/L15,0)</f>
         <v/>
       </c>
+      <c r="O15" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="13">
+        <f>IFERROR(I15/(J15*O15),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -8391,6 +8491,14 @@
         <f>IFERROR(K16/L16,0)</f>
         <v/>
       </c>
+      <c r="O16" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="13">
+        <f>IFERROR(I16/(J16*O16),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -8451,6 +8559,14 @@
         <f>IFERROR(K17/L17,0)</f>
         <v/>
       </c>
+      <c r="O17" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="13">
+        <f>IFERROR(I17/(J17*O17),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -8511,12 +8627,40 @@
         <f>IFERROR(K18/L18,0)</f>
         <v/>
       </c>
+      <c r="O18" s="42">
+        <f>IFERROR(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18,'02_Base'!$G$4:$G$61,1)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18,'02_Base'!$G$4:$G$61,1),0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="13">
+        <f>IFERROR(I18/(J18*O18),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>Indicateur d'attractivité : CAC marginal = coût marketing du prochain inscrit. Vert = investir ici (l'euro rapporte) · Rouge = marché cher/saturé.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A20:P20"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
+  <conditionalFormatting sqref="P5:P18">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -17,6 +17,7 @@
     <sheet name="06_Compta" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="07_PnL" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="08_Saisie_Campus" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="09_Reporting" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;;(#,##0)&quot; €&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +85,12 @@
       <name val="Arial"/>
       <color rgb="000000FF"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="16"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -123,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,11 +152,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -315,6 +366,29 @@
     <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -389,6 +463,140 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>CA par marque — cible vs construit</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'09_Reporting'!G11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'09_Reporting'!$F$12:$F$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'09_Reporting'!$G$12:$G$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'09_Reporting'!H11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'09_Reporting'!$F$12:$F$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'09_Reporting'!$H$12:$H$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1297,6 +1505,406 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:N23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>REPORTING — impact live du cadrage · pont d'explication CA &amp; EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="59">
+        <f>'04_Moteur'!$AA$62</f>
+        <v/>
+      </c>
+      <c r="C3" s="60" t="n"/>
+      <c r="D3" s="61" t="n"/>
+      <c r="E3" s="59">
+        <f>'07_PnL'!$G$33</f>
+        <v/>
+      </c>
+      <c r="F3" s="60" t="n"/>
+      <c r="G3" s="61" t="n"/>
+      <c r="H3" s="62">
+        <f>IFERROR('07_PnL'!$G$33/'04_Moteur'!$AA$62,0)</f>
+        <v/>
+      </c>
+      <c r="I3" s="60" t="n"/>
+      <c r="J3" s="61" t="n"/>
+      <c r="K3" s="63">
+        <f>'04_Moteur'!$Y$62</f>
+        <v/>
+      </c>
+      <c r="L3" s="60" t="n"/>
+      <c r="M3" s="61" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t>CA construit (budget)</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="64" t="inlineStr">
+        <is>
+          <t>EBITDA construit</t>
+        </is>
+      </c>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="61" t="n"/>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>Marge EBITDA</t>
+        </is>
+      </c>
+      <c r="I4" s="60" t="n"/>
+      <c r="J4" s="61" t="n"/>
+      <c r="K4" s="64" t="inlineStr">
+        <is>
+          <t>Effectif construit</t>
+        </is>
+      </c>
+      <c r="L4" s="60" t="n"/>
+      <c r="M4" s="61" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="59">
+        <f>'01_Cadrage'!F7</f>
+        <v/>
+      </c>
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="66">
+        <f>'01_Cadrage'!D12</f>
+        <v/>
+      </c>
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="61" t="n"/>
+      <c r="H6" s="59">
+        <f>IFERROR(SUM('03_Campagnes'!$K$5:$K$18)/SUM('03_Campagnes'!$L$5:$L$18),0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="60" t="n"/>
+      <c r="J6" s="61" t="n"/>
+      <c r="K6" s="59">
+        <f>IFERROR(SUM('03_Campagnes'!$K$5:$K$18)/'04_Moteur'!$W$62,0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="60" t="n"/>
+      <c r="M6" s="61" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>Écart à la cible CA</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>Reste à trouver CA</t>
+        </is>
+      </c>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="61" t="n"/>
+      <c r="H7" s="64" t="inlineStr">
+        <is>
+          <t>CPL effectif moyen</t>
+        </is>
+      </c>
+      <c r="I7" s="60" t="n"/>
+      <c r="J7" s="61" t="n"/>
+      <c r="K7" s="64" t="inlineStr">
+        <is>
+          <t>Coût d'acquisition / inscrit</t>
+        </is>
+      </c>
+      <c r="L7" s="60" t="n"/>
+      <c r="M7" s="61" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Pont CA : Référence 2026 → Budget construit</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>CA par marque : cible vs construit</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>CA Référence 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>21936350</v>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>🎯 Cible</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>🔧 Construit</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>+ Effet volume</t>
+        </is>
+      </c>
+      <c r="D12" s="15">
+        <f>('04_Moteur'!$Y$62-2952)*(21936350/2952)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="G12" s="15">
+        <f>SUMIFS('04_Moteur'!$AJ$4:$AJ$61,'04_Moteur'!$A$4:$A$61,F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="14">
+        <f>SUMIFS('04_Moteur'!$AA$4:$AA$61,'04_Moteur'!$A$4:$A$61,F12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="15">
+        <f>H12-G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>+ Effet prix &amp; mix</t>
+        </is>
+      </c>
+      <c r="D13" s="15">
+        <f>'04_Moteur'!$AA$62-21936350-D12</f>
+        <v/>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="G13" s="15">
+        <f>SUMIFS('04_Moteur'!$AJ$4:$AJ$61,'04_Moteur'!$A$4:$A$61,F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>SUMIFS('04_Moteur'!$AA$4:$AA$61,'04_Moteur'!$A$4:$A$61,F13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="15">
+        <f>H13-G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>→ CA Budget construit</t>
+        </is>
+      </c>
+      <c r="D14" s="44">
+        <f>'04_Moteur'!$AA$62</f>
+        <v/>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="G14" s="15">
+        <f>SUMIFS('04_Moteur'!$AJ$4:$AJ$61,'04_Moteur'!$A$4:$A$61,F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="14">
+        <f>SUMIFS('04_Moteur'!$AA$4:$AA$61,'04_Moteur'!$A$4:$A$61,F14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="15">
+        <f>H14-G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="G15" s="15">
+        <f>SUMIFS('04_Moteur'!$AJ$4:$AJ$61,'04_Moteur'!$A$4:$A$61,F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>SUMIFS('04_Moteur'!$AA$4:$AA$61,'04_Moteur'!$A$4:$A$61,F15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="15">
+        <f>H15-G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Pont EBITDA : Référence 2026 → Budget construit</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="G16" s="15">
+        <f>SUMIFS('04_Moteur'!$AJ$4:$AJ$61,'04_Moteur'!$A$4:$A$61,F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="14">
+        <f>SUMIFS('04_Moteur'!$AA$4:$AA$61,'04_Moteur'!$A$4:$A$61,F16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>H16-G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>EBITDA Référence 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="13">
+        <f>'07_PnL'!$F$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>+ Effet CA (à marge réf.)</t>
+        </is>
+      </c>
+      <c r="D18" s="15">
+        <f>('04_Moteur'!$AA$62-21936350)*IFERROR('07_PnL'!$F$33/21936350,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>+ Effet coûts &amp; levier op.</t>
+        </is>
+      </c>
+      <c r="D19" s="15">
+        <f>'07_PnL'!$G$33-'07_PnL'!$F$33-D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>→ EBITDA Budget construit</t>
+        </is>
+      </c>
+      <c r="D20" s="44">
+        <f>'07_PnL'!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>Les tuiles et les ponts se recalculent en direct quand on bouge un levier du cadrage ou un scénario.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B23:N23"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H6:J6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -18,6 +18,7 @@
     <sheet name="07_PnL" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="08_Saisie_Campus" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="09_Reporting" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10_Allocation" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1905,6 +1906,868 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ALLOCATION EN CASCADE — coûts du siège redescendus sur les campus (clé au choix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Clé d'allocation des coûts groupe :</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Coûts groupe à répartir :</t>
+        </is>
+      </c>
+      <c r="I3" s="14">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$A$4:$A$675,"GROUPE",'06_Compta'!$H$4:$H$675,"Charge",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Coûts propres campus</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Clé</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>Quote-part groupe</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>EBITDA campus</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>Marge %</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D6-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G6" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A6,'02_Base'!$B$4:$B$61,B6),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A6,'02_Base'!$B$4:$B$61,B6),C6))</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>IFERROR(G6/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f>H6*$I$3</f>
+        <v/>
+      </c>
+      <c r="J6" s="14">
+        <f>E6-F6-I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="16">
+        <f>IFERROR(J6/C6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D7-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G7" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A7,'02_Base'!$B$4:$B$61,B7),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A7,'02_Base'!$B$4:$B$61,B7),C7))</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>IFERROR(G7/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>H7*$I$3</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>E7-F7-I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="16">
+        <f>IFERROR(J7/C7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="C8" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D8-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G8" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),C8))</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IFERROR(G8/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="15">
+        <f>H8*$I$3</f>
+        <v/>
+      </c>
+      <c r="J8" s="14">
+        <f>E8-F8-I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="16">
+        <f>IFERROR(J8/C8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="C9" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D9-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G9" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),C9))</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>IFERROR(G9/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>H9*$I$3</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>E9-F9-I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="16">
+        <f>IFERROR(J9/C9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C10" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D10-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G10" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),C10))</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>IFERROR(G10/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I10" s="15">
+        <f>H10*$I$3</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>E10-F10-I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>IFERROR(J10/C10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D11" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D11-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G11" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),C11))</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IFERROR(G11/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="15">
+        <f>H11*$I$3</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>E11-F11-I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="16">
+        <f>IFERROR(J11/C11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="C12" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D12" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D12-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G12" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),C12))</f>
+        <v/>
+      </c>
+      <c r="H12" s="25">
+        <f>IFERROR(G12/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="15">
+        <f>H12*$I$3</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>E12-F12-I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="16">
+        <f>IFERROR(J12/C12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="C13" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D13" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D13-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G13" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),C13))</f>
+        <v/>
+      </c>
+      <c r="H13" s="25">
+        <f>IFERROR(G13/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="15">
+        <f>H13*$I$3</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>E13-F13-I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="16">
+        <f>IFERROR(J13/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="C14" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D14-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G14" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),C14))</f>
+        <v/>
+      </c>
+      <c r="H14" s="25">
+        <f>IFERROR(G14/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="15">
+        <f>H14*$I$3</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>E14-F14-I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="16">
+        <f>IFERROR(J14/C14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="C15" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D15-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G15" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),C15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="25">
+        <f>IFERROR(G15/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="15">
+        <f>H15*$I$3</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>E15-F15-I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="16">
+        <f>IFERROR(J15/C15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="C16" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D16-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G16" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),C16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="25">
+        <f>IFERROR(G16/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>H16*$I$3</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>E16-F16-I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="16">
+        <f>IFERROR(J16/C16,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="C17" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D17" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E17" s="15">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D17-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),C17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="25">
+        <f>IFERROR(G17/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="15">
+        <f>H17*$I$3</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>E17-F17-I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
+        <f>IFERROR(J17/C17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C18" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D18-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),C18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="25">
+        <f>IFERROR(G18/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="15">
+        <f>H18*$I$3</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>E18-F18-I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="16">
+        <f>IFERROR(J18/C18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="C19" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
+        <v/>
+      </c>
+      <c r="D19" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D19-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <v/>
+      </c>
+      <c r="G19" s="23">
+        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),C19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="25">
+        <f>IFERROR(G19/SUM($G$6:$G$19),0)</f>
+        <v/>
+      </c>
+      <c r="I19" s="15">
+        <f>H19*$I$3</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>E19-F19-I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="16">
+        <f>IFERROR(J19/C19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C20" s="44">
+        <f>SUM(C6:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="44">
+        <f>SUM(D6:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="44">
+        <f>SUM(E6:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="44">
+        <f>SUM(F6:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="43">
+        <f>SUM(G6:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I20" s="44">
+        <f>SUM(I6:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="44">
+        <f>SUM(J6:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="55">
+        <f>IFERROR(J20/C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Change la clé (CA / effectif / classes) → la quote-part du siège se redistribue et l'EBITDA par campus bouge. Un campus rentable en contribution peut devenir déficitaire une fois pleinement chargé (effet « piège »). Le total EBITDA reste constant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A22:K23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K6:K19">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.14"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Chiffre d'affaires,Effectif,Nombre de classes"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -1912,33 +1912,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ALLOCATION EN CASCADE — coûts du siège redescendus sur les campus (clé au choix)</t>
+          <t>ALLOCATION EN CASCADE (3 niveaux, clé au choix par niveau) — jusqu'à la classe · vrai coût par étudiant</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Clé d'allocation des coûts groupe :</t>
+          <t>Niveau 1 — Groupe → Marque, clé :</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -1948,7 +1952,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Coûts groupe à répartir :</t>
+          <t>Coûts siège à cascader :</t>
         </is>
       </c>
       <c r="I3" s="14">
@@ -1956,802 +1960,3791 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Niveau 2 — Marque → Campus, clé :</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Niveau 3 — Campus → Classe, clé :</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Nombre de classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Marque</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Ville</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Programme</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Mod.</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>Coûts directs</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Coûts propres campus</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Clé</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Part</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>Quote-part groupe</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>EBITDA campus</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>Marge %</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>MBway</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C6" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E6" s="15">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D6-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A6,'06_Compta'!$D$4:$D$675,B6,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
-        <v/>
-      </c>
-      <c r="G6" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A6,'02_Base'!$B$4:$B$61,B6),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A6,'02_Base'!$B$4:$B$61,B6),C6))</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>IFERROR(G6/SUM($G$6:$G$19),0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="15">
-        <f>H6*$I$3</f>
-        <v/>
-      </c>
-      <c r="J6" s="14">
-        <f>E6-F6-I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="16">
-        <f>IFERROR(J6/C6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>MBway</t>
-        </is>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="C7" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E7" s="15">
-        <f>C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D7-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A7,'06_Compta'!$D$4:$D$675,B7,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
-        <v/>
-      </c>
-      <c r="G7" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A7,'02_Base'!$B$4:$B$61,B7),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A7,'02_Base'!$B$4:$B$61,B7),C7))</f>
-        <v/>
-      </c>
-      <c r="H7" s="25">
-        <f>IFERROR(G7/SUM($G$6:$G$19),0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="15">
-        <f>H7*$I$3</f>
-        <v/>
-      </c>
-      <c r="J7" s="14">
-        <f>E7-F7-I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="16">
-        <f>IFERROR(J7/C7,0)</f>
-        <v/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Siège alloué</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>Structure allouée</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>Coût total</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>Coût / étudiant</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Coût / classe</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Marge / étu.</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>MBway</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
-        <f>C8-D8</f>
+      <c r="A8" s="17">
+        <f>'02_Base'!A4</f>
+        <v/>
+      </c>
+      <c r="B8" s="39">
+        <f>'02_Base'!B4</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>'02_Base'!C4</f>
+        <v/>
+      </c>
+      <c r="D8" s="39">
+        <f>'02_Base'!E4</f>
+        <v/>
+      </c>
+      <c r="E8" s="39">
+        <f>'02_Base'!F4</f>
         <v/>
       </c>
       <c r="F8" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D8-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U4</f>
         <v/>
       </c>
       <c r="G8" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),C8))</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>IFERROR(G8/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M4</f>
+        <v/>
+      </c>
+      <c r="H8" s="23">
+        <f>'02_Base'!O4</f>
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>H8*$I$3</f>
-        <v/>
-      </c>
-      <c r="J8" s="14">
-        <f>E8-F8-I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="16">
-        <f>IFERROR(J8/C8,0)</f>
+        <f>F8*0.141</f>
+        <v/>
+      </c>
+      <c r="J8" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A8)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A8))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M4,IF($E$5="Nombre de classes",'02_Base'!O4,'02_Base'!U4)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8))),0))</f>
+        <v/>
+      </c>
+      <c r="K8" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A8,'06_Compta'!$D$4:$D$675,B8,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M4,IF($E$5="Nombre de classes",'02_Base'!O4,'02_Base'!U4)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A8,'02_Base'!$B$4:$B$61,B8))),0))</f>
+        <v/>
+      </c>
+      <c r="L8" s="14">
+        <f>I8+J8+K8</f>
+        <v/>
+      </c>
+      <c r="M8" s="14">
+        <f>IFERROR(L8/G8,0)</f>
+        <v/>
+      </c>
+      <c r="N8" s="15">
+        <f>IFERROR(L8/H8,0)</f>
+        <v/>
+      </c>
+      <c r="O8" s="15">
+        <f>IFERROR(F8/G8-M8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>MBway</t>
-        </is>
-      </c>
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="C9" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>C9-D9</f>
+      <c r="A9" s="17">
+        <f>'02_Base'!A5</f>
+        <v/>
+      </c>
+      <c r="B9" s="39">
+        <f>'02_Base'!B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>'02_Base'!C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="39">
+        <f>'02_Base'!E5</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
+        <f>'02_Base'!F5</f>
         <v/>
       </c>
       <c r="F9" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D9-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U5</f>
         <v/>
       </c>
       <c r="G9" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),C9))</f>
-        <v/>
-      </c>
-      <c r="H9" s="25">
-        <f>IFERROR(G9/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M5</f>
+        <v/>
+      </c>
+      <c r="H9" s="23">
+        <f>'02_Base'!O5</f>
         <v/>
       </c>
       <c r="I9" s="15">
-        <f>H9*$I$3</f>
-        <v/>
-      </c>
-      <c r="J9" s="14">
-        <f>E9-F9-I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="16">
-        <f>IFERROR(J9/C9,0)</f>
+        <f>F9*0.141</f>
+        <v/>
+      </c>
+      <c r="J9" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A9)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A9))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M5,IF($E$5="Nombre de classes",'02_Base'!O5,'02_Base'!U5)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9))),0))</f>
+        <v/>
+      </c>
+      <c r="K9" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A9,'06_Compta'!$D$4:$D$675,B9,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M5,IF($E$5="Nombre de classes",'02_Base'!O5,'02_Base'!U5)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A9,'02_Base'!$B$4:$B$61,B9))),0))</f>
+        <v/>
+      </c>
+      <c r="L9" s="14">
+        <f>I9+J9+K9</f>
+        <v/>
+      </c>
+      <c r="M9" s="14">
+        <f>IFERROR(L9/G9,0)</f>
+        <v/>
+      </c>
+      <c r="N9" s="15">
+        <f>IFERROR(L9/H9,0)</f>
+        <v/>
+      </c>
+      <c r="O9" s="15">
+        <f>IFERROR(F9/G9-M9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>ISCOM</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C10" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>C10-D10</f>
+      <c r="A10" s="17">
+        <f>'02_Base'!A6</f>
+        <v/>
+      </c>
+      <c r="B10" s="39">
+        <f>'02_Base'!B6</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>'02_Base'!C6</f>
+        <v/>
+      </c>
+      <c r="D10" s="39">
+        <f>'02_Base'!E6</f>
+        <v/>
+      </c>
+      <c r="E10" s="39">
+        <f>'02_Base'!F6</f>
         <v/>
       </c>
       <c r="F10" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D10-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U6</f>
         <v/>
       </c>
       <c r="G10" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),C10))</f>
-        <v/>
-      </c>
-      <c r="H10" s="25">
-        <f>IFERROR(G10/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M6</f>
+        <v/>
+      </c>
+      <c r="H10" s="23">
+        <f>'02_Base'!O6</f>
         <v/>
       </c>
       <c r="I10" s="15">
-        <f>H10*$I$3</f>
-        <v/>
-      </c>
-      <c r="J10" s="14">
-        <f>E10-F10-I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="16">
-        <f>IFERROR(J10/C10,0)</f>
+        <f>F10*0.141</f>
+        <v/>
+      </c>
+      <c r="J10" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A10)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A10))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M6,IF($E$5="Nombre de classes",'02_Base'!O6,'02_Base'!U6)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10))),0))</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A10,'06_Compta'!$D$4:$D$675,B10,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M6,IF($E$5="Nombre de classes",'02_Base'!O6,'02_Base'!U6)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A10,'02_Base'!$B$4:$B$61,B10))),0))</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>I10+J10+K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
+        <f>IFERROR(L10/G10,0)</f>
+        <v/>
+      </c>
+      <c r="N10" s="15">
+        <f>IFERROR(L10/H10,0)</f>
+        <v/>
+      </c>
+      <c r="O10" s="15">
+        <f>IFERROR(F10/G10-M10,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>ISCOM</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="C11" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D11" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E11" s="15">
-        <f>C11-D11</f>
+      <c r="A11" s="17">
+        <f>'02_Base'!A7</f>
+        <v/>
+      </c>
+      <c r="B11" s="39">
+        <f>'02_Base'!B7</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>'02_Base'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="39">
+        <f>'02_Base'!E7</f>
+        <v/>
+      </c>
+      <c r="E11" s="39">
+        <f>'02_Base'!F7</f>
         <v/>
       </c>
       <c r="F11" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D11-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U7</f>
         <v/>
       </c>
       <c r="G11" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),C11))</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
-        <f>IFERROR(G11/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M7</f>
+        <v/>
+      </c>
+      <c r="H11" s="23">
+        <f>'02_Base'!O7</f>
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>H11*$I$3</f>
-        <v/>
-      </c>
-      <c r="J11" s="14">
-        <f>E11-F11-I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="16">
-        <f>IFERROR(J11/C11,0)</f>
+        <f>F11*0.141</f>
+        <v/>
+      </c>
+      <c r="J11" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A11)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A11))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M7,IF($E$5="Nombre de classes",'02_Base'!O7,'02_Base'!U7)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11))),0))</f>
+        <v/>
+      </c>
+      <c r="K11" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A11,'06_Compta'!$D$4:$D$675,B11,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M7,IF($E$5="Nombre de classes",'02_Base'!O7,'02_Base'!U7)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A11,'02_Base'!$B$4:$B$61,B11))),0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="14">
+        <f>I11+J11+K11</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>IFERROR(L11/G11,0)</f>
+        <v/>
+      </c>
+      <c r="N11" s="15">
+        <f>IFERROR(L11/H11,0)</f>
+        <v/>
+      </c>
+      <c r="O11" s="15">
+        <f>IFERROR(F11/G11-M11,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>ISCOM</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="C12" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D12" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E12" s="15">
-        <f>C12-D12</f>
+      <c r="A12" s="17">
+        <f>'02_Base'!A8</f>
+        <v/>
+      </c>
+      <c r="B12" s="39">
+        <f>'02_Base'!B8</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>'02_Base'!C8</f>
+        <v/>
+      </c>
+      <c r="D12" s="39">
+        <f>'02_Base'!E8</f>
+        <v/>
+      </c>
+      <c r="E12" s="39">
+        <f>'02_Base'!F8</f>
         <v/>
       </c>
       <c r="F12" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D12-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U8</f>
         <v/>
       </c>
       <c r="G12" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),C12))</f>
-        <v/>
-      </c>
-      <c r="H12" s="25">
-        <f>IFERROR(G12/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M8</f>
+        <v/>
+      </c>
+      <c r="H12" s="23">
+        <f>'02_Base'!O8</f>
         <v/>
       </c>
       <c r="I12" s="15">
-        <f>H12*$I$3</f>
-        <v/>
-      </c>
-      <c r="J12" s="14">
-        <f>E12-F12-I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="16">
-        <f>IFERROR(J12/C12,0)</f>
+        <f>F12*0.141</f>
+        <v/>
+      </c>
+      <c r="J12" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A12)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A12))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M8,IF($E$5="Nombre de classes",'02_Base'!O8,'02_Base'!U8)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12))),0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A12,'06_Compta'!$D$4:$D$675,B12,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M8,IF($E$5="Nombre de classes",'02_Base'!O8,'02_Base'!U8)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A12,'02_Base'!$B$4:$B$61,B12))),0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="14">
+        <f>I12+J12+K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
+        <f>IFERROR(L12/G12,0)</f>
+        <v/>
+      </c>
+      <c r="N12" s="15">
+        <f>IFERROR(L12/H12,0)</f>
+        <v/>
+      </c>
+      <c r="O12" s="15">
+        <f>IFERROR(F12/G12-M12,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Ipac Bachelor Factory</t>
-        </is>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="C13" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D13" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E13" s="15">
-        <f>C13-D13</f>
+      <c r="A13" s="17">
+        <f>'02_Base'!A9</f>
+        <v/>
+      </c>
+      <c r="B13" s="39">
+        <f>'02_Base'!B9</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
+        <f>'02_Base'!C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="39">
+        <f>'02_Base'!E9</f>
+        <v/>
+      </c>
+      <c r="E13" s="39">
+        <f>'02_Base'!F9</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D13-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U9</f>
         <v/>
       </c>
       <c r="G13" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),C13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="25">
-        <f>IFERROR(G13/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M9</f>
+        <v/>
+      </c>
+      <c r="H13" s="23">
+        <f>'02_Base'!O9</f>
         <v/>
       </c>
       <c r="I13" s="15">
-        <f>H13*$I$3</f>
-        <v/>
-      </c>
-      <c r="J13" s="14">
-        <f>E13-F13-I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="16">
-        <f>IFERROR(J13/C13,0)</f>
+        <f>F13*0.141</f>
+        <v/>
+      </c>
+      <c r="J13" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A13)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A13))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M9,IF($E$5="Nombre de classes",'02_Base'!O9,'02_Base'!U9)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13))),0))</f>
+        <v/>
+      </c>
+      <c r="K13" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A13,'06_Compta'!$D$4:$D$675,B13,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M9,IF($E$5="Nombre de classes",'02_Base'!O9,'02_Base'!U9)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A13,'02_Base'!$B$4:$B$61,B13))),0))</f>
+        <v/>
+      </c>
+      <c r="L13" s="14">
+        <f>I13+J13+K13</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
+        <f>IFERROR(L13/G13,0)</f>
+        <v/>
+      </c>
+      <c r="N13" s="15">
+        <f>IFERROR(L13/H13,0)</f>
+        <v/>
+      </c>
+      <c r="O13" s="15">
+        <f>IFERROR(F13/G13-M13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Ipac Bachelor Factory</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="C14" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E14" s="15">
-        <f>C14-D14</f>
+      <c r="A14" s="17">
+        <f>'02_Base'!A10</f>
+        <v/>
+      </c>
+      <c r="B14" s="39">
+        <f>'02_Base'!B10</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>'02_Base'!C10</f>
+        <v/>
+      </c>
+      <c r="D14" s="39">
+        <f>'02_Base'!E10</f>
+        <v/>
+      </c>
+      <c r="E14" s="39">
+        <f>'02_Base'!F10</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D14-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U10</f>
         <v/>
       </c>
       <c r="G14" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),C14))</f>
-        <v/>
-      </c>
-      <c r="H14" s="25">
-        <f>IFERROR(G14/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M10</f>
+        <v/>
+      </c>
+      <c r="H14" s="23">
+        <f>'02_Base'!O10</f>
         <v/>
       </c>
       <c r="I14" s="15">
-        <f>H14*$I$3</f>
-        <v/>
-      </c>
-      <c r="J14" s="14">
-        <f>E14-F14-I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="16">
-        <f>IFERROR(J14/C14,0)</f>
+        <f>F14*0.141</f>
+        <v/>
+      </c>
+      <c r="J14" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A14)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A14))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M10,IF($E$5="Nombre de classes",'02_Base'!O10,'02_Base'!U10)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14))),0))</f>
+        <v/>
+      </c>
+      <c r="K14" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A14,'06_Compta'!$D$4:$D$675,B14,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M10,IF($E$5="Nombre de classes",'02_Base'!O10,'02_Base'!U10)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A14,'02_Base'!$B$4:$B$61,B14))),0))</f>
+        <v/>
+      </c>
+      <c r="L14" s="14">
+        <f>I14+J14+K14</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
+        <f>IFERROR(L14/G14,0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="15">
+        <f>IFERROR(L14/H14,0)</f>
+        <v/>
+      </c>
+      <c r="O14" s="15">
+        <f>IFERROR(F14/G14-M14,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Ipac Bachelor Factory</t>
-        </is>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="C15" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D15" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E15" s="15">
-        <f>C15-D15</f>
+      <c r="A15" s="17">
+        <f>'02_Base'!A11</f>
+        <v/>
+      </c>
+      <c r="B15" s="39">
+        <f>'02_Base'!B11</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>'02_Base'!C11</f>
+        <v/>
+      </c>
+      <c r="D15" s="39">
+        <f>'02_Base'!E11</f>
+        <v/>
+      </c>
+      <c r="E15" s="39">
+        <f>'02_Base'!F11</f>
         <v/>
       </c>
       <c r="F15" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D15-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U11</f>
         <v/>
       </c>
       <c r="G15" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),C15))</f>
-        <v/>
-      </c>
-      <c r="H15" s="25">
-        <f>IFERROR(G15/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M11</f>
+        <v/>
+      </c>
+      <c r="H15" s="23">
+        <f>'02_Base'!O11</f>
         <v/>
       </c>
       <c r="I15" s="15">
-        <f>H15*$I$3</f>
-        <v/>
-      </c>
-      <c r="J15" s="14">
-        <f>E15-F15-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="16">
-        <f>IFERROR(J15/C15,0)</f>
+        <f>F15*0.141</f>
+        <v/>
+      </c>
+      <c r="J15" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A15)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A15))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M11,IF($E$5="Nombre de classes",'02_Base'!O11,'02_Base'!U11)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15))),0))</f>
+        <v/>
+      </c>
+      <c r="K15" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A15,'06_Compta'!$D$4:$D$675,B15,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M11,IF($E$5="Nombre de classes",'02_Base'!O11,'02_Base'!U11)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A15,'02_Base'!$B$4:$B$61,B15))),0))</f>
+        <v/>
+      </c>
+      <c r="L15" s="14">
+        <f>I15+J15+K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="14">
+        <f>IFERROR(L15/G15,0)</f>
+        <v/>
+      </c>
+      <c r="N15" s="15">
+        <f>IFERROR(L15/H15,0)</f>
+        <v/>
+      </c>
+      <c r="O15" s="15">
+        <f>IFERROR(F15/G15-M15,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Pigier</t>
-        </is>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="C16" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D16" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E16" s="15">
-        <f>C16-D16</f>
+      <c r="A16" s="17">
+        <f>'02_Base'!A12</f>
+        <v/>
+      </c>
+      <c r="B16" s="39">
+        <f>'02_Base'!B12</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
+        <f>'02_Base'!C12</f>
+        <v/>
+      </c>
+      <c r="D16" s="39">
+        <f>'02_Base'!E12</f>
+        <v/>
+      </c>
+      <c r="E16" s="39">
+        <f>'02_Base'!F12</f>
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D16-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U12</f>
         <v/>
       </c>
       <c r="G16" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),C16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="25">
-        <f>IFERROR(G16/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M12</f>
+        <v/>
+      </c>
+      <c r="H16" s="23">
+        <f>'02_Base'!O12</f>
         <v/>
       </c>
       <c r="I16" s="15">
-        <f>H16*$I$3</f>
-        <v/>
-      </c>
-      <c r="J16" s="14">
-        <f>E16-F16-I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="16">
-        <f>IFERROR(J16/C16,0)</f>
+        <f>F16*0.141</f>
+        <v/>
+      </c>
+      <c r="J16" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A16)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A16))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M12,IF($E$5="Nombre de classes",'02_Base'!O12,'02_Base'!U12)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16))),0))</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A16,'06_Compta'!$D$4:$D$675,B16,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M12,IF($E$5="Nombre de classes",'02_Base'!O12,'02_Base'!U12)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A16,'02_Base'!$B$4:$B$61,B16))),0))</f>
+        <v/>
+      </c>
+      <c r="L16" s="14">
+        <f>I16+J16+K16</f>
+        <v/>
+      </c>
+      <c r="M16" s="14">
+        <f>IFERROR(L16/G16,0)</f>
+        <v/>
+      </c>
+      <c r="N16" s="15">
+        <f>IFERROR(L16/H16,0)</f>
+        <v/>
+      </c>
+      <c r="O16" s="15">
+        <f>IFERROR(F16/G16-M16,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Pigier</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="C17" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D17" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E17" s="15">
-        <f>C17-D17</f>
+      <c r="A17" s="17">
+        <f>'02_Base'!A13</f>
+        <v/>
+      </c>
+      <c r="B17" s="39">
+        <f>'02_Base'!B13</f>
+        <v/>
+      </c>
+      <c r="C17" s="17">
+        <f>'02_Base'!C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="39">
+        <f>'02_Base'!E13</f>
+        <v/>
+      </c>
+      <c r="E17" s="39">
+        <f>'02_Base'!F13</f>
         <v/>
       </c>
       <c r="F17" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D17-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U13</f>
         <v/>
       </c>
       <c r="G17" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),C17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="25">
-        <f>IFERROR(G17/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M13</f>
+        <v/>
+      </c>
+      <c r="H17" s="23">
+        <f>'02_Base'!O13</f>
         <v/>
       </c>
       <c r="I17" s="15">
-        <f>H17*$I$3</f>
-        <v/>
-      </c>
-      <c r="J17" s="14">
-        <f>E17-F17-I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="16">
-        <f>IFERROR(J17/C17,0)</f>
+        <f>F17*0.141</f>
+        <v/>
+      </c>
+      <c r="J17" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A17)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A17))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M13,IF($E$5="Nombre de classes",'02_Base'!O13,'02_Base'!U13)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17))),0))</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A17,'06_Compta'!$D$4:$D$675,B17,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M13,IF($E$5="Nombre de classes",'02_Base'!O13,'02_Base'!U13)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A17,'02_Base'!$B$4:$B$61,B17))),0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="14">
+        <f>I17+J17+K17</f>
+        <v/>
+      </c>
+      <c r="M17" s="14">
+        <f>IFERROR(L17/G17,0)</f>
+        <v/>
+      </c>
+      <c r="N17" s="15">
+        <f>IFERROR(L17/H17,0)</f>
+        <v/>
+      </c>
+      <c r="O17" s="15">
+        <f>IFERROR(F17/G17-M17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Tunon</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C18" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D18" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E18" s="15">
-        <f>C18-D18</f>
+      <c r="A18" s="17">
+        <f>'02_Base'!A14</f>
+        <v/>
+      </c>
+      <c r="B18" s="39">
+        <f>'02_Base'!B14</f>
+        <v/>
+      </c>
+      <c r="C18" s="17">
+        <f>'02_Base'!C14</f>
+        <v/>
+      </c>
+      <c r="D18" s="39">
+        <f>'02_Base'!E14</f>
+        <v/>
+      </c>
+      <c r="E18" s="39">
+        <f>'02_Base'!F14</f>
         <v/>
       </c>
       <c r="F18" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D18-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U14</f>
         <v/>
       </c>
       <c r="G18" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),C18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="25">
-        <f>IFERROR(G18/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M14</f>
+        <v/>
+      </c>
+      <c r="H18" s="23">
+        <f>'02_Base'!O14</f>
         <v/>
       </c>
       <c r="I18" s="15">
-        <f>H18*$I$3</f>
-        <v/>
-      </c>
-      <c r="J18" s="14">
-        <f>E18-F18-I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="16">
-        <f>IFERROR(J18/C18,0)</f>
+        <f>F18*0.141</f>
+        <v/>
+      </c>
+      <c r="J18" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A18)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A18))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M14,IF($E$5="Nombre de classes",'02_Base'!O14,'02_Base'!U14)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18))),0))</f>
+        <v/>
+      </c>
+      <c r="K18" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A18,'06_Compta'!$D$4:$D$675,B18,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M14,IF($E$5="Nombre de classes",'02_Base'!O14,'02_Base'!U14)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A18,'02_Base'!$B$4:$B$61,B18))),0))</f>
+        <v/>
+      </c>
+      <c r="L18" s="14">
+        <f>I18+J18+K18</f>
+        <v/>
+      </c>
+      <c r="M18" s="14">
+        <f>IFERROR(L18/G18,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="15">
+        <f>IFERROR(L18/H18,0)</f>
+        <v/>
+      </c>
+      <c r="O18" s="15">
+        <f>IFERROR(F18/G18-M18,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Tunon</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="C19" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Produit")</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Coûts directs")</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f>C19-D19</f>
+      <c r="A19" s="17">
+        <f>'02_Base'!A15</f>
+        <v/>
+      </c>
+      <c r="B19" s="39">
+        <f>'02_Base'!B15</f>
+        <v/>
+      </c>
+      <c r="C19" s="17">
+        <f>'02_Base'!C15</f>
+        <v/>
+      </c>
+      <c r="D19" s="39">
+        <f>'02_Base'!E15</f>
+        <v/>
+      </c>
+      <c r="E19" s="39">
+        <f>'02_Base'!F15</f>
         <v/>
       </c>
       <c r="F19" s="15">
-        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-D19-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")</f>
+        <f>'02_Base'!U15</f>
         <v/>
       </c>
       <c r="G19" s="23">
-        <f>IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),C19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="25">
-        <f>IFERROR(G19/SUM($G$6:$G$19),0)</f>
+        <f>'02_Base'!M15</f>
+        <v/>
+      </c>
+      <c r="H19" s="23">
+        <f>'02_Base'!O15</f>
         <v/>
       </c>
       <c r="I19" s="15">
-        <f>H19*$I$3</f>
-        <v/>
-      </c>
-      <c r="J19" s="14">
-        <f>E19-F19-I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="16">
-        <f>IFERROR(J19/C19,0)</f>
+        <f>F19*0.141</f>
+        <v/>
+      </c>
+      <c r="J19" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A19)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A19))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M15,IF($E$5="Nombre de classes",'02_Base'!O15,'02_Base'!U15)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19))),0))</f>
+        <v/>
+      </c>
+      <c r="K19" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A19,'06_Compta'!$D$4:$D$675,B19,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M15,IF($E$5="Nombre de classes",'02_Base'!O15,'02_Base'!U15)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A19,'02_Base'!$B$4:$B$61,B19))),0))</f>
+        <v/>
+      </c>
+      <c r="L19" s="14">
+        <f>I19+J19+K19</f>
+        <v/>
+      </c>
+      <c r="M19" s="14">
+        <f>IFERROR(L19/G19,0)</f>
+        <v/>
+      </c>
+      <c r="N19" s="15">
+        <f>IFERROR(L19/H19,0)</f>
+        <v/>
+      </c>
+      <c r="O19" s="15">
+        <f>IFERROR(F19/G19-M19,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="17">
+        <f>'02_Base'!A16</f>
+        <v/>
+      </c>
+      <c r="B20" s="39">
+        <f>'02_Base'!B16</f>
+        <v/>
+      </c>
+      <c r="C20" s="17">
+        <f>'02_Base'!C16</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
+        <f>'02_Base'!E16</f>
+        <v/>
+      </c>
+      <c r="E20" s="39">
+        <f>'02_Base'!F16</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>'02_Base'!U16</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
+        <f>'02_Base'!M16</f>
+        <v/>
+      </c>
+      <c r="H20" s="23">
+        <f>'02_Base'!O16</f>
+        <v/>
+      </c>
+      <c r="I20" s="15">
+        <f>F20*0.141</f>
+        <v/>
+      </c>
+      <c r="J20" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A20),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A20),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A20)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A20),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A20),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A20))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M16,IF($E$5="Nombre de classes",'02_Base'!O16,'02_Base'!U16)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20))),0))</f>
+        <v/>
+      </c>
+      <c r="K20" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A20,'06_Compta'!$D$4:$D$675,B20,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A20,'06_Compta'!$D$4:$D$675,B20,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M16,IF($E$5="Nombre de classes",'02_Base'!O16,'02_Base'!U16)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A20,'02_Base'!$B$4:$B$61,B20))),0))</f>
+        <v/>
+      </c>
+      <c r="L20" s="14">
+        <f>I20+J20+K20</f>
+        <v/>
+      </c>
+      <c r="M20" s="14">
+        <f>IFERROR(L20/G20,0)</f>
+        <v/>
+      </c>
+      <c r="N20" s="15">
+        <f>IFERROR(L20/H20,0)</f>
+        <v/>
+      </c>
+      <c r="O20" s="15">
+        <f>IFERROR(F20/G20-M20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17">
+        <f>'02_Base'!A17</f>
+        <v/>
+      </c>
+      <c r="B21" s="39">
+        <f>'02_Base'!B17</f>
+        <v/>
+      </c>
+      <c r="C21" s="17">
+        <f>'02_Base'!C17</f>
+        <v/>
+      </c>
+      <c r="D21" s="39">
+        <f>'02_Base'!E17</f>
+        <v/>
+      </c>
+      <c r="E21" s="39">
+        <f>'02_Base'!F17</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>'02_Base'!U17</f>
+        <v/>
+      </c>
+      <c r="G21" s="23">
+        <f>'02_Base'!M17</f>
+        <v/>
+      </c>
+      <c r="H21" s="23">
+        <f>'02_Base'!O17</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>F21*0.141</f>
+        <v/>
+      </c>
+      <c r="J21" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A21),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A21),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A21)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A21),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A21),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A21))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M17,IF($E$5="Nombre de classes",'02_Base'!O17,'02_Base'!U17)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21))),0))</f>
+        <v/>
+      </c>
+      <c r="K21" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A21,'06_Compta'!$D$4:$D$675,B21,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A21,'06_Compta'!$D$4:$D$675,B21,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M17,IF($E$5="Nombre de classes",'02_Base'!O17,'02_Base'!U17)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A21,'02_Base'!$B$4:$B$61,B21))),0))</f>
+        <v/>
+      </c>
+      <c r="L21" s="14">
+        <f>I21+J21+K21</f>
+        <v/>
+      </c>
+      <c r="M21" s="14">
+        <f>IFERROR(L21/G21,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="15">
+        <f>IFERROR(L21/H21,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="15">
+        <f>IFERROR(F21/G21-M21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17">
+        <f>'02_Base'!A18</f>
+        <v/>
+      </c>
+      <c r="B22" s="39">
+        <f>'02_Base'!B18</f>
+        <v/>
+      </c>
+      <c r="C22" s="17">
+        <f>'02_Base'!C18</f>
+        <v/>
+      </c>
+      <c r="D22" s="39">
+        <f>'02_Base'!E18</f>
+        <v/>
+      </c>
+      <c r="E22" s="39">
+        <f>'02_Base'!F18</f>
+        <v/>
+      </c>
+      <c r="F22" s="15">
+        <f>'02_Base'!U18</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
+        <f>'02_Base'!M18</f>
+        <v/>
+      </c>
+      <c r="H22" s="23">
+        <f>'02_Base'!O18</f>
+        <v/>
+      </c>
+      <c r="I22" s="15">
+        <f>F22*0.141</f>
+        <v/>
+      </c>
+      <c r="J22" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A22),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A22),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A22)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A22),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A22),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A22))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M18,IF($E$5="Nombre de classes",'02_Base'!O18,'02_Base'!U18)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22))),0))</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A22,'06_Compta'!$D$4:$D$675,B22,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A22,'06_Compta'!$D$4:$D$675,B22,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M18,IF($E$5="Nombre de classes",'02_Base'!O18,'02_Base'!U18)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A22,'02_Base'!$B$4:$B$61,B22))),0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="14">
+        <f>I22+J22+K22</f>
+        <v/>
+      </c>
+      <c r="M22" s="14">
+        <f>IFERROR(L22/G22,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="15">
+        <f>IFERROR(L22/H22,0)</f>
+        <v/>
+      </c>
+      <c r="O22" s="15">
+        <f>IFERROR(F22/G22-M22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17">
+        <f>'02_Base'!A19</f>
+        <v/>
+      </c>
+      <c r="B23" s="39">
+        <f>'02_Base'!B19</f>
+        <v/>
+      </c>
+      <c r="C23" s="17">
+        <f>'02_Base'!C19</f>
+        <v/>
+      </c>
+      <c r="D23" s="39">
+        <f>'02_Base'!E19</f>
+        <v/>
+      </c>
+      <c r="E23" s="39">
+        <f>'02_Base'!F19</f>
+        <v/>
+      </c>
+      <c r="F23" s="15">
+        <f>'02_Base'!U19</f>
+        <v/>
+      </c>
+      <c r="G23" s="23">
+        <f>'02_Base'!M19</f>
+        <v/>
+      </c>
+      <c r="H23" s="23">
+        <f>'02_Base'!O19</f>
+        <v/>
+      </c>
+      <c r="I23" s="15">
+        <f>F23*0.141</f>
+        <v/>
+      </c>
+      <c r="J23" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A23),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A23),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A23)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A23),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A23),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A23))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M19,IF($E$5="Nombre de classes",'02_Base'!O19,'02_Base'!U19)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23))),0))</f>
+        <v/>
+      </c>
+      <c r="K23" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A23,'06_Compta'!$D$4:$D$675,B23,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A23,'06_Compta'!$D$4:$D$675,B23,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M19,IF($E$5="Nombre de classes",'02_Base'!O19,'02_Base'!U19)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A23,'02_Base'!$B$4:$B$61,B23))),0))</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>I23+J23+K23</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
+        <f>IFERROR(L23/G23,0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="15">
+        <f>IFERROR(L23/H23,0)</f>
+        <v/>
+      </c>
+      <c r="O23" s="15">
+        <f>IFERROR(F23/G23-M23,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17">
+        <f>'02_Base'!A20</f>
+        <v/>
+      </c>
+      <c r="B24" s="39">
+        <f>'02_Base'!B20</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>'02_Base'!C20</f>
+        <v/>
+      </c>
+      <c r="D24" s="39">
+        <f>'02_Base'!E20</f>
+        <v/>
+      </c>
+      <c r="E24" s="39">
+        <f>'02_Base'!F20</f>
+        <v/>
+      </c>
+      <c r="F24" s="15">
+        <f>'02_Base'!U20</f>
+        <v/>
+      </c>
+      <c r="G24" s="23">
+        <f>'02_Base'!M20</f>
+        <v/>
+      </c>
+      <c r="H24" s="23">
+        <f>'02_Base'!O20</f>
+        <v/>
+      </c>
+      <c r="I24" s="15">
+        <f>F24*0.141</f>
+        <v/>
+      </c>
+      <c r="J24" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A24),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A24),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A24)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A24),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A24),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A24))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M20,IF($E$5="Nombre de classes",'02_Base'!O20,'02_Base'!U20)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24))),0))</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A24,'06_Compta'!$D$4:$D$675,B24,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A24,'06_Compta'!$D$4:$D$675,B24,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M20,IF($E$5="Nombre de classes",'02_Base'!O20,'02_Base'!U20)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A24,'02_Base'!$B$4:$B$61,B24))),0))</f>
+        <v/>
+      </c>
+      <c r="L24" s="14">
+        <f>I24+J24+K24</f>
+        <v/>
+      </c>
+      <c r="M24" s="14">
+        <f>IFERROR(L24/G24,0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="15">
+        <f>IFERROR(L24/H24,0)</f>
+        <v/>
+      </c>
+      <c r="O24" s="15">
+        <f>IFERROR(F24/G24-M24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17">
+        <f>'02_Base'!A21</f>
+        <v/>
+      </c>
+      <c r="B25" s="39">
+        <f>'02_Base'!B21</f>
+        <v/>
+      </c>
+      <c r="C25" s="17">
+        <f>'02_Base'!C21</f>
+        <v/>
+      </c>
+      <c r="D25" s="39">
+        <f>'02_Base'!E21</f>
+        <v/>
+      </c>
+      <c r="E25" s="39">
+        <f>'02_Base'!F21</f>
+        <v/>
+      </c>
+      <c r="F25" s="15">
+        <f>'02_Base'!U21</f>
+        <v/>
+      </c>
+      <c r="G25" s="23">
+        <f>'02_Base'!M21</f>
+        <v/>
+      </c>
+      <c r="H25" s="23">
+        <f>'02_Base'!O21</f>
+        <v/>
+      </c>
+      <c r="I25" s="15">
+        <f>F25*0.141</f>
+        <v/>
+      </c>
+      <c r="J25" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A25),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A25),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A25)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A25),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A25),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A25))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M21,IF($E$5="Nombre de classes",'02_Base'!O21,'02_Base'!U21)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25))),0))</f>
+        <v/>
+      </c>
+      <c r="K25" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A25,'06_Compta'!$D$4:$D$675,B25,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A25,'06_Compta'!$D$4:$D$675,B25,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M21,IF($E$5="Nombre de classes",'02_Base'!O21,'02_Base'!U21)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A25,'02_Base'!$B$4:$B$61,B25))),0))</f>
+        <v/>
+      </c>
+      <c r="L25" s="14">
+        <f>I25+J25+K25</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
+        <f>IFERROR(L25/G25,0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="15">
+        <f>IFERROR(L25/H25,0)</f>
+        <v/>
+      </c>
+      <c r="O25" s="15">
+        <f>IFERROR(F25/G25-M25,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17">
+        <f>'02_Base'!A22</f>
+        <v/>
+      </c>
+      <c r="B26" s="39">
+        <f>'02_Base'!B22</f>
+        <v/>
+      </c>
+      <c r="C26" s="17">
+        <f>'02_Base'!C22</f>
+        <v/>
+      </c>
+      <c r="D26" s="39">
+        <f>'02_Base'!E22</f>
+        <v/>
+      </c>
+      <c r="E26" s="39">
+        <f>'02_Base'!F22</f>
+        <v/>
+      </c>
+      <c r="F26" s="15">
+        <f>'02_Base'!U22</f>
+        <v/>
+      </c>
+      <c r="G26" s="23">
+        <f>'02_Base'!M22</f>
+        <v/>
+      </c>
+      <c r="H26" s="23">
+        <f>'02_Base'!O22</f>
+        <v/>
+      </c>
+      <c r="I26" s="15">
+        <f>F26*0.141</f>
+        <v/>
+      </c>
+      <c r="J26" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A26),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A26),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A26)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A26),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A26),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A26))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M22,IF($E$5="Nombre de classes",'02_Base'!O22,'02_Base'!U22)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26))),0))</f>
+        <v/>
+      </c>
+      <c r="K26" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A26,'06_Compta'!$D$4:$D$675,B26,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A26,'06_Compta'!$D$4:$D$675,B26,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M22,IF($E$5="Nombre de classes",'02_Base'!O22,'02_Base'!U22)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A26,'02_Base'!$B$4:$B$61,B26))),0))</f>
+        <v/>
+      </c>
+      <c r="L26" s="14">
+        <f>I26+J26+K26</f>
+        <v/>
+      </c>
+      <c r="M26" s="14">
+        <f>IFERROR(L26/G26,0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="15">
+        <f>IFERROR(L26/H26,0)</f>
+        <v/>
+      </c>
+      <c r="O26" s="15">
+        <f>IFERROR(F26/G26-M26,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17">
+        <f>'02_Base'!A23</f>
+        <v/>
+      </c>
+      <c r="B27" s="39">
+        <f>'02_Base'!B23</f>
+        <v/>
+      </c>
+      <c r="C27" s="17">
+        <f>'02_Base'!C23</f>
+        <v/>
+      </c>
+      <c r="D27" s="39">
+        <f>'02_Base'!E23</f>
+        <v/>
+      </c>
+      <c r="E27" s="39">
+        <f>'02_Base'!F23</f>
+        <v/>
+      </c>
+      <c r="F27" s="15">
+        <f>'02_Base'!U23</f>
+        <v/>
+      </c>
+      <c r="G27" s="23">
+        <f>'02_Base'!M23</f>
+        <v/>
+      </c>
+      <c r="H27" s="23">
+        <f>'02_Base'!O23</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>F27*0.141</f>
+        <v/>
+      </c>
+      <c r="J27" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A27),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A27),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A27)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A27),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A27),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A27))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M23,IF($E$5="Nombre de classes",'02_Base'!O23,'02_Base'!U23)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27))),0))</f>
+        <v/>
+      </c>
+      <c r="K27" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A27,'06_Compta'!$D$4:$D$675,B27,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A27,'06_Compta'!$D$4:$D$675,B27,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M23,IF($E$5="Nombre de classes",'02_Base'!O23,'02_Base'!U23)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A27,'02_Base'!$B$4:$B$61,B27))),0))</f>
+        <v/>
+      </c>
+      <c r="L27" s="14">
+        <f>I27+J27+K27</f>
+        <v/>
+      </c>
+      <c r="M27" s="14">
+        <f>IFERROR(L27/G27,0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="15">
+        <f>IFERROR(L27/H27,0)</f>
+        <v/>
+      </c>
+      <c r="O27" s="15">
+        <f>IFERROR(F27/G27-M27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17">
+        <f>'02_Base'!A24</f>
+        <v/>
+      </c>
+      <c r="B28" s="39">
+        <f>'02_Base'!B24</f>
+        <v/>
+      </c>
+      <c r="C28" s="17">
+        <f>'02_Base'!C24</f>
+        <v/>
+      </c>
+      <c r="D28" s="39">
+        <f>'02_Base'!E24</f>
+        <v/>
+      </c>
+      <c r="E28" s="39">
+        <f>'02_Base'!F24</f>
+        <v/>
+      </c>
+      <c r="F28" s="15">
+        <f>'02_Base'!U24</f>
+        <v/>
+      </c>
+      <c r="G28" s="23">
+        <f>'02_Base'!M24</f>
+        <v/>
+      </c>
+      <c r="H28" s="23">
+        <f>'02_Base'!O24</f>
+        <v/>
+      </c>
+      <c r="I28" s="15">
+        <f>F28*0.141</f>
+        <v/>
+      </c>
+      <c r="J28" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A28),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A28),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A28)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A28),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A28),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A28))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M24,IF($E$5="Nombre de classes",'02_Base'!O24,'02_Base'!U24)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28))),0))</f>
+        <v/>
+      </c>
+      <c r="K28" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A28,'06_Compta'!$D$4:$D$675,B28,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A28,'06_Compta'!$D$4:$D$675,B28,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M24,IF($E$5="Nombre de classes",'02_Base'!O24,'02_Base'!U24)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A28,'02_Base'!$B$4:$B$61,B28))),0))</f>
+        <v/>
+      </c>
+      <c r="L28" s="14">
+        <f>I28+J28+K28</f>
+        <v/>
+      </c>
+      <c r="M28" s="14">
+        <f>IFERROR(L28/G28,0)</f>
+        <v/>
+      </c>
+      <c r="N28" s="15">
+        <f>IFERROR(L28/H28,0)</f>
+        <v/>
+      </c>
+      <c r="O28" s="15">
+        <f>IFERROR(F28/G28-M28,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17">
+        <f>'02_Base'!A25</f>
+        <v/>
+      </c>
+      <c r="B29" s="39">
+        <f>'02_Base'!B25</f>
+        <v/>
+      </c>
+      <c r="C29" s="17">
+        <f>'02_Base'!C25</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>'02_Base'!E25</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
+        <f>'02_Base'!F25</f>
+        <v/>
+      </c>
+      <c r="F29" s="15">
+        <f>'02_Base'!U25</f>
+        <v/>
+      </c>
+      <c r="G29" s="23">
+        <f>'02_Base'!M25</f>
+        <v/>
+      </c>
+      <c r="H29" s="23">
+        <f>'02_Base'!O25</f>
+        <v/>
+      </c>
+      <c r="I29" s="15">
+        <f>F29*0.141</f>
+        <v/>
+      </c>
+      <c r="J29" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A29),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A29),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A29)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A29),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A29),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A29))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M25,IF($E$5="Nombre de classes",'02_Base'!O25,'02_Base'!U25)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29))),0))</f>
+        <v/>
+      </c>
+      <c r="K29" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A29,'06_Compta'!$D$4:$D$675,B29,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A29,'06_Compta'!$D$4:$D$675,B29,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M25,IF($E$5="Nombre de classes",'02_Base'!O25,'02_Base'!U25)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A29,'02_Base'!$B$4:$B$61,B29))),0))</f>
+        <v/>
+      </c>
+      <c r="L29" s="14">
+        <f>I29+J29+K29</f>
+        <v/>
+      </c>
+      <c r="M29" s="14">
+        <f>IFERROR(L29/G29,0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="15">
+        <f>IFERROR(L29/H29,0)</f>
+        <v/>
+      </c>
+      <c r="O29" s="15">
+        <f>IFERROR(F29/G29-M29,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17">
+        <f>'02_Base'!A26</f>
+        <v/>
+      </c>
+      <c r="B30" s="39">
+        <f>'02_Base'!B26</f>
+        <v/>
+      </c>
+      <c r="C30" s="17">
+        <f>'02_Base'!C26</f>
+        <v/>
+      </c>
+      <c r="D30" s="39">
+        <f>'02_Base'!E26</f>
+        <v/>
+      </c>
+      <c r="E30" s="39">
+        <f>'02_Base'!F26</f>
+        <v/>
+      </c>
+      <c r="F30" s="15">
+        <f>'02_Base'!U26</f>
+        <v/>
+      </c>
+      <c r="G30" s="23">
+        <f>'02_Base'!M26</f>
+        <v/>
+      </c>
+      <c r="H30" s="23">
+        <f>'02_Base'!O26</f>
+        <v/>
+      </c>
+      <c r="I30" s="15">
+        <f>F30*0.141</f>
+        <v/>
+      </c>
+      <c r="J30" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A30),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A30),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A30)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A30),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A30),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A30))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M26,IF($E$5="Nombre de classes",'02_Base'!O26,'02_Base'!U26)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30))),0))</f>
+        <v/>
+      </c>
+      <c r="K30" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A30,'06_Compta'!$D$4:$D$675,B30,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A30,'06_Compta'!$D$4:$D$675,B30,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M26,IF($E$5="Nombre de classes",'02_Base'!O26,'02_Base'!U26)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A30,'02_Base'!$B$4:$B$61,B30))),0))</f>
+        <v/>
+      </c>
+      <c r="L30" s="14">
+        <f>I30+J30+K30</f>
+        <v/>
+      </c>
+      <c r="M30" s="14">
+        <f>IFERROR(L30/G30,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="15">
+        <f>IFERROR(L30/H30,0)</f>
+        <v/>
+      </c>
+      <c r="O30" s="15">
+        <f>IFERROR(F30/G30-M30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17">
+        <f>'02_Base'!A27</f>
+        <v/>
+      </c>
+      <c r="B31" s="39">
+        <f>'02_Base'!B27</f>
+        <v/>
+      </c>
+      <c r="C31" s="17">
+        <f>'02_Base'!C27</f>
+        <v/>
+      </c>
+      <c r="D31" s="39">
+        <f>'02_Base'!E27</f>
+        <v/>
+      </c>
+      <c r="E31" s="39">
+        <f>'02_Base'!F27</f>
+        <v/>
+      </c>
+      <c r="F31" s="15">
+        <f>'02_Base'!U27</f>
+        <v/>
+      </c>
+      <c r="G31" s="23">
+        <f>'02_Base'!M27</f>
+        <v/>
+      </c>
+      <c r="H31" s="23">
+        <f>'02_Base'!O27</f>
+        <v/>
+      </c>
+      <c r="I31" s="15">
+        <f>F31*0.141</f>
+        <v/>
+      </c>
+      <c r="J31" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A31),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A31),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A31)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A31),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A31),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A31))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M27,IF($E$5="Nombre de classes",'02_Base'!O27,'02_Base'!U27)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31))),0))</f>
+        <v/>
+      </c>
+      <c r="K31" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A31,'06_Compta'!$D$4:$D$675,B31,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A31,'06_Compta'!$D$4:$D$675,B31,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M27,IF($E$5="Nombre de classes",'02_Base'!O27,'02_Base'!U27)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A31,'02_Base'!$B$4:$B$61,B31))),0))</f>
+        <v/>
+      </c>
+      <c r="L31" s="14">
+        <f>I31+J31+K31</f>
+        <v/>
+      </c>
+      <c r="M31" s="14">
+        <f>IFERROR(L31/G31,0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="15">
+        <f>IFERROR(L31/H31,0)</f>
+        <v/>
+      </c>
+      <c r="O31" s="15">
+        <f>IFERROR(F31/G31-M31,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17">
+        <f>'02_Base'!A28</f>
+        <v/>
+      </c>
+      <c r="B32" s="39">
+        <f>'02_Base'!B28</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>'02_Base'!C28</f>
+        <v/>
+      </c>
+      <c r="D32" s="39">
+        <f>'02_Base'!E28</f>
+        <v/>
+      </c>
+      <c r="E32" s="39">
+        <f>'02_Base'!F28</f>
+        <v/>
+      </c>
+      <c r="F32" s="15">
+        <f>'02_Base'!U28</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>'02_Base'!M28</f>
+        <v/>
+      </c>
+      <c r="H32" s="23">
+        <f>'02_Base'!O28</f>
+        <v/>
+      </c>
+      <c r="I32" s="15">
+        <f>F32*0.141</f>
+        <v/>
+      </c>
+      <c r="J32" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A32),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A32),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A32)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A32),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A32),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A32))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M28,IF($E$5="Nombre de classes",'02_Base'!O28,'02_Base'!U28)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32))),0))</f>
+        <v/>
+      </c>
+      <c r="K32" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A32,'06_Compta'!$D$4:$D$675,B32,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A32,'06_Compta'!$D$4:$D$675,B32,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M28,IF($E$5="Nombre de classes",'02_Base'!O28,'02_Base'!U28)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A32,'02_Base'!$B$4:$B$61,B32))),0))</f>
+        <v/>
+      </c>
+      <c r="L32" s="14">
+        <f>I32+J32+K32</f>
+        <v/>
+      </c>
+      <c r="M32" s="14">
+        <f>IFERROR(L32/G32,0)</f>
+        <v/>
+      </c>
+      <c r="N32" s="15">
+        <f>IFERROR(L32/H32,0)</f>
+        <v/>
+      </c>
+      <c r="O32" s="15">
+        <f>IFERROR(F32/G32-M32,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17">
+        <f>'02_Base'!A29</f>
+        <v/>
+      </c>
+      <c r="B33" s="39">
+        <f>'02_Base'!B29</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>'02_Base'!C29</f>
+        <v/>
+      </c>
+      <c r="D33" s="39">
+        <f>'02_Base'!E29</f>
+        <v/>
+      </c>
+      <c r="E33" s="39">
+        <f>'02_Base'!F29</f>
+        <v/>
+      </c>
+      <c r="F33" s="15">
+        <f>'02_Base'!U29</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>'02_Base'!M29</f>
+        <v/>
+      </c>
+      <c r="H33" s="23">
+        <f>'02_Base'!O29</f>
+        <v/>
+      </c>
+      <c r="I33" s="15">
+        <f>F33*0.141</f>
+        <v/>
+      </c>
+      <c r="J33" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A33),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A33),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A33)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A33),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A33),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A33))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M29,IF($E$5="Nombre de classes",'02_Base'!O29,'02_Base'!U29)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33))),0))</f>
+        <v/>
+      </c>
+      <c r="K33" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A33,'06_Compta'!$D$4:$D$675,B33,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A33,'06_Compta'!$D$4:$D$675,B33,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M29,IF($E$5="Nombre de classes",'02_Base'!O29,'02_Base'!U29)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A33,'02_Base'!$B$4:$B$61,B33))),0))</f>
+        <v/>
+      </c>
+      <c r="L33" s="14">
+        <f>I33+J33+K33</f>
+        <v/>
+      </c>
+      <c r="M33" s="14">
+        <f>IFERROR(L33/G33,0)</f>
+        <v/>
+      </c>
+      <c r="N33" s="15">
+        <f>IFERROR(L33/H33,0)</f>
+        <v/>
+      </c>
+      <c r="O33" s="15">
+        <f>IFERROR(F33/G33-M33,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17">
+        <f>'02_Base'!A30</f>
+        <v/>
+      </c>
+      <c r="B34" s="39">
+        <f>'02_Base'!B30</f>
+        <v/>
+      </c>
+      <c r="C34" s="17">
+        <f>'02_Base'!C30</f>
+        <v/>
+      </c>
+      <c r="D34" s="39">
+        <f>'02_Base'!E30</f>
+        <v/>
+      </c>
+      <c r="E34" s="39">
+        <f>'02_Base'!F30</f>
+        <v/>
+      </c>
+      <c r="F34" s="15">
+        <f>'02_Base'!U30</f>
+        <v/>
+      </c>
+      <c r="G34" s="23">
+        <f>'02_Base'!M30</f>
+        <v/>
+      </c>
+      <c r="H34" s="23">
+        <f>'02_Base'!O30</f>
+        <v/>
+      </c>
+      <c r="I34" s="15">
+        <f>F34*0.141</f>
+        <v/>
+      </c>
+      <c r="J34" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A34),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A34),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A34)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A34),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A34),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A34))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M30,IF($E$5="Nombre de classes",'02_Base'!O30,'02_Base'!U30)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34))),0))</f>
+        <v/>
+      </c>
+      <c r="K34" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A34,'06_Compta'!$D$4:$D$675,B34,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A34,'06_Compta'!$D$4:$D$675,B34,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M30,IF($E$5="Nombre de classes",'02_Base'!O30,'02_Base'!U30)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A34,'02_Base'!$B$4:$B$61,B34))),0))</f>
+        <v/>
+      </c>
+      <c r="L34" s="14">
+        <f>I34+J34+K34</f>
+        <v/>
+      </c>
+      <c r="M34" s="14">
+        <f>IFERROR(L34/G34,0)</f>
+        <v/>
+      </c>
+      <c r="N34" s="15">
+        <f>IFERROR(L34/H34,0)</f>
+        <v/>
+      </c>
+      <c r="O34" s="15">
+        <f>IFERROR(F34/G34-M34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17">
+        <f>'02_Base'!A31</f>
+        <v/>
+      </c>
+      <c r="B35" s="39">
+        <f>'02_Base'!B31</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>'02_Base'!C31</f>
+        <v/>
+      </c>
+      <c r="D35" s="39">
+        <f>'02_Base'!E31</f>
+        <v/>
+      </c>
+      <c r="E35" s="39">
+        <f>'02_Base'!F31</f>
+        <v/>
+      </c>
+      <c r="F35" s="15">
+        <f>'02_Base'!U31</f>
+        <v/>
+      </c>
+      <c r="G35" s="23">
+        <f>'02_Base'!M31</f>
+        <v/>
+      </c>
+      <c r="H35" s="23">
+        <f>'02_Base'!O31</f>
+        <v/>
+      </c>
+      <c r="I35" s="15">
+        <f>F35*0.141</f>
+        <v/>
+      </c>
+      <c r="J35" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A35),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A35),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A35)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A35),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A35),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A35))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M31,IF($E$5="Nombre de classes",'02_Base'!O31,'02_Base'!U31)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35))),0))</f>
+        <v/>
+      </c>
+      <c r="K35" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A35,'06_Compta'!$D$4:$D$675,B35,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A35,'06_Compta'!$D$4:$D$675,B35,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M31,IF($E$5="Nombre de classes",'02_Base'!O31,'02_Base'!U31)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A35,'02_Base'!$B$4:$B$61,B35))),0))</f>
+        <v/>
+      </c>
+      <c r="L35" s="14">
+        <f>I35+J35+K35</f>
+        <v/>
+      </c>
+      <c r="M35" s="14">
+        <f>IFERROR(L35/G35,0)</f>
+        <v/>
+      </c>
+      <c r="N35" s="15">
+        <f>IFERROR(L35/H35,0)</f>
+        <v/>
+      </c>
+      <c r="O35" s="15">
+        <f>IFERROR(F35/G35-M35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17">
+        <f>'02_Base'!A32</f>
+        <v/>
+      </c>
+      <c r="B36" s="39">
+        <f>'02_Base'!B32</f>
+        <v/>
+      </c>
+      <c r="C36" s="17">
+        <f>'02_Base'!C32</f>
+        <v/>
+      </c>
+      <c r="D36" s="39">
+        <f>'02_Base'!E32</f>
+        <v/>
+      </c>
+      <c r="E36" s="39">
+        <f>'02_Base'!F32</f>
+        <v/>
+      </c>
+      <c r="F36" s="15">
+        <f>'02_Base'!U32</f>
+        <v/>
+      </c>
+      <c r="G36" s="23">
+        <f>'02_Base'!M32</f>
+        <v/>
+      </c>
+      <c r="H36" s="23">
+        <f>'02_Base'!O32</f>
+        <v/>
+      </c>
+      <c r="I36" s="15">
+        <f>F36*0.141</f>
+        <v/>
+      </c>
+      <c r="J36" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A36),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A36),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A36)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A36),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A36),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A36))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M32,IF($E$5="Nombre de classes",'02_Base'!O32,'02_Base'!U32)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36))),0))</f>
+        <v/>
+      </c>
+      <c r="K36" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A36,'06_Compta'!$D$4:$D$675,B36,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A36,'06_Compta'!$D$4:$D$675,B36,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M32,IF($E$5="Nombre de classes",'02_Base'!O32,'02_Base'!U32)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A36,'02_Base'!$B$4:$B$61,B36))),0))</f>
+        <v/>
+      </c>
+      <c r="L36" s="14">
+        <f>I36+J36+K36</f>
+        <v/>
+      </c>
+      <c r="M36" s="14">
+        <f>IFERROR(L36/G36,0)</f>
+        <v/>
+      </c>
+      <c r="N36" s="15">
+        <f>IFERROR(L36/H36,0)</f>
+        <v/>
+      </c>
+      <c r="O36" s="15">
+        <f>IFERROR(F36/G36-M36,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17">
+        <f>'02_Base'!A33</f>
+        <v/>
+      </c>
+      <c r="B37" s="39">
+        <f>'02_Base'!B33</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>'02_Base'!C33</f>
+        <v/>
+      </c>
+      <c r="D37" s="39">
+        <f>'02_Base'!E33</f>
+        <v/>
+      </c>
+      <c r="E37" s="39">
+        <f>'02_Base'!F33</f>
+        <v/>
+      </c>
+      <c r="F37" s="15">
+        <f>'02_Base'!U33</f>
+        <v/>
+      </c>
+      <c r="G37" s="23">
+        <f>'02_Base'!M33</f>
+        <v/>
+      </c>
+      <c r="H37" s="23">
+        <f>'02_Base'!O33</f>
+        <v/>
+      </c>
+      <c r="I37" s="15">
+        <f>F37*0.141</f>
+        <v/>
+      </c>
+      <c r="J37" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A37),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A37),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A37)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A37),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A37),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A37))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M33,IF($E$5="Nombre de classes",'02_Base'!O33,'02_Base'!U33)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37))),0))</f>
+        <v/>
+      </c>
+      <c r="K37" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A37,'06_Compta'!$D$4:$D$675,B37,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A37,'06_Compta'!$D$4:$D$675,B37,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M33,IF($E$5="Nombre de classes",'02_Base'!O33,'02_Base'!U33)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A37,'02_Base'!$B$4:$B$61,B37))),0))</f>
+        <v/>
+      </c>
+      <c r="L37" s="14">
+        <f>I37+J37+K37</f>
+        <v/>
+      </c>
+      <c r="M37" s="14">
+        <f>IFERROR(L37/G37,0)</f>
+        <v/>
+      </c>
+      <c r="N37" s="15">
+        <f>IFERROR(L37/H37,0)</f>
+        <v/>
+      </c>
+      <c r="O37" s="15">
+        <f>IFERROR(F37/G37-M37,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17">
+        <f>'02_Base'!A34</f>
+        <v/>
+      </c>
+      <c r="B38" s="39">
+        <f>'02_Base'!B34</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>'02_Base'!C34</f>
+        <v/>
+      </c>
+      <c r="D38" s="39">
+        <f>'02_Base'!E34</f>
+        <v/>
+      </c>
+      <c r="E38" s="39">
+        <f>'02_Base'!F34</f>
+        <v/>
+      </c>
+      <c r="F38" s="15">
+        <f>'02_Base'!U34</f>
+        <v/>
+      </c>
+      <c r="G38" s="23">
+        <f>'02_Base'!M34</f>
+        <v/>
+      </c>
+      <c r="H38" s="23">
+        <f>'02_Base'!O34</f>
+        <v/>
+      </c>
+      <c r="I38" s="15">
+        <f>F38*0.141</f>
+        <v/>
+      </c>
+      <c r="J38" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A38),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A38),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A38)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A38),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A38),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A38))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M34,IF($E$5="Nombre de classes",'02_Base'!O34,'02_Base'!U34)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38))),0))</f>
+        <v/>
+      </c>
+      <c r="K38" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A38,'06_Compta'!$D$4:$D$675,B38,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A38,'06_Compta'!$D$4:$D$675,B38,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M34,IF($E$5="Nombre de classes",'02_Base'!O34,'02_Base'!U34)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A38,'02_Base'!$B$4:$B$61,B38))),0))</f>
+        <v/>
+      </c>
+      <c r="L38" s="14">
+        <f>I38+J38+K38</f>
+        <v/>
+      </c>
+      <c r="M38" s="14">
+        <f>IFERROR(L38/G38,0)</f>
+        <v/>
+      </c>
+      <c r="N38" s="15">
+        <f>IFERROR(L38/H38,0)</f>
+        <v/>
+      </c>
+      <c r="O38" s="15">
+        <f>IFERROR(F38/G38-M38,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17">
+        <f>'02_Base'!A35</f>
+        <v/>
+      </c>
+      <c r="B39" s="39">
+        <f>'02_Base'!B35</f>
+        <v/>
+      </c>
+      <c r="C39" s="17">
+        <f>'02_Base'!C35</f>
+        <v/>
+      </c>
+      <c r="D39" s="39">
+        <f>'02_Base'!E35</f>
+        <v/>
+      </c>
+      <c r="E39" s="39">
+        <f>'02_Base'!F35</f>
+        <v/>
+      </c>
+      <c r="F39" s="15">
+        <f>'02_Base'!U35</f>
+        <v/>
+      </c>
+      <c r="G39" s="23">
+        <f>'02_Base'!M35</f>
+        <v/>
+      </c>
+      <c r="H39" s="23">
+        <f>'02_Base'!O35</f>
+        <v/>
+      </c>
+      <c r="I39" s="15">
+        <f>F39*0.141</f>
+        <v/>
+      </c>
+      <c r="J39" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A39),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A39),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A39)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A39),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A39),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A39))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M35,IF($E$5="Nombre de classes",'02_Base'!O35,'02_Base'!U35)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39))),0))</f>
+        <v/>
+      </c>
+      <c r="K39" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A39,'06_Compta'!$D$4:$D$675,B39,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A39,'06_Compta'!$D$4:$D$675,B39,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M35,IF($E$5="Nombre de classes",'02_Base'!O35,'02_Base'!U35)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A39,'02_Base'!$B$4:$B$61,B39))),0))</f>
+        <v/>
+      </c>
+      <c r="L39" s="14">
+        <f>I39+J39+K39</f>
+        <v/>
+      </c>
+      <c r="M39" s="14">
+        <f>IFERROR(L39/G39,0)</f>
+        <v/>
+      </c>
+      <c r="N39" s="15">
+        <f>IFERROR(L39/H39,0)</f>
+        <v/>
+      </c>
+      <c r="O39" s="15">
+        <f>IFERROR(F39/G39-M39,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17">
+        <f>'02_Base'!A36</f>
+        <v/>
+      </c>
+      <c r="B40" s="39">
+        <f>'02_Base'!B36</f>
+        <v/>
+      </c>
+      <c r="C40" s="17">
+        <f>'02_Base'!C36</f>
+        <v/>
+      </c>
+      <c r="D40" s="39">
+        <f>'02_Base'!E36</f>
+        <v/>
+      </c>
+      <c r="E40" s="39">
+        <f>'02_Base'!F36</f>
+        <v/>
+      </c>
+      <c r="F40" s="15">
+        <f>'02_Base'!U36</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>'02_Base'!M36</f>
+        <v/>
+      </c>
+      <c r="H40" s="23">
+        <f>'02_Base'!O36</f>
+        <v/>
+      </c>
+      <c r="I40" s="15">
+        <f>F40*0.141</f>
+        <v/>
+      </c>
+      <c r="J40" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A40),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A40),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A40)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A40),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A40),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A40))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M36,IF($E$5="Nombre de classes",'02_Base'!O36,'02_Base'!U36)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40))),0))</f>
+        <v/>
+      </c>
+      <c r="K40" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A40,'06_Compta'!$D$4:$D$675,B40,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A40,'06_Compta'!$D$4:$D$675,B40,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M36,IF($E$5="Nombre de classes",'02_Base'!O36,'02_Base'!U36)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A40,'02_Base'!$B$4:$B$61,B40))),0))</f>
+        <v/>
+      </c>
+      <c r="L40" s="14">
+        <f>I40+J40+K40</f>
+        <v/>
+      </c>
+      <c r="M40" s="14">
+        <f>IFERROR(L40/G40,0)</f>
+        <v/>
+      </c>
+      <c r="N40" s="15">
+        <f>IFERROR(L40/H40,0)</f>
+        <v/>
+      </c>
+      <c r="O40" s="15">
+        <f>IFERROR(F40/G40-M40,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17">
+        <f>'02_Base'!A37</f>
+        <v/>
+      </c>
+      <c r="B41" s="39">
+        <f>'02_Base'!B37</f>
+        <v/>
+      </c>
+      <c r="C41" s="17">
+        <f>'02_Base'!C37</f>
+        <v/>
+      </c>
+      <c r="D41" s="39">
+        <f>'02_Base'!E37</f>
+        <v/>
+      </c>
+      <c r="E41" s="39">
+        <f>'02_Base'!F37</f>
+        <v/>
+      </c>
+      <c r="F41" s="15">
+        <f>'02_Base'!U37</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>'02_Base'!M37</f>
+        <v/>
+      </c>
+      <c r="H41" s="23">
+        <f>'02_Base'!O37</f>
+        <v/>
+      </c>
+      <c r="I41" s="15">
+        <f>F41*0.141</f>
+        <v/>
+      </c>
+      <c r="J41" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A41),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A41),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A41)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A41),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A41),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A41))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M37,IF($E$5="Nombre de classes",'02_Base'!O37,'02_Base'!U37)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41))),0))</f>
+        <v/>
+      </c>
+      <c r="K41" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A41,'06_Compta'!$D$4:$D$675,B41,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A41,'06_Compta'!$D$4:$D$675,B41,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M37,IF($E$5="Nombre de classes",'02_Base'!O37,'02_Base'!U37)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A41,'02_Base'!$B$4:$B$61,B41))),0))</f>
+        <v/>
+      </c>
+      <c r="L41" s="14">
+        <f>I41+J41+K41</f>
+        <v/>
+      </c>
+      <c r="M41" s="14">
+        <f>IFERROR(L41/G41,0)</f>
+        <v/>
+      </c>
+      <c r="N41" s="15">
+        <f>IFERROR(L41/H41,0)</f>
+        <v/>
+      </c>
+      <c r="O41" s="15">
+        <f>IFERROR(F41/G41-M41,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17">
+        <f>'02_Base'!A38</f>
+        <v/>
+      </c>
+      <c r="B42" s="39">
+        <f>'02_Base'!B38</f>
+        <v/>
+      </c>
+      <c r="C42" s="17">
+        <f>'02_Base'!C38</f>
+        <v/>
+      </c>
+      <c r="D42" s="39">
+        <f>'02_Base'!E38</f>
+        <v/>
+      </c>
+      <c r="E42" s="39">
+        <f>'02_Base'!F38</f>
+        <v/>
+      </c>
+      <c r="F42" s="15">
+        <f>'02_Base'!U38</f>
+        <v/>
+      </c>
+      <c r="G42" s="23">
+        <f>'02_Base'!M38</f>
+        <v/>
+      </c>
+      <c r="H42" s="23">
+        <f>'02_Base'!O38</f>
+        <v/>
+      </c>
+      <c r="I42" s="15">
+        <f>F42*0.141</f>
+        <v/>
+      </c>
+      <c r="J42" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A42),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A42),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A42)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A42),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A42),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A42))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M38,IF($E$5="Nombre de classes",'02_Base'!O38,'02_Base'!U38)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42))),0))</f>
+        <v/>
+      </c>
+      <c r="K42" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A42,'06_Compta'!$D$4:$D$675,B42,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A42,'06_Compta'!$D$4:$D$675,B42,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M38,IF($E$5="Nombre de classes",'02_Base'!O38,'02_Base'!U38)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A42,'02_Base'!$B$4:$B$61,B42))),0))</f>
+        <v/>
+      </c>
+      <c r="L42" s="14">
+        <f>I42+J42+K42</f>
+        <v/>
+      </c>
+      <c r="M42" s="14">
+        <f>IFERROR(L42/G42,0)</f>
+        <v/>
+      </c>
+      <c r="N42" s="15">
+        <f>IFERROR(L42/H42,0)</f>
+        <v/>
+      </c>
+      <c r="O42" s="15">
+        <f>IFERROR(F42/G42-M42,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17">
+        <f>'02_Base'!A39</f>
+        <v/>
+      </c>
+      <c r="B43" s="39">
+        <f>'02_Base'!B39</f>
+        <v/>
+      </c>
+      <c r="C43" s="17">
+        <f>'02_Base'!C39</f>
+        <v/>
+      </c>
+      <c r="D43" s="39">
+        <f>'02_Base'!E39</f>
+        <v/>
+      </c>
+      <c r="E43" s="39">
+        <f>'02_Base'!F39</f>
+        <v/>
+      </c>
+      <c r="F43" s="15">
+        <f>'02_Base'!U39</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>'02_Base'!M39</f>
+        <v/>
+      </c>
+      <c r="H43" s="23">
+        <f>'02_Base'!O39</f>
+        <v/>
+      </c>
+      <c r="I43" s="15">
+        <f>F43*0.141</f>
+        <v/>
+      </c>
+      <c r="J43" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A43),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A43),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A43)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A43),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A43),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A43))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M39,IF($E$5="Nombre de classes",'02_Base'!O39,'02_Base'!U39)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43))),0))</f>
+        <v/>
+      </c>
+      <c r="K43" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A43,'06_Compta'!$D$4:$D$675,B43,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A43,'06_Compta'!$D$4:$D$675,B43,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M39,IF($E$5="Nombre de classes",'02_Base'!O39,'02_Base'!U39)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A43,'02_Base'!$B$4:$B$61,B43))),0))</f>
+        <v/>
+      </c>
+      <c r="L43" s="14">
+        <f>I43+J43+K43</f>
+        <v/>
+      </c>
+      <c r="M43" s="14">
+        <f>IFERROR(L43/G43,0)</f>
+        <v/>
+      </c>
+      <c r="N43" s="15">
+        <f>IFERROR(L43/H43,0)</f>
+        <v/>
+      </c>
+      <c r="O43" s="15">
+        <f>IFERROR(F43/G43-M43,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17">
+        <f>'02_Base'!A40</f>
+        <v/>
+      </c>
+      <c r="B44" s="39">
+        <f>'02_Base'!B40</f>
+        <v/>
+      </c>
+      <c r="C44" s="17">
+        <f>'02_Base'!C40</f>
+        <v/>
+      </c>
+      <c r="D44" s="39">
+        <f>'02_Base'!E40</f>
+        <v/>
+      </c>
+      <c r="E44" s="39">
+        <f>'02_Base'!F40</f>
+        <v/>
+      </c>
+      <c r="F44" s="15">
+        <f>'02_Base'!U40</f>
+        <v/>
+      </c>
+      <c r="G44" s="23">
+        <f>'02_Base'!M40</f>
+        <v/>
+      </c>
+      <c r="H44" s="23">
+        <f>'02_Base'!O40</f>
+        <v/>
+      </c>
+      <c r="I44" s="15">
+        <f>F44*0.141</f>
+        <v/>
+      </c>
+      <c r="J44" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A44),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A44),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A44)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A44),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A44),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A44))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M40,IF($E$5="Nombre de classes",'02_Base'!O40,'02_Base'!U40)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44))),0))</f>
+        <v/>
+      </c>
+      <c r="K44" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A44,'06_Compta'!$D$4:$D$675,B44,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A44,'06_Compta'!$D$4:$D$675,B44,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M40,IF($E$5="Nombre de classes",'02_Base'!O40,'02_Base'!U40)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A44,'02_Base'!$B$4:$B$61,B44))),0))</f>
+        <v/>
+      </c>
+      <c r="L44" s="14">
+        <f>I44+J44+K44</f>
+        <v/>
+      </c>
+      <c r="M44" s="14">
+        <f>IFERROR(L44/G44,0)</f>
+        <v/>
+      </c>
+      <c r="N44" s="15">
+        <f>IFERROR(L44/H44,0)</f>
+        <v/>
+      </c>
+      <c r="O44" s="15">
+        <f>IFERROR(F44/G44-M44,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17">
+        <f>'02_Base'!A41</f>
+        <v/>
+      </c>
+      <c r="B45" s="39">
+        <f>'02_Base'!B41</f>
+        <v/>
+      </c>
+      <c r="C45" s="17">
+        <f>'02_Base'!C41</f>
+        <v/>
+      </c>
+      <c r="D45" s="39">
+        <f>'02_Base'!E41</f>
+        <v/>
+      </c>
+      <c r="E45" s="39">
+        <f>'02_Base'!F41</f>
+        <v/>
+      </c>
+      <c r="F45" s="15">
+        <f>'02_Base'!U41</f>
+        <v/>
+      </c>
+      <c r="G45" s="23">
+        <f>'02_Base'!M41</f>
+        <v/>
+      </c>
+      <c r="H45" s="23">
+        <f>'02_Base'!O41</f>
+        <v/>
+      </c>
+      <c r="I45" s="15">
+        <f>F45*0.141</f>
+        <v/>
+      </c>
+      <c r="J45" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A45),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A45),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A45)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A45),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A45),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A45))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M41,IF($E$5="Nombre de classes",'02_Base'!O41,'02_Base'!U41)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45))),0))</f>
+        <v/>
+      </c>
+      <c r="K45" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A45,'06_Compta'!$D$4:$D$675,B45,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A45,'06_Compta'!$D$4:$D$675,B45,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M41,IF($E$5="Nombre de classes",'02_Base'!O41,'02_Base'!U41)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A45,'02_Base'!$B$4:$B$61,B45))),0))</f>
+        <v/>
+      </c>
+      <c r="L45" s="14">
+        <f>I45+J45+K45</f>
+        <v/>
+      </c>
+      <c r="M45" s="14">
+        <f>IFERROR(L45/G45,0)</f>
+        <v/>
+      </c>
+      <c r="N45" s="15">
+        <f>IFERROR(L45/H45,0)</f>
+        <v/>
+      </c>
+      <c r="O45" s="15">
+        <f>IFERROR(F45/G45-M45,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17">
+        <f>'02_Base'!A42</f>
+        <v/>
+      </c>
+      <c r="B46" s="39">
+        <f>'02_Base'!B42</f>
+        <v/>
+      </c>
+      <c r="C46" s="17">
+        <f>'02_Base'!C42</f>
+        <v/>
+      </c>
+      <c r="D46" s="39">
+        <f>'02_Base'!E42</f>
+        <v/>
+      </c>
+      <c r="E46" s="39">
+        <f>'02_Base'!F42</f>
+        <v/>
+      </c>
+      <c r="F46" s="15">
+        <f>'02_Base'!U42</f>
+        <v/>
+      </c>
+      <c r="G46" s="23">
+        <f>'02_Base'!M42</f>
+        <v/>
+      </c>
+      <c r="H46" s="23">
+        <f>'02_Base'!O42</f>
+        <v/>
+      </c>
+      <c r="I46" s="15">
+        <f>F46*0.141</f>
+        <v/>
+      </c>
+      <c r="J46" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A46),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A46),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A46)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A46),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A46),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A46))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M42,IF($E$5="Nombre de classes",'02_Base'!O42,'02_Base'!U42)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46))),0))</f>
+        <v/>
+      </c>
+      <c r="K46" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A46,'06_Compta'!$D$4:$D$675,B46,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A46,'06_Compta'!$D$4:$D$675,B46,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M42,IF($E$5="Nombre de classes",'02_Base'!O42,'02_Base'!U42)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A46,'02_Base'!$B$4:$B$61,B46))),0))</f>
+        <v/>
+      </c>
+      <c r="L46" s="14">
+        <f>I46+J46+K46</f>
+        <v/>
+      </c>
+      <c r="M46" s="14">
+        <f>IFERROR(L46/G46,0)</f>
+        <v/>
+      </c>
+      <c r="N46" s="15">
+        <f>IFERROR(L46/H46,0)</f>
+        <v/>
+      </c>
+      <c r="O46" s="15">
+        <f>IFERROR(F46/G46-M46,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17">
+        <f>'02_Base'!A43</f>
+        <v/>
+      </c>
+      <c r="B47" s="39">
+        <f>'02_Base'!B43</f>
+        <v/>
+      </c>
+      <c r="C47" s="17">
+        <f>'02_Base'!C43</f>
+        <v/>
+      </c>
+      <c r="D47" s="39">
+        <f>'02_Base'!E43</f>
+        <v/>
+      </c>
+      <c r="E47" s="39">
+        <f>'02_Base'!F43</f>
+        <v/>
+      </c>
+      <c r="F47" s="15">
+        <f>'02_Base'!U43</f>
+        <v/>
+      </c>
+      <c r="G47" s="23">
+        <f>'02_Base'!M43</f>
+        <v/>
+      </c>
+      <c r="H47" s="23">
+        <f>'02_Base'!O43</f>
+        <v/>
+      </c>
+      <c r="I47" s="15">
+        <f>F47*0.141</f>
+        <v/>
+      </c>
+      <c r="J47" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A47),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A47),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A47)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A47),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A47),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A47))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M43,IF($E$5="Nombre de classes",'02_Base'!O43,'02_Base'!U43)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47))),0))</f>
+        <v/>
+      </c>
+      <c r="K47" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A47,'06_Compta'!$D$4:$D$675,B47,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A47,'06_Compta'!$D$4:$D$675,B47,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M43,IF($E$5="Nombre de classes",'02_Base'!O43,'02_Base'!U43)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A47,'02_Base'!$B$4:$B$61,B47))),0))</f>
+        <v/>
+      </c>
+      <c r="L47" s="14">
+        <f>I47+J47+K47</f>
+        <v/>
+      </c>
+      <c r="M47" s="14">
+        <f>IFERROR(L47/G47,0)</f>
+        <v/>
+      </c>
+      <c r="N47" s="15">
+        <f>IFERROR(L47/H47,0)</f>
+        <v/>
+      </c>
+      <c r="O47" s="15">
+        <f>IFERROR(F47/G47-M47,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17">
+        <f>'02_Base'!A44</f>
+        <v/>
+      </c>
+      <c r="B48" s="39">
+        <f>'02_Base'!B44</f>
+        <v/>
+      </c>
+      <c r="C48" s="17">
+        <f>'02_Base'!C44</f>
+        <v/>
+      </c>
+      <c r="D48" s="39">
+        <f>'02_Base'!E44</f>
+        <v/>
+      </c>
+      <c r="E48" s="39">
+        <f>'02_Base'!F44</f>
+        <v/>
+      </c>
+      <c r="F48" s="15">
+        <f>'02_Base'!U44</f>
+        <v/>
+      </c>
+      <c r="G48" s="23">
+        <f>'02_Base'!M44</f>
+        <v/>
+      </c>
+      <c r="H48" s="23">
+        <f>'02_Base'!O44</f>
+        <v/>
+      </c>
+      <c r="I48" s="15">
+        <f>F48*0.141</f>
+        <v/>
+      </c>
+      <c r="J48" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A48),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A48),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A48)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A48),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A48),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A48))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M44,IF($E$5="Nombre de classes",'02_Base'!O44,'02_Base'!U44)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48))),0))</f>
+        <v/>
+      </c>
+      <c r="K48" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A48,'06_Compta'!$D$4:$D$675,B48,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A48,'06_Compta'!$D$4:$D$675,B48,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M44,IF($E$5="Nombre de classes",'02_Base'!O44,'02_Base'!U44)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A48,'02_Base'!$B$4:$B$61,B48))),0))</f>
+        <v/>
+      </c>
+      <c r="L48" s="14">
+        <f>I48+J48+K48</f>
+        <v/>
+      </c>
+      <c r="M48" s="14">
+        <f>IFERROR(L48/G48,0)</f>
+        <v/>
+      </c>
+      <c r="N48" s="15">
+        <f>IFERROR(L48/H48,0)</f>
+        <v/>
+      </c>
+      <c r="O48" s="15">
+        <f>IFERROR(F48/G48-M48,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17">
+        <f>'02_Base'!A45</f>
+        <v/>
+      </c>
+      <c r="B49" s="39">
+        <f>'02_Base'!B45</f>
+        <v/>
+      </c>
+      <c r="C49" s="17">
+        <f>'02_Base'!C45</f>
+        <v/>
+      </c>
+      <c r="D49" s="39">
+        <f>'02_Base'!E45</f>
+        <v/>
+      </c>
+      <c r="E49" s="39">
+        <f>'02_Base'!F45</f>
+        <v/>
+      </c>
+      <c r="F49" s="15">
+        <f>'02_Base'!U45</f>
+        <v/>
+      </c>
+      <c r="G49" s="23">
+        <f>'02_Base'!M45</f>
+        <v/>
+      </c>
+      <c r="H49" s="23">
+        <f>'02_Base'!O45</f>
+        <v/>
+      </c>
+      <c r="I49" s="15">
+        <f>F49*0.141</f>
+        <v/>
+      </c>
+      <c r="J49" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A49),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A49),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A49)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A49),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A49),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A49))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M45,IF($E$5="Nombre de classes",'02_Base'!O45,'02_Base'!U45)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49))),0))</f>
+        <v/>
+      </c>
+      <c r="K49" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A49,'06_Compta'!$D$4:$D$675,B49,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A49,'06_Compta'!$D$4:$D$675,B49,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M45,IF($E$5="Nombre de classes",'02_Base'!O45,'02_Base'!U45)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A49,'02_Base'!$B$4:$B$61,B49))),0))</f>
+        <v/>
+      </c>
+      <c r="L49" s="14">
+        <f>I49+J49+K49</f>
+        <v/>
+      </c>
+      <c r="M49" s="14">
+        <f>IFERROR(L49/G49,0)</f>
+        <v/>
+      </c>
+      <c r="N49" s="15">
+        <f>IFERROR(L49/H49,0)</f>
+        <v/>
+      </c>
+      <c r="O49" s="15">
+        <f>IFERROR(F49/G49-M49,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17">
+        <f>'02_Base'!A46</f>
+        <v/>
+      </c>
+      <c r="B50" s="39">
+        <f>'02_Base'!B46</f>
+        <v/>
+      </c>
+      <c r="C50" s="17">
+        <f>'02_Base'!C46</f>
+        <v/>
+      </c>
+      <c r="D50" s="39">
+        <f>'02_Base'!E46</f>
+        <v/>
+      </c>
+      <c r="E50" s="39">
+        <f>'02_Base'!F46</f>
+        <v/>
+      </c>
+      <c r="F50" s="15">
+        <f>'02_Base'!U46</f>
+        <v/>
+      </c>
+      <c r="G50" s="23">
+        <f>'02_Base'!M46</f>
+        <v/>
+      </c>
+      <c r="H50" s="23">
+        <f>'02_Base'!O46</f>
+        <v/>
+      </c>
+      <c r="I50" s="15">
+        <f>F50*0.141</f>
+        <v/>
+      </c>
+      <c r="J50" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A50),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A50),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A50)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A50),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A50),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A50))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M46,IF($E$5="Nombre de classes",'02_Base'!O46,'02_Base'!U46)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50))),0))</f>
+        <v/>
+      </c>
+      <c r="K50" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A50,'06_Compta'!$D$4:$D$675,B50,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A50,'06_Compta'!$D$4:$D$675,B50,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M46,IF($E$5="Nombre de classes",'02_Base'!O46,'02_Base'!U46)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A50,'02_Base'!$B$4:$B$61,B50))),0))</f>
+        <v/>
+      </c>
+      <c r="L50" s="14">
+        <f>I50+J50+K50</f>
+        <v/>
+      </c>
+      <c r="M50" s="14">
+        <f>IFERROR(L50/G50,0)</f>
+        <v/>
+      </c>
+      <c r="N50" s="15">
+        <f>IFERROR(L50/H50,0)</f>
+        <v/>
+      </c>
+      <c r="O50" s="15">
+        <f>IFERROR(F50/G50-M50,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17">
+        <f>'02_Base'!A47</f>
+        <v/>
+      </c>
+      <c r="B51" s="39">
+        <f>'02_Base'!B47</f>
+        <v/>
+      </c>
+      <c r="C51" s="17">
+        <f>'02_Base'!C47</f>
+        <v/>
+      </c>
+      <c r="D51" s="39">
+        <f>'02_Base'!E47</f>
+        <v/>
+      </c>
+      <c r="E51" s="39">
+        <f>'02_Base'!F47</f>
+        <v/>
+      </c>
+      <c r="F51" s="15">
+        <f>'02_Base'!U47</f>
+        <v/>
+      </c>
+      <c r="G51" s="23">
+        <f>'02_Base'!M47</f>
+        <v/>
+      </c>
+      <c r="H51" s="23">
+        <f>'02_Base'!O47</f>
+        <v/>
+      </c>
+      <c r="I51" s="15">
+        <f>F51*0.141</f>
+        <v/>
+      </c>
+      <c r="J51" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A51),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A51),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A51)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A51),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A51),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A51))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M47,IF($E$5="Nombre de classes",'02_Base'!O47,'02_Base'!U47)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51))),0))</f>
+        <v/>
+      </c>
+      <c r="K51" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A51,'06_Compta'!$D$4:$D$675,B51,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A51,'06_Compta'!$D$4:$D$675,B51,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M47,IF($E$5="Nombre de classes",'02_Base'!O47,'02_Base'!U47)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A51,'02_Base'!$B$4:$B$61,B51))),0))</f>
+        <v/>
+      </c>
+      <c r="L51" s="14">
+        <f>I51+J51+K51</f>
+        <v/>
+      </c>
+      <c r="M51" s="14">
+        <f>IFERROR(L51/G51,0)</f>
+        <v/>
+      </c>
+      <c r="N51" s="15">
+        <f>IFERROR(L51/H51,0)</f>
+        <v/>
+      </c>
+      <c r="O51" s="15">
+        <f>IFERROR(F51/G51-M51,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17">
+        <f>'02_Base'!A48</f>
+        <v/>
+      </c>
+      <c r="B52" s="39">
+        <f>'02_Base'!B48</f>
+        <v/>
+      </c>
+      <c r="C52" s="17">
+        <f>'02_Base'!C48</f>
+        <v/>
+      </c>
+      <c r="D52" s="39">
+        <f>'02_Base'!E48</f>
+        <v/>
+      </c>
+      <c r="E52" s="39">
+        <f>'02_Base'!F48</f>
+        <v/>
+      </c>
+      <c r="F52" s="15">
+        <f>'02_Base'!U48</f>
+        <v/>
+      </c>
+      <c r="G52" s="23">
+        <f>'02_Base'!M48</f>
+        <v/>
+      </c>
+      <c r="H52" s="23">
+        <f>'02_Base'!O48</f>
+        <v/>
+      </c>
+      <c r="I52" s="15">
+        <f>F52*0.141</f>
+        <v/>
+      </c>
+      <c r="J52" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A52),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A52),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A52)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A52),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A52),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A52))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M48,IF($E$5="Nombre de classes",'02_Base'!O48,'02_Base'!U48)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52))),0))</f>
+        <v/>
+      </c>
+      <c r="K52" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A52,'06_Compta'!$D$4:$D$675,B52,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A52,'06_Compta'!$D$4:$D$675,B52,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M48,IF($E$5="Nombre de classes",'02_Base'!O48,'02_Base'!U48)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A52,'02_Base'!$B$4:$B$61,B52))),0))</f>
+        <v/>
+      </c>
+      <c r="L52" s="14">
+        <f>I52+J52+K52</f>
+        <v/>
+      </c>
+      <c r="M52" s="14">
+        <f>IFERROR(L52/G52,0)</f>
+        <v/>
+      </c>
+      <c r="N52" s="15">
+        <f>IFERROR(L52/H52,0)</f>
+        <v/>
+      </c>
+      <c r="O52" s="15">
+        <f>IFERROR(F52/G52-M52,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17">
+        <f>'02_Base'!A49</f>
+        <v/>
+      </c>
+      <c r="B53" s="39">
+        <f>'02_Base'!B49</f>
+        <v/>
+      </c>
+      <c r="C53" s="17">
+        <f>'02_Base'!C49</f>
+        <v/>
+      </c>
+      <c r="D53" s="39">
+        <f>'02_Base'!E49</f>
+        <v/>
+      </c>
+      <c r="E53" s="39">
+        <f>'02_Base'!F49</f>
+        <v/>
+      </c>
+      <c r="F53" s="15">
+        <f>'02_Base'!U49</f>
+        <v/>
+      </c>
+      <c r="G53" s="23">
+        <f>'02_Base'!M49</f>
+        <v/>
+      </c>
+      <c r="H53" s="23">
+        <f>'02_Base'!O49</f>
+        <v/>
+      </c>
+      <c r="I53" s="15">
+        <f>F53*0.141</f>
+        <v/>
+      </c>
+      <c r="J53" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A53),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A53),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A53)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A53),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A53),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A53))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M49,IF($E$5="Nombre de classes",'02_Base'!O49,'02_Base'!U49)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53))),0))</f>
+        <v/>
+      </c>
+      <c r="K53" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A53,'06_Compta'!$D$4:$D$675,B53,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A53,'06_Compta'!$D$4:$D$675,B53,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M49,IF($E$5="Nombre de classes",'02_Base'!O49,'02_Base'!U49)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A53,'02_Base'!$B$4:$B$61,B53))),0))</f>
+        <v/>
+      </c>
+      <c r="L53" s="14">
+        <f>I53+J53+K53</f>
+        <v/>
+      </c>
+      <c r="M53" s="14">
+        <f>IFERROR(L53/G53,0)</f>
+        <v/>
+      </c>
+      <c r="N53" s="15">
+        <f>IFERROR(L53/H53,0)</f>
+        <v/>
+      </c>
+      <c r="O53" s="15">
+        <f>IFERROR(F53/G53-M53,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17">
+        <f>'02_Base'!A50</f>
+        <v/>
+      </c>
+      <c r="B54" s="39">
+        <f>'02_Base'!B50</f>
+        <v/>
+      </c>
+      <c r="C54" s="17">
+        <f>'02_Base'!C50</f>
+        <v/>
+      </c>
+      <c r="D54" s="39">
+        <f>'02_Base'!E50</f>
+        <v/>
+      </c>
+      <c r="E54" s="39">
+        <f>'02_Base'!F50</f>
+        <v/>
+      </c>
+      <c r="F54" s="15">
+        <f>'02_Base'!U50</f>
+        <v/>
+      </c>
+      <c r="G54" s="23">
+        <f>'02_Base'!M50</f>
+        <v/>
+      </c>
+      <c r="H54" s="23">
+        <f>'02_Base'!O50</f>
+        <v/>
+      </c>
+      <c r="I54" s="15">
+        <f>F54*0.141</f>
+        <v/>
+      </c>
+      <c r="J54" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A54),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A54),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A54)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A54),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A54),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A54))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M50,IF($E$5="Nombre de classes",'02_Base'!O50,'02_Base'!U50)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54))),0))</f>
+        <v/>
+      </c>
+      <c r="K54" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A54,'06_Compta'!$D$4:$D$675,B54,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A54,'06_Compta'!$D$4:$D$675,B54,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M50,IF($E$5="Nombre de classes",'02_Base'!O50,'02_Base'!U50)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A54,'02_Base'!$B$4:$B$61,B54))),0))</f>
+        <v/>
+      </c>
+      <c r="L54" s="14">
+        <f>I54+J54+K54</f>
+        <v/>
+      </c>
+      <c r="M54" s="14">
+        <f>IFERROR(L54/G54,0)</f>
+        <v/>
+      </c>
+      <c r="N54" s="15">
+        <f>IFERROR(L54/H54,0)</f>
+        <v/>
+      </c>
+      <c r="O54" s="15">
+        <f>IFERROR(F54/G54-M54,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17">
+        <f>'02_Base'!A51</f>
+        <v/>
+      </c>
+      <c r="B55" s="39">
+        <f>'02_Base'!B51</f>
+        <v/>
+      </c>
+      <c r="C55" s="17">
+        <f>'02_Base'!C51</f>
+        <v/>
+      </c>
+      <c r="D55" s="39">
+        <f>'02_Base'!E51</f>
+        <v/>
+      </c>
+      <c r="E55" s="39">
+        <f>'02_Base'!F51</f>
+        <v/>
+      </c>
+      <c r="F55" s="15">
+        <f>'02_Base'!U51</f>
+        <v/>
+      </c>
+      <c r="G55" s="23">
+        <f>'02_Base'!M51</f>
+        <v/>
+      </c>
+      <c r="H55" s="23">
+        <f>'02_Base'!O51</f>
+        <v/>
+      </c>
+      <c r="I55" s="15">
+        <f>F55*0.141</f>
+        <v/>
+      </c>
+      <c r="J55" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A55),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A55),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A55)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A55),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A55),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A55))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M51,IF($E$5="Nombre de classes",'02_Base'!O51,'02_Base'!U51)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55))),0))</f>
+        <v/>
+      </c>
+      <c r="K55" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A55,'06_Compta'!$D$4:$D$675,B55,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A55,'06_Compta'!$D$4:$D$675,B55,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M51,IF($E$5="Nombre de classes",'02_Base'!O51,'02_Base'!U51)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A55,'02_Base'!$B$4:$B$61,B55))),0))</f>
+        <v/>
+      </c>
+      <c r="L55" s="14">
+        <f>I55+J55+K55</f>
+        <v/>
+      </c>
+      <c r="M55" s="14">
+        <f>IFERROR(L55/G55,0)</f>
+        <v/>
+      </c>
+      <c r="N55" s="15">
+        <f>IFERROR(L55/H55,0)</f>
+        <v/>
+      </c>
+      <c r="O55" s="15">
+        <f>IFERROR(F55/G55-M55,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17">
+        <f>'02_Base'!A52</f>
+        <v/>
+      </c>
+      <c r="B56" s="39">
+        <f>'02_Base'!B52</f>
+        <v/>
+      </c>
+      <c r="C56" s="17">
+        <f>'02_Base'!C52</f>
+        <v/>
+      </c>
+      <c r="D56" s="39">
+        <f>'02_Base'!E52</f>
+        <v/>
+      </c>
+      <c r="E56" s="39">
+        <f>'02_Base'!F52</f>
+        <v/>
+      </c>
+      <c r="F56" s="15">
+        <f>'02_Base'!U52</f>
+        <v/>
+      </c>
+      <c r="G56" s="23">
+        <f>'02_Base'!M52</f>
+        <v/>
+      </c>
+      <c r="H56" s="23">
+        <f>'02_Base'!O52</f>
+        <v/>
+      </c>
+      <c r="I56" s="15">
+        <f>F56*0.141</f>
+        <v/>
+      </c>
+      <c r="J56" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A56),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A56),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A56)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A56),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A56),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A56))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M52,IF($E$5="Nombre de classes",'02_Base'!O52,'02_Base'!U52)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56))),0))</f>
+        <v/>
+      </c>
+      <c r="K56" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A56,'06_Compta'!$D$4:$D$675,B56,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A56,'06_Compta'!$D$4:$D$675,B56,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M52,IF($E$5="Nombre de classes",'02_Base'!O52,'02_Base'!U52)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A56,'02_Base'!$B$4:$B$61,B56))),0))</f>
+        <v/>
+      </c>
+      <c r="L56" s="14">
+        <f>I56+J56+K56</f>
+        <v/>
+      </c>
+      <c r="M56" s="14">
+        <f>IFERROR(L56/G56,0)</f>
+        <v/>
+      </c>
+      <c r="N56" s="15">
+        <f>IFERROR(L56/H56,0)</f>
+        <v/>
+      </c>
+      <c r="O56" s="15">
+        <f>IFERROR(F56/G56-M56,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17">
+        <f>'02_Base'!A53</f>
+        <v/>
+      </c>
+      <c r="B57" s="39">
+        <f>'02_Base'!B53</f>
+        <v/>
+      </c>
+      <c r="C57" s="17">
+        <f>'02_Base'!C53</f>
+        <v/>
+      </c>
+      <c r="D57" s="39">
+        <f>'02_Base'!E53</f>
+        <v/>
+      </c>
+      <c r="E57" s="39">
+        <f>'02_Base'!F53</f>
+        <v/>
+      </c>
+      <c r="F57" s="15">
+        <f>'02_Base'!U53</f>
+        <v/>
+      </c>
+      <c r="G57" s="23">
+        <f>'02_Base'!M53</f>
+        <v/>
+      </c>
+      <c r="H57" s="23">
+        <f>'02_Base'!O53</f>
+        <v/>
+      </c>
+      <c r="I57" s="15">
+        <f>F57*0.141</f>
+        <v/>
+      </c>
+      <c r="J57" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A57),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A57),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A57)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A57),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A57),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A57))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M53,IF($E$5="Nombre de classes",'02_Base'!O53,'02_Base'!U53)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57))),0))</f>
+        <v/>
+      </c>
+      <c r="K57" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A57,'06_Compta'!$D$4:$D$675,B57,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A57,'06_Compta'!$D$4:$D$675,B57,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M53,IF($E$5="Nombre de classes",'02_Base'!O53,'02_Base'!U53)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A57,'02_Base'!$B$4:$B$61,B57))),0))</f>
+        <v/>
+      </c>
+      <c r="L57" s="14">
+        <f>I57+J57+K57</f>
+        <v/>
+      </c>
+      <c r="M57" s="14">
+        <f>IFERROR(L57/G57,0)</f>
+        <v/>
+      </c>
+      <c r="N57" s="15">
+        <f>IFERROR(L57/H57,0)</f>
+        <v/>
+      </c>
+      <c r="O57" s="15">
+        <f>IFERROR(F57/G57-M57,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17">
+        <f>'02_Base'!A54</f>
+        <v/>
+      </c>
+      <c r="B58" s="39">
+        <f>'02_Base'!B54</f>
+        <v/>
+      </c>
+      <c r="C58" s="17">
+        <f>'02_Base'!C54</f>
+        <v/>
+      </c>
+      <c r="D58" s="39">
+        <f>'02_Base'!E54</f>
+        <v/>
+      </c>
+      <c r="E58" s="39">
+        <f>'02_Base'!F54</f>
+        <v/>
+      </c>
+      <c r="F58" s="15">
+        <f>'02_Base'!U54</f>
+        <v/>
+      </c>
+      <c r="G58" s="23">
+        <f>'02_Base'!M54</f>
+        <v/>
+      </c>
+      <c r="H58" s="23">
+        <f>'02_Base'!O54</f>
+        <v/>
+      </c>
+      <c r="I58" s="15">
+        <f>F58*0.141</f>
+        <v/>
+      </c>
+      <c r="J58" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A58),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A58),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A58)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A58),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A58),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A58))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M54,IF($E$5="Nombre de classes",'02_Base'!O54,'02_Base'!U54)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58))),0))</f>
+        <v/>
+      </c>
+      <c r="K58" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A58,'06_Compta'!$D$4:$D$675,B58,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A58,'06_Compta'!$D$4:$D$675,B58,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M54,IF($E$5="Nombre de classes",'02_Base'!O54,'02_Base'!U54)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A58,'02_Base'!$B$4:$B$61,B58))),0))</f>
+        <v/>
+      </c>
+      <c r="L58" s="14">
+        <f>I58+J58+K58</f>
+        <v/>
+      </c>
+      <c r="M58" s="14">
+        <f>IFERROR(L58/G58,0)</f>
+        <v/>
+      </c>
+      <c r="N58" s="15">
+        <f>IFERROR(L58/H58,0)</f>
+        <v/>
+      </c>
+      <c r="O58" s="15">
+        <f>IFERROR(F58/G58-M58,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17">
+        <f>'02_Base'!A55</f>
+        <v/>
+      </c>
+      <c r="B59" s="39">
+        <f>'02_Base'!B55</f>
+        <v/>
+      </c>
+      <c r="C59" s="17">
+        <f>'02_Base'!C55</f>
+        <v/>
+      </c>
+      <c r="D59" s="39">
+        <f>'02_Base'!E55</f>
+        <v/>
+      </c>
+      <c r="E59" s="39">
+        <f>'02_Base'!F55</f>
+        <v/>
+      </c>
+      <c r="F59" s="15">
+        <f>'02_Base'!U55</f>
+        <v/>
+      </c>
+      <c r="G59" s="23">
+        <f>'02_Base'!M55</f>
+        <v/>
+      </c>
+      <c r="H59" s="23">
+        <f>'02_Base'!O55</f>
+        <v/>
+      </c>
+      <c r="I59" s="15">
+        <f>F59*0.141</f>
+        <v/>
+      </c>
+      <c r="J59" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A59),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A59),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A59)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A59),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A59),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A59))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M55,IF($E$5="Nombre de classes",'02_Base'!O55,'02_Base'!U55)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59))),0))</f>
+        <v/>
+      </c>
+      <c r="K59" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A59,'06_Compta'!$D$4:$D$675,B59,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A59,'06_Compta'!$D$4:$D$675,B59,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M55,IF($E$5="Nombre de classes",'02_Base'!O55,'02_Base'!U55)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A59,'02_Base'!$B$4:$B$61,B59))),0))</f>
+        <v/>
+      </c>
+      <c r="L59" s="14">
+        <f>I59+J59+K59</f>
+        <v/>
+      </c>
+      <c r="M59" s="14">
+        <f>IFERROR(L59/G59,0)</f>
+        <v/>
+      </c>
+      <c r="N59" s="15">
+        <f>IFERROR(L59/H59,0)</f>
+        <v/>
+      </c>
+      <c r="O59" s="15">
+        <f>IFERROR(F59/G59-M59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17">
+        <f>'02_Base'!A56</f>
+        <v/>
+      </c>
+      <c r="B60" s="39">
+        <f>'02_Base'!B56</f>
+        <v/>
+      </c>
+      <c r="C60" s="17">
+        <f>'02_Base'!C56</f>
+        <v/>
+      </c>
+      <c r="D60" s="39">
+        <f>'02_Base'!E56</f>
+        <v/>
+      </c>
+      <c r="E60" s="39">
+        <f>'02_Base'!F56</f>
+        <v/>
+      </c>
+      <c r="F60" s="15">
+        <f>'02_Base'!U56</f>
+        <v/>
+      </c>
+      <c r="G60" s="23">
+        <f>'02_Base'!M56</f>
+        <v/>
+      </c>
+      <c r="H60" s="23">
+        <f>'02_Base'!O56</f>
+        <v/>
+      </c>
+      <c r="I60" s="15">
+        <f>F60*0.141</f>
+        <v/>
+      </c>
+      <c r="J60" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A60),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A60),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A60)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A60),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A60),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A60))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M56,IF($E$5="Nombre de classes",'02_Base'!O56,'02_Base'!U56)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60))),0))</f>
+        <v/>
+      </c>
+      <c r="K60" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A60,'06_Compta'!$D$4:$D$675,B60,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A60,'06_Compta'!$D$4:$D$675,B60,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M56,IF($E$5="Nombre de classes",'02_Base'!O56,'02_Base'!U56)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A60,'02_Base'!$B$4:$B$61,B60))),0))</f>
+        <v/>
+      </c>
+      <c r="L60" s="14">
+        <f>I60+J60+K60</f>
+        <v/>
+      </c>
+      <c r="M60" s="14">
+        <f>IFERROR(L60/G60,0)</f>
+        <v/>
+      </c>
+      <c r="N60" s="15">
+        <f>IFERROR(L60/H60,0)</f>
+        <v/>
+      </c>
+      <c r="O60" s="15">
+        <f>IFERROR(F60/G60-M60,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17">
+        <f>'02_Base'!A57</f>
+        <v/>
+      </c>
+      <c r="B61" s="39">
+        <f>'02_Base'!B57</f>
+        <v/>
+      </c>
+      <c r="C61" s="17">
+        <f>'02_Base'!C57</f>
+        <v/>
+      </c>
+      <c r="D61" s="39">
+        <f>'02_Base'!E57</f>
+        <v/>
+      </c>
+      <c r="E61" s="39">
+        <f>'02_Base'!F57</f>
+        <v/>
+      </c>
+      <c r="F61" s="15">
+        <f>'02_Base'!U57</f>
+        <v/>
+      </c>
+      <c r="G61" s="23">
+        <f>'02_Base'!M57</f>
+        <v/>
+      </c>
+      <c r="H61" s="23">
+        <f>'02_Base'!O57</f>
+        <v/>
+      </c>
+      <c r="I61" s="15">
+        <f>F61*0.141</f>
+        <v/>
+      </c>
+      <c r="J61" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A61),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A61),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A61)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A61),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A61),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A61))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M57,IF($E$5="Nombre de classes",'02_Base'!O57,'02_Base'!U57)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61))),0))</f>
+        <v/>
+      </c>
+      <c r="K61" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A61,'06_Compta'!$D$4:$D$675,B61,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A61,'06_Compta'!$D$4:$D$675,B61,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M57,IF($E$5="Nombre de classes",'02_Base'!O57,'02_Base'!U57)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A61,'02_Base'!$B$4:$B$61,B61))),0))</f>
+        <v/>
+      </c>
+      <c r="L61" s="14">
+        <f>I61+J61+K61</f>
+        <v/>
+      </c>
+      <c r="M61" s="14">
+        <f>IFERROR(L61/G61,0)</f>
+        <v/>
+      </c>
+      <c r="N61" s="15">
+        <f>IFERROR(L61/H61,0)</f>
+        <v/>
+      </c>
+      <c r="O61" s="15">
+        <f>IFERROR(F61/G61-M61,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17">
+        <f>'02_Base'!A58</f>
+        <v/>
+      </c>
+      <c r="B62" s="39">
+        <f>'02_Base'!B58</f>
+        <v/>
+      </c>
+      <c r="C62" s="17">
+        <f>'02_Base'!C58</f>
+        <v/>
+      </c>
+      <c r="D62" s="39">
+        <f>'02_Base'!E58</f>
+        <v/>
+      </c>
+      <c r="E62" s="39">
+        <f>'02_Base'!F58</f>
+        <v/>
+      </c>
+      <c r="F62" s="15">
+        <f>'02_Base'!U58</f>
+        <v/>
+      </c>
+      <c r="G62" s="23">
+        <f>'02_Base'!M58</f>
+        <v/>
+      </c>
+      <c r="H62" s="23">
+        <f>'02_Base'!O58</f>
+        <v/>
+      </c>
+      <c r="I62" s="15">
+        <f>F62*0.141</f>
+        <v/>
+      </c>
+      <c r="J62" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A62),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A62),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A62)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A62),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A62),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A62))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M58,IF($E$5="Nombre de classes",'02_Base'!O58,'02_Base'!U58)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62))),0))</f>
+        <v/>
+      </c>
+      <c r="K62" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A62,'06_Compta'!$D$4:$D$675,B62,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A62,'06_Compta'!$D$4:$D$675,B62,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M58,IF($E$5="Nombre de classes",'02_Base'!O58,'02_Base'!U58)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A62,'02_Base'!$B$4:$B$61,B62))),0))</f>
+        <v/>
+      </c>
+      <c r="L62" s="14">
+        <f>I62+J62+K62</f>
+        <v/>
+      </c>
+      <c r="M62" s="14">
+        <f>IFERROR(L62/G62,0)</f>
+        <v/>
+      </c>
+      <c r="N62" s="15">
+        <f>IFERROR(L62/H62,0)</f>
+        <v/>
+      </c>
+      <c r="O62" s="15">
+        <f>IFERROR(F62/G62-M62,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17">
+        <f>'02_Base'!A59</f>
+        <v/>
+      </c>
+      <c r="B63" s="39">
+        <f>'02_Base'!B59</f>
+        <v/>
+      </c>
+      <c r="C63" s="17">
+        <f>'02_Base'!C59</f>
+        <v/>
+      </c>
+      <c r="D63" s="39">
+        <f>'02_Base'!E59</f>
+        <v/>
+      </c>
+      <c r="E63" s="39">
+        <f>'02_Base'!F59</f>
+        <v/>
+      </c>
+      <c r="F63" s="15">
+        <f>'02_Base'!U59</f>
+        <v/>
+      </c>
+      <c r="G63" s="23">
+        <f>'02_Base'!M59</f>
+        <v/>
+      </c>
+      <c r="H63" s="23">
+        <f>'02_Base'!O59</f>
+        <v/>
+      </c>
+      <c r="I63" s="15">
+        <f>F63*0.141</f>
+        <v/>
+      </c>
+      <c r="J63" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A63),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A63),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A63)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A63),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A63),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A63))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M59,IF($E$5="Nombre de classes",'02_Base'!O59,'02_Base'!U59)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63))),0))</f>
+        <v/>
+      </c>
+      <c r="K63" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A63,'06_Compta'!$D$4:$D$675,B63,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A63,'06_Compta'!$D$4:$D$675,B63,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M59,IF($E$5="Nombre de classes",'02_Base'!O59,'02_Base'!U59)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A63,'02_Base'!$B$4:$B$61,B63))),0))</f>
+        <v/>
+      </c>
+      <c r="L63" s="14">
+        <f>I63+J63+K63</f>
+        <v/>
+      </c>
+      <c r="M63" s="14">
+        <f>IFERROR(L63/G63,0)</f>
+        <v/>
+      </c>
+      <c r="N63" s="15">
+        <f>IFERROR(L63/H63,0)</f>
+        <v/>
+      </c>
+      <c r="O63" s="15">
+        <f>IFERROR(F63/G63-M63,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17">
+        <f>'02_Base'!A60</f>
+        <v/>
+      </c>
+      <c r="B64" s="39">
+        <f>'02_Base'!B60</f>
+        <v/>
+      </c>
+      <c r="C64" s="17">
+        <f>'02_Base'!C60</f>
+        <v/>
+      </c>
+      <c r="D64" s="39">
+        <f>'02_Base'!E60</f>
+        <v/>
+      </c>
+      <c r="E64" s="39">
+        <f>'02_Base'!F60</f>
+        <v/>
+      </c>
+      <c r="F64" s="15">
+        <f>'02_Base'!U60</f>
+        <v/>
+      </c>
+      <c r="G64" s="23">
+        <f>'02_Base'!M60</f>
+        <v/>
+      </c>
+      <c r="H64" s="23">
+        <f>'02_Base'!O60</f>
+        <v/>
+      </c>
+      <c r="I64" s="15">
+        <f>F64*0.141</f>
+        <v/>
+      </c>
+      <c r="J64" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A64),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A64),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A64)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A64),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A64),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A64))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M60,IF($E$5="Nombre de classes",'02_Base'!O60,'02_Base'!U60)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64))),0))</f>
+        <v/>
+      </c>
+      <c r="K64" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A64,'06_Compta'!$D$4:$D$675,B64,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A64,'06_Compta'!$D$4:$D$675,B64,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M60,IF($E$5="Nombre de classes",'02_Base'!O60,'02_Base'!U60)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A64,'02_Base'!$B$4:$B$61,B64))),0))</f>
+        <v/>
+      </c>
+      <c r="L64" s="14">
+        <f>I64+J64+K64</f>
+        <v/>
+      </c>
+      <c r="M64" s="14">
+        <f>IFERROR(L64/G64,0)</f>
+        <v/>
+      </c>
+      <c r="N64" s="15">
+        <f>IFERROR(L64/H64,0)</f>
+        <v/>
+      </c>
+      <c r="O64" s="15">
+        <f>IFERROR(F64/G64-M64,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17">
+        <f>'02_Base'!A61</f>
+        <v/>
+      </c>
+      <c r="B65" s="39">
+        <f>'02_Base'!B61</f>
+        <v/>
+      </c>
+      <c r="C65" s="17">
+        <f>'02_Base'!C61</f>
+        <v/>
+      </c>
+      <c r="D65" s="39">
+        <f>'02_Base'!E61</f>
+        <v/>
+      </c>
+      <c r="E65" s="39">
+        <f>'02_Base'!F61</f>
+        <v/>
+      </c>
+      <c r="F65" s="15">
+        <f>'02_Base'!U61</f>
+        <v/>
+      </c>
+      <c r="G65" s="23">
+        <f>'02_Base'!M61</f>
+        <v/>
+      </c>
+      <c r="H65" s="23">
+        <f>'02_Base'!O61</f>
+        <v/>
+      </c>
+      <c r="I65" s="15">
+        <f>F65*0.141</f>
+        <v/>
+      </c>
+      <c r="J65" s="15">
+        <f>$I$3*(IFERROR(IF($E$3="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A65),IF($E$3="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A65),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A65)))/IF($E$3="Effectif",SUM('02_Base'!$M$4:$M$61),IF($E$3="Nombre de classes",SUM('02_Base'!$O$4:$O$61),SUM('02_Base'!$U$4:$U$61))),0))*(IFERROR(IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65)))/IF($E$4="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A65),IF($E$4="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A65),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A65))),0))*(IFERROR((IF($E$5="Effectif",'02_Base'!M61,IF($E$5="Nombre de classes",'02_Base'!O61,'02_Base'!U61)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65))),0))</f>
+        <v/>
+      </c>
+      <c r="K65" s="15">
+        <f>(SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A65,'06_Compta'!$D$4:$D$675,B65,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$H$4:$H$675,"Charge")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$C$4:$C$675,A65,'06_Compta'!$D$4:$D$675,B65,'06_Compta'!$J$4:$J$675,"2026ATT_VDEF",'06_Compta'!$I$4:$I$675,"Dotations")-SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65)*0.141)*(IFERROR((IF($E$5="Effectif",'02_Base'!M61,IF($E$5="Nombre de classes",'02_Base'!O61,'02_Base'!U61)))/IF($E$5="Effectif",SUMIFS('02_Base'!$M$4:$M$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65),IF($E$5="Nombre de classes",SUMIFS('02_Base'!$O$4:$O$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65),SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,A65,'02_Base'!$B$4:$B$61,B65))),0))</f>
+        <v/>
+      </c>
+      <c r="L65" s="14">
+        <f>I65+J65+K65</f>
+        <v/>
+      </c>
+      <c r="M65" s="14">
+        <f>IFERROR(L65/G65,0)</f>
+        <v/>
+      </c>
+      <c r="N65" s="15">
+        <f>IFERROR(L65/H65,0)</f>
+        <v/>
+      </c>
+      <c r="O65" s="15">
+        <f>IFERROR(F65/G65-M65,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B66" s="42" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="C20" s="44">
-        <f>SUM(C6:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="44">
-        <f>SUM(D6:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="44">
-        <f>SUM(E6:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="44">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="43">
-        <f>SUM(G6:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="42" t="inlineStr">
+      <c r="C66" s="42" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="I20" s="44">
-        <f>SUM(I6:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="44">
-        <f>SUM(J6:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="55">
-        <f>IFERROR(J20/C20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Change la clé (CA / effectif / classes) → la quote-part du siège se redistribue et l'EBITDA par campus bouge. Un campus rentable en contribution peut devenir déficitaire une fois pleinement chargé (effet « piège »). Le total EBITDA reste constant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E66" s="42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F66" s="44">
+        <f>SUM(F8:F65)</f>
+        <v/>
+      </c>
+      <c r="G66" s="43">
+        <f>SUM(G8:G65)</f>
+        <v/>
+      </c>
+      <c r="H66" s="43">
+        <f>SUM(H8:H65)</f>
+        <v/>
+      </c>
+      <c r="I66" s="44">
+        <f>SUM(I8:I65)</f>
+        <v/>
+      </c>
+      <c r="J66" s="44">
+        <f>SUM(J8:J65)</f>
+        <v/>
+      </c>
+      <c r="K66" s="44">
+        <f>SUM(K8:K65)</f>
+        <v/>
+      </c>
+      <c r="L66" s="44">
+        <f>SUM(L8:L65)</f>
+        <v/>
+      </c>
+      <c r="M66" s="44">
+        <f>IFERROR(L66/G66,0)</f>
+        <v/>
+      </c>
+      <c r="N66" s="44">
+        <f>IFERROR(L66/H66,0)</f>
+        <v/>
+      </c>
+      <c r="O66" s="44">
+        <f>IFERROR(F66/G66-M66,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>Cascade Groupe → Marque → Campus → Classe : la clé se choisit à CHAQUE niveau (CA / effectif / classes). Le coût total par étudiant est PLEINEMENT chargé (directs + siège cascadé + structure). La marge/étudiant en rouge = classe déficitaire → cible du simulateur d'ouverture / fermeture (étape suivante).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A22:K23"/>
+  <mergeCells count="5">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A68:O69"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K6:K19">
+  <conditionalFormatting sqref="O8:O65">
     <cfRule type="colorScale" priority="1">
       <colorScale>
+        <cfvo type="min"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.14"/>
         <cfvo type="max"/>
         <color rgb="00F8696B"/>
         <color rgb="00FFEB84"/>
@@ -2760,7 +5753,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E3 E4 E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Chiffre d'affaires,Effectif,Nombre de classes"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3702,7 +6695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3725,6 +6718,7 @@
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3842,6 +6836,11 @@
           <t>Yield admis→inscrit</t>
         </is>
       </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>CA réf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
@@ -3916,6 +6915,9 @@
       <c r="T4" s="38" t="n">
         <v>0.6</v>
       </c>
+      <c r="U4" s="37" t="n">
+        <v>662220</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -3990,6 +6992,9 @@
       <c r="T5" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U5" s="37" t="n">
+        <v>572320</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -4064,6 +7069,9 @@
       <c r="T6" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U6" s="37" t="n">
+        <v>540960</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -4138,6 +7146,9 @@
       <c r="T7" s="38" t="n">
         <v>0.4194</v>
       </c>
+      <c r="U7" s="37" t="n">
+        <v>662220</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -4212,6 +7223,9 @@
       <c r="T8" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U8" s="37" t="n">
+        <v>630000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
@@ -4286,6 +7300,9 @@
       <c r="T9" s="38" t="n">
         <v>0.6</v>
       </c>
+      <c r="U9" s="37" t="n">
+        <v>525690</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -4360,6 +7377,9 @@
       <c r="T10" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U10" s="37" t="n">
+        <v>448350</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4434,6 +7454,9 @@
       <c r="T11" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U11" s="37" t="n">
+        <v>426300</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -4508,6 +7531,9 @@
       <c r="T12" s="38" t="n">
         <v>0.4204</v>
       </c>
+      <c r="U12" s="37" t="n">
+        <v>525690</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
@@ -4582,6 +7608,9 @@
       <c r="T13" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U13" s="37" t="n">
+        <v>496125</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -4656,6 +7685,9 @@
       <c r="T14" s="38" t="n">
         <v>0.6</v>
       </c>
+      <c r="U14" s="37" t="n">
+        <v>455400</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -4730,6 +7762,9 @@
       <c r="T15" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U15" s="37" t="n">
+        <v>392000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4804,6 +7839,9 @@
       <c r="T16" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U16" s="37" t="n">
+        <v>371000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -4878,6 +7916,9 @@
       <c r="T17" s="38" t="n">
         <v>0.4196</v>
       </c>
+      <c r="U17" s="37" t="n">
+        <v>455400</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -4952,6 +7993,9 @@
       <c r="T18" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U18" s="37" t="n">
+        <v>435000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
@@ -5026,6 +8070,9 @@
       <c r="T19" s="38" t="n">
         <v>0.6</v>
       </c>
+      <c r="U19" s="37" t="n">
+        <v>375615</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
@@ -5100,6 +8147,9 @@
       <c r="T20" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U20" s="37" t="n">
+        <v>319130</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
@@ -5174,6 +8224,9 @@
       <c r="T21" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U21" s="37" t="n">
+        <v>305550</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -5248,6 +8301,9 @@
       <c r="T22" s="38" t="n">
         <v>0.4215</v>
       </c>
+      <c r="U22" s="37" t="n">
+        <v>375615</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
@@ -5322,6 +8378,9 @@
       <c r="T23" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U23" s="37" t="n">
+        <v>356475</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -5396,6 +8455,9 @@
       <c r="T24" s="38" t="n">
         <v>0.6</v>
       </c>
+      <c r="U24" s="37" t="n">
+        <v>611280</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
@@ -5470,6 +8532,9 @@
       <c r="T25" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U25" s="37" t="n">
+        <v>525280</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -5544,6 +8609,9 @@
       <c r="T26" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U26" s="37" t="n">
+        <v>501760</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -5618,6 +8686,9 @@
       <c r="T27" s="38" t="n">
         <v>0.4211</v>
       </c>
+      <c r="U27" s="37" t="n">
+        <v>611280</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
@@ -5692,6 +8763,9 @@
       <c r="T28" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U28" s="37" t="n">
+        <v>579600</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
@@ -5766,6 +8840,9 @@
       <c r="T29" s="38" t="n">
         <v>0.6024</v>
       </c>
+      <c r="U29" s="37" t="n">
+        <v>372000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
@@ -5840,6 +8917,9 @@
       <c r="T30" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U30" s="37" t="n">
+        <v>315560</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -5914,6 +8994,9 @@
       <c r="T31" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U31" s="37" t="n">
+        <v>301840</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
@@ -5988,6 +9071,9 @@
       <c r="T32" s="38" t="n">
         <v>0.4202</v>
       </c>
+      <c r="U32" s="37" t="n">
+        <v>372000</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
@@ -6062,6 +9148,9 @@
       <c r="T33" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U33" s="37" t="n">
+        <v>352800</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -6136,6 +9225,9 @@
       <c r="T34" s="38" t="n">
         <v>0.6026</v>
       </c>
+      <c r="U34" s="37" t="n">
+        <v>342630</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -6210,6 +9302,9 @@
       <c r="T35" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U35" s="37" t="n">
+        <v>295680</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -6284,6 +9379,9 @@
       <c r="T36" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U36" s="37" t="n">
+        <v>282240</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
@@ -6358,6 +9456,9 @@
       <c r="T37" s="38" t="n">
         <v>0.4196</v>
       </c>
+      <c r="U37" s="37" t="n">
+        <v>342630</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -6432,6 +9533,9 @@
       <c r="T38" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U38" s="37" t="n">
+        <v>324000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
@@ -6506,6 +9610,9 @@
       <c r="T39" s="38" t="n">
         <v>0.4202</v>
       </c>
+      <c r="U39" s="37" t="n">
+        <v>354500</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
@@ -6580,6 +9687,9 @@
       <c r="T40" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U40" s="37" t="n">
+        <v>322000</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -6654,6 +9764,9 @@
       <c r="T41" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U41" s="37" t="n">
+        <v>308000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -6728,6 +9841,9 @@
       <c r="T42" s="38" t="n">
         <v>0.4211</v>
       </c>
+      <c r="U42" s="37" t="n">
+        <v>269600</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -6802,6 +9918,9 @@
       <c r="T43" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U43" s="37" t="n">
+        <v>246050</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -6876,6 +9995,9 @@
       <c r="T44" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U44" s="37" t="n">
+        <v>232750</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -6950,6 +10072,9 @@
       <c r="T45" s="38" t="n">
         <v>0.4211</v>
       </c>
+      <c r="U45" s="37" t="n">
+        <v>269600</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
@@ -7024,6 +10149,9 @@
       <c r="T46" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U46" s="37" t="n">
+        <v>246050</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
@@ -7098,6 +10226,9 @@
       <c r="T47" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U47" s="37" t="n">
+        <v>232750</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -7172,6 +10303,9 @@
       <c r="T48" s="38" t="n">
         <v>0.4182</v>
       </c>
+      <c r="U48" s="37" t="n">
+        <v>293940</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -7246,6 +10380,9 @@
       <c r="T49" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U49" s="37" t="n">
+        <v>270900</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -7320,6 +10457,9 @@
       <c r="T50" s="38" t="n">
         <v>0.4182</v>
       </c>
+      <c r="U50" s="37" t="n">
+        <v>342240</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -7394,6 +10534,9 @@
       <c r="T51" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U51" s="37" t="n">
+        <v>323400</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -7468,6 +10611,9 @@
       <c r="T52" s="38" t="n">
         <v>0.4186</v>
       </c>
+      <c r="U52" s="37" t="n">
+        <v>212760</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -7542,6 +10688,9 @@
       <c r="T53" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U53" s="37" t="n">
+        <v>197880</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -7616,6 +10765,9 @@
       <c r="T54" s="38" t="n">
         <v>0.4186</v>
       </c>
+      <c r="U54" s="37" t="n">
+        <v>247680</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -7690,6 +10842,9 @@
       <c r="T55" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U55" s="37" t="n">
+        <v>230860</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -7764,6 +10919,9 @@
       <c r="T56" s="38" t="n">
         <v>0.4196</v>
       </c>
+      <c r="U56" s="37" t="n">
+        <v>372710</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -7838,6 +10996,9 @@
       <c r="T57" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U57" s="37" t="n">
+        <v>344960</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -7912,6 +11073,9 @@
       <c r="T58" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U58" s="37" t="n">
+        <v>329280</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
@@ -7986,6 +11150,9 @@
       <c r="T59" s="38" t="n">
         <v>0.4211</v>
       </c>
+      <c r="U59" s="37" t="n">
+        <v>297600</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -8060,6 +11227,9 @@
       <c r="T60" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U60" s="37" t="n">
+        <v>271950</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
@@ -8134,11 +11304,14 @@
       <c r="T61" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="U61" s="37" t="n">
+        <v>257250</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -19,6 +19,7 @@
     <sheet name="08_Saisie_Campus" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="09_Reporting" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="10_Allocation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11_Reconciliation" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -388,6 +389,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5761,6 +5765,258 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RÉCONCILIATION MULTISOURCE — CRM · Compta · Base se recoupent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Contrôle interne : chaque grandeur est calculée depuis deux systèmes différents ; l'écart doit être nul. Preuve que le « chargement multisource » se réconcilie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Grandeur (atterrissage 2026)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Source A</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Valeur A</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Source B</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Valeur B</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Base (Σ CA réf)</t>
+        </is>
+      </c>
+      <c r="D5" s="15">
+        <f>SUM('02_Base'!$U$4:$U$61)</f>
+        <v/>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Compta (produits)</t>
+        </is>
+      </c>
+      <c r="F5" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Produit",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>D5-F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="68">
+        <f>IF(ABS(G5)&lt;=MAX(1,0.001*D5),"✓ aligné","⚠ écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>CRM (Σ leads)</t>
+        </is>
+      </c>
+      <c r="D6" s="23">
+        <f>SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$D$4:$D$45,2026)</f>
+        <v/>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Base (Σ leads hist)</t>
+        </is>
+      </c>
+      <c r="F6" s="23">
+        <f>SUM('02_Base'!$H$4:$H$61)</f>
+        <v/>
+      </c>
+      <c r="G6" s="22">
+        <f>D6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="68">
+        <f>IF(ABS(G6)&lt;=MAX(1,0.001*D6),"✓ aligné","⚠ écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Dépense marketing</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>CRM (dépense)</t>
+        </is>
+      </c>
+      <c r="D7" s="15">
+        <f>SUMIFS('02_CRM'!$H$4:$H$45,'02_CRM'!$D$4:$D$45,2026)</f>
+        <v/>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Compta (compte 6231)</t>
+        </is>
+      </c>
+      <c r="F7" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6231",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>D7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="68">
+        <f>IF(ABS(G7)&lt;=MAX(1,0.001*D7),"✓ aligné","⚠ écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Dépense marketing (bis)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Compta (6231)</t>
+        </is>
+      </c>
+      <c r="D8" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$E$4:$E$675,"6231",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Campagnes (budget réf)</t>
+        </is>
+      </c>
+      <c r="F8" s="15">
+        <f>SUM('03_Campagnes'!$G$5:$G$18)</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>D8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="68">
+        <f>IF(ABS(G8)&lt;=MAX(1,0.001*D8),"✓ aligné","⚠ écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>P&amp;L (cascade SIG)</t>
+        </is>
+      </c>
+      <c r="D9" s="15">
+        <f>'07_PnL'!$F$33</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Compta (produits − charges)</t>
+        </is>
+      </c>
+      <c r="F9" s="15">
+        <f>SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Produit",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")-SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$H$4:$H$675,"Charge",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")+SUMIFS('06_Compta'!$L$4:$L$675,'06_Compta'!$I$4:$I$675,"Dotations",'06_Compta'!$J$4:$J$675,"2026ATT_VDEF")</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>D9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="68">
+        <f>IF(ABS(G9)&lt;=MAX(1,0.001*D9),"✓ aligné","⚠ écart")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Toutes les grandeurs se recoupent (écart nul aux arrondis près) : le CRM, la compta et la base racontent le même chiffre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B11:H11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -31968,7 +32224,7 @@
         </is>
       </c>
       <c r="L109" s="13" t="n">
-        <v>160273</v>
+        <v>160834</v>
       </c>
     </row>
     <row r="110">
@@ -32028,7 +32284,7 @@
         </is>
       </c>
       <c r="L110" s="13" t="n">
-        <v>138903</v>
+        <v>139390</v>
       </c>
     </row>
     <row r="111">
@@ -32088,7 +32344,7 @@
         </is>
       </c>
       <c r="L111" s="13" t="n">
-        <v>128218</v>
+        <v>128667</v>
       </c>
     </row>
     <row r="112">
@@ -32148,7 +32404,7 @@
         </is>
       </c>
       <c r="L112" s="13" t="n">
-        <v>106849</v>
+        <v>107223</v>
       </c>
     </row>
     <row r="113">
@@ -32208,7 +32464,7 @@
         </is>
       </c>
       <c r="L113" s="13" t="n">
-        <v>149588</v>
+        <v>150112</v>
       </c>
     </row>
     <row r="114">
@@ -32268,7 +32524,7 @@
         </is>
       </c>
       <c r="L114" s="13" t="n">
-        <v>106849</v>
+        <v>107223</v>
       </c>
     </row>
     <row r="115">
@@ -32328,7 +32584,7 @@
         </is>
       </c>
       <c r="L115" s="13" t="n">
-        <v>106849</v>
+        <v>107223</v>
       </c>
     </row>
     <row r="116">
@@ -32388,7 +32644,7 @@
         </is>
       </c>
       <c r="L116" s="13" t="n">
-        <v>64109</v>
+        <v>64334</v>
       </c>
     </row>
     <row r="117">
@@ -32448,7 +32704,7 @@
         </is>
       </c>
       <c r="L117" s="13" t="n">
-        <v>64109</v>
+        <v>64334</v>
       </c>
     </row>
     <row r="118">
@@ -32508,7 +32764,7 @@
         </is>
       </c>
       <c r="L118" s="13" t="n">
-        <v>64109</v>
+        <v>64334</v>
       </c>
     </row>
     <row r="119">
@@ -32568,7 +32824,7 @@
         </is>
       </c>
       <c r="L119" s="13" t="n">
-        <v>85479</v>
+        <v>85778</v>
       </c>
     </row>
     <row r="120">
@@ -32628,7 +32884,7 @@
         </is>
       </c>
       <c r="L120" s="13" t="n">
-        <v>85479</v>
+        <v>85778</v>
       </c>
     </row>
     <row r="121">
@@ -32688,7 +32944,7 @@
         </is>
       </c>
       <c r="L121" s="13" t="n">
-        <v>64109</v>
+        <v>64334</v>
       </c>
     </row>
     <row r="122">
@@ -32748,7 +33004,7 @@
         </is>
       </c>
       <c r="L122" s="13" t="n">
-        <v>64109</v>
+        <v>64334</v>
       </c>
     </row>
     <row r="123">
@@ -32808,7 +33064,7 @@
         </is>
       </c>
       <c r="L123" s="13" t="n">
-        <v>168324</v>
+        <v>168740</v>
       </c>
     </row>
     <row r="124">
@@ -32868,7 +33124,7 @@
         </is>
       </c>
       <c r="L124" s="13" t="n">
-        <v>145880</v>
+        <v>146241</v>
       </c>
     </row>
     <row r="125">
@@ -32928,7 +33184,7 @@
         </is>
       </c>
       <c r="L125" s="13" t="n">
-        <v>134659</v>
+        <v>134992</v>
       </c>
     </row>
     <row r="126">
@@ -32988,7 +33244,7 @@
         </is>
       </c>
       <c r="L126" s="13" t="n">
-        <v>112216</v>
+        <v>112493</v>
       </c>
     </row>
     <row r="127">
@@ -33048,7 +33304,7 @@
         </is>
       </c>
       <c r="L127" s="13" t="n">
-        <v>157102</v>
+        <v>157491</v>
       </c>
     </row>
     <row r="128">
@@ -33108,7 +33364,7 @@
         </is>
       </c>
       <c r="L128" s="13" t="n">
-        <v>112216</v>
+        <v>112493</v>
       </c>
     </row>
     <row r="129">
@@ -33168,7 +33424,7 @@
         </is>
       </c>
       <c r="L129" s="13" t="n">
-        <v>112216</v>
+        <v>112493</v>
       </c>
     </row>
     <row r="130">
@@ -33228,7 +33484,7 @@
         </is>
       </c>
       <c r="L130" s="13" t="n">
-        <v>67329</v>
+        <v>67496</v>
       </c>
     </row>
     <row r="131">
@@ -33288,7 +33544,7 @@
         </is>
       </c>
       <c r="L131" s="13" t="n">
-        <v>67329</v>
+        <v>67496</v>
       </c>
     </row>
     <row r="132">
@@ -33348,7 +33604,7 @@
         </is>
       </c>
       <c r="L132" s="13" t="n">
-        <v>67329</v>
+        <v>67496</v>
       </c>
     </row>
     <row r="133">
@@ -33408,7 +33664,7 @@
         </is>
       </c>
       <c r="L133" s="13" t="n">
-        <v>89773</v>
+        <v>89995</v>
       </c>
     </row>
     <row r="134">
@@ -33468,7 +33724,7 @@
         </is>
       </c>
       <c r="L134" s="13" t="n">
-        <v>89773</v>
+        <v>89995</v>
       </c>
     </row>
     <row r="135">
@@ -33528,7 +33784,7 @@
         </is>
       </c>
       <c r="L135" s="13" t="n">
-        <v>67329</v>
+        <v>67496</v>
       </c>
     </row>
     <row r="136">
@@ -33588,7 +33844,7 @@
         </is>
       </c>
       <c r="L136" s="13" t="n">
-        <v>67329</v>
+        <v>67496</v>
       </c>
     </row>
     <row r="137">
@@ -33648,7 +33904,7 @@
         </is>
       </c>
       <c r="L137" s="13" t="n">
-        <v>177178</v>
+        <v>177435</v>
       </c>
     </row>
     <row r="138">
@@ -33708,7 +33964,7 @@
         </is>
       </c>
       <c r="L138" s="13" t="n">
-        <v>153554</v>
+        <v>153777</v>
       </c>
     </row>
     <row r="139">
@@ -33768,7 +34024,7 @@
         </is>
       </c>
       <c r="L139" s="13" t="n">
-        <v>141743</v>
+        <v>141948</v>
       </c>
     </row>
     <row r="140">
@@ -33828,7 +34084,7 @@
         </is>
       </c>
       <c r="L140" s="13" t="n">
-        <v>118119</v>
+        <v>118290</v>
       </c>
     </row>
     <row r="141">
@@ -33888,7 +34144,7 @@
         </is>
       </c>
       <c r="L141" s="13" t="n">
-        <v>165366</v>
+        <v>165606</v>
       </c>
     </row>
     <row r="142">
@@ -33948,7 +34204,7 @@
         </is>
       </c>
       <c r="L142" s="13" t="n">
-        <v>118119</v>
+        <v>118290</v>
       </c>
     </row>
     <row r="143">
@@ -34008,7 +34264,7 @@
         </is>
       </c>
       <c r="L143" s="13" t="n">
-        <v>118119</v>
+        <v>118290</v>
       </c>
     </row>
     <row r="144">
@@ -34068,7 +34324,7 @@
         </is>
       </c>
       <c r="L144" s="13" t="n">
-        <v>70871</v>
+        <v>70974</v>
       </c>
     </row>
     <row r="145">
@@ -34128,7 +34384,7 @@
         </is>
       </c>
       <c r="L145" s="13" t="n">
-        <v>70871</v>
+        <v>70974</v>
       </c>
     </row>
     <row r="146">
@@ -34188,7 +34444,7 @@
         </is>
       </c>
       <c r="L146" s="13" t="n">
-        <v>70871</v>
+        <v>70974</v>
       </c>
     </row>
     <row r="147">
@@ -34248,7 +34504,7 @@
         </is>
       </c>
       <c r="L147" s="13" t="n">
-        <v>94495</v>
+        <v>94632</v>
       </c>
     </row>
     <row r="148">
@@ -34308,7 +34564,7 @@
         </is>
       </c>
       <c r="L148" s="13" t="n">
-        <v>94495</v>
+        <v>94632</v>
       </c>
     </row>
     <row r="149">
@@ -34368,7 +34624,7 @@
         </is>
       </c>
       <c r="L149" s="13" t="n">
-        <v>70871</v>
+        <v>70974</v>
       </c>
     </row>
     <row r="150">
@@ -34428,7 +34684,7 @@
         </is>
       </c>
       <c r="L150" s="13" t="n">
-        <v>70871</v>
+        <v>70974</v>
       </c>
     </row>
     <row r="151">
@@ -34488,7 +34744,7 @@
         </is>
       </c>
       <c r="L151" s="13" t="n">
-        <v>75219</v>
+        <v>75483</v>
       </c>
     </row>
     <row r="152">
@@ -34548,7 +34804,7 @@
         </is>
       </c>
       <c r="L152" s="13" t="n">
-        <v>63321</v>
+        <v>63543</v>
       </c>
     </row>
     <row r="153">
@@ -34608,7 +34864,7 @@
         </is>
       </c>
       <c r="L153" s="13" t="n">
-        <v>57876</v>
+        <v>58079</v>
       </c>
     </row>
     <row r="154">
@@ -34668,7 +34924,7 @@
         </is>
       </c>
       <c r="L154" s="13" t="n">
-        <v>49003</v>
+        <v>49175</v>
       </c>
     </row>
     <row r="155">
@@ -34728,7 +34984,7 @@
         </is>
       </c>
       <c r="L155" s="13" t="n">
-        <v>69371</v>
+        <v>69614</v>
       </c>
     </row>
     <row r="156">
@@ -34788,7 +35044,7 @@
         </is>
       </c>
       <c r="L156" s="13" t="n">
-        <v>47995</v>
+        <v>48163</v>
       </c>
     </row>
     <row r="157">
@@ -34848,7 +35104,7 @@
         </is>
       </c>
       <c r="L157" s="13" t="n">
-        <v>45373</v>
+        <v>45532</v>
       </c>
     </row>
     <row r="158">
@@ -34908,7 +35164,7 @@
         </is>
       </c>
       <c r="L158" s="13" t="n">
-        <v>28232</v>
+        <v>28331</v>
       </c>
     </row>
     <row r="159">
@@ -34968,7 +35224,7 @@
         </is>
       </c>
       <c r="L159" s="13" t="n">
-        <v>22586</v>
+        <v>22665</v>
       </c>
     </row>
     <row r="160">
@@ -35028,7 +35284,7 @@
         </is>
       </c>
       <c r="L160" s="13" t="n">
-        <v>22586</v>
+        <v>22665</v>
       </c>
     </row>
     <row r="161">
@@ -35088,7 +35344,7 @@
         </is>
       </c>
       <c r="L161" s="13" t="n">
-        <v>36097</v>
+        <v>36224</v>
       </c>
     </row>
     <row r="162">
@@ -35148,7 +35404,7 @@
         </is>
       </c>
       <c r="L162" s="13" t="n">
-        <v>28232</v>
+        <v>28331</v>
       </c>
     </row>
     <row r="163">
@@ -35208,7 +35464,7 @@
         </is>
       </c>
       <c r="L163" s="13" t="n">
-        <v>26821</v>
+        <v>26915</v>
       </c>
     </row>
     <row r="164">
@@ -35268,7 +35524,7 @@
         </is>
       </c>
       <c r="L164" s="13" t="n">
-        <v>22586</v>
+        <v>22665</v>
       </c>
     </row>
     <row r="165">
@@ -35328,7 +35584,7 @@
         </is>
       </c>
       <c r="L165" s="13" t="n">
-        <v>78997</v>
+        <v>79193</v>
       </c>
     </row>
     <row r="166">
@@ -35388,7 +35644,7 @@
         </is>
       </c>
       <c r="L166" s="13" t="n">
-        <v>66502</v>
+        <v>66666</v>
       </c>
     </row>
     <row r="167">
@@ -35448,7 +35704,7 @@
         </is>
       </c>
       <c r="L167" s="13" t="n">
-        <v>60784</v>
+        <v>60934</v>
       </c>
     </row>
     <row r="168">
@@ -35508,7 +35764,7 @@
         </is>
       </c>
       <c r="L168" s="13" t="n">
-        <v>51465</v>
+        <v>51592</v>
       </c>
     </row>
     <row r="169">
@@ -35568,7 +35824,7 @@
         </is>
       </c>
       <c r="L169" s="13" t="n">
-        <v>72856</v>
+        <v>73036</v>
       </c>
     </row>
     <row r="170">
@@ -35628,7 +35884,7 @@
         </is>
       </c>
       <c r="L170" s="13" t="n">
-        <v>50406</v>
+        <v>50531</v>
       </c>
     </row>
     <row r="171">
@@ -35688,7 +35944,7 @@
         </is>
       </c>
       <c r="L171" s="13" t="n">
-        <v>47653</v>
+        <v>47770</v>
       </c>
     </row>
     <row r="172">
@@ -35748,7 +36004,7 @@
         </is>
       </c>
       <c r="L172" s="13" t="n">
-        <v>29650</v>
+        <v>29724</v>
       </c>
     </row>
     <row r="173">
@@ -35808,7 +36064,7 @@
         </is>
       </c>
       <c r="L173" s="13" t="n">
-        <v>23720</v>
+        <v>23779</v>
       </c>
     </row>
     <row r="174">
@@ -35868,7 +36124,7 @@
         </is>
       </c>
       <c r="L174" s="13" t="n">
-        <v>23720</v>
+        <v>23779</v>
       </c>
     </row>
     <row r="175">
@@ -35928,7 +36184,7 @@
         </is>
       </c>
       <c r="L175" s="13" t="n">
-        <v>37910</v>
+        <v>38004</v>
       </c>
     </row>
     <row r="176">
@@ -35988,7 +36244,7 @@
         </is>
       </c>
       <c r="L176" s="13" t="n">
-        <v>29650</v>
+        <v>29724</v>
       </c>
     </row>
     <row r="177">
@@ -36048,7 +36304,7 @@
         </is>
       </c>
       <c r="L177" s="13" t="n">
-        <v>28168</v>
+        <v>28238</v>
       </c>
     </row>
     <row r="178">
@@ -36108,7 +36364,7 @@
         </is>
       </c>
       <c r="L178" s="13" t="n">
-        <v>23720</v>
+        <v>23779</v>
       </c>
     </row>
     <row r="179">
@@ -36168,7 +36424,7 @@
         </is>
       </c>
       <c r="L179" s="13" t="n">
-        <v>83153</v>
+        <v>83274</v>
       </c>
     </row>
     <row r="180">
@@ -36228,7 +36484,7 @@
         </is>
       </c>
       <c r="L180" s="13" t="n">
-        <v>70000</v>
+        <v>70102</v>
       </c>
     </row>
     <row r="181">
@@ -36288,7 +36544,7 @@
         </is>
       </c>
       <c r="L181" s="13" t="n">
-        <v>63981</v>
+        <v>64074</v>
       </c>
     </row>
     <row r="182">
@@ -36348,7 +36604,7 @@
         </is>
       </c>
       <c r="L182" s="13" t="n">
-        <v>54172</v>
+        <v>54251</v>
       </c>
     </row>
     <row r="183">
@@ -36408,7 +36664,7 @@
         </is>
       </c>
       <c r="L183" s="13" t="n">
-        <v>76688</v>
+        <v>76799</v>
       </c>
     </row>
     <row r="184">
@@ -36468,7 +36724,7 @@
         </is>
       </c>
       <c r="L184" s="13" t="n">
-        <v>53057</v>
+        <v>53134</v>
       </c>
     </row>
     <row r="185">
@@ -36528,7 +36784,7 @@
         </is>
       </c>
       <c r="L185" s="13" t="n">
-        <v>50159</v>
+        <v>50232</v>
       </c>
     </row>
     <row r="186">
@@ -36588,7 +36844,7 @@
         </is>
       </c>
       <c r="L186" s="13" t="n">
-        <v>31210</v>
+        <v>31255</v>
       </c>
     </row>
     <row r="187">
@@ -36648,7 +36904,7 @@
         </is>
       </c>
       <c r="L187" s="13" t="n">
-        <v>24968</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="188">
@@ -36708,7 +36964,7 @@
         </is>
       </c>
       <c r="L188" s="13" t="n">
-        <v>24968</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="189">
@@ -36768,7 +37024,7 @@
         </is>
       </c>
       <c r="L189" s="13" t="n">
-        <v>39905</v>
+        <v>39962</v>
       </c>
     </row>
     <row r="190">
@@ -36828,7 +37084,7 @@
         </is>
       </c>
       <c r="L190" s="13" t="n">
-        <v>31210</v>
+        <v>31255</v>
       </c>
     </row>
     <row r="191">
@@ -36888,7 +37144,7 @@
         </is>
       </c>
       <c r="L191" s="13" t="n">
-        <v>29650</v>
+        <v>29693</v>
       </c>
     </row>
     <row r="192">
@@ -36948,7 +37204,7 @@
         </is>
       </c>
       <c r="L192" s="13" t="n">
-        <v>24968</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="193">
@@ -37008,7 +37264,7 @@
         </is>
       </c>
       <c r="L193" s="13" t="n">
-        <v>50146</v>
+        <v>50322</v>
       </c>
     </row>
     <row r="194">
@@ -37068,7 +37324,7 @@
         </is>
       </c>
       <c r="L194" s="13" t="n">
-        <v>42214</v>
+        <v>42362</v>
       </c>
     </row>
     <row r="195">
@@ -37128,7 +37384,7 @@
         </is>
       </c>
       <c r="L195" s="13" t="n">
-        <v>38584</v>
+        <v>38719</v>
       </c>
     </row>
     <row r="196">
@@ -37188,7 +37444,7 @@
         </is>
       </c>
       <c r="L196" s="13" t="n">
-        <v>32669</v>
+        <v>32783</v>
       </c>
     </row>
     <row r="197">
@@ -37248,7 +37504,7 @@
         </is>
       </c>
       <c r="L197" s="13" t="n">
-        <v>46247</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="198">
@@ -37308,7 +37564,7 @@
         </is>
       </c>
       <c r="L198" s="13" t="n">
-        <v>31997</v>
+        <v>32109</v>
       </c>
     </row>
     <row r="199">
@@ -37368,7 +37624,7 @@
         </is>
       </c>
       <c r="L199" s="13" t="n">
-        <v>30249</v>
+        <v>30355</v>
       </c>
     </row>
     <row r="200">
@@ -37428,7 +37684,7 @@
         </is>
       </c>
       <c r="L200" s="13" t="n">
-        <v>18822</v>
+        <v>18888</v>
       </c>
     </row>
     <row r="201">
@@ -37488,7 +37744,7 @@
         </is>
       </c>
       <c r="L201" s="13" t="n">
-        <v>15057</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="202">
@@ -37548,7 +37804,7 @@
         </is>
       </c>
       <c r="L202" s="13" t="n">
-        <v>15057</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="203">
@@ -37608,7 +37864,7 @@
         </is>
       </c>
       <c r="L203" s="13" t="n">
-        <v>24065</v>
+        <v>24149</v>
       </c>
     </row>
     <row r="204">
@@ -37668,7 +37924,7 @@
         </is>
       </c>
       <c r="L204" s="13" t="n">
-        <v>18822</v>
+        <v>18888</v>
       </c>
     </row>
     <row r="205">
@@ -37728,7 +37984,7 @@
         </is>
       </c>
       <c r="L205" s="13" t="n">
-        <v>17881</v>
+        <v>17943</v>
       </c>
     </row>
     <row r="206">
@@ -37788,7 +38044,7 @@
         </is>
       </c>
       <c r="L206" s="13" t="n">
-        <v>15057</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="207">
@@ -37848,7 +38104,7 @@
         </is>
       </c>
       <c r="L207" s="13" t="n">
-        <v>52665</v>
+        <v>52795</v>
       </c>
     </row>
     <row r="208">
@@ -37908,7 +38164,7 @@
         </is>
       </c>
       <c r="L208" s="13" t="n">
-        <v>44335</v>
+        <v>44444</v>
       </c>
     </row>
     <row r="209">
@@ -37968,7 +38224,7 @@
         </is>
       </c>
       <c r="L209" s="13" t="n">
-        <v>40522</v>
+        <v>40623</v>
       </c>
     </row>
     <row r="210">
@@ -38028,7 +38284,7 @@
         </is>
       </c>
       <c r="L210" s="13" t="n">
-        <v>34310</v>
+        <v>34395</v>
       </c>
     </row>
     <row r="211">
@@ -38088,7 +38344,7 @@
         </is>
       </c>
       <c r="L211" s="13" t="n">
-        <v>48570</v>
+        <v>48690</v>
       </c>
     </row>
     <row r="212">
@@ -38148,7 +38404,7 @@
         </is>
       </c>
       <c r="L212" s="13" t="n">
-        <v>33604</v>
+        <v>33687</v>
       </c>
     </row>
     <row r="213">
@@ -38208,7 +38464,7 @@
         </is>
       </c>
       <c r="L213" s="13" t="n">
-        <v>31768</v>
+        <v>31847</v>
       </c>
     </row>
     <row r="214">
@@ -38268,7 +38524,7 @@
         </is>
       </c>
       <c r="L214" s="13" t="n">
-        <v>19767</v>
+        <v>19816</v>
       </c>
     </row>
     <row r="215">
@@ -38328,7 +38584,7 @@
         </is>
       </c>
       <c r="L215" s="13" t="n">
-        <v>15814</v>
+        <v>15853</v>
       </c>
     </row>
     <row r="216">
@@ -38388,7 +38644,7 @@
         </is>
       </c>
       <c r="L216" s="13" t="n">
-        <v>15814</v>
+        <v>15853</v>
       </c>
     </row>
     <row r="217">
@@ -38448,7 +38704,7 @@
         </is>
       </c>
       <c r="L217" s="13" t="n">
-        <v>25274</v>
+        <v>25336</v>
       </c>
     </row>
     <row r="218">
@@ -38508,7 +38764,7 @@
         </is>
       </c>
       <c r="L218" s="13" t="n">
-        <v>19767</v>
+        <v>19816</v>
       </c>
     </row>
     <row r="219">
@@ -38568,7 +38824,7 @@
         </is>
       </c>
       <c r="L219" s="13" t="n">
-        <v>18779</v>
+        <v>18825</v>
       </c>
     </row>
     <row r="220">
@@ -38628,7 +38884,7 @@
         </is>
       </c>
       <c r="L220" s="13" t="n">
-        <v>15814</v>
+        <v>15853</v>
       </c>
     </row>
     <row r="221">
@@ -38688,7 +38944,7 @@
         </is>
       </c>
       <c r="L221" s="13" t="n">
-        <v>55435</v>
+        <v>55516</v>
       </c>
     </row>
     <row r="222">
@@ -38748,7 +39004,7 @@
         </is>
       </c>
       <c r="L222" s="13" t="n">
-        <v>46667</v>
+        <v>46734</v>
       </c>
     </row>
     <row r="223">
@@ -38808,7 +39064,7 @@
         </is>
       </c>
       <c r="L223" s="13" t="n">
-        <v>42654</v>
+        <v>42716</v>
       </c>
     </row>
     <row r="224">
@@ -38868,7 +39124,7 @@
         </is>
       </c>
       <c r="L224" s="13" t="n">
-        <v>36115</v>
+        <v>36167</v>
       </c>
     </row>
     <row r="225">
@@ -38928,7 +39184,7 @@
         </is>
       </c>
       <c r="L225" s="13" t="n">
-        <v>51125</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="226">
@@ -38988,7 +39244,7 @@
         </is>
       </c>
       <c r="L226" s="13" t="n">
-        <v>35372</v>
+        <v>35423</v>
       </c>
     </row>
     <row r="227">
@@ -39048,7 +39304,7 @@
         </is>
       </c>
       <c r="L227" s="13" t="n">
-        <v>33440</v>
+        <v>33488</v>
       </c>
     </row>
     <row r="228">
@@ -39108,7 +39364,7 @@
         </is>
       </c>
       <c r="L228" s="13" t="n">
-        <v>20807</v>
+        <v>20837</v>
       </c>
     </row>
     <row r="229">
@@ -39168,7 +39424,7 @@
         </is>
       </c>
       <c r="L229" s="13" t="n">
-        <v>16645</v>
+        <v>16670</v>
       </c>
     </row>
     <row r="230">
@@ -39228,7 +39484,7 @@
         </is>
       </c>
       <c r="L230" s="13" t="n">
-        <v>16645</v>
+        <v>16670</v>
       </c>
     </row>
     <row r="231">
@@ -39288,7 +39544,7 @@
         </is>
       </c>
       <c r="L231" s="13" t="n">
-        <v>26603</v>
+        <v>26642</v>
       </c>
     </row>
     <row r="232">
@@ -39348,7 +39604,7 @@
         </is>
       </c>
       <c r="L232" s="13" t="n">
-        <v>20807</v>
+        <v>20837</v>
       </c>
     </row>
     <row r="233">
@@ -39408,7 +39664,7 @@
         </is>
       </c>
       <c r="L233" s="13" t="n">
-        <v>19766</v>
+        <v>19795</v>
       </c>
     </row>
     <row r="234">
@@ -39468,7 +39724,7 @@
         </is>
       </c>
       <c r="L234" s="13" t="n">
-        <v>16645</v>
+        <v>16670</v>
       </c>
     </row>
     <row r="235">
@@ -39528,7 +39784,7 @@
         </is>
       </c>
       <c r="L235" s="13" t="n">
-        <v>48082</v>
+        <v>56438</v>
       </c>
     </row>
     <row r="236">
@@ -39588,7 +39844,7 @@
         </is>
       </c>
       <c r="L236" s="13" t="n">
-        <v>41671</v>
+        <v>34532</v>
       </c>
     </row>
     <row r="237">
@@ -39648,7 +39904,7 @@
         </is>
       </c>
       <c r="L237" s="13" t="n">
-        <v>38466</v>
+        <v>26060</v>
       </c>
     </row>
     <row r="238">
@@ -39708,7 +39964,7 @@
         </is>
       </c>
       <c r="L238" s="13" t="n">
-        <v>32055</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="239">
@@ -39768,7 +40024,7 @@
         </is>
       </c>
       <c r="L239" s="13" t="n">
-        <v>44876</v>
+        <v>50248</v>
       </c>
     </row>
     <row r="240">
@@ -39828,7 +40084,7 @@
         </is>
       </c>
       <c r="L240" s="13" t="n">
-        <v>32055</v>
+        <v>20843</v>
       </c>
     </row>
     <row r="241">
@@ -39888,7 +40144,7 @@
         </is>
       </c>
       <c r="L241" s="13" t="n">
-        <v>32055</v>
+        <v>18251</v>
       </c>
     </row>
     <row r="242">
@@ -39948,7 +40204,7 @@
         </is>
       </c>
       <c r="L242" s="13" t="n">
-        <v>19233</v>
+        <v>17983</v>
       </c>
     </row>
     <row r="243">
@@ -40008,7 +40264,7 @@
         </is>
       </c>
       <c r="L243" s="13" t="n">
-        <v>19233</v>
+        <v>12341</v>
       </c>
     </row>
     <row r="244">
@@ -40068,7 +40324,7 @@
         </is>
       </c>
       <c r="L244" s="13" t="n">
-        <v>19233</v>
+        <v>12543</v>
       </c>
     </row>
     <row r="245">
@@ -40128,7 +40384,7 @@
         </is>
       </c>
       <c r="L245" s="13" t="n">
-        <v>25644</v>
+        <v>30258</v>
       </c>
     </row>
     <row r="246">
@@ -40188,7 +40444,7 @@
         </is>
       </c>
       <c r="L246" s="13" t="n">
-        <v>25644</v>
+        <v>18155</v>
       </c>
     </row>
     <row r="247">
@@ -40248,7 +40504,7 @@
         </is>
       </c>
       <c r="L247" s="13" t="n">
-        <v>19233</v>
+        <v>24992</v>
       </c>
     </row>
     <row r="248">
@@ -40308,7 +40564,7 @@
         </is>
       </c>
       <c r="L248" s="13" t="n">
-        <v>19233</v>
+        <v>15578</v>
       </c>
     </row>
     <row r="249">
@@ -40368,7 +40624,7 @@
         </is>
       </c>
       <c r="L249" s="13" t="n">
-        <v>50497</v>
+        <v>62082</v>
       </c>
     </row>
     <row r="250">
@@ -40428,7 +40684,7 @@
         </is>
       </c>
       <c r="L250" s="13" t="n">
-        <v>43764</v>
+        <v>37985</v>
       </c>
     </row>
     <row r="251">
@@ -40488,7 +40744,7 @@
         </is>
       </c>
       <c r="L251" s="13" t="n">
-        <v>40398</v>
+        <v>28666</v>
       </c>
     </row>
     <row r="252">
@@ -40548,7 +40804,7 @@
         </is>
       </c>
       <c r="L252" s="13" t="n">
-        <v>33665</v>
+        <v>22657</v>
       </c>
     </row>
     <row r="253">
@@ -40608,7 +40864,7 @@
         </is>
       </c>
       <c r="L253" s="13" t="n">
-        <v>47131</v>
+        <v>55272</v>
       </c>
     </row>
     <row r="254">
@@ -40668,7 +40924,7 @@
         </is>
       </c>
       <c r="L254" s="13" t="n">
-        <v>33665</v>
+        <v>22927</v>
       </c>
     </row>
     <row r="255">
@@ -40728,7 +40984,7 @@
         </is>
       </c>
       <c r="L255" s="13" t="n">
-        <v>33665</v>
+        <v>20076</v>
       </c>
     </row>
     <row r="256">
@@ -40788,7 +41044,7 @@
         </is>
       </c>
       <c r="L256" s="13" t="n">
-        <v>20199</v>
+        <v>19782</v>
       </c>
     </row>
     <row r="257">
@@ -40848,7 +41104,7 @@
         </is>
       </c>
       <c r="L257" s="13" t="n">
-        <v>20199</v>
+        <v>13575</v>
       </c>
     </row>
     <row r="258">
@@ -40908,7 +41164,7 @@
         </is>
       </c>
       <c r="L258" s="13" t="n">
-        <v>20199</v>
+        <v>13798</v>
       </c>
     </row>
     <row r="259">
@@ -40968,7 +41224,7 @@
         </is>
       </c>
       <c r="L259" s="13" t="n">
-        <v>26932</v>
+        <v>33284</v>
       </c>
     </row>
     <row r="260">
@@ -41028,7 +41284,7 @@
         </is>
       </c>
       <c r="L260" s="13" t="n">
-        <v>26932</v>
+        <v>19971</v>
       </c>
     </row>
     <row r="261">
@@ -41088,7 +41344,7 @@
         </is>
       </c>
       <c r="L261" s="13" t="n">
-        <v>20199</v>
+        <v>27491</v>
       </c>
     </row>
     <row r="262">
@@ -41148,7 +41404,7 @@
         </is>
       </c>
       <c r="L262" s="13" t="n">
-        <v>20199</v>
+        <v>17136</v>
       </c>
     </row>
     <row r="263">
@@ -41208,7 +41464,7 @@
         </is>
       </c>
       <c r="L263" s="13" t="n">
-        <v>53153</v>
+        <v>68291</v>
       </c>
     </row>
     <row r="264">
@@ -41268,7 +41524,7 @@
         </is>
       </c>
       <c r="L264" s="13" t="n">
-        <v>46066</v>
+        <v>41783</v>
       </c>
     </row>
     <row r="265">
@@ -41328,7 +41584,7 @@
         </is>
       </c>
       <c r="L265" s="13" t="n">
-        <v>42523</v>
+        <v>31533</v>
       </c>
     </row>
     <row r="266">
@@ -41388,7 +41644,7 @@
         </is>
       </c>
       <c r="L266" s="13" t="n">
-        <v>35436</v>
+        <v>24923</v>
       </c>
     </row>
     <row r="267">
@@ -41448,7 +41704,7 @@
         </is>
       </c>
       <c r="L267" s="13" t="n">
-        <v>49610</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="268">
@@ -41508,7 +41764,7 @@
         </is>
       </c>
       <c r="L268" s="13" t="n">
-        <v>35436</v>
+        <v>25220</v>
       </c>
     </row>
     <row r="269">
@@ -41568,7 +41824,7 @@
         </is>
       </c>
       <c r="L269" s="13" t="n">
-        <v>35436</v>
+        <v>22083</v>
       </c>
     </row>
     <row r="270">
@@ -41628,7 +41884,7 @@
         </is>
       </c>
       <c r="L270" s="13" t="n">
-        <v>21261</v>
+        <v>21760</v>
       </c>
     </row>
     <row r="271">
@@ -41688,7 +41944,7 @@
         </is>
       </c>
       <c r="L271" s="13" t="n">
-        <v>21261</v>
+        <v>14933</v>
       </c>
     </row>
     <row r="272">
@@ -41748,7 +42004,7 @@
         </is>
       </c>
       <c r="L272" s="13" t="n">
-        <v>21261</v>
+        <v>15178</v>
       </c>
     </row>
     <row r="273">
@@ -41808,7 +42064,7 @@
         </is>
       </c>
       <c r="L273" s="13" t="n">
-        <v>28349</v>
+        <v>36612</v>
       </c>
     </row>
     <row r="274">
@@ -41868,7 +42124,7 @@
         </is>
       </c>
       <c r="L274" s="13" t="n">
-        <v>28349</v>
+        <v>21968</v>
       </c>
     </row>
     <row r="275">
@@ -41928,7 +42184,7 @@
         </is>
       </c>
       <c r="L275" s="13" t="n">
-        <v>21261</v>
+        <v>30240</v>
       </c>
     </row>
     <row r="276">
@@ -41988,7 +42244,7 @@
         </is>
       </c>
       <c r="L276" s="13" t="n">
-        <v>21261</v>
+        <v>18850</v>
       </c>
     </row>
     <row r="277">
@@ -42048,7 +42304,7 @@
         </is>
       </c>
       <c r="L277" s="13" t="n">
-        <v>389234</v>
+        <v>390598</v>
       </c>
     </row>
     <row r="278">
@@ -42108,7 +42364,7 @@
         </is>
       </c>
       <c r="L278" s="13" t="n">
-        <v>337337</v>
+        <v>338518</v>
       </c>
     </row>
     <row r="279">
@@ -42168,7 +42424,7 @@
         </is>
       </c>
       <c r="L279" s="13" t="n">
-        <v>311388</v>
+        <v>312478</v>
       </c>
     </row>
     <row r="280">
@@ -42228,7 +42484,7 @@
         </is>
       </c>
       <c r="L280" s="13" t="n">
-        <v>259490</v>
+        <v>260398</v>
       </c>
     </row>
     <row r="281">
@@ -42288,7 +42544,7 @@
         </is>
       </c>
       <c r="L281" s="13" t="n">
-        <v>363286</v>
+        <v>364558</v>
       </c>
     </row>
     <row r="282">
@@ -42348,7 +42604,7 @@
         </is>
       </c>
       <c r="L282" s="13" t="n">
-        <v>259490</v>
+        <v>260398</v>
       </c>
     </row>
     <row r="283">
@@ -42408,7 +42664,7 @@
         </is>
       </c>
       <c r="L283" s="13" t="n">
-        <v>259490</v>
+        <v>260398</v>
       </c>
     </row>
     <row r="284">
@@ -42468,7 +42724,7 @@
         </is>
       </c>
       <c r="L284" s="13" t="n">
-        <v>155694</v>
+        <v>156239</v>
       </c>
     </row>
     <row r="285">
@@ -42528,7 +42784,7 @@
         </is>
       </c>
       <c r="L285" s="13" t="n">
-        <v>155694</v>
+        <v>156239</v>
       </c>
     </row>
     <row r="286">
@@ -42588,7 +42844,7 @@
         </is>
       </c>
       <c r="L286" s="13" t="n">
-        <v>155694</v>
+        <v>156239</v>
       </c>
     </row>
     <row r="287">
@@ -42648,7 +42904,7 @@
         </is>
       </c>
       <c r="L287" s="13" t="n">
-        <v>207592</v>
+        <v>208319</v>
       </c>
     </row>
     <row r="288">
@@ -42708,7 +42964,7 @@
         </is>
       </c>
       <c r="L288" s="13" t="n">
-        <v>207592</v>
+        <v>208319</v>
       </c>
     </row>
     <row r="289">
@@ -42768,7 +43024,7 @@
         </is>
       </c>
       <c r="L289" s="13" t="n">
-        <v>155694</v>
+        <v>156239</v>
       </c>
     </row>
     <row r="290">
@@ -42828,7 +43084,7 @@
         </is>
       </c>
       <c r="L290" s="13" t="n">
-        <v>155694</v>
+        <v>156239</v>
       </c>
     </row>
     <row r="291">
@@ -42888,7 +43144,7 @@
         </is>
       </c>
       <c r="L291" s="13" t="n">
-        <v>408786</v>
+        <v>409797</v>
       </c>
     </row>
     <row r="292">
@@ -42948,7 +43204,7 @@
         </is>
       </c>
       <c r="L292" s="13" t="n">
-        <v>354281</v>
+        <v>355157</v>
       </c>
     </row>
     <row r="293">
@@ -43008,7 +43264,7 @@
         </is>
       </c>
       <c r="L293" s="13" t="n">
-        <v>327029</v>
+        <v>327838</v>
       </c>
     </row>
     <row r="294">
@@ -43068,7 +43324,7 @@
         </is>
       </c>
       <c r="L294" s="13" t="n">
-        <v>272524</v>
+        <v>273198</v>
       </c>
     </row>
     <row r="295">
@@ -43128,7 +43384,7 @@
         </is>
       </c>
       <c r="L295" s="13" t="n">
-        <v>381534</v>
+        <v>382477</v>
       </c>
     </row>
     <row r="296">
@@ -43188,7 +43444,7 @@
         </is>
       </c>
       <c r="L296" s="13" t="n">
-        <v>272524</v>
+        <v>273198</v>
       </c>
     </row>
     <row r="297">
@@ -43248,7 +43504,7 @@
         </is>
       </c>
       <c r="L297" s="13" t="n">
-        <v>272524</v>
+        <v>273198</v>
       </c>
     </row>
     <row r="298">
@@ -43308,7 +43564,7 @@
         </is>
       </c>
       <c r="L298" s="13" t="n">
-        <v>163514</v>
+        <v>163919</v>
       </c>
     </row>
     <row r="299">
@@ -43368,7 +43624,7 @@
         </is>
       </c>
       <c r="L299" s="13" t="n">
-        <v>163514</v>
+        <v>163919</v>
       </c>
     </row>
     <row r="300">
@@ -43428,7 +43684,7 @@
         </is>
       </c>
       <c r="L300" s="13" t="n">
-        <v>163514</v>
+        <v>163919</v>
       </c>
     </row>
     <row r="301">
@@ -43488,7 +43744,7 @@
         </is>
       </c>
       <c r="L301" s="13" t="n">
-        <v>218019</v>
+        <v>218558</v>
       </c>
     </row>
     <row r="302">
@@ -43548,7 +43804,7 @@
         </is>
       </c>
       <c r="L302" s="13" t="n">
-        <v>218019</v>
+        <v>218558</v>
       </c>
     </row>
     <row r="303">
@@ -43608,7 +43864,7 @@
         </is>
       </c>
       <c r="L303" s="13" t="n">
-        <v>163514</v>
+        <v>163919</v>
       </c>
     </row>
     <row r="304">
@@ -43668,7 +43924,7 @@
         </is>
       </c>
       <c r="L304" s="13" t="n">
-        <v>163514</v>
+        <v>163919</v>
       </c>
     </row>
     <row r="305">
@@ -43728,7 +43984,7 @@
         </is>
       </c>
       <c r="L305" s="13" t="n">
-        <v>430290</v>
+        <v>430914</v>
       </c>
     </row>
     <row r="306">
@@ -43788,7 +44044,7 @@
         </is>
       </c>
       <c r="L306" s="13" t="n">
-        <v>372918</v>
+        <v>373459</v>
       </c>
     </row>
     <row r="307">
@@ -43848,7 +44104,7 @@
         </is>
       </c>
       <c r="L307" s="13" t="n">
-        <v>344232</v>
+        <v>344731</v>
       </c>
     </row>
     <row r="308">
@@ -43908,7 +44164,7 @@
         </is>
       </c>
       <c r="L308" s="13" t="n">
-        <v>286860</v>
+        <v>287276</v>
       </c>
     </row>
     <row r="309">
@@ -43968,7 +44224,7 @@
         </is>
       </c>
       <c r="L309" s="13" t="n">
-        <v>401604</v>
+        <v>402186</v>
       </c>
     </row>
     <row r="310">
@@ -44028,7 +44284,7 @@
         </is>
       </c>
       <c r="L310" s="13" t="n">
-        <v>286860</v>
+        <v>287276</v>
       </c>
     </row>
     <row r="311">
@@ -44088,7 +44344,7 @@
         </is>
       </c>
       <c r="L311" s="13" t="n">
-        <v>286860</v>
+        <v>287276</v>
       </c>
     </row>
     <row r="312">
@@ -44148,7 +44404,7 @@
         </is>
       </c>
       <c r="L312" s="13" t="n">
-        <v>172116</v>
+        <v>172365</v>
       </c>
     </row>
     <row r="313">
@@ -44208,7 +44464,7 @@
         </is>
       </c>
       <c r="L313" s="13" t="n">
-        <v>172116</v>
+        <v>172365</v>
       </c>
     </row>
     <row r="314">
@@ -44268,7 +44524,7 @@
         </is>
       </c>
       <c r="L314" s="13" t="n">
-        <v>172116</v>
+        <v>172365</v>
       </c>
     </row>
     <row r="315">
@@ -44328,7 +44584,7 @@
         </is>
       </c>
       <c r="L315" s="13" t="n">
-        <v>229488</v>
+        <v>229821</v>
       </c>
     </row>
     <row r="316">
@@ -44388,7 +44644,7 @@
         </is>
       </c>
       <c r="L316" s="13" t="n">
-        <v>229488</v>
+        <v>229821</v>
       </c>
     </row>
     <row r="317">
@@ -44448,7 +44704,7 @@
         </is>
       </c>
       <c r="L317" s="13" t="n">
-        <v>172116</v>
+        <v>172365</v>
       </c>
     </row>
     <row r="318">
@@ -44508,7 +44764,7 @@
         </is>
       </c>
       <c r="L318" s="13" t="n">
-        <v>172116</v>
+        <v>172365</v>
       </c>
     </row>
     <row r="319">
@@ -44568,7 +44824,7 @@
         </is>
       </c>
       <c r="L319" s="13" t="n">
-        <v>225657</v>
+        <v>226448</v>
       </c>
     </row>
     <row r="320">
@@ -44628,7 +44884,7 @@
         </is>
       </c>
       <c r="L320" s="13" t="n">
-        <v>189964</v>
+        <v>190629</v>
       </c>
     </row>
     <row r="321">
@@ -44688,7 +44944,7 @@
         </is>
       </c>
       <c r="L321" s="13" t="n">
-        <v>173629</v>
+        <v>174237</v>
       </c>
     </row>
     <row r="322">
@@ -44748,7 +45004,7 @@
         </is>
       </c>
       <c r="L322" s="13" t="n">
-        <v>147010</v>
+        <v>147525</v>
       </c>
     </row>
     <row r="323">
@@ -44808,7 +45064,7 @@
         </is>
       </c>
       <c r="L323" s="13" t="n">
-        <v>208113</v>
+        <v>208842</v>
       </c>
     </row>
     <row r="324">
@@ -44868,7 +45124,7 @@
         </is>
       </c>
       <c r="L324" s="13" t="n">
-        <v>143985</v>
+        <v>144489</v>
       </c>
     </row>
     <row r="325">
@@ -44928,7 +45184,7 @@
         </is>
       </c>
       <c r="L325" s="13" t="n">
-        <v>136120</v>
+        <v>136597</v>
       </c>
     </row>
     <row r="326">
@@ -44988,7 +45244,7 @@
         </is>
       </c>
       <c r="L326" s="13" t="n">
-        <v>84697</v>
+        <v>84994</v>
       </c>
     </row>
     <row r="327">
@@ -45048,7 +45304,7 @@
         </is>
       </c>
       <c r="L327" s="13" t="n">
-        <v>67758</v>
+        <v>67995</v>
       </c>
     </row>
     <row r="328">
@@ -45108,7 +45364,7 @@
         </is>
       </c>
       <c r="L328" s="13" t="n">
-        <v>67758</v>
+        <v>67995</v>
       </c>
     </row>
     <row r="329">
@@ -45168,7 +45424,7 @@
         </is>
       </c>
       <c r="L329" s="13" t="n">
-        <v>108291</v>
+        <v>108671</v>
       </c>
     </row>
     <row r="330">
@@ -45228,7 +45484,7 @@
         </is>
       </c>
       <c r="L330" s="13" t="n">
-        <v>84697</v>
+        <v>84994</v>
       </c>
     </row>
     <row r="331">
@@ -45288,7 +45544,7 @@
         </is>
       </c>
       <c r="L331" s="13" t="n">
-        <v>80462</v>
+        <v>80744</v>
       </c>
     </row>
     <row r="332">
@@ -45348,7 +45604,7 @@
         </is>
       </c>
       <c r="L332" s="13" t="n">
-        <v>67758</v>
+        <v>67995</v>
       </c>
     </row>
     <row r="333">
@@ -45408,7 +45664,7 @@
         </is>
       </c>
       <c r="L333" s="13" t="n">
-        <v>236992</v>
+        <v>237578</v>
       </c>
     </row>
     <row r="334">
@@ -45468,7 +45724,7 @@
         </is>
       </c>
       <c r="L334" s="13" t="n">
-        <v>199506</v>
+        <v>199999</v>
       </c>
     </row>
     <row r="335">
@@ -45528,7 +45784,7 @@
         </is>
       </c>
       <c r="L335" s="13" t="n">
-        <v>182351</v>
+        <v>182802</v>
       </c>
     </row>
     <row r="336">
@@ -45588,7 +45844,7 @@
         </is>
       </c>
       <c r="L336" s="13" t="n">
-        <v>154394</v>
+        <v>154776</v>
       </c>
     </row>
     <row r="337">
@@ -45648,7 +45904,7 @@
         </is>
       </c>
       <c r="L337" s="13" t="n">
-        <v>218567</v>
+        <v>219107</v>
       </c>
     </row>
     <row r="338">
@@ -45708,7 +45964,7 @@
         </is>
       </c>
       <c r="L338" s="13" t="n">
-        <v>151218</v>
+        <v>151592</v>
       </c>
     </row>
     <row r="339">
@@ -45768,7 +46024,7 @@
         </is>
       </c>
       <c r="L339" s="13" t="n">
-        <v>142958</v>
+        <v>143311</v>
       </c>
     </row>
     <row r="340">
@@ -45828,7 +46084,7 @@
         </is>
       </c>
       <c r="L340" s="13" t="n">
-        <v>88951</v>
+        <v>89172</v>
       </c>
     </row>
     <row r="341">
@@ -45888,7 +46144,7 @@
         </is>
       </c>
       <c r="L341" s="13" t="n">
-        <v>71161</v>
+        <v>71337</v>
       </c>
     </row>
     <row r="342">
@@ -45948,7 +46204,7 @@
         </is>
       </c>
       <c r="L342" s="13" t="n">
-        <v>71161</v>
+        <v>71337</v>
       </c>
     </row>
     <row r="343">
@@ -46008,7 +46264,7 @@
         </is>
       </c>
       <c r="L343" s="13" t="n">
-        <v>113731</v>
+        <v>114012</v>
       </c>
     </row>
     <row r="344">
@@ -46068,7 +46324,7 @@
         </is>
       </c>
       <c r="L344" s="13" t="n">
-        <v>88951</v>
+        <v>89172</v>
       </c>
     </row>
     <row r="345">
@@ -46128,7 +46384,7 @@
         </is>
       </c>
       <c r="L345" s="13" t="n">
-        <v>84504</v>
+        <v>84713</v>
       </c>
     </row>
     <row r="346">
@@ -46188,7 +46444,7 @@
         </is>
       </c>
       <c r="L346" s="13" t="n">
-        <v>71161</v>
+        <v>71337</v>
       </c>
     </row>
     <row r="347">
@@ -46248,7 +46504,7 @@
         </is>
       </c>
       <c r="L347" s="13" t="n">
-        <v>249459</v>
+        <v>249821</v>
       </c>
     </row>
     <row r="348">
@@ -46308,7 +46564,7 @@
         </is>
       </c>
       <c r="L348" s="13" t="n">
-        <v>210000</v>
+        <v>210305</v>
       </c>
     </row>
     <row r="349">
@@ -46368,7 +46624,7 @@
         </is>
       </c>
       <c r="L349" s="13" t="n">
-        <v>191943</v>
+        <v>192221</v>
       </c>
     </row>
     <row r="350">
@@ -46428,7 +46684,7 @@
         </is>
       </c>
       <c r="L350" s="13" t="n">
-        <v>162516</v>
+        <v>162752</v>
       </c>
     </row>
     <row r="351">
@@ -46488,7 +46744,7 @@
         </is>
       </c>
       <c r="L351" s="13" t="n">
-        <v>230064</v>
+        <v>230398</v>
       </c>
     </row>
     <row r="352">
@@ -46548,7 +46804,7 @@
         </is>
       </c>
       <c r="L352" s="13" t="n">
-        <v>159172</v>
+        <v>159403</v>
       </c>
     </row>
     <row r="353">
@@ -46608,7 +46864,7 @@
         </is>
       </c>
       <c r="L353" s="13" t="n">
-        <v>150478</v>
+        <v>150696</v>
       </c>
     </row>
     <row r="354">
@@ -46668,7 +46924,7 @@
         </is>
       </c>
       <c r="L354" s="13" t="n">
-        <v>93631</v>
+        <v>93766</v>
       </c>
     </row>
     <row r="355">
@@ -46728,7 +46984,7 @@
         </is>
       </c>
       <c r="L355" s="13" t="n">
-        <v>74905</v>
+        <v>75013</v>
       </c>
     </row>
     <row r="356">
@@ -46788,7 +47044,7 @@
         </is>
       </c>
       <c r="L356" s="13" t="n">
-        <v>74905</v>
+        <v>75013</v>
       </c>
     </row>
     <row r="357">
@@ -46848,7 +47104,7 @@
         </is>
       </c>
       <c r="L357" s="13" t="n">
-        <v>119714</v>
+        <v>119887</v>
       </c>
     </row>
     <row r="358">
@@ -46908,7 +47164,7 @@
         </is>
       </c>
       <c r="L358" s="13" t="n">
-        <v>93631</v>
+        <v>93766</v>
       </c>
     </row>
     <row r="359">
@@ -46968,7 +47224,7 @@
         </is>
       </c>
       <c r="L359" s="13" t="n">
-        <v>88949</v>
+        <v>89078</v>
       </c>
     </row>
     <row r="360">
@@ -47028,7 +47284,7 @@
         </is>
       </c>
       <c r="L360" s="13" t="n">
-        <v>74905</v>
+        <v>75013</v>
       </c>
     </row>
     <row r="361">
@@ -47088,7 +47344,7 @@
         </is>
       </c>
       <c r="L361" s="13" t="n">
-        <v>1091383</v>
+        <v>1095205</v>
       </c>
     </row>
     <row r="362">
@@ -47148,7 +47404,7 @@
         </is>
       </c>
       <c r="L362" s="13" t="n">
-        <v>1146204</v>
+        <v>1149039</v>
       </c>
     </row>
     <row r="363">
@@ -47208,7 +47464,7 @@
         </is>
       </c>
       <c r="L363" s="13" t="n">
-        <v>1206499</v>
+        <v>1208248</v>
       </c>
     </row>
     <row r="364">
@@ -47268,7 +47524,7 @@
         </is>
       </c>
       <c r="L364" s="13" t="n">
-        <v>351023</v>
+        <v>352252</v>
       </c>
     </row>
     <row r="365">
@@ -47328,7 +47584,7 @@
         </is>
       </c>
       <c r="L365" s="13" t="n">
-        <v>295499</v>
+        <v>296534</v>
       </c>
     </row>
     <row r="366">
@@ -47388,7 +47644,7 @@
         </is>
       </c>
       <c r="L366" s="13" t="n">
-        <v>270090</v>
+        <v>271036</v>
       </c>
     </row>
     <row r="367">
@@ -47448,7 +47704,7 @@
         </is>
       </c>
       <c r="L367" s="13" t="n">
-        <v>228682</v>
+        <v>229483</v>
       </c>
     </row>
     <row r="368">
@@ -47508,7 +47764,7 @@
         </is>
       </c>
       <c r="L368" s="13" t="n">
-        <v>323731</v>
+        <v>324865</v>
       </c>
     </row>
     <row r="369">
@@ -47568,7 +47824,7 @@
         </is>
       </c>
       <c r="L369" s="13" t="n">
-        <v>223977</v>
+        <v>224761</v>
       </c>
     </row>
     <row r="370">
@@ -47628,7 +47884,7 @@
         </is>
       </c>
       <c r="L370" s="13" t="n">
-        <v>211743</v>
+        <v>212484</v>
       </c>
     </row>
     <row r="371">
@@ -47688,7 +47944,7 @@
         </is>
       </c>
       <c r="L371" s="13" t="n">
-        <v>131751</v>
+        <v>132213</v>
       </c>
     </row>
     <row r="372">
@@ -47748,7 +48004,7 @@
         </is>
       </c>
       <c r="L372" s="13" t="n">
-        <v>105401</v>
+        <v>105770</v>
       </c>
     </row>
     <row r="373">
@@ -47808,7 +48064,7 @@
         </is>
       </c>
       <c r="L373" s="13" t="n">
-        <v>105401</v>
+        <v>105770</v>
       </c>
     </row>
     <row r="374">
@@ -47868,7 +48124,7 @@
         </is>
       </c>
       <c r="L374" s="13" t="n">
-        <v>168453</v>
+        <v>169043</v>
       </c>
     </row>
     <row r="375">
@@ -47928,7 +48184,7 @@
         </is>
       </c>
       <c r="L375" s="13" t="n">
-        <v>131751</v>
+        <v>132213</v>
       </c>
     </row>
     <row r="376">
@@ -47988,7 +48244,7 @@
         </is>
       </c>
       <c r="L376" s="13" t="n">
-        <v>125164</v>
+        <v>125602</v>
       </c>
     </row>
     <row r="377">
@@ -48048,7 +48304,7 @@
         </is>
       </c>
       <c r="L377" s="13" t="n">
-        <v>105401</v>
+        <v>105770</v>
       </c>
     </row>
     <row r="378">
@@ -48108,7 +48364,7 @@
         </is>
       </c>
       <c r="L378" s="13" t="n">
-        <v>368655</v>
+        <v>369566</v>
       </c>
     </row>
     <row r="379">
@@ -48168,7 +48424,7 @@
         </is>
       </c>
       <c r="L379" s="13" t="n">
-        <v>310342</v>
+        <v>311110</v>
       </c>
     </row>
     <row r="380">
@@ -48228,7 +48484,7 @@
         </is>
       </c>
       <c r="L380" s="13" t="n">
-        <v>283656</v>
+        <v>284358</v>
       </c>
     </row>
     <row r="381">
@@ -48288,7 +48544,7 @@
         </is>
       </c>
       <c r="L381" s="13" t="n">
-        <v>240169</v>
+        <v>240763</v>
       </c>
     </row>
     <row r="382">
@@ -48348,7 +48604,7 @@
         </is>
       </c>
       <c r="L382" s="13" t="n">
-        <v>339992</v>
+        <v>340833</v>
       </c>
     </row>
     <row r="383">
@@ -48408,7 +48664,7 @@
         </is>
       </c>
       <c r="L383" s="13" t="n">
-        <v>235227</v>
+        <v>235809</v>
       </c>
     </row>
     <row r="384">
@@ -48468,7 +48724,7 @@
         </is>
       </c>
       <c r="L384" s="13" t="n">
-        <v>222379</v>
+        <v>222929</v>
       </c>
     </row>
     <row r="385">
@@ -48528,7 +48784,7 @@
         </is>
       </c>
       <c r="L385" s="13" t="n">
-        <v>138369</v>
+        <v>138711</v>
       </c>
     </row>
     <row r="386">
@@ -48588,7 +48844,7 @@
         </is>
       </c>
       <c r="L386" s="13" t="n">
-        <v>110695</v>
+        <v>110969</v>
       </c>
     </row>
     <row r="387">
@@ -48648,7 +48904,7 @@
         </is>
       </c>
       <c r="L387" s="13" t="n">
-        <v>110695</v>
+        <v>110969</v>
       </c>
     </row>
     <row r="388">
@@ -48708,7 +48964,7 @@
         </is>
       </c>
       <c r="L388" s="13" t="n">
-        <v>176915</v>
+        <v>177352</v>
       </c>
     </row>
     <row r="389">
@@ -48768,7 +49024,7 @@
         </is>
       </c>
       <c r="L389" s="13" t="n">
-        <v>138369</v>
+        <v>138711</v>
       </c>
     </row>
     <row r="390">
@@ -48828,7 +49084,7 @@
         </is>
       </c>
       <c r="L390" s="13" t="n">
-        <v>131451</v>
+        <v>131776</v>
       </c>
     </row>
     <row r="391">
@@ -48888,7 +49144,7 @@
         </is>
       </c>
       <c r="L391" s="13" t="n">
-        <v>110695</v>
+        <v>110969</v>
       </c>
     </row>
     <row r="392">
@@ -48948,7 +49204,7 @@
         </is>
       </c>
       <c r="L392" s="13" t="n">
-        <v>388047</v>
+        <v>388610</v>
       </c>
     </row>
     <row r="393">
@@ -49008,7 +49264,7 @@
         </is>
       </c>
       <c r="L393" s="13" t="n">
-        <v>326667</v>
+        <v>327141</v>
       </c>
     </row>
     <row r="394">
@@ -49068,7 +49324,7 @@
         </is>
       </c>
       <c r="L394" s="13" t="n">
-        <v>298578</v>
+        <v>299011</v>
       </c>
     </row>
     <row r="395">
@@ -49128,7 +49384,7 @@
         </is>
       </c>
       <c r="L395" s="13" t="n">
-        <v>252803</v>
+        <v>253170</v>
       </c>
     </row>
     <row r="396">
@@ -49188,7 +49444,7 @@
         </is>
       </c>
       <c r="L396" s="13" t="n">
-        <v>357878</v>
+        <v>358396</v>
       </c>
     </row>
     <row r="397">
@@ -49248,7 +49504,7 @@
         </is>
       </c>
       <c r="L397" s="13" t="n">
-        <v>247601</v>
+        <v>247960</v>
       </c>
     </row>
     <row r="398">
@@ -49308,7 +49564,7 @@
         </is>
       </c>
       <c r="L398" s="13" t="n">
-        <v>234077</v>
+        <v>234416</v>
       </c>
     </row>
     <row r="399">
@@ -49368,7 +49624,7 @@
         </is>
       </c>
       <c r="L399" s="13" t="n">
-        <v>145648</v>
+        <v>145859</v>
       </c>
     </row>
     <row r="400">
@@ -49428,7 +49684,7 @@
         </is>
       </c>
       <c r="L400" s="13" t="n">
-        <v>116518</v>
+        <v>116687</v>
       </c>
     </row>
     <row r="401">
@@ -49488,7 +49744,7 @@
         </is>
       </c>
       <c r="L401" s="13" t="n">
-        <v>116518</v>
+        <v>116687</v>
       </c>
     </row>
     <row r="402">
@@ -49548,7 +49804,7 @@
         </is>
       </c>
       <c r="L402" s="13" t="n">
-        <v>186221</v>
+        <v>186491</v>
       </c>
     </row>
     <row r="403">
@@ -49608,7 +49864,7 @@
         </is>
       </c>
       <c r="L403" s="13" t="n">
-        <v>145648</v>
+        <v>145859</v>
       </c>
     </row>
     <row r="404">
@@ -49668,7 +49924,7 @@
         </is>
       </c>
       <c r="L404" s="13" t="n">
-        <v>138365</v>
+        <v>138566</v>
       </c>
     </row>
     <row r="405">
@@ -49728,7 +49984,7 @@
         </is>
       </c>
       <c r="L405" s="13" t="n">
-        <v>116518</v>
+        <v>116687</v>
       </c>
     </row>
     <row r="406">
@@ -49788,7 +50044,7 @@
         </is>
       </c>
       <c r="L406" s="13" t="n">
-        <v>240410</v>
+        <v>241252</v>
       </c>
     </row>
     <row r="407">
@@ -49848,7 +50104,7 @@
         </is>
       </c>
       <c r="L407" s="13" t="n">
-        <v>208355</v>
+        <v>209085</v>
       </c>
     </row>
     <row r="408">
@@ -49908,7 +50164,7 @@
         </is>
       </c>
       <c r="L408" s="13" t="n">
-        <v>192328</v>
+        <v>193001</v>
       </c>
     </row>
     <row r="409">
@@ -49968,7 +50224,7 @@
         </is>
       </c>
       <c r="L409" s="13" t="n">
-        <v>160273</v>
+        <v>160834</v>
       </c>
     </row>
     <row r="410">
@@ -50028,7 +50284,7 @@
         </is>
       </c>
       <c r="L410" s="13" t="n">
-        <v>224382</v>
+        <v>225168</v>
       </c>
     </row>
     <row r="411">
@@ -50088,7 +50344,7 @@
         </is>
       </c>
       <c r="L411" s="13" t="n">
-        <v>160273</v>
+        <v>160834</v>
       </c>
     </row>
     <row r="412">
@@ -50148,7 +50404,7 @@
         </is>
       </c>
       <c r="L412" s="13" t="n">
-        <v>160273</v>
+        <v>160834</v>
       </c>
     </row>
     <row r="413">
@@ -50208,7 +50464,7 @@
         </is>
       </c>
       <c r="L413" s="13" t="n">
-        <v>96164</v>
+        <v>96501</v>
       </c>
     </row>
     <row r="414">
@@ -50268,7 +50524,7 @@
         </is>
       </c>
       <c r="L414" s="13" t="n">
-        <v>96164</v>
+        <v>96501</v>
       </c>
     </row>
     <row r="415">
@@ -50328,7 +50584,7 @@
         </is>
       </c>
       <c r="L415" s="13" t="n">
-        <v>96164</v>
+        <v>96501</v>
       </c>
     </row>
     <row r="416">
@@ -50388,7 +50644,7 @@
         </is>
       </c>
       <c r="L416" s="13" t="n">
-        <v>128218</v>
+        <v>128667</v>
       </c>
     </row>
     <row r="417">
@@ -50448,7 +50704,7 @@
         </is>
       </c>
       <c r="L417" s="13" t="n">
-        <v>128218</v>
+        <v>128667</v>
       </c>
     </row>
     <row r="418">
@@ -50508,7 +50764,7 @@
         </is>
       </c>
       <c r="L418" s="13" t="n">
-        <v>96164</v>
+        <v>96501</v>
       </c>
     </row>
     <row r="419">
@@ -50568,7 +50824,7 @@
         </is>
       </c>
       <c r="L419" s="13" t="n">
-        <v>96164</v>
+        <v>96501</v>
       </c>
     </row>
     <row r="420">
@@ -50628,7 +50884,7 @@
         </is>
       </c>
       <c r="L420" s="13" t="n">
-        <v>252485</v>
+        <v>253110</v>
       </c>
     </row>
     <row r="421">
@@ -50688,7 +50944,7 @@
         </is>
       </c>
       <c r="L421" s="13" t="n">
-        <v>218821</v>
+        <v>219362</v>
       </c>
     </row>
     <row r="422">
@@ -50748,7 +51004,7 @@
         </is>
       </c>
       <c r="L422" s="13" t="n">
-        <v>201988</v>
+        <v>202488</v>
       </c>
     </row>
     <row r="423">
@@ -50808,7 +51064,7 @@
         </is>
       </c>
       <c r="L423" s="13" t="n">
-        <v>168324</v>
+        <v>168740</v>
       </c>
     </row>
     <row r="424">
@@ -50868,7 +51124,7 @@
         </is>
       </c>
       <c r="L424" s="13" t="n">
-        <v>235653</v>
+        <v>236236</v>
       </c>
     </row>
     <row r="425">
@@ -50928,7 +51184,7 @@
         </is>
       </c>
       <c r="L425" s="13" t="n">
-        <v>168324</v>
+        <v>168740</v>
       </c>
     </row>
     <row r="426">
@@ -50988,7 +51244,7 @@
         </is>
       </c>
       <c r="L426" s="13" t="n">
-        <v>168324</v>
+        <v>168740</v>
       </c>
     </row>
     <row r="427">
@@ -51048,7 +51304,7 @@
         </is>
       </c>
       <c r="L427" s="13" t="n">
-        <v>100994</v>
+        <v>101244</v>
       </c>
     </row>
     <row r="428">
@@ -51108,7 +51364,7 @@
         </is>
       </c>
       <c r="L428" s="13" t="n">
-        <v>100994</v>
+        <v>101244</v>
       </c>
     </row>
     <row r="429">
@@ -51168,7 +51424,7 @@
         </is>
       </c>
       <c r="L429" s="13" t="n">
-        <v>100994</v>
+        <v>101244</v>
       </c>
     </row>
     <row r="430">
@@ -51228,7 +51484,7 @@
         </is>
       </c>
       <c r="L430" s="13" t="n">
-        <v>134659</v>
+        <v>134992</v>
       </c>
     </row>
     <row r="431">
@@ -51288,7 +51544,7 @@
         </is>
       </c>
       <c r="L431" s="13" t="n">
-        <v>134659</v>
+        <v>134992</v>
       </c>
     </row>
     <row r="432">
@@ -51348,7 +51604,7 @@
         </is>
       </c>
       <c r="L432" s="13" t="n">
-        <v>100994</v>
+        <v>101244</v>
       </c>
     </row>
     <row r="433">
@@ -51408,7 +51664,7 @@
         </is>
       </c>
       <c r="L433" s="13" t="n">
-        <v>100994</v>
+        <v>101244</v>
       </c>
     </row>
     <row r="434">
@@ -51468,7 +51724,7 @@
         </is>
       </c>
       <c r="L434" s="13" t="n">
-        <v>265767</v>
+        <v>266153</v>
       </c>
     </row>
     <row r="435">
@@ -51528,7 +51784,7 @@
         </is>
       </c>
       <c r="L435" s="13" t="n">
-        <v>230332</v>
+        <v>230666</v>
       </c>
     </row>
     <row r="436">
@@ -51588,7 +51844,7 @@
         </is>
       </c>
       <c r="L436" s="13" t="n">
-        <v>212614</v>
+        <v>212922</v>
       </c>
     </row>
     <row r="437">
@@ -51648,7 +51904,7 @@
         </is>
       </c>
       <c r="L437" s="13" t="n">
-        <v>177178</v>
+        <v>177435</v>
       </c>
     </row>
     <row r="438">
@@ -51708,7 +51964,7 @@
         </is>
       </c>
       <c r="L438" s="13" t="n">
-        <v>248049</v>
+        <v>248409</v>
       </c>
     </row>
     <row r="439">
@@ -51768,7 +52024,7 @@
         </is>
       </c>
       <c r="L439" s="13" t="n">
-        <v>177178</v>
+        <v>177435</v>
       </c>
     </row>
     <row r="440">
@@ -51828,7 +52084,7 @@
         </is>
       </c>
       <c r="L440" s="13" t="n">
-        <v>177178</v>
+        <v>177435</v>
       </c>
     </row>
     <row r="441">
@@ -51888,7 +52144,7 @@
         </is>
       </c>
       <c r="L441" s="13" t="n">
-        <v>106307</v>
+        <v>106461</v>
       </c>
     </row>
     <row r="442">
@@ -51948,7 +52204,7 @@
         </is>
       </c>
       <c r="L442" s="13" t="n">
-        <v>106307</v>
+        <v>106461</v>
       </c>
     </row>
     <row r="443">
@@ -52008,7 +52264,7 @@
         </is>
       </c>
       <c r="L443" s="13" t="n">
-        <v>106307</v>
+        <v>106461</v>
       </c>
     </row>
     <row r="444">
@@ -52068,7 +52324,7 @@
         </is>
       </c>
       <c r="L444" s="13" t="n">
-        <v>141743</v>
+        <v>141948</v>
       </c>
     </row>
     <row r="445">
@@ -52128,7 +52384,7 @@
         </is>
       </c>
       <c r="L445" s="13" t="n">
-        <v>141743</v>
+        <v>141948</v>
       </c>
     </row>
     <row r="446">
@@ -52188,7 +52444,7 @@
         </is>
       </c>
       <c r="L446" s="13" t="n">
-        <v>106307</v>
+        <v>106461</v>
       </c>
     </row>
     <row r="447">
@@ -52248,7 +52504,7 @@
         </is>
       </c>
       <c r="L447" s="13" t="n">
-        <v>106307</v>
+        <v>106461</v>
       </c>
     </row>
     <row r="448">
@@ -52308,7 +52564,7 @@
         </is>
       </c>
       <c r="L448" s="13" t="n">
-        <v>34344</v>
+        <v>34465</v>
       </c>
     </row>
     <row r="449">
@@ -52368,7 +52624,7 @@
         </is>
       </c>
       <c r="L449" s="13" t="n">
-        <v>29765</v>
+        <v>29869</v>
       </c>
     </row>
     <row r="450">
@@ -52428,7 +52684,7 @@
         </is>
       </c>
       <c r="L450" s="13" t="n">
-        <v>27475</v>
+        <v>27572</v>
       </c>
     </row>
     <row r="451">
@@ -52488,7 +52744,7 @@
         </is>
       </c>
       <c r="L451" s="13" t="n">
-        <v>22896</v>
+        <v>22976</v>
       </c>
     </row>
     <row r="452">
@@ -52548,7 +52804,7 @@
         </is>
       </c>
       <c r="L452" s="13" t="n">
-        <v>32055</v>
+        <v>32167</v>
       </c>
     </row>
     <row r="453">
@@ -52608,7 +52864,7 @@
         </is>
       </c>
       <c r="L453" s="13" t="n">
-        <v>22896</v>
+        <v>22976</v>
       </c>
     </row>
     <row r="454">
@@ -52668,7 +52924,7 @@
         </is>
       </c>
       <c r="L454" s="13" t="n">
-        <v>22896</v>
+        <v>22976</v>
       </c>
     </row>
     <row r="455">
@@ -52728,7 +52984,7 @@
         </is>
       </c>
       <c r="L455" s="13" t="n">
-        <v>13738</v>
+        <v>13786</v>
       </c>
     </row>
     <row r="456">
@@ -52788,7 +53044,7 @@
         </is>
       </c>
       <c r="L456" s="13" t="n">
-        <v>13738</v>
+        <v>13786</v>
       </c>
     </row>
     <row r="457">
@@ -52848,7 +53104,7 @@
         </is>
       </c>
       <c r="L457" s="13" t="n">
-        <v>13738</v>
+        <v>13786</v>
       </c>
     </row>
     <row r="458">
@@ -52908,7 +53164,7 @@
         </is>
       </c>
       <c r="L458" s="13" t="n">
-        <v>18317</v>
+        <v>18381</v>
       </c>
     </row>
     <row r="459">
@@ -52968,7 +53224,7 @@
         </is>
       </c>
       <c r="L459" s="13" t="n">
-        <v>18317</v>
+        <v>18381</v>
       </c>
     </row>
     <row r="460">
@@ -53028,7 +53284,7 @@
         </is>
       </c>
       <c r="L460" s="13" t="n">
-        <v>13738</v>
+        <v>13786</v>
       </c>
     </row>
     <row r="461">
@@ -53088,7 +53344,7 @@
         </is>
       </c>
       <c r="L461" s="13" t="n">
-        <v>13738</v>
+        <v>13786</v>
       </c>
     </row>
     <row r="462">
@@ -53148,7 +53404,7 @@
         </is>
       </c>
       <c r="L462" s="13" t="n">
-        <v>36069</v>
+        <v>36159</v>
       </c>
     </row>
     <row r="463">
@@ -53208,7 +53464,7 @@
         </is>
       </c>
       <c r="L463" s="13" t="n">
-        <v>31260</v>
+        <v>31337</v>
       </c>
     </row>
     <row r="464">
@@ -53268,7 +53524,7 @@
         </is>
       </c>
       <c r="L464" s="13" t="n">
-        <v>28855</v>
+        <v>28927</v>
       </c>
     </row>
     <row r="465">
@@ -53328,7 +53584,7 @@
         </is>
       </c>
       <c r="L465" s="13" t="n">
-        <v>24046</v>
+        <v>24106</v>
       </c>
     </row>
     <row r="466">
@@ -53388,7 +53644,7 @@
         </is>
       </c>
       <c r="L466" s="13" t="n">
-        <v>33665</v>
+        <v>33748</v>
       </c>
     </row>
     <row r="467">
@@ -53448,7 +53704,7 @@
         </is>
       </c>
       <c r="L467" s="13" t="n">
-        <v>24046</v>
+        <v>24106</v>
       </c>
     </row>
     <row r="468">
@@ -53508,7 +53764,7 @@
         </is>
       </c>
       <c r="L468" s="13" t="n">
-        <v>24046</v>
+        <v>24106</v>
       </c>
     </row>
     <row r="469">
@@ -53568,7 +53824,7 @@
         </is>
       </c>
       <c r="L469" s="13" t="n">
-        <v>14428</v>
+        <v>14463</v>
       </c>
     </row>
     <row r="470">
@@ -53628,7 +53884,7 @@
         </is>
       </c>
       <c r="L470" s="13" t="n">
-        <v>14428</v>
+        <v>14463</v>
       </c>
     </row>
     <row r="471">
@@ -53688,7 +53944,7 @@
         </is>
       </c>
       <c r="L471" s="13" t="n">
-        <v>14428</v>
+        <v>14463</v>
       </c>
     </row>
     <row r="472">
@@ -53748,7 +54004,7 @@
         </is>
       </c>
       <c r="L472" s="13" t="n">
-        <v>19237</v>
+        <v>19285</v>
       </c>
     </row>
     <row r="473">
@@ -53808,7 +54064,7 @@
         </is>
       </c>
       <c r="L473" s="13" t="n">
-        <v>19237</v>
+        <v>19285</v>
       </c>
     </row>
     <row r="474">
@@ -53868,7 +54124,7 @@
         </is>
       </c>
       <c r="L474" s="13" t="n">
-        <v>14428</v>
+        <v>14463</v>
       </c>
     </row>
     <row r="475">
@@ -53928,7 +54184,7 @@
         </is>
       </c>
       <c r="L475" s="13" t="n">
-        <v>14428</v>
+        <v>14463</v>
       </c>
     </row>
     <row r="476">
@@ -53988,7 +54244,7 @@
         </is>
       </c>
       <c r="L476" s="13" t="n">
-        <v>37967</v>
+        <v>38022</v>
       </c>
     </row>
     <row r="477">
@@ -54048,7 +54304,7 @@
         </is>
       </c>
       <c r="L477" s="13" t="n">
-        <v>32905</v>
+        <v>32952</v>
       </c>
     </row>
     <row r="478">
@@ -54108,7 +54364,7 @@
         </is>
       </c>
       <c r="L478" s="13" t="n">
-        <v>30373</v>
+        <v>30417</v>
       </c>
     </row>
     <row r="479">
@@ -54168,7 +54424,7 @@
         </is>
       </c>
       <c r="L479" s="13" t="n">
-        <v>25311</v>
+        <v>25348</v>
       </c>
     </row>
     <row r="480">
@@ -54228,7 +54484,7 @@
         </is>
       </c>
       <c r="L480" s="13" t="n">
-        <v>35436</v>
+        <v>35487</v>
       </c>
     </row>
     <row r="481">
@@ -54288,7 +54544,7 @@
         </is>
       </c>
       <c r="L481" s="13" t="n">
-        <v>25311</v>
+        <v>25348</v>
       </c>
     </row>
     <row r="482">
@@ -54348,7 +54604,7 @@
         </is>
       </c>
       <c r="L482" s="13" t="n">
-        <v>25311</v>
+        <v>25348</v>
       </c>
     </row>
     <row r="483">
@@ -54408,7 +54664,7 @@
         </is>
       </c>
       <c r="L483" s="13" t="n">
-        <v>15187</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="484">
@@ -54468,7 +54724,7 @@
         </is>
       </c>
       <c r="L484" s="13" t="n">
-        <v>15187</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="485">
@@ -54528,7 +54784,7 @@
         </is>
       </c>
       <c r="L485" s="13" t="n">
-        <v>15187</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="486">
@@ -54588,7 +54844,7 @@
         </is>
       </c>
       <c r="L486" s="13" t="n">
-        <v>20249</v>
+        <v>20278</v>
       </c>
     </row>
     <row r="487">
@@ -54648,7 +54904,7 @@
         </is>
       </c>
       <c r="L487" s="13" t="n">
-        <v>20249</v>
+        <v>20278</v>
       </c>
     </row>
     <row r="488">
@@ -54708,7 +54964,7 @@
         </is>
       </c>
       <c r="L488" s="13" t="n">
-        <v>15187</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="489">
@@ -54768,7 +55024,7 @@
         </is>
       </c>
       <c r="L489" s="13" t="n">
-        <v>15187</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="490">
@@ -54828,7 +55084,7 @@
         </is>
       </c>
       <c r="L490" s="13" t="n">
-        <v>25073</v>
+        <v>25161</v>
       </c>
     </row>
     <row r="491">
@@ -54888,7 +55144,7 @@
         </is>
       </c>
       <c r="L491" s="13" t="n">
-        <v>21107</v>
+        <v>21181</v>
       </c>
     </row>
     <row r="492">
@@ -54948,7 +55204,7 @@
         </is>
       </c>
       <c r="L492" s="13" t="n">
-        <v>19292</v>
+        <v>19360</v>
       </c>
     </row>
     <row r="493">
@@ -55008,7 +55264,7 @@
         </is>
       </c>
       <c r="L493" s="13" t="n">
-        <v>16334</v>
+        <v>16392</v>
       </c>
     </row>
     <row r="494">
@@ -55068,7 +55324,7 @@
         </is>
       </c>
       <c r="L494" s="13" t="n">
-        <v>23124</v>
+        <v>23205</v>
       </c>
     </row>
     <row r="495">
@@ -55128,7 +55384,7 @@
         </is>
       </c>
       <c r="L495" s="13" t="n">
-        <v>15998</v>
+        <v>16054</v>
       </c>
     </row>
     <row r="496">
@@ -55188,7 +55444,7 @@
         </is>
       </c>
       <c r="L496" s="13" t="n">
-        <v>15124</v>
+        <v>15177</v>
       </c>
     </row>
     <row r="497">
@@ -55248,7 +55504,7 @@
         </is>
       </c>
       <c r="L497" s="13" t="n">
-        <v>9411</v>
+        <v>9444</v>
       </c>
     </row>
     <row r="498">
@@ -55308,7 +55564,7 @@
         </is>
       </c>
       <c r="L498" s="13" t="n">
-        <v>7529</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="499">
@@ -55368,7 +55624,7 @@
         </is>
       </c>
       <c r="L499" s="13" t="n">
-        <v>7529</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="500">
@@ -55428,7 +55684,7 @@
         </is>
       </c>
       <c r="L500" s="13" t="n">
-        <v>12032</v>
+        <v>12075</v>
       </c>
     </row>
     <row r="501">
@@ -55488,7 +55744,7 @@
         </is>
       </c>
       <c r="L501" s="13" t="n">
-        <v>9411</v>
+        <v>9444</v>
       </c>
     </row>
     <row r="502">
@@ -55548,7 +55804,7 @@
         </is>
       </c>
       <c r="L502" s="13" t="n">
-        <v>8940</v>
+        <v>8972</v>
       </c>
     </row>
     <row r="503">
@@ -55608,7 +55864,7 @@
         </is>
       </c>
       <c r="L503" s="13" t="n">
-        <v>7529</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="504">
@@ -55668,7 +55924,7 @@
         </is>
       </c>
       <c r="L504" s="13" t="n">
-        <v>26332</v>
+        <v>26398</v>
       </c>
     </row>
     <row r="505">
@@ -55728,7 +55984,7 @@
         </is>
       </c>
       <c r="L505" s="13" t="n">
-        <v>22167</v>
+        <v>22222</v>
       </c>
     </row>
     <row r="506">
@@ -55788,7 +56044,7 @@
         </is>
       </c>
       <c r="L506" s="13" t="n">
-        <v>20261</v>
+        <v>20311</v>
       </c>
     </row>
     <row r="507">
@@ -55848,7 +56104,7 @@
         </is>
       </c>
       <c r="L507" s="13" t="n">
-        <v>17155</v>
+        <v>17197</v>
       </c>
     </row>
     <row r="508">
@@ -55908,7 +56164,7 @@
         </is>
       </c>
       <c r="L508" s="13" t="n">
-        <v>24285</v>
+        <v>24345</v>
       </c>
     </row>
     <row r="509">
@@ -55968,7 +56224,7 @@
         </is>
       </c>
       <c r="L509" s="13" t="n">
-        <v>16802</v>
+        <v>16844</v>
       </c>
     </row>
     <row r="510">
@@ -56028,7 +56284,7 @@
         </is>
       </c>
       <c r="L510" s="13" t="n">
-        <v>15884</v>
+        <v>15923</v>
       </c>
     </row>
     <row r="511">
@@ -56088,7 +56344,7 @@
         </is>
       </c>
       <c r="L511" s="13" t="n">
-        <v>9883</v>
+        <v>9908</v>
       </c>
     </row>
     <row r="512">
@@ -56148,7 +56404,7 @@
         </is>
       </c>
       <c r="L512" s="13" t="n">
-        <v>7907</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="513">
@@ -56208,7 +56464,7 @@
         </is>
       </c>
       <c r="L513" s="13" t="n">
-        <v>7907</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="514">
@@ -56268,7 +56524,7 @@
         </is>
       </c>
       <c r="L514" s="13" t="n">
-        <v>12637</v>
+        <v>12668</v>
       </c>
     </row>
     <row r="515">
@@ -56328,7 +56584,7 @@
         </is>
       </c>
       <c r="L515" s="13" t="n">
-        <v>9883</v>
+        <v>9908</v>
       </c>
     </row>
     <row r="516">
@@ -56388,7 +56644,7 @@
         </is>
       </c>
       <c r="L516" s="13" t="n">
-        <v>9389</v>
+        <v>9413</v>
       </c>
     </row>
     <row r="517">
@@ -56448,7 +56704,7 @@
         </is>
       </c>
       <c r="L517" s="13" t="n">
-        <v>7907</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="518">
@@ -56508,7 +56764,7 @@
         </is>
       </c>
       <c r="L518" s="13" t="n">
-        <v>27718</v>
+        <v>27758</v>
       </c>
     </row>
     <row r="519">
@@ -56568,7 +56824,7 @@
         </is>
       </c>
       <c r="L519" s="13" t="n">
-        <v>23333</v>
+        <v>23367</v>
       </c>
     </row>
     <row r="520">
@@ -56628,7 +56884,7 @@
         </is>
       </c>
       <c r="L520" s="13" t="n">
-        <v>21327</v>
+        <v>21358</v>
       </c>
     </row>
     <row r="521">
@@ -56688,7 +56944,7 @@
         </is>
       </c>
       <c r="L521" s="13" t="n">
-        <v>18057</v>
+        <v>18084</v>
       </c>
     </row>
     <row r="522">
@@ -56748,7 +57004,7 @@
         </is>
       </c>
       <c r="L522" s="13" t="n">
-        <v>25563</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="523">
@@ -56808,7 +57064,7 @@
         </is>
       </c>
       <c r="L523" s="13" t="n">
-        <v>17686</v>
+        <v>17711</v>
       </c>
     </row>
     <row r="524">
@@ -56868,7 +57124,7 @@
         </is>
       </c>
       <c r="L524" s="13" t="n">
-        <v>16720</v>
+        <v>16744</v>
       </c>
     </row>
     <row r="525">
@@ -56928,7 +57184,7 @@
         </is>
       </c>
       <c r="L525" s="13" t="n">
-        <v>10403</v>
+        <v>10418</v>
       </c>
     </row>
     <row r="526">
@@ -56988,7 +57244,7 @@
         </is>
       </c>
       <c r="L526" s="13" t="n">
-        <v>8323</v>
+        <v>8335</v>
       </c>
     </row>
     <row r="527">
@@ -57048,7 +57304,7 @@
         </is>
       </c>
       <c r="L527" s="13" t="n">
-        <v>8323</v>
+        <v>8335</v>
       </c>
     </row>
     <row r="528">
@@ -57108,7 +57364,7 @@
         </is>
       </c>
       <c r="L528" s="13" t="n">
-        <v>13302</v>
+        <v>13321</v>
       </c>
     </row>
     <row r="529">
@@ -57168,7 +57424,7 @@
         </is>
       </c>
       <c r="L529" s="13" t="n">
-        <v>10403</v>
+        <v>10418</v>
       </c>
     </row>
     <row r="530">
@@ -57228,7 +57484,7 @@
         </is>
       </c>
       <c r="L530" s="13" t="n">
-        <v>9883</v>
+        <v>9898</v>
       </c>
     </row>
     <row r="531">
@@ -57288,7 +57544,7 @@
         </is>
       </c>
       <c r="L531" s="13" t="n">
-        <v>8323</v>
+        <v>8335</v>
       </c>
     </row>
     <row r="532">
@@ -57348,7 +57604,7 @@
         </is>
       </c>
       <c r="L532" s="13" t="n">
-        <v>496083</v>
+        <v>497821</v>
       </c>
     </row>
     <row r="533">
@@ -57408,7 +57664,7 @@
         </is>
       </c>
       <c r="L533" s="13" t="n">
-        <v>521002</v>
+        <v>522290</v>
       </c>
     </row>
     <row r="534">
@@ -57468,7 +57724,7 @@
         </is>
       </c>
       <c r="L534" s="13" t="n">
-        <v>548409</v>
+        <v>549204</v>
       </c>
     </row>
     <row r="535">
@@ -57528,7 +57784,7 @@
         </is>
       </c>
       <c r="L535" s="13" t="n">
-        <v>595300</v>
+        <v>597385</v>
       </c>
     </row>
     <row r="536">
@@ -57588,7 +57844,7 @@
         </is>
       </c>
       <c r="L536" s="13" t="n">
-        <v>625202</v>
+        <v>626748</v>
       </c>
     </row>
     <row r="537">
@@ -57648,7 +57904,7 @@
         </is>
       </c>
       <c r="L537" s="13" t="n">
-        <v>658090</v>
+        <v>659044</v>
       </c>
     </row>
     <row r="538">
@@ -57708,7 +57964,7 @@
         </is>
       </c>
       <c r="L538" s="13" t="n">
-        <v>37610</v>
+        <v>37741</v>
       </c>
     </row>
     <row r="539">
@@ -57768,7 +58024,7 @@
         </is>
       </c>
       <c r="L539" s="13" t="n">
-        <v>31661</v>
+        <v>31771</v>
       </c>
     </row>
     <row r="540">
@@ -57828,7 +58084,7 @@
         </is>
       </c>
       <c r="L540" s="13" t="n">
-        <v>28938</v>
+        <v>29040</v>
       </c>
     </row>
     <row r="541">
@@ -57888,7 +58144,7 @@
         </is>
       </c>
       <c r="L541" s="13" t="n">
-        <v>24502</v>
+        <v>24587</v>
       </c>
     </row>
     <row r="542">
@@ -57948,7 +58204,7 @@
         </is>
       </c>
       <c r="L542" s="13" t="n">
-        <v>34685</v>
+        <v>34807</v>
       </c>
     </row>
     <row r="543">
@@ -58008,7 +58264,7 @@
         </is>
       </c>
       <c r="L543" s="13" t="n">
-        <v>23998</v>
+        <v>24082</v>
       </c>
     </row>
     <row r="544">
@@ -58068,7 +58324,7 @@
         </is>
       </c>
       <c r="L544" s="13" t="n">
-        <v>22687</v>
+        <v>22766</v>
       </c>
     </row>
     <row r="545">
@@ -58128,7 +58384,7 @@
         </is>
       </c>
       <c r="L545" s="13" t="n">
-        <v>14116</v>
+        <v>14166</v>
       </c>
     </row>
     <row r="546">
@@ -58188,7 +58444,7 @@
         </is>
       </c>
       <c r="L546" s="13" t="n">
-        <v>11293</v>
+        <v>11333</v>
       </c>
     </row>
     <row r="547">
@@ -58248,7 +58504,7 @@
         </is>
       </c>
       <c r="L547" s="13" t="n">
-        <v>11293</v>
+        <v>11333</v>
       </c>
     </row>
     <row r="548">
@@ -58308,7 +58564,7 @@
         </is>
       </c>
       <c r="L548" s="13" t="n">
-        <v>18049</v>
+        <v>18112</v>
       </c>
     </row>
     <row r="549">
@@ -58368,7 +58624,7 @@
         </is>
       </c>
       <c r="L549" s="13" t="n">
-        <v>14116</v>
+        <v>14166</v>
       </c>
     </row>
     <row r="550">
@@ -58428,7 +58684,7 @@
         </is>
       </c>
       <c r="L550" s="13" t="n">
-        <v>13410</v>
+        <v>13457</v>
       </c>
     </row>
     <row r="551">
@@ -58488,7 +58744,7 @@
         </is>
       </c>
       <c r="L551" s="13" t="n">
-        <v>11293</v>
+        <v>11333</v>
       </c>
     </row>
     <row r="552">
@@ -58548,7 +58804,7 @@
         </is>
       </c>
       <c r="L552" s="13" t="n">
-        <v>39499</v>
+        <v>39596</v>
       </c>
     </row>
     <row r="553">
@@ -58608,7 +58864,7 @@
         </is>
       </c>
       <c r="L553" s="13" t="n">
-        <v>33251</v>
+        <v>33333</v>
       </c>
     </row>
     <row r="554">
@@ -58668,7 +58924,7 @@
         </is>
       </c>
       <c r="L554" s="13" t="n">
-        <v>30392</v>
+        <v>30467</v>
       </c>
     </row>
     <row r="555">
@@ -58728,7 +58984,7 @@
         </is>
       </c>
       <c r="L555" s="13" t="n">
-        <v>25732</v>
+        <v>25796</v>
       </c>
     </row>
     <row r="556">
@@ -58788,7 +59044,7 @@
         </is>
       </c>
       <c r="L556" s="13" t="n">
-        <v>36428</v>
+        <v>36518</v>
       </c>
     </row>
     <row r="557">
@@ -58848,7 +59104,7 @@
         </is>
       </c>
       <c r="L557" s="13" t="n">
-        <v>25203</v>
+        <v>25265</v>
       </c>
     </row>
     <row r="558">
@@ -58908,7 +59164,7 @@
         </is>
       </c>
       <c r="L558" s="13" t="n">
-        <v>23826</v>
+        <v>23885</v>
       </c>
     </row>
     <row r="559">
@@ -58968,7 +59224,7 @@
         </is>
       </c>
       <c r="L559" s="13" t="n">
-        <v>14825</v>
+        <v>14862</v>
       </c>
     </row>
     <row r="560">
@@ -59028,7 +59284,7 @@
         </is>
       </c>
       <c r="L560" s="13" t="n">
-        <v>11860</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="561">
@@ -59088,7 +59344,7 @@
         </is>
       </c>
       <c r="L561" s="13" t="n">
-        <v>11860</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="562">
@@ -59148,7 +59404,7 @@
         </is>
       </c>
       <c r="L562" s="13" t="n">
-        <v>18955</v>
+        <v>19002</v>
       </c>
     </row>
     <row r="563">
@@ -59208,7 +59464,7 @@
         </is>
       </c>
       <c r="L563" s="13" t="n">
-        <v>14825</v>
+        <v>14862</v>
       </c>
     </row>
     <row r="564">
@@ -59268,7 +59524,7 @@
         </is>
       </c>
       <c r="L564" s="13" t="n">
-        <v>14084</v>
+        <v>14119</v>
       </c>
     </row>
     <row r="565">
@@ -59328,7 +59584,7 @@
         </is>
       </c>
       <c r="L565" s="13" t="n">
-        <v>11860</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="566">
@@ -59388,7 +59644,7 @@
         </is>
       </c>
       <c r="L566" s="13" t="n">
-        <v>41577</v>
+        <v>41637</v>
       </c>
     </row>
     <row r="567">
@@ -59448,7 +59704,7 @@
         </is>
       </c>
       <c r="L567" s="13" t="n">
-        <v>35000</v>
+        <v>35051</v>
       </c>
     </row>
     <row r="568">
@@ -59508,7 +59764,7 @@
         </is>
       </c>
       <c r="L568" s="13" t="n">
-        <v>31991</v>
+        <v>32037</v>
       </c>
     </row>
     <row r="569">
@@ -59568,7 +59824,7 @@
         </is>
       </c>
       <c r="L569" s="13" t="n">
-        <v>27086</v>
+        <v>27125</v>
       </c>
     </row>
     <row r="570">
@@ -59628,7 +59884,7 @@
         </is>
       </c>
       <c r="L570" s="13" t="n">
-        <v>38344</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="571">
@@ -59688,7 +59944,7 @@
         </is>
       </c>
       <c r="L571" s="13" t="n">
-        <v>26529</v>
+        <v>26567</v>
       </c>
     </row>
     <row r="572">
@@ -59748,7 +60004,7 @@
         </is>
       </c>
       <c r="L572" s="13" t="n">
-        <v>25080</v>
+        <v>25116</v>
       </c>
     </row>
     <row r="573">
@@ -59808,7 +60064,7 @@
         </is>
       </c>
       <c r="L573" s="13" t="n">
-        <v>15605</v>
+        <v>15628</v>
       </c>
     </row>
     <row r="574">
@@ -59868,7 +60124,7 @@
         </is>
       </c>
       <c r="L574" s="13" t="n">
-        <v>12484</v>
+        <v>12502</v>
       </c>
     </row>
     <row r="575">
@@ -59928,7 +60184,7 @@
         </is>
       </c>
       <c r="L575" s="13" t="n">
-        <v>12484</v>
+        <v>12502</v>
       </c>
     </row>
     <row r="576">
@@ -59988,7 +60244,7 @@
         </is>
       </c>
       <c r="L576" s="13" t="n">
-        <v>19952</v>
+        <v>19981</v>
       </c>
     </row>
     <row r="577">
@@ -60048,7 +60304,7 @@
         </is>
       </c>
       <c r="L577" s="13" t="n">
-        <v>15605</v>
+        <v>15628</v>
       </c>
     </row>
     <row r="578">
@@ -60108,7 +60364,7 @@
         </is>
       </c>
       <c r="L578" s="13" t="n">
-        <v>14825</v>
+        <v>14846</v>
       </c>
     </row>
     <row r="579">
@@ -60168,7 +60424,7 @@
         </is>
       </c>
       <c r="L579" s="13" t="n">
-        <v>12484</v>
+        <v>12502</v>
       </c>
     </row>
     <row r="580">
@@ -60228,7 +60484,7 @@
         </is>
       </c>
       <c r="L580" s="13" t="n">
-        <v>396867</v>
+        <v>398256</v>
       </c>
     </row>
     <row r="581">
@@ -60288,7 +60544,7 @@
         </is>
       </c>
       <c r="L581" s="13" t="n">
-        <v>416801</v>
+        <v>417832</v>
       </c>
     </row>
     <row r="582">
@@ -60348,7 +60604,7 @@
         </is>
       </c>
       <c r="L582" s="13" t="n">
-        <v>438727</v>
+        <v>439363</v>
       </c>
     </row>
     <row r="583">
@@ -60408,7 +60664,7 @@
         </is>
       </c>
       <c r="L583" s="13" t="n">
-        <v>158747</v>
+        <v>159303</v>
       </c>
     </row>
     <row r="584">
@@ -60468,7 +60724,7 @@
         </is>
       </c>
       <c r="L584" s="13" t="n">
-        <v>166721</v>
+        <v>167133</v>
       </c>
     </row>
     <row r="585">
@@ -60528,7 +60784,7 @@
         </is>
       </c>
       <c r="L585" s="13" t="n">
-        <v>175491</v>
+        <v>175745</v>
       </c>
     </row>
     <row r="586">
@@ -60588,7 +60844,7 @@
         </is>
       </c>
       <c r="L586" s="13" t="n">
-        <v>297650</v>
+        <v>298692</v>
       </c>
     </row>
     <row r="587">
@@ -60648,7 +60904,7 @@
         </is>
       </c>
       <c r="L587" s="13" t="n">
-        <v>312601</v>
+        <v>313374</v>
       </c>
     </row>
     <row r="588">
@@ -60708,7 +60964,7 @@
         </is>
       </c>
       <c r="L588" s="13" t="n">
-        <v>329045</v>
+        <v>329522</v>
       </c>
     </row>
     <row r="589">
@@ -60768,7 +61024,7 @@
         </is>
       </c>
       <c r="L589" s="13" t="n">
-        <v>22896</v>
+        <v>22976</v>
       </c>
     </row>
     <row r="590">
@@ -60828,7 +61084,7 @@
         </is>
       </c>
       <c r="L590" s="13" t="n">
-        <v>19843</v>
+        <v>19913</v>
       </c>
     </row>
     <row r="591">
@@ -60888,7 +61144,7 @@
         </is>
       </c>
       <c r="L591" s="13" t="n">
-        <v>18317</v>
+        <v>18381</v>
       </c>
     </row>
     <row r="592">
@@ -60948,7 +61204,7 @@
         </is>
       </c>
       <c r="L592" s="13" t="n">
-        <v>15264</v>
+        <v>15318</v>
       </c>
     </row>
     <row r="593">
@@ -61008,7 +61264,7 @@
         </is>
       </c>
       <c r="L593" s="13" t="n">
-        <v>21370</v>
+        <v>21445</v>
       </c>
     </row>
     <row r="594">
@@ -61068,7 +61324,7 @@
         </is>
       </c>
       <c r="L594" s="13" t="n">
-        <v>15264</v>
+        <v>15318</v>
       </c>
     </row>
     <row r="595">
@@ -61128,7 +61384,7 @@
         </is>
       </c>
       <c r="L595" s="13" t="n">
-        <v>15264</v>
+        <v>15318</v>
       </c>
     </row>
     <row r="596">
@@ -61188,7 +61444,7 @@
         </is>
       </c>
       <c r="L596" s="13" t="n">
-        <v>9158</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="597">
@@ -61248,7 +61504,7 @@
         </is>
       </c>
       <c r="L597" s="13" t="n">
-        <v>9158</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="598">
@@ -61308,7 +61564,7 @@
         </is>
       </c>
       <c r="L598" s="13" t="n">
-        <v>9158</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="599">
@@ -61368,7 +61624,7 @@
         </is>
       </c>
       <c r="L599" s="13" t="n">
-        <v>12211</v>
+        <v>12254</v>
       </c>
     </row>
     <row r="600">
@@ -61428,7 +61684,7 @@
         </is>
       </c>
       <c r="L600" s="13" t="n">
-        <v>12211</v>
+        <v>12254</v>
       </c>
     </row>
     <row r="601">
@@ -61488,7 +61744,7 @@
         </is>
       </c>
       <c r="L601" s="13" t="n">
-        <v>9158</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="602">
@@ -61548,7 +61804,7 @@
         </is>
       </c>
       <c r="L602" s="13" t="n">
-        <v>9158</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="603">
@@ -61608,7 +61864,7 @@
         </is>
       </c>
       <c r="L603" s="13" t="n">
-        <v>24046</v>
+        <v>24106</v>
       </c>
     </row>
     <row r="604">
@@ -61668,7 +61924,7 @@
         </is>
       </c>
       <c r="L604" s="13" t="n">
-        <v>20840</v>
+        <v>20892</v>
       </c>
     </row>
     <row r="605">
@@ -61728,7 +61984,7 @@
         </is>
       </c>
       <c r="L605" s="13" t="n">
-        <v>19237</v>
+        <v>19285</v>
       </c>
     </row>
     <row r="606">
@@ -61788,7 +62044,7 @@
         </is>
       </c>
       <c r="L606" s="13" t="n">
-        <v>16031</v>
+        <v>16070</v>
       </c>
     </row>
     <row r="607">
@@ -61848,7 +62104,7 @@
         </is>
       </c>
       <c r="L607" s="13" t="n">
-        <v>22443</v>
+        <v>22499</v>
       </c>
     </row>
     <row r="608">
@@ -61908,7 +62164,7 @@
         </is>
       </c>
       <c r="L608" s="13" t="n">
-        <v>16031</v>
+        <v>16070</v>
       </c>
     </row>
     <row r="609">
@@ -61968,7 +62224,7 @@
         </is>
       </c>
       <c r="L609" s="13" t="n">
-        <v>16031</v>
+        <v>16070</v>
       </c>
     </row>
     <row r="610">
@@ -62028,7 +62284,7 @@
         </is>
       </c>
       <c r="L610" s="13" t="n">
-        <v>9618</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="611">
@@ -62088,7 +62344,7 @@
         </is>
       </c>
       <c r="L611" s="13" t="n">
-        <v>9618</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="612">
@@ -62148,7 +62404,7 @@
         </is>
       </c>
       <c r="L612" s="13" t="n">
-        <v>9618</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="613">
@@ -62208,7 +62464,7 @@
         </is>
       </c>
       <c r="L613" s="13" t="n">
-        <v>12825</v>
+        <v>12856</v>
       </c>
     </row>
     <row r="614">
@@ -62268,7 +62524,7 @@
         </is>
       </c>
       <c r="L614" s="13" t="n">
-        <v>12825</v>
+        <v>12856</v>
       </c>
     </row>
     <row r="615">
@@ -62328,7 +62584,7 @@
         </is>
       </c>
       <c r="L615" s="13" t="n">
-        <v>9618</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="616">
@@ -62388,7 +62644,7 @@
         </is>
       </c>
       <c r="L616" s="13" t="n">
-        <v>9618</v>
+        <v>9642</v>
       </c>
     </row>
     <row r="617">
@@ -62448,7 +62704,7 @@
         </is>
       </c>
       <c r="L617" s="13" t="n">
-        <v>25311</v>
+        <v>25348</v>
       </c>
     </row>
     <row r="618">
@@ -62508,7 +62764,7 @@
         </is>
       </c>
       <c r="L618" s="13" t="n">
-        <v>21936</v>
+        <v>21968</v>
       </c>
     </row>
     <row r="619">
@@ -62568,7 +62824,7 @@
         </is>
       </c>
       <c r="L619" s="13" t="n">
-        <v>20249</v>
+        <v>20278</v>
       </c>
     </row>
     <row r="620">
@@ -62628,7 +62884,7 @@
         </is>
       </c>
       <c r="L620" s="13" t="n">
-        <v>16874</v>
+        <v>16899</v>
       </c>
     </row>
     <row r="621">
@@ -62688,7 +62944,7 @@
         </is>
       </c>
       <c r="L621" s="13" t="n">
-        <v>23624</v>
+        <v>23658</v>
       </c>
     </row>
     <row r="622">
@@ -62748,7 +63004,7 @@
         </is>
       </c>
       <c r="L622" s="13" t="n">
-        <v>16874</v>
+        <v>16899</v>
       </c>
     </row>
     <row r="623">
@@ -62808,7 +63064,7 @@
         </is>
       </c>
       <c r="L623" s="13" t="n">
-        <v>16874</v>
+        <v>16899</v>
       </c>
     </row>
     <row r="624">
@@ -62868,7 +63124,7 @@
         </is>
       </c>
       <c r="L624" s="13" t="n">
-        <v>10124</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="625">
@@ -62928,7 +63184,7 @@
         </is>
       </c>
       <c r="L625" s="13" t="n">
-        <v>10124</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="626">
@@ -62988,7 +63244,7 @@
         </is>
       </c>
       <c r="L626" s="13" t="n">
-        <v>10124</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="627">
@@ -63048,7 +63304,7 @@
         </is>
       </c>
       <c r="L627" s="13" t="n">
-        <v>13499</v>
+        <v>13519</v>
       </c>
     </row>
     <row r="628">
@@ -63108,7 +63364,7 @@
         </is>
       </c>
       <c r="L628" s="13" t="n">
-        <v>13499</v>
+        <v>13519</v>
       </c>
     </row>
     <row r="629">
@@ -63168,7 +63424,7 @@
         </is>
       </c>
       <c r="L629" s="13" t="n">
-        <v>10124</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="630">
@@ -63228,7 +63484,7 @@
         </is>
       </c>
       <c r="L630" s="13" t="n">
-        <v>10124</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="631">
@@ -63288,7 +63544,7 @@
         </is>
       </c>
       <c r="L631" s="13" t="n">
-        <v>99217</v>
+        <v>99564</v>
       </c>
     </row>
     <row r="632">
@@ -63348,7 +63604,7 @@
         </is>
       </c>
       <c r="L632" s="13" t="n">
-        <v>104200</v>
+        <v>104458</v>
       </c>
     </row>
     <row r="633">
@@ -63408,7 +63664,7 @@
         </is>
       </c>
       <c r="L633" s="13" t="n">
-        <v>109682</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="634">

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -6608,7 +6608,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Cap stratégique par marque (décision)</t>
+          <t>Cap stratégique — concentre le budget marketing (→ CA construit)</t>
         </is>
       </c>
       <c r="K13" s="4" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>Poids CA réf</t>
+          <t>Budget mkt réf</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>Poids norm.</t>
+          <t>Part budget après cap</t>
         </is>
       </c>
     </row>
@@ -6689,8 +6689,8 @@
           <t>MBway</t>
         </is>
       </c>
-      <c r="K15" s="25" t="n">
-        <v>0.4254</v>
+      <c r="K15" s="15" t="n">
+        <v>166530</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>1</v>
@@ -6732,8 +6732,8 @@
           <t>ISCOM</t>
         </is>
       </c>
-      <c r="K16" s="25" t="n">
-        <v>0.2795</v>
+      <c r="K16" s="15" t="n">
+        <v>108103</v>
       </c>
       <c r="L16" s="18" t="n">
         <v>1</v>
@@ -6775,8 +6775,8 @@
           <t>Ipac Bachelor Factory</t>
         </is>
       </c>
-      <c r="K17" s="25" t="n">
-        <v>0.1131</v>
+      <c r="K17" s="15" t="n">
+        <v>51871</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1</v>
@@ -6818,8 +6818,8 @@
           <t>Pigier</t>
         </is>
       </c>
-      <c r="K18" s="25" t="n">
-        <v>0.09660000000000001</v>
+      <c r="K18" s="15" t="n">
+        <v>58580</v>
       </c>
       <c r="L18" s="18" t="n">
         <v>1</v>
@@ -6861,8 +6861,8 @@
           <t>Tunon</t>
         </is>
       </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0854</v>
+      <c r="K19" s="15" t="n">
+        <v>49090</v>
       </c>
       <c r="L19" s="18" t="n">
         <v>1</v>
@@ -8198,7 +8198,7 @@
       <c r="G77" s="42" t="n"/>
       <c r="H77" s="36" t="n"/>
     </row>
-    <row r="78" ht="30" customHeight="1">
+    <row r="78" ht="42" customHeight="1">
       <c r="B78" s="5" t="inlineStr">
         <is>
           <t>🔵 Cap stratégique</t>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Poids d'arbitrage : concentre ou allège la croissance sur une marque. Jeu à SOMME NULLE — le total groupe ne bouge pas, seule la répartition change.</t>
+          <t>Concentre le BUDGET MARKETING d'acquisition sur une marque, à enveloppe groupe CONSTANTE (somme nulle). Monter le cap d'une marque → plus de budget → plus de leads → son CA CONSTRUIT monte, celui des autres baisse. Cap = 1 partout = aucune redistribution.</t>
         </is>
       </c>
       <c r="D78" s="42" t="n"/>
@@ -14533,7 +14533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -14556,6 +14556,7 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -14673,6 +14674,11 @@
           <t>Leads org. actif</t>
         </is>
       </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>Cap marque</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -14718,7 +14724,7 @@
         <v/>
       </c>
       <c r="K5" s="14">
-        <f>G5*(1+'01_Cadrage'!$H$16)</f>
+        <f>G5*(1+'01_Cadrage'!$H$16)*U5*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L5" s="22">
@@ -14757,6 +14763,10 @@
         <f>D5*(S5/Q5)^R5</f>
         <v/>
       </c>
+      <c r="U5" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A5,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -14802,7 +14812,7 @@
         <v/>
       </c>
       <c r="K6" s="14">
-        <f>G6*(1+'01_Cadrage'!$H$16)</f>
+        <f>G6*(1+'01_Cadrage'!$H$16)*U6*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L6" s="22">
@@ -14841,6 +14851,10 @@
         <f>D6*(S6/Q6)^R6</f>
         <v/>
       </c>
+      <c r="U6" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A6,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
@@ -14886,7 +14900,7 @@
         <v/>
       </c>
       <c r="K7" s="14">
-        <f>G7*(1+'01_Cadrage'!$H$16)</f>
+        <f>G7*(1+'01_Cadrage'!$H$16)*U7*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L7" s="22">
@@ -14925,6 +14939,10 @@
         <f>D7*(S7/Q7)^R7</f>
         <v/>
       </c>
+      <c r="U7" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A7,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -14970,7 +14988,7 @@
         <v/>
       </c>
       <c r="K8" s="14">
-        <f>G8*(1+'01_Cadrage'!$H$16)</f>
+        <f>G8*(1+'01_Cadrage'!$H$16)*U8*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L8" s="22">
@@ -15009,6 +15027,10 @@
         <f>D8*(S8/Q8)^R8</f>
         <v/>
       </c>
+      <c r="U8" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A8,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
@@ -15054,7 +15076,7 @@
         <v/>
       </c>
       <c r="K9" s="14">
-        <f>G9*(1+'01_Cadrage'!$H$16)</f>
+        <f>G9*(1+'01_Cadrage'!$H$16)*U9*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L9" s="22">
@@ -15093,6 +15115,10 @@
         <f>D9*(S9/Q9)^R9</f>
         <v/>
       </c>
+      <c r="U9" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A9,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -15138,7 +15164,7 @@
         <v/>
       </c>
       <c r="K10" s="14">
-        <f>G10*(1+'01_Cadrage'!$H$16)</f>
+        <f>G10*(1+'01_Cadrage'!$H$16)*U10*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L10" s="22">
@@ -15177,6 +15203,10 @@
         <f>D10*(S10/Q10)^R10</f>
         <v/>
       </c>
+      <c r="U10" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A10,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -15222,7 +15252,7 @@
         <v/>
       </c>
       <c r="K11" s="14">
-        <f>G11*(1+'01_Cadrage'!$H$16)</f>
+        <f>G11*(1+'01_Cadrage'!$H$16)*U11*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L11" s="22">
@@ -15261,6 +15291,10 @@
         <f>D11*(S11/Q11)^R11</f>
         <v/>
       </c>
+      <c r="U11" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A11,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -15306,7 +15340,7 @@
         <v/>
       </c>
       <c r="K12" s="14">
-        <f>G12*(1+'01_Cadrage'!$H$16)</f>
+        <f>G12*(1+'01_Cadrage'!$H$16)*U12*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L12" s="22">
@@ -15345,6 +15379,10 @@
         <f>D12*(S12/Q12)^R12</f>
         <v/>
       </c>
+      <c r="U12" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A12,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
@@ -15390,7 +15428,7 @@
         <v/>
       </c>
       <c r="K13" s="14">
-        <f>G13*(1+'01_Cadrage'!$H$16)</f>
+        <f>G13*(1+'01_Cadrage'!$H$16)*U13*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L13" s="22">
@@ -15429,6 +15467,10 @@
         <f>D13*(S13/Q13)^R13</f>
         <v/>
       </c>
+      <c r="U13" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A13,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -15474,7 +15516,7 @@
         <v/>
       </c>
       <c r="K14" s="14">
-        <f>G14*(1+'01_Cadrage'!$H$16)</f>
+        <f>G14*(1+'01_Cadrage'!$H$16)*U14*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L14" s="22">
@@ -15513,6 +15555,10 @@
         <f>D14*(S14/Q14)^R14</f>
         <v/>
       </c>
+      <c r="U14" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A14,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -15558,7 +15604,7 @@
         <v/>
       </c>
       <c r="K15" s="14">
-        <f>G15*(1+'01_Cadrage'!$H$16)</f>
+        <f>G15*(1+'01_Cadrage'!$H$16)*U15*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L15" s="22">
@@ -15597,6 +15643,10 @@
         <f>D15*(S15/Q15)^R15</f>
         <v/>
       </c>
+      <c r="U15" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A15,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -15642,7 +15692,7 @@
         <v/>
       </c>
       <c r="K16" s="14">
-        <f>G16*(1+'01_Cadrage'!$H$16)</f>
+        <f>G16*(1+'01_Cadrage'!$H$16)*U16*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L16" s="22">
@@ -15681,6 +15731,10 @@
         <f>D16*(S16/Q16)^R16</f>
         <v/>
       </c>
+      <c r="U16" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A16,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -15726,7 +15780,7 @@
         <v/>
       </c>
       <c r="K17" s="14">
-        <f>G17*(1+'01_Cadrage'!$H$16)</f>
+        <f>G17*(1+'01_Cadrage'!$H$16)*U17*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L17" s="22">
@@ -15765,6 +15819,10 @@
         <f>D17*(S17/Q17)^R17</f>
         <v/>
       </c>
+      <c r="U17" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A17,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -15810,7 +15868,7 @@
         <v/>
       </c>
       <c r="K18" s="14">
-        <f>G18*(1+'01_Cadrage'!$H$16)</f>
+        <f>G18*(1+'01_Cadrage'!$H$16)*U18*SUM($G$5:$G$18)/SUMPRODUCT($G$5:$G$18,$U$5:$U$18)</f>
         <v/>
       </c>
       <c r="L18" s="22">
@@ -15849,19 +15907,23 @@
         <f>D18*(S18/Q18)^R18</f>
         <v/>
       </c>
+      <c r="U18" s="31">
+        <f>INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A18,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>Indicateur d'attractivité : CAC marginal = coût marketing du prochain inscrit. Vert = investir ici (l'euro rapporte) · Rouge = marché cher/saturé. Colonnes Q-T : le socle ORGANIQUE n'est plus gratuit — il répond au budget de MARQUE (rendement mesuré en agrégé).</t>
+          <t>Indicateur d'attractivité : CAC marginal = coût marketing du prochain inscrit. Vert = investir ici (l'euro rapporte) · Rouge = marché cher/saturé. Colonnes Q-T : le socle ORGANIQUE répond au budget de MARQUE. Colonne U : le cap concentre le budget d'acquisition par marque (enveloppe groupe constante).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A20:T20"/>
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A20:U20"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <conditionalFormatting sqref="P5:P18">
     <cfRule type="colorScale" priority="1">
@@ -16268,7 +16330,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="23">
-        <f>K4*M4*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A4,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K4*M4</f>
         <v/>
       </c>
       <c r="AJ4" s="14">
@@ -16423,7 +16485,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="23">
-        <f>K5*M5*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A5,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K5*M5</f>
         <v/>
       </c>
       <c r="AJ5" s="14">
@@ -16578,7 +16640,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="23">
-        <f>K6*M6*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A6,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K6*M6</f>
         <v/>
       </c>
       <c r="AJ6" s="14">
@@ -16733,7 +16795,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="23">
-        <f>K7*M7*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A7,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K7*M7</f>
         <v/>
       </c>
       <c r="AJ7" s="14">
@@ -16888,7 +16950,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="23">
-        <f>K8*M8*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A8,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K8*M8</f>
         <v/>
       </c>
       <c r="AJ8" s="14">
@@ -17046,7 +17108,7 @@
         <v/>
       </c>
       <c r="AI9" s="23">
-        <f>K9*M9*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A9,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K9*M9</f>
         <v/>
       </c>
       <c r="AJ9" s="14">
@@ -17204,7 +17266,7 @@
         <v/>
       </c>
       <c r="AI10" s="23">
-        <f>K10*M10*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A10,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K10*M10</f>
         <v/>
       </c>
       <c r="AJ10" s="14">
@@ -17362,7 +17424,7 @@
         <v/>
       </c>
       <c r="AI11" s="23">
-        <f>K11*M11*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A11,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K11*M11</f>
         <v/>
       </c>
       <c r="AJ11" s="14">
@@ -17520,7 +17582,7 @@
         <v/>
       </c>
       <c r="AI12" s="23">
-        <f>K12*M12*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A12,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K12*M12</f>
         <v/>
       </c>
       <c r="AJ12" s="14">
@@ -17678,7 +17740,7 @@
         <v/>
       </c>
       <c r="AI13" s="23">
-        <f>K13*M13*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A13,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K13*M13</f>
         <v/>
       </c>
       <c r="AJ13" s="14">
@@ -17833,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="23">
-        <f>K14*M14*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A14,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K14*M14</f>
         <v/>
       </c>
       <c r="AJ14" s="14">
@@ -17988,7 +18050,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="23">
-        <f>K15*M15*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A15,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K15*M15</f>
         <v/>
       </c>
       <c r="AJ15" s="14">
@@ -18143,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="23">
-        <f>K16*M16*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A16,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K16*M16</f>
         <v/>
       </c>
       <c r="AJ16" s="14">
@@ -18298,7 +18360,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="23">
-        <f>K17*M17*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A17,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K17*M17</f>
         <v/>
       </c>
       <c r="AJ17" s="14">
@@ -18453,7 +18515,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="23">
-        <f>K18*M18*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A18,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K18*M18</f>
         <v/>
       </c>
       <c r="AJ18" s="14">
@@ -18608,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="23">
-        <f>K19*M19*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A19,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K19*M19</f>
         <v/>
       </c>
       <c r="AJ19" s="14">
@@ -18763,7 +18825,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="23">
-        <f>K20*M20*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A20,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K20*M20</f>
         <v/>
       </c>
       <c r="AJ20" s="14">
@@ -18918,7 +18980,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="23">
-        <f>K21*M21*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A21,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K21*M21</f>
         <v/>
       </c>
       <c r="AJ21" s="14">
@@ -19073,7 +19135,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="23">
-        <f>K22*M22*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A22,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K22*M22</f>
         <v/>
       </c>
       <c r="AJ22" s="14">
@@ -19228,7 +19290,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="23">
-        <f>K23*M23*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A23,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K23*M23</f>
         <v/>
       </c>
       <c r="AJ23" s="14">
@@ -19383,7 +19445,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="23">
-        <f>K24*M24*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A24,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K24*M24</f>
         <v/>
       </c>
       <c r="AJ24" s="14">
@@ -19538,7 +19600,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="23">
-        <f>K25*M25*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A25,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K25*M25</f>
         <v/>
       </c>
       <c r="AJ25" s="14">
@@ -19693,7 +19755,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="23">
-        <f>K26*M26*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A26,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K26*M26</f>
         <v/>
       </c>
       <c r="AJ26" s="14">
@@ -19848,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="23">
-        <f>K27*M27*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A27,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K27*M27</f>
         <v/>
       </c>
       <c r="AJ27" s="14">
@@ -20003,7 +20065,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="23">
-        <f>K28*M28*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A28,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K28*M28</f>
         <v/>
       </c>
       <c r="AJ28" s="14">
@@ -20158,7 +20220,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="23">
-        <f>K29*M29*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A29,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K29*M29</f>
         <v/>
       </c>
       <c r="AJ29" s="14">
@@ -20313,7 +20375,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="23">
-        <f>K30*M30*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A30,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K30*M30</f>
         <v/>
       </c>
       <c r="AJ30" s="14">
@@ -20468,7 +20530,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="23">
-        <f>K31*M31*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A31,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K31*M31</f>
         <v/>
       </c>
       <c r="AJ31" s="14">
@@ -20623,7 +20685,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="23">
-        <f>K32*M32*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A32,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K32*M32</f>
         <v/>
       </c>
       <c r="AJ32" s="14">
@@ -20778,7 +20840,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="23">
-        <f>K33*M33*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A33,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K33*M33</f>
         <v/>
       </c>
       <c r="AJ33" s="14">
@@ -20933,7 +20995,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="23">
-        <f>K34*M34*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A34,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K34*M34</f>
         <v/>
       </c>
       <c r="AJ34" s="14">
@@ -21088,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="23">
-        <f>K35*M35*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A35,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K35*M35</f>
         <v/>
       </c>
       <c r="AJ35" s="14">
@@ -21243,7 +21305,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="23">
-        <f>K36*M36*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A36,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K36*M36</f>
         <v/>
       </c>
       <c r="AJ36" s="14">
@@ -21398,7 +21460,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="23">
-        <f>K37*M37*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A37,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K37*M37</f>
         <v/>
       </c>
       <c r="AJ37" s="14">
@@ -21553,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="23">
-        <f>K38*M38*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A38,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K38*M38</f>
         <v/>
       </c>
       <c r="AJ38" s="14">
@@ -21708,7 +21770,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="23">
-        <f>K39*M39*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A39,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K39*M39</f>
         <v/>
       </c>
       <c r="AJ39" s="14">
@@ -21863,7 +21925,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="23">
-        <f>K40*M40*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A40,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K40*M40</f>
         <v/>
       </c>
       <c r="AJ40" s="14">
@@ -22018,7 +22080,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="23">
-        <f>K41*M41*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A41,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K41*M41</f>
         <v/>
       </c>
       <c r="AJ41" s="14">
@@ -22173,7 +22235,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="23">
-        <f>K42*M42*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A42,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K42*M42</f>
         <v/>
       </c>
       <c r="AJ42" s="14">
@@ -22328,7 +22390,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="23">
-        <f>K43*M43*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A43,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K43*M43</f>
         <v/>
       </c>
       <c r="AJ43" s="14">
@@ -22483,7 +22545,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="23">
-        <f>K44*M44*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A44,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K44*M44</f>
         <v/>
       </c>
       <c r="AJ44" s="14">
@@ -22638,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="23">
-        <f>K45*M45*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A45,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K45*M45</f>
         <v/>
       </c>
       <c r="AJ45" s="14">
@@ -22793,7 +22855,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="23">
-        <f>K46*M46*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A46,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K46*M46</f>
         <v/>
       </c>
       <c r="AJ46" s="14">
@@ -22948,7 +23010,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="23">
-        <f>K47*M47*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A47,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K47*M47</f>
         <v/>
       </c>
       <c r="AJ47" s="14">
@@ -23103,7 +23165,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="23">
-        <f>K48*M48*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A48,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K48*M48</f>
         <v/>
       </c>
       <c r="AJ48" s="14">
@@ -23258,7 +23320,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="23">
-        <f>K49*M49*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A49,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K49*M49</f>
         <v/>
       </c>
       <c r="AJ49" s="14">
@@ -23413,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="23">
-        <f>K50*M50*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A50,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K50*M50</f>
         <v/>
       </c>
       <c r="AJ50" s="14">
@@ -23568,7 +23630,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="23">
-        <f>K51*M51*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A51,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K51*M51</f>
         <v/>
       </c>
       <c r="AJ51" s="14">
@@ -23723,7 +23785,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="23">
-        <f>K52*M52*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A52,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K52*M52</f>
         <v/>
       </c>
       <c r="AJ52" s="14">
@@ -23878,7 +23940,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="23">
-        <f>K53*M53*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A53,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K53*M53</f>
         <v/>
       </c>
       <c r="AJ53" s="14">
@@ -24033,7 +24095,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="23">
-        <f>K54*M54*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A54,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K54*M54</f>
         <v/>
       </c>
       <c r="AJ54" s="14">
@@ -24188,7 +24250,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="23">
-        <f>K55*M55*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A55,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K55*M55</f>
         <v/>
       </c>
       <c r="AJ55" s="14">
@@ -24343,7 +24405,7 @@
         <v>0</v>
       </c>
       <c r="AI56" s="23">
-        <f>K56*M56*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A56,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K56*M56</f>
         <v/>
       </c>
       <c r="AJ56" s="14">
@@ -24498,7 +24560,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="23">
-        <f>K57*M57*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A57,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K57*M57</f>
         <v/>
       </c>
       <c r="AJ57" s="14">
@@ -24653,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="23">
-        <f>K58*M58*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A58,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K58*M58</f>
         <v/>
       </c>
       <c r="AJ58" s="14">
@@ -24808,7 +24870,7 @@
         <v>0</v>
       </c>
       <c r="AI59" s="23">
-        <f>K59*M59*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A59,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K59*M59</f>
         <v/>
       </c>
       <c r="AJ59" s="14">
@@ -24963,7 +25025,7 @@
         <v>0</v>
       </c>
       <c r="AI60" s="23">
-        <f>K60*M60*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A60,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K60*M60</f>
         <v/>
       </c>
       <c r="AJ60" s="14">
@@ -25118,7 +25180,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="23">
-        <f>K61*M61*INDEX('01_Cadrage'!$L$15:$L$19,MATCH(A61,'01_Cadrage'!$J$15:$J$19,0))</f>
+        <f>K61*M61</f>
         <v/>
       </c>
       <c r="AJ61" s="14">
@@ -25315,7 +25377,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>① CIBLE éclatée : poids (CA réf × cap marque) → CA cible → effectif cible</t>
+          <t>① CIBLE éclatée : poids (CA réf, proportionnel) → CA cible → effectif cible</t>
         </is>
       </c>
     </row>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -1069,7 +1069,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Votre périmètre. Vous n'ajustez que vos TAUX OPÉRATIONNELS (🟢 jaune) — prix, budget marketing et cible sont fixés par le groupe. Vos ajustements s'AJOUTENT au semé (ils ne l'écrasent pas) et remontent au modèle en temps réel.</t>
+          <t>Votre périmètre. « Cadrés (groupe) » = valeurs pré-allouées par le groupe (budget marketing, cible) que vous recevez. Vous n'ajustez que vos TAUX OPÉRATIONNELS (🟢 jaune) — prix, budget marketing et cible sont fixés par le groupe. Vos ajustements s'AJOUTENT au cadré (ils ne l'écrasent pas) et remontent au modèle en temps réel.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Leads semé</t>
+          <t>Leads cadrés (groupe)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Effectif semé ②</t>
+          <t>Effectif cadré ② (groupe)</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P80"/>
+  <dimension ref="B1:P84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6941,7 +6941,7 @@
         <v>0.8100000000000001</v>
       </c>
     </row>
-    <row r="20" ht="40" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Gain conversion admis → inscrit</t>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Caps PROPOSÉS (vert) = suggestions mesurées sur l'historique ; le CFO garde la main via « Cap retenu » (bleu). Seuls les caps RELATIFS comptent (la formule normalise). Éff. = efficience (CAC marginal bas) · Mom. = momentum (croissance leads 24→26) · Pot. = potentiel (sous-investissement marketing).</t>
+          <t>Cap retenu (bleu) = choix CFO · Caps proposés (vert) = Éff./Mom./Pot. mesurés sur l'historique. Détail de chacun dans le Lexique (bas de feuille).</t>
         </is>
       </c>
     </row>
@@ -8275,12 +8275,12 @@
     <row r="78" ht="42" customHeight="1">
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>🔵 Cap stratégique</t>
+          <t>🔵 Cap retenu</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Concentre le BUDGET MARKETING d'acquisition sur une marque, à enveloppe groupe CONSTANTE (somme nulle). Monter le cap d'une marque → plus de budget → plus de leads → son CA CONSTRUIT monte, celui des autres baisse. Cap = 1 partout = aucune redistribution.</t>
+          <t>LE choix du CFO. Concentre le BUDGET MARKETING d'acquisition sur une marque, à enveloppe groupe CONSTANTE (somme nulle). Monter le cap d'une marque → plus de budget → plus de leads → son CA CONSTRUIT monte, celui des autres baisse. Cap = 1 partout = aucune redistribution. Seuls les caps RELATIFS comptent (la formule normalise).</t>
         </is>
       </c>
       <c r="D78" s="43" t="n"/>
@@ -8292,12 +8292,12 @@
     <row r="79" ht="42" customHeight="1">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Indice prix ville</t>
+          <t>🟢 Cap éff. (proposé)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>DÉDUIT du réalisé (prix moyen ville ÷ national). Informationnel : la géographie tarifaire est déjà dans les revenus. Non saisissable (sinon double compte).</t>
+          <t>SUGGESTION mesurée : cap ∝ 1 / CAC marginal. Pousse le budget là où l'euro marketing produit le plus d'inscrits (rendement élevé, CAC bas). Le plus rigoureux — tend vers l'allocation qui égalise le CAC marginal entre marques. Cap &gt; 1 = marque efficace, à renforcer.</t>
         </is>
       </c>
       <c r="D79" s="43" t="n"/>
@@ -8309,12 +8309,12 @@
     <row r="80" ht="42" customHeight="1">
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>🔵 Clés d'allocation</t>
+          <t>🟢 Cap mom. (proposé)</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Le driver de répartition des coûts (CA / effectif / classes), figé par le CFO. Méthode centrale ; les campus ne la choisissent pas, ils contestent l'assiette.</t>
+          <t>SUGGESTION mesurée : cap ∝ taux de croissance des leads 2024→2026. Pousse les marques qui montent déjà. Suit la dynamique commerciale — mais peut sur-investir une marque proche du plafond. Cap &gt; 1 = marque en accélération.</t>
         </is>
       </c>
       <c r="D80" s="43" t="n"/>
@@ -8323,8 +8323,77 @@
       <c r="G80" s="43" t="n"/>
       <c r="H80" s="37" t="n"/>
     </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Cap pot. (proposé)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>SUGGESTION mesurée : cap ∝ 1 / intensité marketing (budget ÷ CA). Pousse les marques SOUS-investies vs leur taille — le potentiel dormant. Plus spéculatif : on parie que la marge de progression existe. Cap &gt; 1 = marque sous-exploitée.</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="n"/>
+      <c r="E81" s="43" t="n"/>
+      <c r="F81" s="43" t="n"/>
+      <c r="G81" s="43" t="n"/>
+      <c r="H81" s="37" t="n"/>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Lire les 3 ensemble</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Le plus instructif est la DIVERGENCE. Ex. une marque avec Éff. et Pot. élevés mais Mom. bas = rentable et sous-exploitée, mais son élan faiblit → au CFO de trancher : je pousse (pari) ou je laisse (prudence) ? Les caps proposés éclairent, ils ne décident pas.</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="n"/>
+      <c r="E82" s="43" t="n"/>
+      <c r="F82" s="43" t="n"/>
+      <c r="G82" s="43" t="n"/>
+      <c r="H82" s="37" t="n"/>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Indice prix ville</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>DÉDUIT du réalisé (prix moyen ville ÷ national). Informationnel : la géographie tarifaire est déjà dans les revenus. Non saisissable (sinon double compte).</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="n"/>
+      <c r="E83" s="43" t="n"/>
+      <c r="F83" s="43" t="n"/>
+      <c r="G83" s="43" t="n"/>
+      <c r="H83" s="37" t="n"/>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>🔵 Clés d'allocation</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Le driver de répartition des coûts (CA / effectif / classes), figé par le CFO. Méthode centrale ; les campus ne la choisissent pas, ils contestent l'assiette.</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="n"/>
+      <c r="E84" s="43" t="n"/>
+      <c r="F84" s="43" t="n"/>
+      <c r="G84" s="43" t="n"/>
+      <c r="H84" s="37" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="38">
+    <mergeCell ref="C84:H84"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="C80:H80"/>
     <mergeCell ref="C75:H75"/>
@@ -8338,9 +8407,11 @@
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="J32:M33"/>
+    <mergeCell ref="C82:H82"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="C72:H72"/>
     <mergeCell ref="J35:K35"/>
+    <mergeCell ref="C81:H81"/>
     <mergeCell ref="L35:M35"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="B5:G5"/>
@@ -8349,6 +8420,7 @@
     <mergeCell ref="J34:M34"/>
     <mergeCell ref="B70:H70"/>
     <mergeCell ref="C78:H78"/>
+    <mergeCell ref="C83:H83"/>
     <mergeCell ref="C77:H77"/>
     <mergeCell ref="J40:M42"/>
     <mergeCell ref="B14:H14"/>
@@ -16069,7 +16141,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MOTEUR DE CA (cellule) — ① CIBLE (éclatée top-down) · ② CADRÉ (semé) · ③ AJUSTÉ (semé + ajustement contrôleur) · écart</t>
+          <t>MOTEUR DE CA (cellule) — ① CIBLE (éclatée top-down) · ② CADRÉ (groupe) · ③ AJUSTÉ (cadré + ajustement contrôleur) · écart</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25500,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>② CADRÉ : le même SANS ajustement (pré-budget semé top-down)</t>
+          <t>② CADRÉ : le même SANS ajustement (pré-budget cadré par le groupe, top-down)</t>
         </is>
       </c>
     </row>
@@ -25440,7 +25512,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>🟢 AJUSTEMENTS contrôleur (Δ lead→cand / Δ yield / Δ passage) — s'ajoutent au semé, n'écrasent rien</t>
+          <t>🟢 AJUSTEMENTS contrôleur (Δ lead→cand / Δ yield / Δ passage) — s'ajoutent au cadré, n'écrasent rien</t>
         </is>
       </c>
     </row>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -6329,7 +6329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P84"/>
+  <dimension ref="B1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6723,14 +6723,17 @@
         <f>IFERROR(K15*L15/SUMPRODUCT($K$15:$K$19,$L$15:$L$19),0)</f>
         <v/>
       </c>
-      <c r="N15" s="26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="O15" s="26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P15" s="26" t="n">
-        <v>1.19</v>
+      <c r="N15" s="26">
+        <f>F92</f>
+        <v/>
+      </c>
+      <c r="O15" s="26">
+        <f>G92</f>
+        <v/>
+      </c>
+      <c r="P15" s="26">
+        <f>H92</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -6775,14 +6778,17 @@
         <f>IFERROR(K16*L16/SUMPRODUCT($K$15:$K$19,$L$15:$L$19),0)</f>
         <v/>
       </c>
-      <c r="N16" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O16" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P16" s="26" t="n">
-        <v>1.21</v>
+      <c r="N16" s="26">
+        <f>F93</f>
+        <v/>
+      </c>
+      <c r="O16" s="26">
+        <f>G93</f>
+        <v/>
+      </c>
+      <c r="P16" s="26">
+        <f>H93</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -6827,14 +6833,17 @@
         <f>IFERROR(K17*L17/SUMPRODUCT($K$15:$K$19,$L$15:$L$19),0)</f>
         <v/>
       </c>
-      <c r="N17" s="26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O17" s="26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P17" s="26" t="n">
-        <v>1.02</v>
+      <c r="N17" s="26">
+        <f>F94</f>
+        <v/>
+      </c>
+      <c r="O17" s="26">
+        <f>G94</f>
+        <v/>
+      </c>
+      <c r="P17" s="26">
+        <f>H94</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -6879,14 +6888,17 @@
         <f>IFERROR(K18*L18/SUMPRODUCT($K$15:$K$19,$L$15:$L$19),0)</f>
         <v/>
       </c>
-      <c r="N18" s="26" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="O18" s="26" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P18" s="26" t="n">
-        <v>0.77</v>
+      <c r="N18" s="26">
+        <f>F95</f>
+        <v/>
+      </c>
+      <c r="O18" s="26">
+        <f>G95</f>
+        <v/>
+      </c>
+      <c r="P18" s="26">
+        <f>H95</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -6931,14 +6943,17 @@
         <f>IFERROR(K19*L19/SUMPRODUCT($K$15:$K$19,$L$15:$L$19),0)</f>
         <v/>
       </c>
-      <c r="N19" s="26" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="O19" s="26" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P19" s="26" t="n">
-        <v>0.8100000000000001</v>
+      <c r="N19" s="26">
+        <f>F96</f>
+        <v/>
+      </c>
+      <c r="O19" s="26">
+        <f>G96</f>
+        <v/>
+      </c>
+      <c r="P19" s="26">
+        <f>H96</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -6970,7 +6985,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Cap retenu (bleu) = choix CFO · Caps proposés (vert) = Éff./Mom./Pot. mesurés sur l'historique. Détail de chacun dans le Lexique (bas de feuille).</t>
+          <t>Cap retenu (bleu) = choix CFO · Caps proposés (vert) = calculés dans « Justification des caps » (bas de feuille) : cliquez un cap pour voir sa formule et ses inputs mesurés.</t>
         </is>
       </c>
     </row>
@@ -8391,8 +8406,228 @@
       <c r="G84" s="43" t="n"/>
       <c r="H84" s="37" t="n"/>
     </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Justification des caps proposés — le calcul, marque par marque (inputs MESURÉS → formule → cap)</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>CAC marginal (mesuré)</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Croiss. leads 24→26</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Intensité mkt (bud÷CA)</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>🟢 Cap éff.</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>🟢 Cap mom.</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>🟢 Cap pot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C92" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B92)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B92))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B92)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B92))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B92)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B92))),0)</f>
+        <v/>
+      </c>
+      <c r="D92" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B92,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B92,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E92" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B92)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B92),0)</f>
+        <v/>
+      </c>
+      <c r="F92" s="26">
+        <f>IFERROR((1/C92)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
+        <v/>
+      </c>
+      <c r="G92" s="26">
+        <f>IFERROR(D92/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
+        <v/>
+      </c>
+      <c r="H92" s="26">
+        <f>IFERROR((1/E92)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C93" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B93)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B93))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B93)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B93))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B93)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B93))),0)</f>
+        <v/>
+      </c>
+      <c r="D93" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B93,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B93,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E93" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B93)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B93),0)</f>
+        <v/>
+      </c>
+      <c r="F93" s="26">
+        <f>IFERROR((1/C93)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
+        <v/>
+      </c>
+      <c r="G93" s="26">
+        <f>IFERROR(D93/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="26">
+        <f>IFERROR((1/E93)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C94" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B94)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B94))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B94)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B94))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B94)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B94))),0)</f>
+        <v/>
+      </c>
+      <c r="D94" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B94,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B94,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E94" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B94)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B94),0)</f>
+        <v/>
+      </c>
+      <c r="F94" s="26">
+        <f>IFERROR((1/C94)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
+        <v/>
+      </c>
+      <c r="G94" s="26">
+        <f>IFERROR(D94/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
+        <v/>
+      </c>
+      <c r="H94" s="26">
+        <f>IFERROR((1/E94)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C95" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B95)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B95))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B95)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B95))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B95)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B95))),0)</f>
+        <v/>
+      </c>
+      <c r="D95" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B95,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B95,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E95" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B95)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B95),0)</f>
+        <v/>
+      </c>
+      <c r="F95" s="26">
+        <f>IFERROR((1/C95)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
+        <v/>
+      </c>
+      <c r="G95" s="26">
+        <f>IFERROR(D95/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
+        <v/>
+      </c>
+      <c r="H95" s="26">
+        <f>IFERROR((1/E95)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="C96" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B96)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B96))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B96)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B96))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B96)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B96))),0)</f>
+        <v/>
+      </c>
+      <c r="D96" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B96,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B96,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E96" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B96)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B96),0)</f>
+        <v/>
+      </c>
+      <c r="F96" s="26">
+        <f>IFERROR((1/C96)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
+        <v/>
+      </c>
+      <c r="G96" s="26">
+        <f>IFERROR(D96/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
+        <v/>
+      </c>
+      <c r="H96" s="26">
+        <f>IFERROR((1/E96)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Formules : CAC marginal = CPL ÷ (rendement × conversion) ; Cap éff. = (1÷CAC) ÷ moyenne(1÷CAC) · Cap mom. = croissance ÷ moyenne(croissance) · Cap pot. = (1÷intensité) ÷ moyenne(1÷intensité). Normalisés à moyenne 1 (seul le relatif compte).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Sources (100 % mesuré, rien de saisi) : CAC marginal, rendement &amp; budget = 03_Campagnes (mesurés sur le CRM) · croissance des leads = 02_CRM (2024→2026) · CA &amp; effectif = 02_Base. Le cap du bloc en haut = ces cellules (drill).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="41">
+    <mergeCell ref="B99:H99"/>
     <mergeCell ref="C84:H84"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="C80:H80"/>
@@ -8404,6 +8639,7 @@
     <mergeCell ref="C71:H71"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="C76:H76"/>
+    <mergeCell ref="B90:H90"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="J32:M33"/>
@@ -8421,6 +8657,7 @@
     <mergeCell ref="B70:H70"/>
     <mergeCell ref="C78:H78"/>
     <mergeCell ref="C83:H83"/>
+    <mergeCell ref="B98:H98"/>
     <mergeCell ref="C77:H77"/>
     <mergeCell ref="J40:M42"/>
     <mergeCell ref="B14:H14"/>

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -6335,7 +6335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P99"/>
+  <dimension ref="B1:P137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6735,15 +6735,15 @@
         <v/>
       </c>
       <c r="N15" s="26">
-        <f>F92</f>
+        <f>F130</f>
         <v/>
       </c>
       <c r="O15" s="26">
-        <f>G92</f>
+        <f>G130</f>
         <v/>
       </c>
       <c r="P15" s="26">
-        <f>H92</f>
+        <f>H130</f>
         <v/>
       </c>
     </row>
@@ -6790,15 +6790,15 @@
         <v/>
       </c>
       <c r="N16" s="26">
-        <f>F93</f>
+        <f>F131</f>
         <v/>
       </c>
       <c r="O16" s="26">
-        <f>G93</f>
+        <f>G131</f>
         <v/>
       </c>
       <c r="P16" s="26">
-        <f>H93</f>
+        <f>H131</f>
         <v/>
       </c>
     </row>
@@ -6845,15 +6845,15 @@
         <v/>
       </c>
       <c r="N17" s="26">
-        <f>F94</f>
+        <f>F132</f>
         <v/>
       </c>
       <c r="O17" s="26">
-        <f>G94</f>
+        <f>G132</f>
         <v/>
       </c>
       <c r="P17" s="26">
-        <f>H94</f>
+        <f>H132</f>
         <v/>
       </c>
     </row>
@@ -6900,15 +6900,15 @@
         <v/>
       </c>
       <c r="N18" s="26">
-        <f>F95</f>
+        <f>F133</f>
         <v/>
       </c>
       <c r="O18" s="26">
-        <f>G95</f>
+        <f>G133</f>
         <v/>
       </c>
       <c r="P18" s="26">
-        <f>H95</f>
+        <f>H133</f>
         <v/>
       </c>
     </row>
@@ -6955,15 +6955,15 @@
         <v/>
       </c>
       <c r="N19" s="26">
-        <f>F96</f>
+        <f>F134</f>
         <v/>
       </c>
       <c r="O19" s="26">
-        <f>G96</f>
+        <f>G134</f>
         <v/>
       </c>
       <c r="P19" s="26">
-        <f>H96</f>
+        <f>H134</f>
         <v/>
       </c>
     </row>
@@ -7197,10 +7197,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>Leviers 1-6 → CA (moteur) · leviers 7-10 → coûts (P&amp;L Budget → EBITDA). Acquisition = achat de leads (payant) · Marque = notoriété (socle organique). « Référence » remet tout à 0 = atterrissage.</t>
-        </is>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Variation des coûts de structure (loyers, IT, siège…)</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G26" s="30" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H26" s="31">
+        <f>INDEX(D26:G26,MATCH($D$3,$D$15:$G$15,0))</f>
+        <v/>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
@@ -7214,18 +7235,12 @@
         <v>0.969</v>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>③ Constante — frais de dossier (décision)</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
+    <row r="27">
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>Leviers 1-6 → CA (moteur) · leviers 7-11 → coûts (P&amp;L Budget → EBITDA). Acquisition = achat de leads (payant) · Marque = notoriété (socle organique). « Référence » remet tout à 0 = atterrissage.</t>
+        </is>
+      </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
           <t>Toulouse</t>
@@ -7238,42 +7253,18 @@
         <v>0.949</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Paramètre</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Unité</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Cadrage</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>Optimiste</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>Prudent</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>ACTIF</t>
-        </is>
-      </c>
+    <row r="28" ht="20" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>③ Constante — frais de dossier (décision)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
       <c r="J28" s="17" t="inlineStr">
         <is>
           <t>Bordeaux</t>
@@ -7287,31 +7278,40 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Frais de dossier / nouvel inscrit</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>€</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="n">
-        <v>90</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="F29" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>90</v>
-      </c>
-      <c r="H29" s="36">
-        <f>INDEX(D29:G29,MATCH($D$3,$D$15:$G$15,0))</f>
-        <v/>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Paramètre</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Référence</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Cadrage</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Optimiste</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Prudent</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>ACTIF</t>
+        </is>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
@@ -7326,6 +7326,32 @@
       </c>
     </row>
     <row r="30">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Frais de dossier / nouvel inscrit</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>90</v>
+      </c>
+      <c r="E30" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="F30" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="H30" s="36">
+        <f>INDEX(D30:G30,MATCH($D$3,$D$15:$G$15,0))</f>
+        <v/>
+      </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
           <t>Montpellier</t>
@@ -7338,14 +7364,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="33" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Rendement, CPL, part organique et rendement de marque ne sont pas saisis : ils sont MESURÉS depuis le CRM (voir 03_Campagnes).</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
       <c r="J32" s="33" t="inlineStr">
         <is>
           <t>Indice = prix moyen ville ÷ national, calculé sur le réalisé (le niveau de prix par ville est déjà dans les revenus). Le pouvoir de prix se pilote par MARQUE ci-dessus.</t>
@@ -8169,7 +8193,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Lexique — que veut dire chaque colonne / paramètre ?</t>
+          <t>⑥ EBITDA par marque / campus — réparti selon les CLÉS d'allocation (atterrissage ; changez une clé → l'EBITDA se redéploie)</t>
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
@@ -8179,507 +8203,1067 @@
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="4" t="n"/>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>CA référence</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Le CA de l'atterrissage 2026, marque/campus (base réelle). C'est le point de départ : leviers à 0 → le construit revient dessus.</t>
-        </is>
-      </c>
-      <c r="D71" s="43" t="n"/>
-      <c r="E71" s="43" t="n"/>
-      <c r="F71" s="43" t="n"/>
-      <c r="G71" s="43" t="n"/>
-      <c r="H71" s="37" t="n"/>
-    </row>
-    <row r="72" ht="42" customHeight="1">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>🎯 CA cible</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>La part du CA cible du GROUPE (réf × croissance) attribuée à cette marque/campus par l'ÉCLATEMENT top-down : poids = CA réf × cap stratégique, normalisé. La somme des cibles = exactement l'objectif groupe.</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="n"/>
-      <c r="E72" s="43" t="n"/>
-      <c r="F72" s="43" t="n"/>
-      <c r="G72" s="43" t="n"/>
-      <c r="H72" s="37" t="n"/>
-    </row>
-    <row r="73" ht="42" customHeight="1">
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>🔧 CA construit</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Ce que le moteur RECONSTRUIT réellement du bas vers le haut (budget marketing → leads → funnel → effectif → CA), après leviers et ajustements des contrôleurs. C'est le budget réel.</t>
-        </is>
-      </c>
-      <c r="D73" s="43" t="n"/>
-      <c r="E73" s="43" t="n"/>
-      <c r="F73" s="43" t="n"/>
-      <c r="G73" s="43" t="n"/>
-      <c r="H73" s="37" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Construit − Cible. Positif = la marque/campus dépasse sa cible ; négatif = il reste à trouver. C'est là que le CFO voit qui tient la promesse.</t>
-        </is>
-      </c>
-      <c r="D74" s="43" t="n"/>
-      <c r="E74" s="43" t="n"/>
-      <c r="F74" s="43" t="n"/>
-      <c r="G74" s="43" t="n"/>
-      <c r="H74" s="37" t="n"/>
-    </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Croissance</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Construit ÷ Référence − 1 : la progression réelle vs l'atterrissage. La couleur (rouge→vert) montre d'un coup d'œil où le cadrage crée ou détruit de la croissance.</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="n"/>
-      <c r="E75" s="43" t="n"/>
-      <c r="F75" s="43" t="n"/>
-      <c r="G75" s="43" t="n"/>
-      <c r="H75" s="37" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Effectif constr.</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>L'effectif qui découle du CA construit (conséquence, jamais saisi). Utile pour vérifier la faisabilité opérationnelle (salles, classes).</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="n"/>
-      <c r="E76" s="43" t="n"/>
-      <c r="F76" s="43" t="n"/>
-      <c r="G76" s="43" t="n"/>
-      <c r="H76" s="37" t="n"/>
-    </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>🔵 Coeff prix (marque)</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Sensibilité de la marque à une décision de prix : prix appliqué = prix réf × (1 + levier prix × coeff + override campus). Décision au niveau MARQUE ; l'écart de prix entre villes est déjà déduit dans la base. Un override par CAMPUS (03_Campagnes) gère les exceptions locales sans double compte.</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="n"/>
-      <c r="E77" s="43" t="n"/>
-      <c r="F77" s="43" t="n"/>
-      <c r="G77" s="43" t="n"/>
-      <c r="H77" s="37" t="n"/>
-    </row>
-    <row r="78" ht="42" customHeight="1">
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>🔵 Cap retenu</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>LE choix du CFO. Concentre le BUDGET MARKETING d'acquisition, à enveloppe groupe CONSTANTE (somme nulle). Saisi au niveau MARQUE (cascade sur ses campus) ; override par CAMPUS (marque×ville) dans 03_Campagnes → cap effectif = marque × override. Monter le cap → plus de budget → plus de leads → CA CONSTRUIT en hausse (baisse ailleurs). Cap = 1 partout = aucune redistribution ; seuls les caps RELATIFS comptent.</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="n"/>
-      <c r="E78" s="43" t="n"/>
-      <c r="F78" s="43" t="n"/>
-      <c r="G78" s="43" t="n"/>
-      <c r="H78" s="37" t="n"/>
-    </row>
-    <row r="79" ht="42" customHeight="1">
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>🟢 Cap éff. (proposé)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>SUGGESTION mesurée : cap ∝ 1 / CAC marginal. Pousse le budget là où l'euro marketing produit le plus d'inscrits (rendement élevé, CAC bas). Le plus rigoureux — tend vers l'allocation qui égalise le CAC marginal entre marques. Cap &gt; 1 = marque efficace, à renforcer.</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="n"/>
-      <c r="E79" s="43" t="n"/>
-      <c r="F79" s="43" t="n"/>
-      <c r="G79" s="43" t="n"/>
-      <c r="H79" s="37" t="n"/>
-    </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>🟢 Cap mom. (proposé)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>SUGGESTION mesurée : cap ∝ taux de croissance des leads 2024→2026. Pousse les marques qui montent déjà. Suit la dynamique commerciale — mais peut sur-investir une marque proche du plafond. Cap &gt; 1 = marque en accélération.</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="n"/>
-      <c r="E80" s="43" t="n"/>
-      <c r="F80" s="43" t="n"/>
-      <c r="G80" s="43" t="n"/>
-      <c r="H80" s="37" t="n"/>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>🟢 Cap pot. (proposé)</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>SUGGESTION mesurée : cap ∝ 1 / intensité marketing (budget ÷ CA). Pousse les marques SOUS-investies vs leur taille — le potentiel dormant. Plus spéculatif : on parie que la marge de progression existe. Cap &gt; 1 = marque sous-exploitée.</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="n"/>
-      <c r="E81" s="43" t="n"/>
-      <c r="F81" s="43" t="n"/>
-      <c r="G81" s="43" t="n"/>
-      <c r="H81" s="37" t="n"/>
-    </row>
-    <row r="82" ht="42" customHeight="1">
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>Lire les 3 ensemble</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Le plus instructif est la DIVERGENCE. Ex. une marque avec Éff. et Pot. élevés mais Mom. bas = rentable et sous-exploitée, mais son élan faiblit → au CFO de trancher : je pousse (pari) ou je laisse (prudence) ? Les caps proposés éclairent, ils ne décident pas.</t>
-        </is>
-      </c>
-      <c r="D82" s="43" t="n"/>
-      <c r="E82" s="43" t="n"/>
-      <c r="F82" s="43" t="n"/>
-      <c r="G82" s="43" t="n"/>
-      <c r="H82" s="37" t="n"/>
-    </row>
-    <row r="83" ht="42" customHeight="1">
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Indice prix ville</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>DÉDUIT du réalisé (prix moyen ville ÷ national). Informationnel : la géographie tarifaire est déjà dans les revenus. Non saisissable (sinon double compte).</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="n"/>
-      <c r="E83" s="43" t="n"/>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="43" t="n"/>
-      <c r="H83" s="37" t="n"/>
-    </row>
-    <row r="84" ht="42" customHeight="1">
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>🔵 Clés d'allocation</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Le driver de répartition des coûts (CA / effectif / classes), figé par le CFO. Méthode centrale ; les campus ne la choisissent pas, ils contestent l'assiette.</t>
-        </is>
-      </c>
-      <c r="D84" s="43" t="n"/>
-      <c r="E84" s="43" t="n"/>
-      <c r="F84" s="43" t="n"/>
-      <c r="G84" s="43" t="n"/>
-      <c r="H84" s="37" t="n"/>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Justification des caps proposés — le calcul, marque par marque (inputs MESURÉS → formule → cap)</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="n"/>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>Marque</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>CAC marginal (mesuré)</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>Croiss. leads 24→26</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>Intensité mkt (bud÷CA)</t>
-        </is>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Cap éff.</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Cap mom.</t>
-        </is>
-      </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Cap pot.</t>
-        </is>
+    <row r="71" ht="22" customHeight="1">
+      <c r="B71" s="38" t="inlineStr">
+        <is>
+          <t>Par marque</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>CA réf</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Coût alloué</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>Marge %</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C72" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"MBway")</f>
+        <v/>
+      </c>
+      <c r="D72" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"MBway")</f>
+        <v/>
+      </c>
+      <c r="E72" s="14">
+        <f>C72-D72</f>
+        <v/>
+      </c>
+      <c r="F72" s="25">
+        <f>IFERROR(E72/C72,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C73" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"ISCOM")</f>
+        <v/>
+      </c>
+      <c r="D73" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"ISCOM")</f>
+        <v/>
+      </c>
+      <c r="E73" s="14">
+        <f>C73-D73</f>
+        <v/>
+      </c>
+      <c r="F73" s="25">
+        <f>IFERROR(E73/C73,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C74" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory")</f>
+        <v/>
+      </c>
+      <c r="D74" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory")</f>
+        <v/>
+      </c>
+      <c r="E74" s="14">
+        <f>C74-D74</f>
+        <v/>
+      </c>
+      <c r="F74" s="25">
+        <f>IFERROR(E74/C74,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C75" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Pigier")</f>
+        <v/>
+      </c>
+      <c r="D75" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Pigier")</f>
+        <v/>
+      </c>
+      <c r="E75" s="14">
+        <f>C75-D75</f>
+        <v/>
+      </c>
+      <c r="F75" s="25">
+        <f>IFERROR(E75/C75,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="C76" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Tunon")</f>
+        <v/>
+      </c>
+      <c r="D76" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Tunon")</f>
+        <v/>
+      </c>
+      <c r="E76" s="14">
+        <f>C76-D76</f>
+        <v/>
+      </c>
+      <c r="F76" s="25">
+        <f>IFERROR(E76/C76,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL GROUPE</t>
+        </is>
+      </c>
+      <c r="C77" s="40">
+        <f>SUM(C72:C76)</f>
+        <v/>
+      </c>
+      <c r="D77" s="40">
+        <f>SUM(D72:D76)</f>
+        <v/>
+      </c>
+      <c r="E77" s="40">
+        <f>SUM(E72:E76)</f>
+        <v/>
+      </c>
+      <c r="F77" s="41">
+        <f>IFERROR(E77/C77,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="B78" s="38" t="inlineStr">
+        <is>
+          <t>Par campus (marque — ville)</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>CA réf</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>Coût alloué</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>Marge %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>MBway — Paris</t>
+        </is>
+      </c>
+      <c r="C79" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Paris")</f>
+        <v/>
+      </c>
+      <c r="D79" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Paris")</f>
+        <v/>
+      </c>
+      <c r="E79" s="14">
+        <f>C79-D79</f>
+        <v/>
+      </c>
+      <c r="F79" s="25">
+        <f>IFERROR(E79/C79,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>MBway — Lyon</t>
+        </is>
+      </c>
+      <c r="C80" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Lyon")</f>
+        <v/>
+      </c>
+      <c r="D80" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Lyon")</f>
+        <v/>
+      </c>
+      <c r="E80" s="14">
+        <f>C80-D80</f>
+        <v/>
+      </c>
+      <c r="F80" s="25">
+        <f>IFERROR(E80/C80,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>MBway — Nantes</t>
+        </is>
+      </c>
+      <c r="C81" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Nantes")</f>
+        <v/>
+      </c>
+      <c r="D81" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Nantes")</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>C81-D81</f>
+        <v/>
+      </c>
+      <c r="F81" s="25">
+        <f>IFERROR(E81/C81,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>MBway — Bordeaux</t>
+        </is>
+      </c>
+      <c r="C82" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Bordeaux")</f>
+        <v/>
+      </c>
+      <c r="D82" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"MBway",'10_Allocation'!$B$8:$B$65,"Bordeaux")</f>
+        <v/>
+      </c>
+      <c r="E82" s="14">
+        <f>C82-D82</f>
+        <v/>
+      </c>
+      <c r="F82" s="25">
+        <f>IFERROR(E82/C82,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM — Paris</t>
+        </is>
+      </c>
+      <c r="C83" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"ISCOM",'10_Allocation'!$B$8:$B$65,"Paris")</f>
+        <v/>
+      </c>
+      <c r="D83" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"ISCOM",'10_Allocation'!$B$8:$B$65,"Paris")</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>C83-D83</f>
+        <v/>
+      </c>
+      <c r="F83" s="25">
+        <f>IFERROR(E83/C83,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM — Lille</t>
+        </is>
+      </c>
+      <c r="C84" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"ISCOM",'10_Allocation'!$B$8:$B$65,"Lille")</f>
+        <v/>
+      </c>
+      <c r="D84" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"ISCOM",'10_Allocation'!$B$8:$B$65,"Lille")</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>C84-D84</f>
+        <v/>
+      </c>
+      <c r="F84" s="25">
+        <f>IFERROR(E84/C84,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>ISCOM — Toulouse</t>
+        </is>
+      </c>
+      <c r="C85" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"ISCOM",'10_Allocation'!$B$8:$B$65,"Toulouse")</f>
+        <v/>
+      </c>
+      <c r="D85" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"ISCOM",'10_Allocation'!$B$8:$B$65,"Toulouse")</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>C85-D85</f>
+        <v/>
+      </c>
+      <c r="F85" s="25">
+        <f>IFERROR(E85/C85,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory — Nantes</t>
+        </is>
+      </c>
+      <c r="C86" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory",'10_Allocation'!$B$8:$B$65,"Nantes")</f>
+        <v/>
+      </c>
+      <c r="D86" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory",'10_Allocation'!$B$8:$B$65,"Nantes")</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>C86-D86</f>
+        <v/>
+      </c>
+      <c r="F86" s="25">
+        <f>IFERROR(E86/C86,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory — Rennes</t>
+        </is>
+      </c>
+      <c r="C87" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory",'10_Allocation'!$B$8:$B$65,"Rennes")</f>
+        <v/>
+      </c>
+      <c r="D87" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory",'10_Allocation'!$B$8:$B$65,"Rennes")</f>
+        <v/>
+      </c>
+      <c r="E87" s="14">
+        <f>C87-D87</f>
+        <v/>
+      </c>
+      <c r="F87" s="25">
+        <f>IFERROR(E87/C87,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory — Montpellier</t>
+        </is>
+      </c>
+      <c r="C88" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory",'10_Allocation'!$B$8:$B$65,"Montpellier")</f>
+        <v/>
+      </c>
+      <c r="D88" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Ipac Bachelor Factory",'10_Allocation'!$B$8:$B$65,"Montpellier")</f>
+        <v/>
+      </c>
+      <c r="E88" s="14">
+        <f>C88-D88</f>
+        <v/>
+      </c>
+      <c r="F88" s="25">
+        <f>IFERROR(E88/C88,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Pigier — Lyon</t>
+        </is>
+      </c>
+      <c r="C89" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Pigier",'10_Allocation'!$B$8:$B$65,"Lyon")</f>
+        <v/>
+      </c>
+      <c r="D89" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Pigier",'10_Allocation'!$B$8:$B$65,"Lyon")</f>
+        <v/>
+      </c>
+      <c r="E89" s="14">
+        <f>C89-D89</f>
+        <v/>
+      </c>
+      <c r="F89" s="25">
+        <f>IFERROR(E89/C89,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Pigier — Bordeaux</t>
+        </is>
+      </c>
+      <c r="C90" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Pigier",'10_Allocation'!$B$8:$B$65,"Bordeaux")</f>
+        <v/>
+      </c>
+      <c r="D90" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Pigier",'10_Allocation'!$B$8:$B$65,"Bordeaux")</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>C90-D90</f>
+        <v/>
+      </c>
+      <c r="F90" s="25">
+        <f>IFERROR(E90/C90,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Tunon — Paris</t>
+        </is>
+      </c>
+      <c r="C91" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Tunon",'10_Allocation'!$B$8:$B$65,"Paris")</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Tunon",'10_Allocation'!$B$8:$B$65,"Paris")</f>
+        <v/>
+      </c>
+      <c r="E91" s="14">
+        <f>C91-D91</f>
+        <v/>
+      </c>
+      <c r="F91" s="25">
+        <f>IFERROR(E91/C91,0)</f>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="17" t="inlineStr">
         <is>
+          <t>Tunon — Lyon</t>
+        </is>
+      </c>
+      <c r="C92" s="15">
+        <f>SUMIFS('10_Allocation'!$F$8:$F$65,'10_Allocation'!$A$8:$A$65,"Tunon",'10_Allocation'!$B$8:$B$65,"Lyon")</f>
+        <v/>
+      </c>
+      <c r="D92" s="15">
+        <f>SUMIFS('10_Allocation'!$L$8:$L$65,'10_Allocation'!$A$8:$A$65,"Tunon",'10_Allocation'!$B$8:$B$65,"Lyon")</f>
+        <v/>
+      </c>
+      <c r="E92" s="14">
+        <f>C92-D92</f>
+        <v/>
+      </c>
+      <c r="F92" s="25">
+        <f>IFERROR(E92/C92,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL GROUPE</t>
+        </is>
+      </c>
+      <c r="C93" s="40">
+        <f>SUM(C79:C92)</f>
+        <v/>
+      </c>
+      <c r="D93" s="40">
+        <f>SUM(D79:D92)</f>
+        <v/>
+      </c>
+      <c r="E93" s="40">
+        <f>SUM(E79:E92)</f>
+        <v/>
+      </c>
+      <c r="F93" s="41">
+        <f>IFERROR(E93/C93,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA = CA − coût pleinement alloué (directs + siège cascadé + structure), selon les 3 clés du bloc « Clés d'allocation ». Clé Groupe→Marque : déplace l'EBITDA entre marques · Marque→Campus : entre campus · Campus→Classe : visible dans 10_Allocation. Total groupe constant (somme nulle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95"/>
+    <row r="98" ht="20" customHeight="1">
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Lexique — que veut dire chaque colonne / paramètre ?</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>CA référence</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Le CA de l'atterrissage 2026, marque/campus (base réelle). C'est le point de départ : leviers à 0 → le construit revient dessus.</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="n"/>
+      <c r="E99" s="43" t="n"/>
+      <c r="F99" s="43" t="n"/>
+      <c r="G99" s="43" t="n"/>
+      <c r="H99" s="37" t="n"/>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>🎯 CA cible</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>La part du CA cible du GROUPE (réf × croissance) attribuée à cette marque/campus par l'ÉCLATEMENT top-down : poids = CA réf × cap stratégique, normalisé. La somme des cibles = exactement l'objectif groupe.</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="n"/>
+      <c r="E100" s="43" t="n"/>
+      <c r="F100" s="43" t="n"/>
+      <c r="G100" s="43" t="n"/>
+      <c r="H100" s="37" t="n"/>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>🔧 CA construit</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Ce que le moteur RECONSTRUIT réellement du bas vers le haut (budget marketing → leads → funnel → effectif → CA), après leviers et ajustements des contrôleurs. C'est le budget réel.</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="n"/>
+      <c r="E101" s="43" t="n"/>
+      <c r="F101" s="43" t="n"/>
+      <c r="G101" s="43" t="n"/>
+      <c r="H101" s="37" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Construit − Cible. Positif = la marque/campus dépasse sa cible ; négatif = il reste à trouver. C'est là que le CFO voit qui tient la promesse.</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="n"/>
+      <c r="E102" s="43" t="n"/>
+      <c r="F102" s="43" t="n"/>
+      <c r="G102" s="43" t="n"/>
+      <c r="H102" s="37" t="n"/>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Croissance</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Construit ÷ Référence − 1 : la progression réelle vs l'atterrissage. La couleur (rouge→vert) montre d'un coup d'œil où le cadrage crée ou détruit de la croissance.</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="n"/>
+      <c r="E103" s="43" t="n"/>
+      <c r="F103" s="43" t="n"/>
+      <c r="G103" s="43" t="n"/>
+      <c r="H103" s="37" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Effectif constr.</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>L'effectif qui découle du CA construit (conséquence, jamais saisi). Utile pour vérifier la faisabilité opérationnelle (salles, classes).</t>
+        </is>
+      </c>
+      <c r="D104" s="43" t="n"/>
+      <c r="E104" s="43" t="n"/>
+      <c r="F104" s="43" t="n"/>
+      <c r="G104" s="43" t="n"/>
+      <c r="H104" s="37" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>🔵 Coeff prix (marque)</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Sensibilité de la marque à une décision de prix : prix appliqué = prix réf × (1 + levier prix × coeff + override campus). Décision au niveau MARQUE ; l'écart de prix entre villes est déjà déduit dans la base. Un override par CAMPUS (03_Campagnes) gère les exceptions locales sans double compte.</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="n"/>
+      <c r="E105" s="43" t="n"/>
+      <c r="F105" s="43" t="n"/>
+      <c r="G105" s="43" t="n"/>
+      <c r="H105" s="37" t="n"/>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>🔵 Cap retenu</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>LE choix du CFO. Concentre le BUDGET MARKETING d'acquisition, à enveloppe groupe CONSTANTE (somme nulle). Saisi au niveau MARQUE (cascade sur ses campus) ; override par CAMPUS (marque×ville) dans 03_Campagnes → cap effectif = marque × override. Monter le cap → plus de budget → plus de leads → CA CONSTRUIT en hausse (baisse ailleurs). Cap = 1 partout = aucune redistribution ; seuls les caps RELATIFS comptent.</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="n"/>
+      <c r="E106" s="43" t="n"/>
+      <c r="F106" s="43" t="n"/>
+      <c r="G106" s="43" t="n"/>
+      <c r="H106" s="37" t="n"/>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Cap éff. (proposé)</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>SUGGESTION mesurée : cap ∝ 1 / CAC marginal. Pousse le budget là où l'euro marketing produit le plus d'inscrits (rendement élevé, CAC bas). Le plus rigoureux — tend vers l'allocation qui égalise le CAC marginal entre marques. Cap &gt; 1 = marque efficace, à renforcer.</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="n"/>
+      <c r="E107" s="43" t="n"/>
+      <c r="F107" s="43" t="n"/>
+      <c r="G107" s="43" t="n"/>
+      <c r="H107" s="37" t="n"/>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Cap mom. (proposé)</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>SUGGESTION mesurée : cap ∝ taux de croissance des leads 2024→2026. Pousse les marques qui montent déjà. Suit la dynamique commerciale — mais peut sur-investir une marque proche du plafond. Cap &gt; 1 = marque en accélération.</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="n"/>
+      <c r="E108" s="43" t="n"/>
+      <c r="F108" s="43" t="n"/>
+      <c r="G108" s="43" t="n"/>
+      <c r="H108" s="37" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Cap pot. (proposé)</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>SUGGESTION mesurée : cap ∝ 1 / intensité marketing (budget ÷ CA). Pousse les marques SOUS-investies vs leur taille — le potentiel dormant. Plus spéculatif : on parie que la marge de progression existe. Cap &gt; 1 = marque sous-exploitée.</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="n"/>
+      <c r="E109" s="43" t="n"/>
+      <c r="F109" s="43" t="n"/>
+      <c r="G109" s="43" t="n"/>
+      <c r="H109" s="37" t="n"/>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Lire les 3 ensemble</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Le plus instructif est la DIVERGENCE. Ex. une marque avec Éff. et Pot. élevés mais Mom. bas = rentable et sous-exploitée, mais son élan faiblit → au CFO de trancher : je pousse (pari) ou je laisse (prudence) ? Les caps proposés éclairent, ils ne décident pas.</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="n"/>
+      <c r="E110" s="43" t="n"/>
+      <c r="F110" s="43" t="n"/>
+      <c r="G110" s="43" t="n"/>
+      <c r="H110" s="37" t="n"/>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Indice prix ville</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>DÉDUIT du réalisé (prix moyen ville ÷ national). Informationnel : la géographie tarifaire est déjà dans les revenus. Non saisissable (sinon double compte).</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="n"/>
+      <c r="E111" s="43" t="n"/>
+      <c r="F111" s="43" t="n"/>
+      <c r="G111" s="43" t="n"/>
+      <c r="H111" s="37" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>🔵 Clés d'allocation</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Le driver de répartition des coûts (CA / effectif / classes), figé par le CFO. Méthode centrale ; les campus ne la choisissent pas, ils contestent l'assiette.</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="n"/>
+      <c r="E112" s="43" t="n"/>
+      <c r="F112" s="43" t="n"/>
+      <c r="G112" s="43" t="n"/>
+      <c r="H112" s="37" t="n"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Justification des caps proposés — le calcul, marque par marque (inputs MESURÉS → formule → cap)</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
+      <c r="H128" s="4" t="n"/>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>CAC marginal (mesuré)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Croiss. leads 24→26</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Intensité mkt (bud÷CA)</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>🟢 Cap éff.</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>🟢 Cap mom.</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>🟢 Cap pot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="17" t="inlineStr">
+        <is>
           <t>MBway</t>
         </is>
       </c>
-      <c r="C92" s="15">
-        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B92)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B92))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B92)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B92))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B92)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B92))),0)</f>
-        <v/>
-      </c>
-      <c r="D92" s="25">
-        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B92,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B92,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
-        <v/>
-      </c>
-      <c r="E92" s="25">
-        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B92)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B92),0)</f>
-        <v/>
-      </c>
-      <c r="F92" s="26">
-        <f>IFERROR((1/C92)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
-        <v/>
-      </c>
-      <c r="G92" s="26">
-        <f>IFERROR(D92/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
-        <v/>
-      </c>
-      <c r="H92" s="26">
-        <f>IFERROR((1/E92)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="17" t="inlineStr">
+      <c r="C130" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B130)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B130))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B130)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B130))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B130)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B130))),0)</f>
+        <v/>
+      </c>
+      <c r="D130" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B130,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B130,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E130" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B130)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B130),0)</f>
+        <v/>
+      </c>
+      <c r="F130" s="26">
+        <f>IFERROR((1/C130)/(SUMPRODUCT(1/$C$130:$C$134)/COUNT($C$130:$C$134)),0)</f>
+        <v/>
+      </c>
+      <c r="G130" s="26">
+        <f>IFERROR(D130/(SUM($D$130:$D$134)/COUNT($D$130:$D$134)),0)</f>
+        <v/>
+      </c>
+      <c r="H130" s="26">
+        <f>IFERROR((1/E130)/(SUMPRODUCT(1/$E$130:$E$134)/COUNT($E$130:$E$134)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="17" t="inlineStr">
         <is>
           <t>ISCOM</t>
         </is>
       </c>
-      <c r="C93" s="15">
-        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B93)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B93))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B93)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B93))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B93)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B93))),0)</f>
-        <v/>
-      </c>
-      <c r="D93" s="25">
-        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B93,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B93,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
-        <v/>
-      </c>
-      <c r="E93" s="25">
-        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B93)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B93),0)</f>
-        <v/>
-      </c>
-      <c r="F93" s="26">
-        <f>IFERROR((1/C93)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
-        <v/>
-      </c>
-      <c r="G93" s="26">
-        <f>IFERROR(D93/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
-        <v/>
-      </c>
-      <c r="H93" s="26">
-        <f>IFERROR((1/E93)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="17" t="inlineStr">
+      <c r="C131" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B131)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B131))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B131)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B131))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B131)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B131))),0)</f>
+        <v/>
+      </c>
+      <c r="D131" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B131,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B131,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E131" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B131)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B131),0)</f>
+        <v/>
+      </c>
+      <c r="F131" s="26">
+        <f>IFERROR((1/C131)/(SUMPRODUCT(1/$C$130:$C$134)/COUNT($C$130:$C$134)),0)</f>
+        <v/>
+      </c>
+      <c r="G131" s="26">
+        <f>IFERROR(D131/(SUM($D$130:$D$134)/COUNT($D$130:$D$134)),0)</f>
+        <v/>
+      </c>
+      <c r="H131" s="26">
+        <f>IFERROR((1/E131)/(SUMPRODUCT(1/$E$130:$E$134)/COUNT($E$130:$E$134)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="17" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory</t>
         </is>
       </c>
-      <c r="C94" s="15">
-        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B94)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B94))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B94)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B94))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B94)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B94))),0)</f>
-        <v/>
-      </c>
-      <c r="D94" s="25">
-        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B94,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B94,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
-        <v/>
-      </c>
-      <c r="E94" s="25">
-        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B94)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B94),0)</f>
-        <v/>
-      </c>
-      <c r="F94" s="26">
-        <f>IFERROR((1/C94)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
-        <v/>
-      </c>
-      <c r="G94" s="26">
-        <f>IFERROR(D94/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
-        <v/>
-      </c>
-      <c r="H94" s="26">
-        <f>IFERROR((1/E94)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="17" t="inlineStr">
+      <c r="C132" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B132)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B132))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B132)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B132))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B132)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B132))),0)</f>
+        <v/>
+      </c>
+      <c r="D132" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B132,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B132,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E132" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B132)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B132),0)</f>
+        <v/>
+      </c>
+      <c r="F132" s="26">
+        <f>IFERROR((1/C132)/(SUMPRODUCT(1/$C$130:$C$134)/COUNT($C$130:$C$134)),0)</f>
+        <v/>
+      </c>
+      <c r="G132" s="26">
+        <f>IFERROR(D132/(SUM($D$130:$D$134)/COUNT($D$130:$D$134)),0)</f>
+        <v/>
+      </c>
+      <c r="H132" s="26">
+        <f>IFERROR((1/E132)/(SUMPRODUCT(1/$E$130:$E$134)/COUNT($E$130:$E$134)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="17" t="inlineStr">
         <is>
           <t>Pigier</t>
         </is>
       </c>
-      <c r="C95" s="15">
-        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B95)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B95))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B95)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B95))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B95)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B95))),0)</f>
-        <v/>
-      </c>
-      <c r="D95" s="25">
-        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B95,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B95,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
-        <v/>
-      </c>
-      <c r="E95" s="25">
-        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B95)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B95),0)</f>
-        <v/>
-      </c>
-      <c r="F95" s="26">
-        <f>IFERROR((1/C95)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
-        <v/>
-      </c>
-      <c r="G95" s="26">
-        <f>IFERROR(D95/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
-        <v/>
-      </c>
-      <c r="H95" s="26">
-        <f>IFERROR((1/E95)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="17" t="inlineStr">
+      <c r="C133" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B133)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B133))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B133)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B133))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B133)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B133))),0)</f>
+        <v/>
+      </c>
+      <c r="D133" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B133,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B133,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E133" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B133)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B133),0)</f>
+        <v/>
+      </c>
+      <c r="F133" s="26">
+        <f>IFERROR((1/C133)/(SUMPRODUCT(1/$C$130:$C$134)/COUNT($C$130:$C$134)),0)</f>
+        <v/>
+      </c>
+      <c r="G133" s="26">
+        <f>IFERROR(D133/(SUM($D$130:$D$134)/COUNT($D$130:$D$134)),0)</f>
+        <v/>
+      </c>
+      <c r="H133" s="26">
+        <f>IFERROR((1/E133)/(SUMPRODUCT(1/$E$130:$E$134)/COUNT($E$130:$E$134)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="17" t="inlineStr">
         <is>
           <t>Tunon</t>
         </is>
       </c>
-      <c r="C96" s="15">
-        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B96)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B96))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B96)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B96))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B96)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B96))),0)</f>
-        <v/>
-      </c>
-      <c r="D96" s="25">
-        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B96,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B96,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
-        <v/>
-      </c>
-      <c r="E96" s="25">
-        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B96)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B96),0)</f>
-        <v/>
-      </c>
-      <c r="F96" s="26">
-        <f>IFERROR((1/C96)/(SUMPRODUCT(1/$C$92:$C$96)/COUNT($C$92:$C$96)),0)</f>
-        <v/>
-      </c>
-      <c r="G96" s="26">
-        <f>IFERROR(D96/(SUM($D$92:$D$96)/COUNT($D$92:$D$96)),0)</f>
-        <v/>
-      </c>
-      <c r="H96" s="26">
-        <f>IFERROR((1/E96)/(SUMPRODUCT(1/$E$92:$E$96)/COUNT($E$92:$E$96)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="B98" s="7" t="inlineStr">
+      <c r="C134" s="15">
+        <f>IFERROR((SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B134)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B134))/((SUMPRODUCT(('03_Campagnes'!$A$5:$A$18=B134)*'03_Campagnes'!$J$5:$J$18*'03_Campagnes'!$E$5:$E$18)/SUMIFS('03_Campagnes'!$E$5:$E$18,'03_Campagnes'!$A$5:$A$18,B134))*(SUMIFS('02_Base'!$K$4:$K$61,'02_Base'!$A$4:$A$61,B134)/SUMIFS('02_Base'!$H$4:$H$61,'02_Base'!$A$4:$A$61,B134))),0)</f>
+        <v/>
+      </c>
+      <c r="D134" s="25">
+        <f>IFERROR(SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B134,'02_CRM'!$D$4:$D$45,2026)/SUMIFS('02_CRM'!$G$4:$G$45,'02_CRM'!$A$4:$A$45,B134,'02_CRM'!$D$4:$D$45,2024)-1,0)</f>
+        <v/>
+      </c>
+      <c r="E134" s="25">
+        <f>IFERROR(SUMIFS('03_Campagnes'!$G$5:$G$18,'03_Campagnes'!$A$5:$A$18,B134)/SUMIFS('02_Base'!$U$4:$U$61,'02_Base'!$A$4:$A$61,B134),0)</f>
+        <v/>
+      </c>
+      <c r="F134" s="26">
+        <f>IFERROR((1/C134)/(SUMPRODUCT(1/$C$130:$C$134)/COUNT($C$130:$C$134)),0)</f>
+        <v/>
+      </c>
+      <c r="G134" s="26">
+        <f>IFERROR(D134/(SUM($D$130:$D$134)/COUNT($D$130:$D$134)),0)</f>
+        <v/>
+      </c>
+      <c r="H134" s="26">
+        <f>IFERROR((1/E134)/(SUMPRODUCT(1/$E$130:$E$134)/COUNT($E$130:$E$134)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>Formules : CAC marginal = CPL ÷ (rendement × conversion) ; Cap éff. = (1÷CAC) ÷ moyenne(1÷CAC) · Cap mom. = croissance ÷ moyenne(croissance) · Cap pot. = (1÷intensité) ÷ moyenne(1÷intensité). Normalisés à moyenne 1 (seul le relatif compte).</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="B99" s="7" t="inlineStr">
+    <row r="137" ht="28" customHeight="1">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>Sources (100 % mesuré, rien de saisi) : CAC marginal, rendement &amp; budget = 03_Campagnes (mesurés sur le CRM) · croissance des leads = 02_CRM (2024→2026) · CA &amp; effectif = 02_Base. Le cap du bloc en haut = ces cellules (drill).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="B99:H99"/>
-    <mergeCell ref="C84:H84"/>
+  <mergeCells count="44">
+    <mergeCell ref="B137:H137"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C109:H109"/>
+    <mergeCell ref="C99:H99"/>
     <mergeCell ref="J38:K38"/>
-    <mergeCell ref="C80:H80"/>
-    <mergeCell ref="C75:H75"/>
     <mergeCell ref="J12:M12"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J21:M21"/>
     <mergeCell ref="L37:M37"/>
+    <mergeCell ref="C105:H105"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="C71:H71"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="C110:H110"/>
+    <mergeCell ref="C106:H106"/>
+    <mergeCell ref="B94:H95"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="J32:M33"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="C72:H72"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="C81:H81"/>
     <mergeCell ref="L35:M35"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="J13:P13"/>
     <mergeCell ref="L38:M38"/>
+    <mergeCell ref="C102:H102"/>
     <mergeCell ref="J34:M34"/>
     <mergeCell ref="B70:H70"/>
-    <mergeCell ref="C78:H78"/>
-    <mergeCell ref="C83:H83"/>
+    <mergeCell ref="C111:H111"/>
+    <mergeCell ref="C101:H101"/>
     <mergeCell ref="B98:H98"/>
-    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="B136:H136"/>
     <mergeCell ref="J40:M42"/>
+    <mergeCell ref="C108:H108"/>
     <mergeCell ref="B14:H14"/>
+    <mergeCell ref="C112:H112"/>
+    <mergeCell ref="C107:H107"/>
     <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C104:H104"/>
     <mergeCell ref="B44:H44"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="C79:H79"/>
     <mergeCell ref="J20:P20"/>
-    <mergeCell ref="C73:H73"/>
     <mergeCell ref="L36:M36"/>
+    <mergeCell ref="B128:H128"/>
+    <mergeCell ref="C100:H100"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <conditionalFormatting sqref="E46:E50">
     <cfRule type="dataBar" priority="1">
@@ -8716,6 +9300,48 @@
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E72:E76">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="0070AD47"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F72:F76">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79:E92">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="0070AD47"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F79:F92">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="00F8696B"/>
         <color rgb="00FFEB84"/>
@@ -8966,7 +9592,7 @@
         <v/>
       </c>
       <c r="U4" s="46">
-        <f>M4*P4+K4*'01_Cadrage'!$D$29</f>
+        <f>M4*P4+K4*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9048,7 +9674,7 @@
         <v/>
       </c>
       <c r="U5" s="46">
-        <f>M5*P5+K5*'01_Cadrage'!$D$29</f>
+        <f>M5*P5+K5*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9130,7 +9756,7 @@
         <v/>
       </c>
       <c r="U6" s="46">
-        <f>M6*P6+K6*'01_Cadrage'!$D$29</f>
+        <f>M6*P6+K6*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9212,7 +9838,7 @@
         <v/>
       </c>
       <c r="U7" s="46">
-        <f>M7*P7+K7*'01_Cadrage'!$D$29</f>
+        <f>M7*P7+K7*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9294,7 +9920,7 @@
         <v/>
       </c>
       <c r="U8" s="46">
-        <f>M8*P8+K8*'01_Cadrage'!$D$29</f>
+        <f>M8*P8+K8*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9376,7 +10002,7 @@
         <v/>
       </c>
       <c r="U9" s="46">
-        <f>M9*P9+K9*'01_Cadrage'!$D$29</f>
+        <f>M9*P9+K9*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9458,7 +10084,7 @@
         <v/>
       </c>
       <c r="U10" s="46">
-        <f>M10*P10+K10*'01_Cadrage'!$D$29</f>
+        <f>M10*P10+K10*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9540,7 +10166,7 @@
         <v/>
       </c>
       <c r="U11" s="46">
-        <f>M11*P11+K11*'01_Cadrage'!$D$29</f>
+        <f>M11*P11+K11*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9622,7 +10248,7 @@
         <v/>
       </c>
       <c r="U12" s="46">
-        <f>M12*P12+K12*'01_Cadrage'!$D$29</f>
+        <f>M12*P12+K12*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9704,7 +10330,7 @@
         <v/>
       </c>
       <c r="U13" s="46">
-        <f>M13*P13+K13*'01_Cadrage'!$D$29</f>
+        <f>M13*P13+K13*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9786,7 +10412,7 @@
         <v/>
       </c>
       <c r="U14" s="46">
-        <f>M14*P14+K14*'01_Cadrage'!$D$29</f>
+        <f>M14*P14+K14*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9868,7 +10494,7 @@
         <v/>
       </c>
       <c r="U15" s="46">
-        <f>M15*P15+K15*'01_Cadrage'!$D$29</f>
+        <f>M15*P15+K15*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -9950,7 +10576,7 @@
         <v/>
       </c>
       <c r="U16" s="46">
-        <f>M16*P16+K16*'01_Cadrage'!$D$29</f>
+        <f>M16*P16+K16*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10032,7 +10658,7 @@
         <v/>
       </c>
       <c r="U17" s="46">
-        <f>M17*P17+K17*'01_Cadrage'!$D$29</f>
+        <f>M17*P17+K17*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10114,7 +10740,7 @@
         <v/>
       </c>
       <c r="U18" s="46">
-        <f>M18*P18+K18*'01_Cadrage'!$D$29</f>
+        <f>M18*P18+K18*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10196,7 +10822,7 @@
         <v/>
       </c>
       <c r="U19" s="46">
-        <f>M19*P19+K19*'01_Cadrage'!$D$29</f>
+        <f>M19*P19+K19*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10278,7 +10904,7 @@
         <v/>
       </c>
       <c r="U20" s="46">
-        <f>M20*P20+K20*'01_Cadrage'!$D$29</f>
+        <f>M20*P20+K20*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10360,7 +10986,7 @@
         <v/>
       </c>
       <c r="U21" s="46">
-        <f>M21*P21+K21*'01_Cadrage'!$D$29</f>
+        <f>M21*P21+K21*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10442,7 +11068,7 @@
         <v/>
       </c>
       <c r="U22" s="46">
-        <f>M22*P22+K22*'01_Cadrage'!$D$29</f>
+        <f>M22*P22+K22*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10524,7 +11150,7 @@
         <v/>
       </c>
       <c r="U23" s="46">
-        <f>M23*P23+K23*'01_Cadrage'!$D$29</f>
+        <f>M23*P23+K23*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10606,7 +11232,7 @@
         <v/>
       </c>
       <c r="U24" s="46">
-        <f>M24*P24+K24*'01_Cadrage'!$D$29</f>
+        <f>M24*P24+K24*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10688,7 +11314,7 @@
         <v/>
       </c>
       <c r="U25" s="46">
-        <f>M25*P25+K25*'01_Cadrage'!$D$29</f>
+        <f>M25*P25+K25*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10770,7 +11396,7 @@
         <v/>
       </c>
       <c r="U26" s="46">
-        <f>M26*P26+K26*'01_Cadrage'!$D$29</f>
+        <f>M26*P26+K26*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10852,7 +11478,7 @@
         <v/>
       </c>
       <c r="U27" s="46">
-        <f>M27*P27+K27*'01_Cadrage'!$D$29</f>
+        <f>M27*P27+K27*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -10934,7 +11560,7 @@
         <v/>
       </c>
       <c r="U28" s="46">
-        <f>M28*P28+K28*'01_Cadrage'!$D$29</f>
+        <f>M28*P28+K28*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11016,7 +11642,7 @@
         <v/>
       </c>
       <c r="U29" s="46">
-        <f>M29*P29+K29*'01_Cadrage'!$D$29</f>
+        <f>M29*P29+K29*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11098,7 +11724,7 @@
         <v/>
       </c>
       <c r="U30" s="46">
-        <f>M30*P30+K30*'01_Cadrage'!$D$29</f>
+        <f>M30*P30+K30*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11180,7 +11806,7 @@
         <v/>
       </c>
       <c r="U31" s="46">
-        <f>M31*P31+K31*'01_Cadrage'!$D$29</f>
+        <f>M31*P31+K31*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11262,7 +11888,7 @@
         <v/>
       </c>
       <c r="U32" s="46">
-        <f>M32*P32+K32*'01_Cadrage'!$D$29</f>
+        <f>M32*P32+K32*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11344,7 +11970,7 @@
         <v/>
       </c>
       <c r="U33" s="46">
-        <f>M33*P33+K33*'01_Cadrage'!$D$29</f>
+        <f>M33*P33+K33*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11426,7 +12052,7 @@
         <v/>
       </c>
       <c r="U34" s="46">
-        <f>M34*P34+K34*'01_Cadrage'!$D$29</f>
+        <f>M34*P34+K34*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11508,7 +12134,7 @@
         <v/>
       </c>
       <c r="U35" s="46">
-        <f>M35*P35+K35*'01_Cadrage'!$D$29</f>
+        <f>M35*P35+K35*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11590,7 +12216,7 @@
         <v/>
       </c>
       <c r="U36" s="46">
-        <f>M36*P36+K36*'01_Cadrage'!$D$29</f>
+        <f>M36*P36+K36*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11672,7 +12298,7 @@
         <v/>
       </c>
       <c r="U37" s="46">
-        <f>M37*P37+K37*'01_Cadrage'!$D$29</f>
+        <f>M37*P37+K37*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11754,7 +12380,7 @@
         <v/>
       </c>
       <c r="U38" s="46">
-        <f>M38*P38+K38*'01_Cadrage'!$D$29</f>
+        <f>M38*P38+K38*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11836,7 +12462,7 @@
         <v/>
       </c>
       <c r="U39" s="46">
-        <f>M39*P39+K39*'01_Cadrage'!$D$29</f>
+        <f>M39*P39+K39*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -11918,7 +12544,7 @@
         <v/>
       </c>
       <c r="U40" s="46">
-        <f>M40*P40+K40*'01_Cadrage'!$D$29</f>
+        <f>M40*P40+K40*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12000,7 +12626,7 @@
         <v/>
       </c>
       <c r="U41" s="46">
-        <f>M41*P41+K41*'01_Cadrage'!$D$29</f>
+        <f>M41*P41+K41*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12082,7 +12708,7 @@
         <v/>
       </c>
       <c r="U42" s="46">
-        <f>M42*P42+K42*'01_Cadrage'!$D$29</f>
+        <f>M42*P42+K42*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12164,7 +12790,7 @@
         <v/>
       </c>
       <c r="U43" s="46">
-        <f>M43*P43+K43*'01_Cadrage'!$D$29</f>
+        <f>M43*P43+K43*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12246,7 +12872,7 @@
         <v/>
       </c>
       <c r="U44" s="46">
-        <f>M44*P44+K44*'01_Cadrage'!$D$29</f>
+        <f>M44*P44+K44*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12328,7 +12954,7 @@
         <v/>
       </c>
       <c r="U45" s="46">
-        <f>M45*P45+K45*'01_Cadrage'!$D$29</f>
+        <f>M45*P45+K45*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12410,7 +13036,7 @@
         <v/>
       </c>
       <c r="U46" s="46">
-        <f>M46*P46+K46*'01_Cadrage'!$D$29</f>
+        <f>M46*P46+K46*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12492,7 +13118,7 @@
         <v/>
       </c>
       <c r="U47" s="46">
-        <f>M47*P47+K47*'01_Cadrage'!$D$29</f>
+        <f>M47*P47+K47*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12574,7 +13200,7 @@
         <v/>
       </c>
       <c r="U48" s="46">
-        <f>M48*P48+K48*'01_Cadrage'!$D$29</f>
+        <f>M48*P48+K48*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12656,7 +13282,7 @@
         <v/>
       </c>
       <c r="U49" s="46">
-        <f>M49*P49+K49*'01_Cadrage'!$D$29</f>
+        <f>M49*P49+K49*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12738,7 +13364,7 @@
         <v/>
       </c>
       <c r="U50" s="46">
-        <f>M50*P50+K50*'01_Cadrage'!$D$29</f>
+        <f>M50*P50+K50*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12820,7 +13446,7 @@
         <v/>
       </c>
       <c r="U51" s="46">
-        <f>M51*P51+K51*'01_Cadrage'!$D$29</f>
+        <f>M51*P51+K51*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12902,7 +13528,7 @@
         <v/>
       </c>
       <c r="U52" s="46">
-        <f>M52*P52+K52*'01_Cadrage'!$D$29</f>
+        <f>M52*P52+K52*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -12984,7 +13610,7 @@
         <v/>
       </c>
       <c r="U53" s="46">
-        <f>M53*P53+K53*'01_Cadrage'!$D$29</f>
+        <f>M53*P53+K53*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13066,7 +13692,7 @@
         <v/>
       </c>
       <c r="U54" s="46">
-        <f>M54*P54+K54*'01_Cadrage'!$D$29</f>
+        <f>M54*P54+K54*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13148,7 +13774,7 @@
         <v/>
       </c>
       <c r="U55" s="46">
-        <f>M55*P55+K55*'01_Cadrage'!$D$29</f>
+        <f>M55*P55+K55*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13230,7 +13856,7 @@
         <v/>
       </c>
       <c r="U56" s="46">
-        <f>M56*P56+K56*'01_Cadrage'!$D$29</f>
+        <f>M56*P56+K56*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13312,7 +13938,7 @@
         <v/>
       </c>
       <c r="U57" s="46">
-        <f>M57*P57+K57*'01_Cadrage'!$D$29</f>
+        <f>M57*P57+K57*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13394,7 +14020,7 @@
         <v/>
       </c>
       <c r="U58" s="46">
-        <f>M58*P58+K58*'01_Cadrage'!$D$29</f>
+        <f>M58*P58+K58*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13476,7 +14102,7 @@
         <v/>
       </c>
       <c r="U59" s="46">
-        <f>M59*P59+K59*'01_Cadrage'!$D$29</f>
+        <f>M59*P59+K59*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13558,7 +14184,7 @@
         <v/>
       </c>
       <c r="U60" s="46">
-        <f>M60*P60+K60*'01_Cadrage'!$D$29</f>
+        <f>M60*P60+K60*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -13640,7 +14266,7 @@
         <v/>
       </c>
       <c r="U61" s="46">
-        <f>M61*P61+K61*'01_Cadrage'!$D$29</f>
+        <f>M61*P61+K61*'01_Cadrage'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -17145,7 +17771,7 @@
         <v/>
       </c>
       <c r="AA4" s="14">
-        <f>Y4*Z4+W4*'01_Cadrage'!$H$29</f>
+        <f>Y4*Z4+W4*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB4" s="23">
@@ -17161,7 +17787,7 @@
         <v/>
       </c>
       <c r="AE4" s="15">
-        <f>AD4*Z4+AB4*'01_Cadrage'!$H$29</f>
+        <f>AD4*Z4+AB4*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF4" s="10" t="n">
@@ -17300,7 +17926,7 @@
         <v/>
       </c>
       <c r="AA5" s="14">
-        <f>Y5*Z5+W5*'01_Cadrage'!$H$29</f>
+        <f>Y5*Z5+W5*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB5" s="23">
@@ -17316,7 +17942,7 @@
         <v/>
       </c>
       <c r="AE5" s="15">
-        <f>AD5*Z5+AB5*'01_Cadrage'!$H$29</f>
+        <f>AD5*Z5+AB5*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF5" s="10" t="n">
@@ -17455,7 +18081,7 @@
         <v/>
       </c>
       <c r="AA6" s="14">
-        <f>Y6*Z6+W6*'01_Cadrage'!$H$29</f>
+        <f>Y6*Z6+W6*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB6" s="23">
@@ -17471,7 +18097,7 @@
         <v/>
       </c>
       <c r="AE6" s="15">
-        <f>AD6*Z6+AB6*'01_Cadrage'!$H$29</f>
+        <f>AD6*Z6+AB6*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF6" s="10" t="n">
@@ -17610,7 +18236,7 @@
         <v/>
       </c>
       <c r="AA7" s="14">
-        <f>Y7*Z7+W7*'01_Cadrage'!$H$29</f>
+        <f>Y7*Z7+W7*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB7" s="23">
@@ -17626,7 +18252,7 @@
         <v/>
       </c>
       <c r="AE7" s="15">
-        <f>AD7*Z7+AB7*'01_Cadrage'!$H$29</f>
+        <f>AD7*Z7+AB7*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF7" s="10" t="n">
@@ -17765,7 +18391,7 @@
         <v/>
       </c>
       <c r="AA8" s="14">
-        <f>Y8*Z8+W8*'01_Cadrage'!$H$29</f>
+        <f>Y8*Z8+W8*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB8" s="23">
@@ -17781,7 +18407,7 @@
         <v/>
       </c>
       <c r="AE8" s="15">
-        <f>AD8*Z8+AB8*'01_Cadrage'!$H$29</f>
+        <f>AD8*Z8+AB8*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF8" s="10" t="n">
@@ -17920,7 +18546,7 @@
         <v/>
       </c>
       <c r="AA9" s="14">
-        <f>Y9*Z9+W9*'01_Cadrage'!$H$29</f>
+        <f>Y9*Z9+W9*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB9" s="23">
@@ -17936,7 +18562,7 @@
         <v/>
       </c>
       <c r="AE9" s="15">
-        <f>AD9*Z9+AB9*'01_Cadrage'!$H$29</f>
+        <f>AD9*Z9+AB9*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF9" s="50">
@@ -18078,7 +18704,7 @@
         <v/>
       </c>
       <c r="AA10" s="14">
-        <f>Y10*Z10+W10*'01_Cadrage'!$H$29</f>
+        <f>Y10*Z10+W10*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB10" s="23">
@@ -18094,7 +18720,7 @@
         <v/>
       </c>
       <c r="AE10" s="15">
-        <f>AD10*Z10+AB10*'01_Cadrage'!$H$29</f>
+        <f>AD10*Z10+AB10*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF10" s="50">
@@ -18236,7 +18862,7 @@
         <v/>
       </c>
       <c r="AA11" s="14">
-        <f>Y11*Z11+W11*'01_Cadrage'!$H$29</f>
+        <f>Y11*Z11+W11*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB11" s="23">
@@ -18252,7 +18878,7 @@
         <v/>
       </c>
       <c r="AE11" s="15">
-        <f>AD11*Z11+AB11*'01_Cadrage'!$H$29</f>
+        <f>AD11*Z11+AB11*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF11" s="50">
@@ -18394,7 +19020,7 @@
         <v/>
       </c>
       <c r="AA12" s="14">
-        <f>Y12*Z12+W12*'01_Cadrage'!$H$29</f>
+        <f>Y12*Z12+W12*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB12" s="23">
@@ -18410,7 +19036,7 @@
         <v/>
       </c>
       <c r="AE12" s="15">
-        <f>AD12*Z12+AB12*'01_Cadrage'!$H$29</f>
+        <f>AD12*Z12+AB12*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF12" s="50">
@@ -18552,7 +19178,7 @@
         <v/>
       </c>
       <c r="AA13" s="14">
-        <f>Y13*Z13+W13*'01_Cadrage'!$H$29</f>
+        <f>Y13*Z13+W13*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB13" s="23">
@@ -18568,7 +19194,7 @@
         <v/>
       </c>
       <c r="AE13" s="15">
-        <f>AD13*Z13+AB13*'01_Cadrage'!$H$29</f>
+        <f>AD13*Z13+AB13*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF13" s="50">
@@ -18710,7 +19336,7 @@
         <v/>
       </c>
       <c r="AA14" s="14">
-        <f>Y14*Z14+W14*'01_Cadrage'!$H$29</f>
+        <f>Y14*Z14+W14*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB14" s="23">
@@ -18726,7 +19352,7 @@
         <v/>
       </c>
       <c r="AE14" s="15">
-        <f>AD14*Z14+AB14*'01_Cadrage'!$H$29</f>
+        <f>AD14*Z14+AB14*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF14" s="10" t="n">
@@ -18865,7 +19491,7 @@
         <v/>
       </c>
       <c r="AA15" s="14">
-        <f>Y15*Z15+W15*'01_Cadrage'!$H$29</f>
+        <f>Y15*Z15+W15*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB15" s="23">
@@ -18881,7 +19507,7 @@
         <v/>
       </c>
       <c r="AE15" s="15">
-        <f>AD15*Z15+AB15*'01_Cadrage'!$H$29</f>
+        <f>AD15*Z15+AB15*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF15" s="10" t="n">
@@ -19020,7 +19646,7 @@
         <v/>
       </c>
       <c r="AA16" s="14">
-        <f>Y16*Z16+W16*'01_Cadrage'!$H$29</f>
+        <f>Y16*Z16+W16*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB16" s="23">
@@ -19036,7 +19662,7 @@
         <v/>
       </c>
       <c r="AE16" s="15">
-        <f>AD16*Z16+AB16*'01_Cadrage'!$H$29</f>
+        <f>AD16*Z16+AB16*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF16" s="10" t="n">
@@ -19175,7 +19801,7 @@
         <v/>
       </c>
       <c r="AA17" s="14">
-        <f>Y17*Z17+W17*'01_Cadrage'!$H$29</f>
+        <f>Y17*Z17+W17*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB17" s="23">
@@ -19191,7 +19817,7 @@
         <v/>
       </c>
       <c r="AE17" s="15">
-        <f>AD17*Z17+AB17*'01_Cadrage'!$H$29</f>
+        <f>AD17*Z17+AB17*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF17" s="10" t="n">
@@ -19330,7 +19956,7 @@
         <v/>
       </c>
       <c r="AA18" s="14">
-        <f>Y18*Z18+W18*'01_Cadrage'!$H$29</f>
+        <f>Y18*Z18+W18*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB18" s="23">
@@ -19346,7 +19972,7 @@
         <v/>
       </c>
       <c r="AE18" s="15">
-        <f>AD18*Z18+AB18*'01_Cadrage'!$H$29</f>
+        <f>AD18*Z18+AB18*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF18" s="10" t="n">
@@ -19485,7 +20111,7 @@
         <v/>
       </c>
       <c r="AA19" s="14">
-        <f>Y19*Z19+W19*'01_Cadrage'!$H$29</f>
+        <f>Y19*Z19+W19*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB19" s="23">
@@ -19501,7 +20127,7 @@
         <v/>
       </c>
       <c r="AE19" s="15">
-        <f>AD19*Z19+AB19*'01_Cadrage'!$H$29</f>
+        <f>AD19*Z19+AB19*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF19" s="10" t="n">
@@ -19640,7 +20266,7 @@
         <v/>
       </c>
       <c r="AA20" s="14">
-        <f>Y20*Z20+W20*'01_Cadrage'!$H$29</f>
+        <f>Y20*Z20+W20*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB20" s="23">
@@ -19656,7 +20282,7 @@
         <v/>
       </c>
       <c r="AE20" s="15">
-        <f>AD20*Z20+AB20*'01_Cadrage'!$H$29</f>
+        <f>AD20*Z20+AB20*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF20" s="10" t="n">
@@ -19795,7 +20421,7 @@
         <v/>
       </c>
       <c r="AA21" s="14">
-        <f>Y21*Z21+W21*'01_Cadrage'!$H$29</f>
+        <f>Y21*Z21+W21*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB21" s="23">
@@ -19811,7 +20437,7 @@
         <v/>
       </c>
       <c r="AE21" s="15">
-        <f>AD21*Z21+AB21*'01_Cadrage'!$H$29</f>
+        <f>AD21*Z21+AB21*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF21" s="10" t="n">
@@ -19950,7 +20576,7 @@
         <v/>
       </c>
       <c r="AA22" s="14">
-        <f>Y22*Z22+W22*'01_Cadrage'!$H$29</f>
+        <f>Y22*Z22+W22*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB22" s="23">
@@ -19966,7 +20592,7 @@
         <v/>
       </c>
       <c r="AE22" s="15">
-        <f>AD22*Z22+AB22*'01_Cadrage'!$H$29</f>
+        <f>AD22*Z22+AB22*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF22" s="10" t="n">
@@ -20105,7 +20731,7 @@
         <v/>
       </c>
       <c r="AA23" s="14">
-        <f>Y23*Z23+W23*'01_Cadrage'!$H$29</f>
+        <f>Y23*Z23+W23*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB23" s="23">
@@ -20121,7 +20747,7 @@
         <v/>
       </c>
       <c r="AE23" s="15">
-        <f>AD23*Z23+AB23*'01_Cadrage'!$H$29</f>
+        <f>AD23*Z23+AB23*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF23" s="10" t="n">
@@ -20260,7 +20886,7 @@
         <v/>
       </c>
       <c r="AA24" s="14">
-        <f>Y24*Z24+W24*'01_Cadrage'!$H$29</f>
+        <f>Y24*Z24+W24*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB24" s="23">
@@ -20276,7 +20902,7 @@
         <v/>
       </c>
       <c r="AE24" s="15">
-        <f>AD24*Z24+AB24*'01_Cadrage'!$H$29</f>
+        <f>AD24*Z24+AB24*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF24" s="10" t="n">
@@ -20415,7 +21041,7 @@
         <v/>
       </c>
       <c r="AA25" s="14">
-        <f>Y25*Z25+W25*'01_Cadrage'!$H$29</f>
+        <f>Y25*Z25+W25*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB25" s="23">
@@ -20431,7 +21057,7 @@
         <v/>
       </c>
       <c r="AE25" s="15">
-        <f>AD25*Z25+AB25*'01_Cadrage'!$H$29</f>
+        <f>AD25*Z25+AB25*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF25" s="10" t="n">
@@ -20570,7 +21196,7 @@
         <v/>
       </c>
       <c r="AA26" s="14">
-        <f>Y26*Z26+W26*'01_Cadrage'!$H$29</f>
+        <f>Y26*Z26+W26*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB26" s="23">
@@ -20586,7 +21212,7 @@
         <v/>
       </c>
       <c r="AE26" s="15">
-        <f>AD26*Z26+AB26*'01_Cadrage'!$H$29</f>
+        <f>AD26*Z26+AB26*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF26" s="10" t="n">
@@ -20725,7 +21351,7 @@
         <v/>
       </c>
       <c r="AA27" s="14">
-        <f>Y27*Z27+W27*'01_Cadrage'!$H$29</f>
+        <f>Y27*Z27+W27*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB27" s="23">
@@ -20741,7 +21367,7 @@
         <v/>
       </c>
       <c r="AE27" s="15">
-        <f>AD27*Z27+AB27*'01_Cadrage'!$H$29</f>
+        <f>AD27*Z27+AB27*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF27" s="10" t="n">
@@ -20880,7 +21506,7 @@
         <v/>
       </c>
       <c r="AA28" s="14">
-        <f>Y28*Z28+W28*'01_Cadrage'!$H$29</f>
+        <f>Y28*Z28+W28*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB28" s="23">
@@ -20896,7 +21522,7 @@
         <v/>
       </c>
       <c r="AE28" s="15">
-        <f>AD28*Z28+AB28*'01_Cadrage'!$H$29</f>
+        <f>AD28*Z28+AB28*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF28" s="10" t="n">
@@ -21035,7 +21661,7 @@
         <v/>
       </c>
       <c r="AA29" s="14">
-        <f>Y29*Z29+W29*'01_Cadrage'!$H$29</f>
+        <f>Y29*Z29+W29*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB29" s="23">
@@ -21051,7 +21677,7 @@
         <v/>
       </c>
       <c r="AE29" s="15">
-        <f>AD29*Z29+AB29*'01_Cadrage'!$H$29</f>
+        <f>AD29*Z29+AB29*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF29" s="10" t="n">
@@ -21190,7 +21816,7 @@
         <v/>
       </c>
       <c r="AA30" s="14">
-        <f>Y30*Z30+W30*'01_Cadrage'!$H$29</f>
+        <f>Y30*Z30+W30*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB30" s="23">
@@ -21206,7 +21832,7 @@
         <v/>
       </c>
       <c r="AE30" s="15">
-        <f>AD30*Z30+AB30*'01_Cadrage'!$H$29</f>
+        <f>AD30*Z30+AB30*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF30" s="10" t="n">
@@ -21345,7 +21971,7 @@
         <v/>
       </c>
       <c r="AA31" s="14">
-        <f>Y31*Z31+W31*'01_Cadrage'!$H$29</f>
+        <f>Y31*Z31+W31*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB31" s="23">
@@ -21361,7 +21987,7 @@
         <v/>
       </c>
       <c r="AE31" s="15">
-        <f>AD31*Z31+AB31*'01_Cadrage'!$H$29</f>
+        <f>AD31*Z31+AB31*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF31" s="10" t="n">
@@ -21500,7 +22126,7 @@
         <v/>
       </c>
       <c r="AA32" s="14">
-        <f>Y32*Z32+W32*'01_Cadrage'!$H$29</f>
+        <f>Y32*Z32+W32*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB32" s="23">
@@ -21516,7 +22142,7 @@
         <v/>
       </c>
       <c r="AE32" s="15">
-        <f>AD32*Z32+AB32*'01_Cadrage'!$H$29</f>
+        <f>AD32*Z32+AB32*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF32" s="10" t="n">
@@ -21655,7 +22281,7 @@
         <v/>
       </c>
       <c r="AA33" s="14">
-        <f>Y33*Z33+W33*'01_Cadrage'!$H$29</f>
+        <f>Y33*Z33+W33*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB33" s="23">
@@ -21671,7 +22297,7 @@
         <v/>
       </c>
       <c r="AE33" s="15">
-        <f>AD33*Z33+AB33*'01_Cadrage'!$H$29</f>
+        <f>AD33*Z33+AB33*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF33" s="10" t="n">
@@ -21810,7 +22436,7 @@
         <v/>
       </c>
       <c r="AA34" s="14">
-        <f>Y34*Z34+W34*'01_Cadrage'!$H$29</f>
+        <f>Y34*Z34+W34*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB34" s="23">
@@ -21826,7 +22452,7 @@
         <v/>
       </c>
       <c r="AE34" s="15">
-        <f>AD34*Z34+AB34*'01_Cadrage'!$H$29</f>
+        <f>AD34*Z34+AB34*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF34" s="10" t="n">
@@ -21965,7 +22591,7 @@
         <v/>
       </c>
       <c r="AA35" s="14">
-        <f>Y35*Z35+W35*'01_Cadrage'!$H$29</f>
+        <f>Y35*Z35+W35*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB35" s="23">
@@ -21981,7 +22607,7 @@
         <v/>
       </c>
       <c r="AE35" s="15">
-        <f>AD35*Z35+AB35*'01_Cadrage'!$H$29</f>
+        <f>AD35*Z35+AB35*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF35" s="10" t="n">
@@ -22120,7 +22746,7 @@
         <v/>
       </c>
       <c r="AA36" s="14">
-        <f>Y36*Z36+W36*'01_Cadrage'!$H$29</f>
+        <f>Y36*Z36+W36*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB36" s="23">
@@ -22136,7 +22762,7 @@
         <v/>
       </c>
       <c r="AE36" s="15">
-        <f>AD36*Z36+AB36*'01_Cadrage'!$H$29</f>
+        <f>AD36*Z36+AB36*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF36" s="10" t="n">
@@ -22275,7 +22901,7 @@
         <v/>
       </c>
       <c r="AA37" s="14">
-        <f>Y37*Z37+W37*'01_Cadrage'!$H$29</f>
+        <f>Y37*Z37+W37*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB37" s="23">
@@ -22291,7 +22917,7 @@
         <v/>
       </c>
       <c r="AE37" s="15">
-        <f>AD37*Z37+AB37*'01_Cadrage'!$H$29</f>
+        <f>AD37*Z37+AB37*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF37" s="10" t="n">
@@ -22430,7 +23056,7 @@
         <v/>
       </c>
       <c r="AA38" s="14">
-        <f>Y38*Z38+W38*'01_Cadrage'!$H$29</f>
+        <f>Y38*Z38+W38*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB38" s="23">
@@ -22446,7 +23072,7 @@
         <v/>
       </c>
       <c r="AE38" s="15">
-        <f>AD38*Z38+AB38*'01_Cadrage'!$H$29</f>
+        <f>AD38*Z38+AB38*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF38" s="10" t="n">
@@ -22585,7 +23211,7 @@
         <v/>
       </c>
       <c r="AA39" s="14">
-        <f>Y39*Z39+W39*'01_Cadrage'!$H$29</f>
+        <f>Y39*Z39+W39*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB39" s="23">
@@ -22601,7 +23227,7 @@
         <v/>
       </c>
       <c r="AE39" s="15">
-        <f>AD39*Z39+AB39*'01_Cadrage'!$H$29</f>
+        <f>AD39*Z39+AB39*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF39" s="10" t="n">
@@ -22740,7 +23366,7 @@
         <v/>
       </c>
       <c r="AA40" s="14">
-        <f>Y40*Z40+W40*'01_Cadrage'!$H$29</f>
+        <f>Y40*Z40+W40*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB40" s="23">
@@ -22756,7 +23382,7 @@
         <v/>
       </c>
       <c r="AE40" s="15">
-        <f>AD40*Z40+AB40*'01_Cadrage'!$H$29</f>
+        <f>AD40*Z40+AB40*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF40" s="10" t="n">
@@ -22895,7 +23521,7 @@
         <v/>
       </c>
       <c r="AA41" s="14">
-        <f>Y41*Z41+W41*'01_Cadrage'!$H$29</f>
+        <f>Y41*Z41+W41*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB41" s="23">
@@ -22911,7 +23537,7 @@
         <v/>
       </c>
       <c r="AE41" s="15">
-        <f>AD41*Z41+AB41*'01_Cadrage'!$H$29</f>
+        <f>AD41*Z41+AB41*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF41" s="10" t="n">
@@ -23050,7 +23676,7 @@
         <v/>
       </c>
       <c r="AA42" s="14">
-        <f>Y42*Z42+W42*'01_Cadrage'!$H$29</f>
+        <f>Y42*Z42+W42*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB42" s="23">
@@ -23066,7 +23692,7 @@
         <v/>
       </c>
       <c r="AE42" s="15">
-        <f>AD42*Z42+AB42*'01_Cadrage'!$H$29</f>
+        <f>AD42*Z42+AB42*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF42" s="10" t="n">
@@ -23205,7 +23831,7 @@
         <v/>
       </c>
       <c r="AA43" s="14">
-        <f>Y43*Z43+W43*'01_Cadrage'!$H$29</f>
+        <f>Y43*Z43+W43*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB43" s="23">
@@ -23221,7 +23847,7 @@
         <v/>
       </c>
       <c r="AE43" s="15">
-        <f>AD43*Z43+AB43*'01_Cadrage'!$H$29</f>
+        <f>AD43*Z43+AB43*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF43" s="10" t="n">
@@ -23360,7 +23986,7 @@
         <v/>
       </c>
       <c r="AA44" s="14">
-        <f>Y44*Z44+W44*'01_Cadrage'!$H$29</f>
+        <f>Y44*Z44+W44*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB44" s="23">
@@ -23376,7 +24002,7 @@
         <v/>
       </c>
       <c r="AE44" s="15">
-        <f>AD44*Z44+AB44*'01_Cadrage'!$H$29</f>
+        <f>AD44*Z44+AB44*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF44" s="10" t="n">
@@ -23515,7 +24141,7 @@
         <v/>
       </c>
       <c r="AA45" s="14">
-        <f>Y45*Z45+W45*'01_Cadrage'!$H$29</f>
+        <f>Y45*Z45+W45*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB45" s="23">
@@ -23531,7 +24157,7 @@
         <v/>
       </c>
       <c r="AE45" s="15">
-        <f>AD45*Z45+AB45*'01_Cadrage'!$H$29</f>
+        <f>AD45*Z45+AB45*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF45" s="10" t="n">
@@ -23670,7 +24296,7 @@
         <v/>
       </c>
       <c r="AA46" s="14">
-        <f>Y46*Z46+W46*'01_Cadrage'!$H$29</f>
+        <f>Y46*Z46+W46*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB46" s="23">
@@ -23686,7 +24312,7 @@
         <v/>
       </c>
       <c r="AE46" s="15">
-        <f>AD46*Z46+AB46*'01_Cadrage'!$H$29</f>
+        <f>AD46*Z46+AB46*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF46" s="10" t="n">
@@ -23825,7 +24451,7 @@
         <v/>
       </c>
       <c r="AA47" s="14">
-        <f>Y47*Z47+W47*'01_Cadrage'!$H$29</f>
+        <f>Y47*Z47+W47*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB47" s="23">
@@ -23841,7 +24467,7 @@
         <v/>
       </c>
       <c r="AE47" s="15">
-        <f>AD47*Z47+AB47*'01_Cadrage'!$H$29</f>
+        <f>AD47*Z47+AB47*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF47" s="10" t="n">
@@ -23980,7 +24606,7 @@
         <v/>
       </c>
       <c r="AA48" s="14">
-        <f>Y48*Z48+W48*'01_Cadrage'!$H$29</f>
+        <f>Y48*Z48+W48*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB48" s="23">
@@ -23996,7 +24622,7 @@
         <v/>
       </c>
       <c r="AE48" s="15">
-        <f>AD48*Z48+AB48*'01_Cadrage'!$H$29</f>
+        <f>AD48*Z48+AB48*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF48" s="10" t="n">
@@ -24135,7 +24761,7 @@
         <v/>
       </c>
       <c r="AA49" s="14">
-        <f>Y49*Z49+W49*'01_Cadrage'!$H$29</f>
+        <f>Y49*Z49+W49*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB49" s="23">
@@ -24151,7 +24777,7 @@
         <v/>
       </c>
       <c r="AE49" s="15">
-        <f>AD49*Z49+AB49*'01_Cadrage'!$H$29</f>
+        <f>AD49*Z49+AB49*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF49" s="10" t="n">
@@ -24290,7 +24916,7 @@
         <v/>
       </c>
       <c r="AA50" s="14">
-        <f>Y50*Z50+W50*'01_Cadrage'!$H$29</f>
+        <f>Y50*Z50+W50*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB50" s="23">
@@ -24306,7 +24932,7 @@
         <v/>
       </c>
       <c r="AE50" s="15">
-        <f>AD50*Z50+AB50*'01_Cadrage'!$H$29</f>
+        <f>AD50*Z50+AB50*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF50" s="10" t="n">
@@ -24445,7 +25071,7 @@
         <v/>
       </c>
       <c r="AA51" s="14">
-        <f>Y51*Z51+W51*'01_Cadrage'!$H$29</f>
+        <f>Y51*Z51+W51*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB51" s="23">
@@ -24461,7 +25087,7 @@
         <v/>
       </c>
       <c r="AE51" s="15">
-        <f>AD51*Z51+AB51*'01_Cadrage'!$H$29</f>
+        <f>AD51*Z51+AB51*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF51" s="10" t="n">
@@ -24600,7 +25226,7 @@
         <v/>
       </c>
       <c r="AA52" s="14">
-        <f>Y52*Z52+W52*'01_Cadrage'!$H$29</f>
+        <f>Y52*Z52+W52*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB52" s="23">
@@ -24616,7 +25242,7 @@
         <v/>
       </c>
       <c r="AE52" s="15">
-        <f>AD52*Z52+AB52*'01_Cadrage'!$H$29</f>
+        <f>AD52*Z52+AB52*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF52" s="10" t="n">
@@ -24755,7 +25381,7 @@
         <v/>
       </c>
       <c r="AA53" s="14">
-        <f>Y53*Z53+W53*'01_Cadrage'!$H$29</f>
+        <f>Y53*Z53+W53*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB53" s="23">
@@ -24771,7 +25397,7 @@
         <v/>
       </c>
       <c r="AE53" s="15">
-        <f>AD53*Z53+AB53*'01_Cadrage'!$H$29</f>
+        <f>AD53*Z53+AB53*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF53" s="10" t="n">
@@ -24910,7 +25536,7 @@
         <v/>
       </c>
       <c r="AA54" s="14">
-        <f>Y54*Z54+W54*'01_Cadrage'!$H$29</f>
+        <f>Y54*Z54+W54*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB54" s="23">
@@ -24926,7 +25552,7 @@
         <v/>
       </c>
       <c r="AE54" s="15">
-        <f>AD54*Z54+AB54*'01_Cadrage'!$H$29</f>
+        <f>AD54*Z54+AB54*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF54" s="10" t="n">
@@ -25065,7 +25691,7 @@
         <v/>
       </c>
       <c r="AA55" s="14">
-        <f>Y55*Z55+W55*'01_Cadrage'!$H$29</f>
+        <f>Y55*Z55+W55*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB55" s="23">
@@ -25081,7 +25707,7 @@
         <v/>
       </c>
       <c r="AE55" s="15">
-        <f>AD55*Z55+AB55*'01_Cadrage'!$H$29</f>
+        <f>AD55*Z55+AB55*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF55" s="10" t="n">
@@ -25220,7 +25846,7 @@
         <v/>
       </c>
       <c r="AA56" s="14">
-        <f>Y56*Z56+W56*'01_Cadrage'!$H$29</f>
+        <f>Y56*Z56+W56*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB56" s="23">
@@ -25236,7 +25862,7 @@
         <v/>
       </c>
       <c r="AE56" s="15">
-        <f>AD56*Z56+AB56*'01_Cadrage'!$H$29</f>
+        <f>AD56*Z56+AB56*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF56" s="10" t="n">
@@ -25375,7 +26001,7 @@
         <v/>
       </c>
       <c r="AA57" s="14">
-        <f>Y57*Z57+W57*'01_Cadrage'!$H$29</f>
+        <f>Y57*Z57+W57*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB57" s="23">
@@ -25391,7 +26017,7 @@
         <v/>
       </c>
       <c r="AE57" s="15">
-        <f>AD57*Z57+AB57*'01_Cadrage'!$H$29</f>
+        <f>AD57*Z57+AB57*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF57" s="10" t="n">
@@ -25530,7 +26156,7 @@
         <v/>
       </c>
       <c r="AA58" s="14">
-        <f>Y58*Z58+W58*'01_Cadrage'!$H$29</f>
+        <f>Y58*Z58+W58*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB58" s="23">
@@ -25546,7 +26172,7 @@
         <v/>
       </c>
       <c r="AE58" s="15">
-        <f>AD58*Z58+AB58*'01_Cadrage'!$H$29</f>
+        <f>AD58*Z58+AB58*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF58" s="10" t="n">
@@ -25685,7 +26311,7 @@
         <v/>
       </c>
       <c r="AA59" s="14">
-        <f>Y59*Z59+W59*'01_Cadrage'!$H$29</f>
+        <f>Y59*Z59+W59*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB59" s="23">
@@ -25701,7 +26327,7 @@
         <v/>
       </c>
       <c r="AE59" s="15">
-        <f>AD59*Z59+AB59*'01_Cadrage'!$H$29</f>
+        <f>AD59*Z59+AB59*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF59" s="10" t="n">
@@ -25840,7 +26466,7 @@
         <v/>
       </c>
       <c r="AA60" s="14">
-        <f>Y60*Z60+W60*'01_Cadrage'!$H$29</f>
+        <f>Y60*Z60+W60*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB60" s="23">
@@ -25856,7 +26482,7 @@
         <v/>
       </c>
       <c r="AE60" s="15">
-        <f>AD60*Z60+AB60*'01_Cadrage'!$H$29</f>
+        <f>AD60*Z60+AB60*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF60" s="10" t="n">
@@ -25995,7 +26621,7 @@
         <v/>
       </c>
       <c r="AA61" s="14">
-        <f>Y61*Z61+W61*'01_Cadrage'!$H$29</f>
+        <f>Y61*Z61+W61*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AB61" s="23">
@@ -26011,7 +26637,7 @@
         <v/>
       </c>
       <c r="AE61" s="15">
-        <f>AD61*Z61+AB61*'01_Cadrage'!$H$29</f>
+        <f>AD61*Z61+AB61*'01_Cadrage'!$H$30</f>
         <v/>
       </c>
       <c r="AF61" s="10" t="n">
@@ -69431,7 +70057,7 @@
         <v/>
       </c>
       <c r="G21" s="59">
-        <f>F21*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F21*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H21" s="16">
@@ -69463,7 +70089,7 @@
         <v/>
       </c>
       <c r="G22" s="59">
-        <f>F22*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F22*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H22" s="16">
@@ -69495,7 +70121,7 @@
         <v/>
       </c>
       <c r="G23" s="59">
-        <f>F23*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F23*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H23" s="16">
@@ -69527,7 +70153,7 @@
         <v/>
       </c>
       <c r="G24" s="59">
-        <f>F24*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F24*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H24" s="16">
@@ -69591,7 +70217,7 @@
         <v/>
       </c>
       <c r="G26" s="59">
-        <f>F26*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F26*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H26" s="16">
@@ -69623,7 +70249,7 @@
         <v/>
       </c>
       <c r="G27" s="59">
-        <f>F27*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F27*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H27" s="16">
@@ -69655,7 +70281,7 @@
         <v/>
       </c>
       <c r="G28" s="59">
-        <f>F28*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25))</f>
+        <f>F28*((1+'01_Cadrage'!$H$22)*(1-'01_Cadrage'!$H$25)*(1+'01_Cadrage'!$H$26))</f>
         <v/>
       </c>
       <c r="H28" s="16">

--- a/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
+++ b/eduservices/EDUSERVICES_Modele_CA_v3.xlsx
@@ -8937,7 +8937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V177"/>
+  <dimension ref="A1:W177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8961,7 +8961,8 @@
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9086,6 +9087,11 @@
       </c>
       <c r="V3" s="11" t="inlineStr">
         <is>
+          <t>Frais/inscrit</t>
+        </is>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
           <t>Exercice</t>
         </is>
       </c>
@@ -9168,10 +9174,13 @@
         <v/>
       </c>
       <c r="U4" s="48">
-        <f>M4*P4+K4*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V4" s="37" t="n">
+        <f>M4*P4+K4*V4</f>
+        <v/>
+      </c>
+      <c r="V4" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W4" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9253,10 +9262,13 @@
         <v/>
       </c>
       <c r="U5" s="48">
-        <f>M5*P5+K5*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V5" s="37" t="n">
+        <f>M5*P5+K5*V5</f>
+        <v/>
+      </c>
+      <c r="V5" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W5" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9338,10 +9350,13 @@
         <v/>
       </c>
       <c r="U6" s="48">
-        <f>M6*P6+K6*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V6" s="37" t="n">
+        <f>M6*P6+K6*V6</f>
+        <v/>
+      </c>
+      <c r="V6" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W6" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9423,10 +9438,13 @@
         <v/>
       </c>
       <c r="U7" s="48">
-        <f>M7*P7+K7*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V7" s="37" t="n">
+        <f>M7*P7+K7*V7</f>
+        <v/>
+      </c>
+      <c r="V7" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W7" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9508,10 +9526,13 @@
         <v/>
       </c>
       <c r="U8" s="48">
-        <f>M8*P8+K8*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V8" s="37" t="n">
+        <f>M8*P8+K8*V8</f>
+        <v/>
+      </c>
+      <c r="V8" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W8" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9593,10 +9614,13 @@
         <v/>
       </c>
       <c r="U9" s="48">
-        <f>M9*P9+K9*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V9" s="37" t="n">
+        <f>M9*P9+K9*V9</f>
+        <v/>
+      </c>
+      <c r="V9" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W9" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9678,10 +9702,13 @@
         <v/>
       </c>
       <c r="U10" s="48">
-        <f>M10*P10+K10*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V10" s="37" t="n">
+        <f>M10*P10+K10*V10</f>
+        <v/>
+      </c>
+      <c r="V10" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W10" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9763,10 +9790,13 @@
         <v/>
       </c>
       <c r="U11" s="48">
-        <f>M11*P11+K11*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V11" s="37" t="n">
+        <f>M11*P11+K11*V11</f>
+        <v/>
+      </c>
+      <c r="V11" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W11" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9848,10 +9878,13 @@
         <v/>
       </c>
       <c r="U12" s="48">
-        <f>M12*P12+K12*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V12" s="37" t="n">
+        <f>M12*P12+K12*V12</f>
+        <v/>
+      </c>
+      <c r="V12" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W12" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9933,10 +9966,13 @@
         <v/>
       </c>
       <c r="U13" s="48">
-        <f>M13*P13+K13*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V13" s="37" t="n">
+        <f>M13*P13+K13*V13</f>
+        <v/>
+      </c>
+      <c r="V13" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W13" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10018,10 +10054,13 @@
         <v/>
       </c>
       <c r="U14" s="48">
-        <f>M14*P14+K14*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V14" s="37" t="n">
+        <f>M14*P14+K14*V14</f>
+        <v/>
+      </c>
+      <c r="V14" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W14" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10103,10 +10142,13 @@
         <v/>
       </c>
       <c r="U15" s="48">
-        <f>M15*P15+K15*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V15" s="37" t="n">
+        <f>M15*P15+K15*V15</f>
+        <v/>
+      </c>
+      <c r="V15" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W15" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10188,10 +10230,13 @@
         <v/>
       </c>
       <c r="U16" s="48">
-        <f>M16*P16+K16*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V16" s="37" t="n">
+        <f>M16*P16+K16*V16</f>
+        <v/>
+      </c>
+      <c r="V16" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W16" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10273,10 +10318,13 @@
         <v/>
       </c>
       <c r="U17" s="48">
-        <f>M17*P17+K17*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V17" s="37" t="n">
+        <f>M17*P17+K17*V17</f>
+        <v/>
+      </c>
+      <c r="V17" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W17" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10358,10 +10406,13 @@
         <v/>
       </c>
       <c r="U18" s="48">
-        <f>M18*P18+K18*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V18" s="37" t="n">
+        <f>M18*P18+K18*V18</f>
+        <v/>
+      </c>
+      <c r="V18" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W18" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10443,10 +10494,13 @@
         <v/>
       </c>
       <c r="U19" s="48">
-        <f>M19*P19+K19*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V19" s="37" t="n">
+        <f>M19*P19+K19*V19</f>
+        <v/>
+      </c>
+      <c r="V19" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W19" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10528,10 +10582,13 @@
         <v/>
       </c>
       <c r="U20" s="48">
-        <f>M20*P20+K20*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V20" s="37" t="n">
+        <f>M20*P20+K20*V20</f>
+        <v/>
+      </c>
+      <c r="V20" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W20" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10613,10 +10670,13 @@
         <v/>
       </c>
       <c r="U21" s="48">
-        <f>M21*P21+K21*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V21" s="37" t="n">
+        <f>M21*P21+K21*V21</f>
+        <v/>
+      </c>
+      <c r="V21" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W21" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10698,10 +10758,13 @@
         <v/>
       </c>
       <c r="U22" s="48">
-        <f>M22*P22+K22*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V22" s="37" t="n">
+        <f>M22*P22+K22*V22</f>
+        <v/>
+      </c>
+      <c r="V22" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W22" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10783,10 +10846,13 @@
         <v/>
       </c>
       <c r="U23" s="48">
-        <f>M23*P23+K23*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V23" s="37" t="n">
+        <f>M23*P23+K23*V23</f>
+        <v/>
+      </c>
+      <c r="V23" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W23" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10868,10 +10934,13 @@
         <v/>
       </c>
       <c r="U24" s="48">
-        <f>M24*P24+K24*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V24" s="37" t="n">
+        <f>M24*P24+K24*V24</f>
+        <v/>
+      </c>
+      <c r="V24" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W24" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10953,10 +11022,13 @@
         <v/>
       </c>
       <c r="U25" s="48">
-        <f>M25*P25+K25*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V25" s="37" t="n">
+        <f>M25*P25+K25*V25</f>
+        <v/>
+      </c>
+      <c r="V25" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W25" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11038,10 +11110,13 @@
         <v/>
       </c>
       <c r="U26" s="48">
-        <f>M26*P26+K26*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V26" s="37" t="n">
+        <f>M26*P26+K26*V26</f>
+        <v/>
+      </c>
+      <c r="V26" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W26" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11123,10 +11198,13 @@
         <v/>
       </c>
       <c r="U27" s="48">
-        <f>M27*P27+K27*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V27" s="37" t="n">
+        <f>M27*P27+K27*V27</f>
+        <v/>
+      </c>
+      <c r="V27" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W27" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11208,10 +11286,13 @@
         <v/>
       </c>
       <c r="U28" s="48">
-        <f>M28*P28+K28*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V28" s="37" t="n">
+        <f>M28*P28+K28*V28</f>
+        <v/>
+      </c>
+      <c r="V28" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W28" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11293,10 +11374,13 @@
         <v/>
       </c>
       <c r="U29" s="48">
-        <f>M29*P29+K29*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V29" s="37" t="n">
+        <f>M29*P29+K29*V29</f>
+        <v/>
+      </c>
+      <c r="V29" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W29" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11378,10 +11462,13 @@
         <v/>
       </c>
       <c r="U30" s="48">
-        <f>M30*P30+K30*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V30" s="37" t="n">
+        <f>M30*P30+K30*V30</f>
+        <v/>
+      </c>
+      <c r="V30" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W30" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11463,10 +11550,13 @@
         <v/>
       </c>
       <c r="U31" s="48">
-        <f>M31*P31+K31*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V31" s="37" t="n">
+        <f>M31*P31+K31*V31</f>
+        <v/>
+      </c>
+      <c r="V31" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W31" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11548,10 +11638,13 @@
         <v/>
       </c>
       <c r="U32" s="48">
-        <f>M32*P32+K32*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V32" s="37" t="n">
+        <f>M32*P32+K32*V32</f>
+        <v/>
+      </c>
+      <c r="V32" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W32" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11633,10 +11726,13 @@
         <v/>
       </c>
       <c r="U33" s="48">
-        <f>M33*P33+K33*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V33" s="37" t="n">
+        <f>M33*P33+K33*V33</f>
+        <v/>
+      </c>
+      <c r="V33" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W33" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11718,10 +11814,13 @@
         <v/>
       </c>
       <c r="U34" s="48">
-        <f>M34*P34+K34*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V34" s="37" t="n">
+        <f>M34*P34+K34*V34</f>
+        <v/>
+      </c>
+      <c r="V34" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W34" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11803,10 +11902,13 @@
         <v/>
       </c>
       <c r="U35" s="48">
-        <f>M35*P35+K35*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V35" s="37" t="n">
+        <f>M35*P35+K35*V35</f>
+        <v/>
+      </c>
+      <c r="V35" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W35" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11888,10 +11990,13 @@
         <v/>
       </c>
       <c r="U36" s="48">
-        <f>M36*P36+K36*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V36" s="37" t="n">
+        <f>M36*P36+K36*V36</f>
+        <v/>
+      </c>
+      <c r="V36" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W36" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11973,10 +12078,13 @@
         <v/>
       </c>
       <c r="U37" s="48">
-        <f>M37*P37+K37*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V37" s="37" t="n">
+        <f>M37*P37+K37*V37</f>
+        <v/>
+      </c>
+      <c r="V37" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W37" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12058,10 +12166,13 @@
         <v/>
       </c>
       <c r="U38" s="48">
-        <f>M38*P38+K38*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V38" s="37" t="n">
+        <f>M38*P38+K38*V38</f>
+        <v/>
+      </c>
+      <c r="V38" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W38" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12143,10 +12254,13 @@
         <v/>
       </c>
       <c r="U39" s="48">
-        <f>M39*P39+K39*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V39" s="37" t="n">
+        <f>M39*P39+K39*V39</f>
+        <v/>
+      </c>
+      <c r="V39" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W39" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12228,10 +12342,13 @@
         <v/>
       </c>
       <c r="U40" s="48">
-        <f>M40*P40+K40*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V40" s="37" t="n">
+        <f>M40*P40+K40*V40</f>
+        <v/>
+      </c>
+      <c r="V40" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W40" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12313,10 +12430,13 @@
         <v/>
       </c>
       <c r="U41" s="48">
-        <f>M41*P41+K41*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V41" s="37" t="n">
+        <f>M41*P41+K41*V41</f>
+        <v/>
+      </c>
+      <c r="V41" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W41" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12398,10 +12518,13 @@
         <v/>
       </c>
       <c r="U42" s="48">
-        <f>M42*P42+K42*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V42" s="37" t="n">
+        <f>M42*P42+K42*V42</f>
+        <v/>
+      </c>
+      <c r="V42" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W42" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12483,10 +12606,13 @@
         <v/>
       </c>
       <c r="U43" s="48">
-        <f>M43*P43+K43*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V43" s="37" t="n">
+        <f>M43*P43+K43*V43</f>
+        <v/>
+      </c>
+      <c r="V43" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W43" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12568,10 +12694,13 @@
         <v/>
       </c>
       <c r="U44" s="48">
-        <f>M44*P44+K44*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V44" s="37" t="n">
+        <f>M44*P44+K44*V44</f>
+        <v/>
+      </c>
+      <c r="V44" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W44" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12653,10 +12782,13 @@
         <v/>
       </c>
       <c r="U45" s="48">
-        <f>M45*P45+K45*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V45" s="37" t="n">
+        <f>M45*P45+K45*V45</f>
+        <v/>
+      </c>
+      <c r="V45" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W45" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12738,10 +12870,13 @@
         <v/>
       </c>
       <c r="U46" s="48">
-        <f>M46*P46+K46*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V46" s="37" t="n">
+        <f>M46*P46+K46*V46</f>
+        <v/>
+      </c>
+      <c r="V46" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W46" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12823,10 +12958,13 @@
         <v/>
       </c>
       <c r="U47" s="48">
-        <f>M47*P47+K47*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V47" s="37" t="n">
+        <f>M47*P47+K47*V47</f>
+        <v/>
+      </c>
+      <c r="V47" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W47" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12908,10 +13046,13 @@
         <v/>
       </c>
       <c r="U48" s="48">
-        <f>M48*P48+K48*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V48" s="37" t="n">
+        <f>M48*P48+K48*V48</f>
+        <v/>
+      </c>
+      <c r="V48" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W48" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12993,10 +13134,13 @@
         <v/>
       </c>
       <c r="U49" s="48">
-        <f>M49*P49+K49*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V49" s="37" t="n">
+        <f>M49*P49+K49*V49</f>
+        <v/>
+      </c>
+      <c r="V49" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W49" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13078,10 +13222,13 @@
         <v/>
       </c>
       <c r="U50" s="48">
-        <f>M50*P50+K50*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V50" s="37" t="n">
+        <f>M50*P50+K50*V50</f>
+        <v/>
+      </c>
+      <c r="V50" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W50" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13163,10 +13310,13 @@
         <v/>
       </c>
       <c r="U51" s="48">
-        <f>M51*P51+K51*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V51" s="37" t="n">
+        <f>M51*P51+K51*V51</f>
+        <v/>
+      </c>
+      <c r="V51" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W51" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13248,10 +13398,13 @@
         <v/>
       </c>
       <c r="U52" s="48">
-        <f>M52*P52+K52*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V52" s="37" t="n">
+        <f>M52*P52+K52*V52</f>
+        <v/>
+      </c>
+      <c r="V52" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W52" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13333,10 +13486,13 @@
         <v/>
       </c>
       <c r="U53" s="48">
-        <f>M53*P53+K53*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V53" s="37" t="n">
+        <f>M53*P53+K53*V53</f>
+        <v/>
+      </c>
+      <c r="V53" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W53" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13418,10 +13574,13 @@
         <v/>
       </c>
       <c r="U54" s="48">
-        <f>M54*P54+K54*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V54" s="37" t="n">
+        <f>M54*P54+K54*V54</f>
+        <v/>
+      </c>
+      <c r="V54" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W54" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13503,10 +13662,13 @@
         <v/>
       </c>
       <c r="U55" s="48">
-        <f>M55*P55+K55*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V55" s="37" t="n">
+        <f>M55*P55+K55*V55</f>
+        <v/>
+      </c>
+      <c r="V55" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W55" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13588,10 +13750,13 @@
         <v/>
       </c>
       <c r="U56" s="48">
-        <f>M56*P56+K56*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V56" s="37" t="n">
+        <f>M56*P56+K56*V56</f>
+        <v/>
+      </c>
+      <c r="V56" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W56" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13673,10 +13838,13 @@
         <v/>
       </c>
       <c r="U57" s="48">
-        <f>M57*P57+K57*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V57" s="37" t="n">
+        <f>M57*P57+K57*V57</f>
+        <v/>
+      </c>
+      <c r="V57" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W57" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13758,10 +13926,13 @@
         <v/>
       </c>
       <c r="U58" s="48">
-        <f>M58*P58+K58*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V58" s="37" t="n">
+        <f>M58*P58+K58*V58</f>
+        <v/>
+      </c>
+      <c r="V58" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W58" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13843,10 +14014,13 @@
         <v/>
       </c>
       <c r="U59" s="48">
-        <f>M59*P59+K59*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V59" s="37" t="n">
+        <f>M59*P59+K59*V59</f>
+        <v/>
+      </c>
+      <c r="V59" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W59" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13928,10 +14102,13 @@
         <v/>
       </c>
       <c r="U60" s="48">
-        <f>M60*P60+K60*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V60" s="37" t="n">
+        <f>M60*P60+K60*V60</f>
+        <v/>
+      </c>
+      <c r="V60" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W60" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14013,10 +14190,13 @@
         <v/>
       </c>
       <c r="U61" s="48">
-        <f>M61*P61+K61*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V61" s="37" t="n">
+        <f>M61*P61+K61*V61</f>
+        <v/>
+      </c>
+      <c r="V61" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W61" s="37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14098,10 +14278,13 @@
         <v/>
       </c>
       <c r="U62" s="48">
-        <f>M62*P62+K62*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V62" s="37" t="n">
+        <f>M62*P62+K62*V62</f>
+        <v/>
+      </c>
+      <c r="V62" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W62" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14183,10 +14366,13 @@
         <v/>
       </c>
       <c r="U63" s="48">
-        <f>M63*P63+K63*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V63" s="37" t="n">
+        <f>M63*P63+K63*V63</f>
+        <v/>
+      </c>
+      <c r="V63" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W63" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14268,10 +14454,13 @@
         <v/>
       </c>
       <c r="U64" s="48">
-        <f>M64*P64+K64*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V64" s="37" t="n">
+        <f>M64*P64+K64*V64</f>
+        <v/>
+      </c>
+      <c r="V64" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W64" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14353,10 +14542,13 @@
         <v/>
       </c>
       <c r="U65" s="48">
-        <f>M65*P65+K65*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V65" s="37" t="n">
+        <f>M65*P65+K65*V65</f>
+        <v/>
+      </c>
+      <c r="V65" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W65" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14438,10 +14630,13 @@
         <v/>
       </c>
       <c r="U66" s="48">
-        <f>M66*P66+K66*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V66" s="37" t="n">
+        <f>M66*P66+K66*V66</f>
+        <v/>
+      </c>
+      <c r="V66" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W66" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14523,10 +14718,13 @@
         <v/>
       </c>
       <c r="U67" s="48">
-        <f>M67*P67+K67*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V67" s="37" t="n">
+        <f>M67*P67+K67*V67</f>
+        <v/>
+      </c>
+      <c r="V67" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W67" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14608,10 +14806,13 @@
         <v/>
       </c>
       <c r="U68" s="48">
-        <f>M68*P68+K68*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V68" s="37" t="n">
+        <f>M68*P68+K68*V68</f>
+        <v/>
+      </c>
+      <c r="V68" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W68" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14693,10 +14894,13 @@
         <v/>
       </c>
       <c r="U69" s="48">
-        <f>M69*P69+K69*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V69" s="37" t="n">
+        <f>M69*P69+K69*V69</f>
+        <v/>
+      </c>
+      <c r="V69" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W69" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14778,10 +14982,13 @@
         <v/>
       </c>
       <c r="U70" s="48">
-        <f>M70*P70+K70*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V70" s="37" t="n">
+        <f>M70*P70+K70*V70</f>
+        <v/>
+      </c>
+      <c r="V70" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W70" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14863,10 +15070,13 @@
         <v/>
       </c>
       <c r="U71" s="48">
-        <f>M71*P71+K71*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V71" s="37" t="n">
+        <f>M71*P71+K71*V71</f>
+        <v/>
+      </c>
+      <c r="V71" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W71" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -14948,10 +15158,13 @@
         <v/>
       </c>
       <c r="U72" s="48">
-        <f>M72*P72+K72*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V72" s="37" t="n">
+        <f>M72*P72+K72*V72</f>
+        <v/>
+      </c>
+      <c r="V72" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W72" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15033,10 +15246,13 @@
         <v/>
       </c>
       <c r="U73" s="48">
-        <f>M73*P73+K73*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V73" s="37" t="n">
+        <f>M73*P73+K73*V73</f>
+        <v/>
+      </c>
+      <c r="V73" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W73" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15118,10 +15334,13 @@
         <v/>
       </c>
       <c r="U74" s="48">
-        <f>M74*P74+K74*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V74" s="37" t="n">
+        <f>M74*P74+K74*V74</f>
+        <v/>
+      </c>
+      <c r="V74" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W74" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15203,10 +15422,13 @@
         <v/>
       </c>
       <c r="U75" s="48">
-        <f>M75*P75+K75*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V75" s="37" t="n">
+        <f>M75*P75+K75*V75</f>
+        <v/>
+      </c>
+      <c r="V75" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W75" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15288,10 +15510,13 @@
         <v/>
       </c>
       <c r="U76" s="48">
-        <f>M76*P76+K76*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V76" s="37" t="n">
+        <f>M76*P76+K76*V76</f>
+        <v/>
+      </c>
+      <c r="V76" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W76" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15373,10 +15598,13 @@
         <v/>
       </c>
       <c r="U77" s="48">
-        <f>M77*P77+K77*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V77" s="37" t="n">
+        <f>M77*P77+K77*V77</f>
+        <v/>
+      </c>
+      <c r="V77" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W77" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15458,10 +15686,13 @@
         <v/>
       </c>
       <c r="U78" s="48">
-        <f>M78*P78+K78*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V78" s="37" t="n">
+        <f>M78*P78+K78*V78</f>
+        <v/>
+      </c>
+      <c r="V78" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W78" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15543,10 +15774,13 @@
         <v/>
       </c>
       <c r="U79" s="48">
-        <f>M79*P79+K79*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V79" s="37" t="n">
+        <f>M79*P79+K79*V79</f>
+        <v/>
+      </c>
+      <c r="V79" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W79" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15628,10 +15862,13 @@
         <v/>
       </c>
       <c r="U80" s="48">
-        <f>M80*P80+K80*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V80" s="37" t="n">
+        <f>M80*P80+K80*V80</f>
+        <v/>
+      </c>
+      <c r="V80" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W80" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15713,10 +15950,13 @@
         <v/>
       </c>
       <c r="U81" s="48">
-        <f>M81*P81+K81*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V81" s="37" t="n">
+        <f>M81*P81+K81*V81</f>
+        <v/>
+      </c>
+      <c r="V81" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W81" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15798,10 +16038,13 @@
         <v/>
       </c>
       <c r="U82" s="48">
-        <f>M82*P82+K82*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V82" s="37" t="n">
+        <f>M82*P82+K82*V82</f>
+        <v/>
+      </c>
+      <c r="V82" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W82" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15883,10 +16126,13 @@
         <v/>
       </c>
       <c r="U83" s="48">
-        <f>M83*P83+K83*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V83" s="37" t="n">
+        <f>M83*P83+K83*V83</f>
+        <v/>
+      </c>
+      <c r="V83" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W83" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -15968,10 +16214,13 @@
         <v/>
       </c>
       <c r="U84" s="48">
-        <f>M84*P84+K84*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V84" s="37" t="n">
+        <f>M84*P84+K84*V84</f>
+        <v/>
+      </c>
+      <c r="V84" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W84" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16053,10 +16302,13 @@
         <v/>
       </c>
       <c r="U85" s="48">
-        <f>M85*P85+K85*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V85" s="37" t="n">
+        <f>M85*P85+K85*V85</f>
+        <v/>
+      </c>
+      <c r="V85" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W85" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16138,10 +16390,13 @@
         <v/>
       </c>
       <c r="U86" s="48">
-        <f>M86*P86+K86*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V86" s="37" t="n">
+        <f>M86*P86+K86*V86</f>
+        <v/>
+      </c>
+      <c r="V86" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W86" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16223,10 +16478,13 @@
         <v/>
       </c>
       <c r="U87" s="48">
-        <f>M87*P87+K87*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V87" s="37" t="n">
+        <f>M87*P87+K87*V87</f>
+        <v/>
+      </c>
+      <c r="V87" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W87" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16308,10 +16566,13 @@
         <v/>
       </c>
       <c r="U88" s="48">
-        <f>M88*P88+K88*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V88" s="37" t="n">
+        <f>M88*P88+K88*V88</f>
+        <v/>
+      </c>
+      <c r="V88" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W88" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16393,10 +16654,13 @@
         <v/>
       </c>
       <c r="U89" s="48">
-        <f>M89*P89+K89*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V89" s="37" t="n">
+        <f>M89*P89+K89*V89</f>
+        <v/>
+      </c>
+      <c r="V89" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W89" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16478,10 +16742,13 @@
         <v/>
       </c>
       <c r="U90" s="48">
-        <f>M90*P90+K90*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V90" s="37" t="n">
+        <f>M90*P90+K90*V90</f>
+        <v/>
+      </c>
+      <c r="V90" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W90" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16563,10 +16830,13 @@
         <v/>
       </c>
       <c r="U91" s="48">
-        <f>M91*P91+K91*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V91" s="37" t="n">
+        <f>M91*P91+K91*V91</f>
+        <v/>
+      </c>
+      <c r="V91" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W91" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16648,10 +16918,13 @@
         <v/>
       </c>
       <c r="U92" s="48">
-        <f>M92*P92+K92*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V92" s="37" t="n">
+        <f>M92*P92+K92*V92</f>
+        <v/>
+      </c>
+      <c r="V92" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W92" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16733,10 +17006,13 @@
         <v/>
       </c>
       <c r="U93" s="48">
-        <f>M93*P93+K93*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V93" s="37" t="n">
+        <f>M93*P93+K93*V93</f>
+        <v/>
+      </c>
+      <c r="V93" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W93" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16818,10 +17094,13 @@
         <v/>
       </c>
       <c r="U94" s="48">
-        <f>M94*P94+K94*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V94" s="37" t="n">
+        <f>M94*P94+K94*V94</f>
+        <v/>
+      </c>
+      <c r="V94" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W94" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16903,10 +17182,13 @@
         <v/>
       </c>
       <c r="U95" s="48">
-        <f>M95*P95+K95*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V95" s="37" t="n">
+        <f>M95*P95+K95*V95</f>
+        <v/>
+      </c>
+      <c r="V95" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W95" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -16988,10 +17270,13 @@
         <v/>
       </c>
       <c r="U96" s="48">
-        <f>M96*P96+K96*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V96" s="37" t="n">
+        <f>M96*P96+K96*V96</f>
+        <v/>
+      </c>
+      <c r="V96" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W96" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17073,10 +17358,13 @@
         <v/>
       </c>
       <c r="U97" s="48">
-        <f>M97*P97+K97*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V97" s="37" t="n">
+        <f>M97*P97+K97*V97</f>
+        <v/>
+      </c>
+      <c r="V97" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W97" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17158,10 +17446,13 @@
         <v/>
       </c>
       <c r="U98" s="48">
-        <f>M98*P98+K98*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V98" s="37" t="n">
+        <f>M98*P98+K98*V98</f>
+        <v/>
+      </c>
+      <c r="V98" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W98" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17243,10 +17534,13 @@
         <v/>
       </c>
       <c r="U99" s="48">
-        <f>M99*P99+K99*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V99" s="37" t="n">
+        <f>M99*P99+K99*V99</f>
+        <v/>
+      </c>
+      <c r="V99" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W99" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17328,10 +17622,13 @@
         <v/>
       </c>
       <c r="U100" s="48">
-        <f>M100*P100+K100*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V100" s="37" t="n">
+        <f>M100*P100+K100*V100</f>
+        <v/>
+      </c>
+      <c r="V100" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W100" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17413,10 +17710,13 @@
         <v/>
       </c>
       <c r="U101" s="48">
-        <f>M101*P101+K101*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V101" s="37" t="n">
+        <f>M101*P101+K101*V101</f>
+        <v/>
+      </c>
+      <c r="V101" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W101" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17498,10 +17798,13 @@
         <v/>
       </c>
       <c r="U102" s="48">
-        <f>M102*P102+K102*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V102" s="37" t="n">
+        <f>M102*P102+K102*V102</f>
+        <v/>
+      </c>
+      <c r="V102" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W102" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17583,10 +17886,13 @@
         <v/>
       </c>
       <c r="U103" s="48">
-        <f>M103*P103+K103*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V103" s="37" t="n">
+        <f>M103*P103+K103*V103</f>
+        <v/>
+      </c>
+      <c r="V103" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W103" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17668,10 +17974,13 @@
         <v/>
       </c>
       <c r="U104" s="48">
-        <f>M104*P104+K104*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V104" s="37" t="n">
+        <f>M104*P104+K104*V104</f>
+        <v/>
+      </c>
+      <c r="V104" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W104" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17753,10 +18062,13 @@
         <v/>
       </c>
       <c r="U105" s="48">
-        <f>M105*P105+K105*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V105" s="37" t="n">
+        <f>M105*P105+K105*V105</f>
+        <v/>
+      </c>
+      <c r="V105" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W105" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17838,10 +18150,13 @@
         <v/>
       </c>
       <c r="U106" s="48">
-        <f>M106*P106+K106*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V106" s="37" t="n">
+        <f>M106*P106+K106*V106</f>
+        <v/>
+      </c>
+      <c r="V106" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W106" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -17923,10 +18238,13 @@
         <v/>
       </c>
       <c r="U107" s="48">
-        <f>M107*P107+K107*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V107" s="37" t="n">
+        <f>M107*P107+K107*V107</f>
+        <v/>
+      </c>
+      <c r="V107" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W107" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18008,10 +18326,13 @@
         <v/>
       </c>
       <c r="U108" s="48">
-        <f>M108*P108+K108*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V108" s="37" t="n">
+        <f>M108*P108+K108*V108</f>
+        <v/>
+      </c>
+      <c r="V108" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W108" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18093,10 +18414,13 @@
         <v/>
       </c>
       <c r="U109" s="48">
-        <f>M109*P109+K109*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V109" s="37" t="n">
+        <f>M109*P109+K109*V109</f>
+        <v/>
+      </c>
+      <c r="V109" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W109" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18178,10 +18502,13 @@
         <v/>
       </c>
       <c r="U110" s="48">
-        <f>M110*P110+K110*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V110" s="37" t="n">
+        <f>M110*P110+K110*V110</f>
+        <v/>
+      </c>
+      <c r="V110" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W110" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18263,10 +18590,13 @@
         <v/>
       </c>
       <c r="U111" s="48">
-        <f>M111*P111+K111*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V111" s="37" t="n">
+        <f>M111*P111+K111*V111</f>
+        <v/>
+      </c>
+      <c r="V111" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W111" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18348,10 +18678,13 @@
         <v/>
       </c>
       <c r="U112" s="48">
-        <f>M112*P112+K112*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V112" s="37" t="n">
+        <f>M112*P112+K112*V112</f>
+        <v/>
+      </c>
+      <c r="V112" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W112" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18433,10 +18766,13 @@
         <v/>
       </c>
       <c r="U113" s="48">
-        <f>M113*P113+K113*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V113" s="37" t="n">
+        <f>M113*P113+K113*V113</f>
+        <v/>
+      </c>
+      <c r="V113" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W113" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18518,10 +18854,13 @@
         <v/>
       </c>
       <c r="U114" s="48">
-        <f>M114*P114+K114*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V114" s="37" t="n">
+        <f>M114*P114+K114*V114</f>
+        <v/>
+      </c>
+      <c r="V114" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W114" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18603,10 +18942,13 @@
         <v/>
       </c>
       <c r="U115" s="48">
-        <f>M115*P115+K115*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V115" s="37" t="n">
+        <f>M115*P115+K115*V115</f>
+        <v/>
+      </c>
+      <c r="V115" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W115" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18688,10 +19030,13 @@
         <v/>
       </c>
       <c r="U116" s="48">
-        <f>M116*P116+K116*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V116" s="37" t="n">
+        <f>M116*P116+K116*V116</f>
+        <v/>
+      </c>
+      <c r="V116" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W116" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18773,10 +19118,13 @@
         <v/>
       </c>
       <c r="U117" s="48">
-        <f>M117*P117+K117*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V117" s="37" t="n">
+        <f>M117*P117+K117*V117</f>
+        <v/>
+      </c>
+      <c r="V117" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W117" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18858,10 +19206,13 @@
         <v/>
       </c>
       <c r="U118" s="48">
-        <f>M118*P118+K118*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V118" s="37" t="n">
+        <f>M118*P118+K118*V118</f>
+        <v/>
+      </c>
+      <c r="V118" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W118" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -18943,10 +19294,13 @@
         <v/>
       </c>
       <c r="U119" s="48">
-        <f>M119*P119+K119*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V119" s="37" t="n">
+        <f>M119*P119+K119*V119</f>
+        <v/>
+      </c>
+      <c r="V119" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W119" s="37" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -19028,10 +19382,13 @@
         <v/>
       </c>
       <c r="U120" s="48">
-        <f>M120*P120+K120*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V120" s="37" t="n">
+        <f>M120*P120+K120*V120</f>
+        <v/>
+      </c>
+      <c r="V120" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W120" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19113,10 +19470,13 @@
         <v/>
       </c>
       <c r="U121" s="48">
-        <f>M121*P121+K121*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V121" s="37" t="n">
+        <f>M121*P121+K121*V121</f>
+        <v/>
+      </c>
+      <c r="V121" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W121" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19198,10 +19558,13 @@
         <v/>
       </c>
       <c r="U122" s="48">
-        <f>M122*P122+K122*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V122" s="37" t="n">
+        <f>M122*P122+K122*V122</f>
+        <v/>
+      </c>
+      <c r="V122" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W122" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19283,10 +19646,13 @@
         <v/>
       </c>
       <c r="U123" s="48">
-        <f>M123*P123+K123*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V123" s="37" t="n">
+        <f>M123*P123+K123*V123</f>
+        <v/>
+      </c>
+      <c r="V123" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W123" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19368,10 +19734,13 @@
         <v/>
       </c>
       <c r="U124" s="48">
-        <f>M124*P124+K124*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V124" s="37" t="n">
+        <f>M124*P124+K124*V124</f>
+        <v/>
+      </c>
+      <c r="V124" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W124" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19453,10 +19822,13 @@
         <v/>
       </c>
       <c r="U125" s="48">
-        <f>M125*P125+K125*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V125" s="37" t="n">
+        <f>M125*P125+K125*V125</f>
+        <v/>
+      </c>
+      <c r="V125" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W125" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19538,10 +19910,13 @@
         <v/>
       </c>
       <c r="U126" s="48">
-        <f>M126*P126+K126*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V126" s="37" t="n">
+        <f>M126*P126+K126*V126</f>
+        <v/>
+      </c>
+      <c r="V126" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W126" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19623,10 +19998,13 @@
         <v/>
       </c>
       <c r="U127" s="48">
-        <f>M127*P127+K127*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V127" s="37" t="n">
+        <f>M127*P127+K127*V127</f>
+        <v/>
+      </c>
+      <c r="V127" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W127" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19708,10 +20086,13 @@
         <v/>
       </c>
       <c r="U128" s="48">
-        <f>M128*P128+K128*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V128" s="37" t="n">
+        <f>M128*P128+K128*V128</f>
+        <v/>
+      </c>
+      <c r="V128" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W128" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19793,10 +20174,13 @@
         <v/>
       </c>
       <c r="U129" s="48">
-        <f>M129*P129+K129*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V129" s="37" t="n">
+        <f>M129*P129+K129*V129</f>
+        <v/>
+      </c>
+      <c r="V129" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W129" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19878,10 +20262,13 @@
         <v/>
       </c>
       <c r="U130" s="48">
-        <f>M130*P130+K130*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V130" s="37" t="n">
+        <f>M130*P130+K130*V130</f>
+        <v/>
+      </c>
+      <c r="V130" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W130" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -19963,10 +20350,13 @@
         <v/>
       </c>
       <c r="U131" s="48">
-        <f>M131*P131+K131*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V131" s="37" t="n">
+        <f>M131*P131+K131*V131</f>
+        <v/>
+      </c>
+      <c r="V131" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W131" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20048,10 +20438,13 @@
         <v/>
       </c>
       <c r="U132" s="48">
-        <f>M132*P132+K132*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V132" s="37" t="n">
+        <f>M132*P132+K132*V132</f>
+        <v/>
+      </c>
+      <c r="V132" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W132" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20133,10 +20526,13 @@
         <v/>
       </c>
       <c r="U133" s="48">
-        <f>M133*P133+K133*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V133" s="37" t="n">
+        <f>M133*P133+K133*V133</f>
+        <v/>
+      </c>
+      <c r="V133" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W133" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20218,10 +20614,13 @@
         <v/>
       </c>
       <c r="U134" s="48">
-        <f>M134*P134+K134*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V134" s="37" t="n">
+        <f>M134*P134+K134*V134</f>
+        <v/>
+      </c>
+      <c r="V134" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W134" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20303,10 +20702,13 @@
         <v/>
       </c>
       <c r="U135" s="48">
-        <f>M135*P135+K135*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V135" s="37" t="n">
+        <f>M135*P135+K135*V135</f>
+        <v/>
+      </c>
+      <c r="V135" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W135" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20388,10 +20790,13 @@
         <v/>
       </c>
       <c r="U136" s="48">
-        <f>M136*P136+K136*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V136" s="37" t="n">
+        <f>M136*P136+K136*V136</f>
+        <v/>
+      </c>
+      <c r="V136" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W136" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20473,10 +20878,13 @@
         <v/>
       </c>
       <c r="U137" s="48">
-        <f>M137*P137+K137*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V137" s="37" t="n">
+        <f>M137*P137+K137*V137</f>
+        <v/>
+      </c>
+      <c r="V137" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W137" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20558,10 +20966,13 @@
         <v/>
       </c>
       <c r="U138" s="48">
-        <f>M138*P138+K138*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V138" s="37" t="n">
+        <f>M138*P138+K138*V138</f>
+        <v/>
+      </c>
+      <c r="V138" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W138" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20643,10 +21054,13 @@
         <v/>
       </c>
       <c r="U139" s="48">
-        <f>M139*P139+K139*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V139" s="37" t="n">
+        <f>M139*P139+K139*V139</f>
+        <v/>
+      </c>
+      <c r="V139" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W139" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20728,10 +21142,13 @@
         <v/>
       </c>
       <c r="U140" s="48">
-        <f>M140*P140+K140*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V140" s="37" t="n">
+        <f>M140*P140+K140*V140</f>
+        <v/>
+      </c>
+      <c r="V140" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W140" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20813,10 +21230,13 @@
         <v/>
       </c>
       <c r="U141" s="48">
-        <f>M141*P141+K141*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V141" s="37" t="n">
+        <f>M141*P141+K141*V141</f>
+        <v/>
+      </c>
+      <c r="V141" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W141" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20898,10 +21318,13 @@
         <v/>
       </c>
       <c r="U142" s="48">
-        <f>M142*P142+K142*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V142" s="37" t="n">
+        <f>M142*P142+K142*V142</f>
+        <v/>
+      </c>
+      <c r="V142" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W142" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -20983,10 +21406,13 @@
         <v/>
       </c>
       <c r="U143" s="48">
-        <f>M143*P143+K143*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V143" s="37" t="n">
+        <f>M143*P143+K143*V143</f>
+        <v/>
+      </c>
+      <c r="V143" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W143" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21068,10 +21494,13 @@
         <v/>
       </c>
       <c r="U144" s="48">
-        <f>M144*P144+K144*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V144" s="37" t="n">
+        <f>M144*P144+K144*V144</f>
+        <v/>
+      </c>
+      <c r="V144" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W144" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21153,10 +21582,13 @@
         <v/>
       </c>
       <c r="U145" s="48">
-        <f>M145*P145+K145*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V145" s="37" t="n">
+        <f>M145*P145+K145*V145</f>
+        <v/>
+      </c>
+      <c r="V145" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W145" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21238,10 +21670,13 @@
         <v/>
       </c>
       <c r="U146" s="48">
-        <f>M146*P146+K146*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V146" s="37" t="n">
+        <f>M146*P146+K146*V146</f>
+        <v/>
+      </c>
+      <c r="V146" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W146" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21323,10 +21758,13 @@
         <v/>
       </c>
       <c r="U147" s="48">
-        <f>M147*P147+K147*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V147" s="37" t="n">
+        <f>M147*P147+K147*V147</f>
+        <v/>
+      </c>
+      <c r="V147" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W147" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21408,10 +21846,13 @@
         <v/>
       </c>
       <c r="U148" s="48">
-        <f>M148*P148+K148*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V148" s="37" t="n">
+        <f>M148*P148+K148*V148</f>
+        <v/>
+      </c>
+      <c r="V148" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W148" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21493,10 +21934,13 @@
         <v/>
       </c>
       <c r="U149" s="48">
-        <f>M149*P149+K149*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V149" s="37" t="n">
+        <f>M149*P149+K149*V149</f>
+        <v/>
+      </c>
+      <c r="V149" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W149" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21578,10 +22022,13 @@
         <v/>
       </c>
       <c r="U150" s="48">
-        <f>M150*P150+K150*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V150" s="37" t="n">
+        <f>M150*P150+K150*V150</f>
+        <v/>
+      </c>
+      <c r="V150" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W150" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21663,10 +22110,13 @@
         <v/>
       </c>
       <c r="U151" s="48">
-        <f>M151*P151+K151*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V151" s="37" t="n">
+        <f>M151*P151+K151*V151</f>
+        <v/>
+      </c>
+      <c r="V151" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W151" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21748,10 +22198,13 @@
         <v/>
       </c>
       <c r="U152" s="48">
-        <f>M152*P152+K152*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V152" s="37" t="n">
+        <f>M152*P152+K152*V152</f>
+        <v/>
+      </c>
+      <c r="V152" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W152" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21833,10 +22286,13 @@
         <v/>
       </c>
       <c r="U153" s="48">
-        <f>M153*P153+K153*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V153" s="37" t="n">
+        <f>M153*P153+K153*V153</f>
+        <v/>
+      </c>
+      <c r="V153" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W153" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -21918,10 +22374,13 @@
         <v/>
       </c>
       <c r="U154" s="48">
-        <f>M154*P154+K154*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V154" s="37" t="n">
+        <f>M154*P154+K154*V154</f>
+        <v/>
+      </c>
+      <c r="V154" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W154" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22003,10 +22462,13 @@
         <v/>
       </c>
       <c r="U155" s="48">
-        <f>M155*P155+K155*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V155" s="37" t="n">
+        <f>M155*P155+K155*V155</f>
+        <v/>
+      </c>
+      <c r="V155" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W155" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22088,10 +22550,13 @@
         <v/>
       </c>
       <c r="U156" s="48">
-        <f>M156*P156+K156*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V156" s="37" t="n">
+        <f>M156*P156+K156*V156</f>
+        <v/>
+      </c>
+      <c r="V156" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W156" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22173,10 +22638,13 @@
         <v/>
       </c>
       <c r="U157" s="48">
-        <f>M157*P157+K157*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V157" s="37" t="n">
+        <f>M157*P157+K157*V157</f>
+        <v/>
+      </c>
+      <c r="V157" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W157" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22258,10 +22726,13 @@
         <v/>
       </c>
       <c r="U158" s="48">
-        <f>M158*P158+K158*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V158" s="37" t="n">
+        <f>M158*P158+K158*V158</f>
+        <v/>
+      </c>
+      <c r="V158" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W158" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22343,10 +22814,13 @@
         <v/>
       </c>
       <c r="U159" s="48">
-        <f>M159*P159+K159*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V159" s="37" t="n">
+        <f>M159*P159+K159*V159</f>
+        <v/>
+      </c>
+      <c r="V159" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W159" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22428,10 +22902,13 @@
         <v/>
       </c>
       <c r="U160" s="48">
-        <f>M160*P160+K160*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V160" s="37" t="n">
+        <f>M160*P160+K160*V160</f>
+        <v/>
+      </c>
+      <c r="V160" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W160" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22513,10 +22990,13 @@
         <v/>
       </c>
       <c r="U161" s="48">
-        <f>M161*P161+K161*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V161" s="37" t="n">
+        <f>M161*P161+K161*V161</f>
+        <v/>
+      </c>
+      <c r="V161" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W161" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22598,10 +23078,13 @@
         <v/>
       </c>
       <c r="U162" s="48">
-        <f>M162*P162+K162*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V162" s="37" t="n">
+        <f>M162*P162+K162*V162</f>
+        <v/>
+      </c>
+      <c r="V162" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W162" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22683,10 +23166,13 @@
         <v/>
       </c>
       <c r="U163" s="48">
-        <f>M163*P163+K163*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V163" s="37" t="n">
+        <f>M163*P163+K163*V163</f>
+        <v/>
+      </c>
+      <c r="V163" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W163" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22768,10 +23254,13 @@
         <v/>
       </c>
       <c r="U164" s="48">
-        <f>M164*P164+K164*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V164" s="37" t="n">
+        <f>M164*P164+K164*V164</f>
+        <v/>
+      </c>
+      <c r="V164" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W164" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22853,10 +23342,13 @@
         <v/>
       </c>
       <c r="U165" s="48">
-        <f>M165*P165+K165*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V165" s="37" t="n">
+        <f>M165*P165+K165*V165</f>
+        <v/>
+      </c>
+      <c r="V165" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W165" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -22938,10 +23430,13 @@
         <v/>
       </c>
       <c r="U166" s="48">
-        <f>M166*P166+K166*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V166" s="37" t="n">
+        <f>M166*P166+K166*V166</f>
+        <v/>
+      </c>
+      <c r="V166" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W166" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23023,10 +23518,13 @@
         <v/>
       </c>
       <c r="U167" s="48">
-        <f>M167*P167+K167*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V167" s="37" t="n">
+        <f>M167*P167+K167*V167</f>
+        <v/>
+      </c>
+      <c r="V167" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W167" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23108,10 +23606,13 @@
         <v/>
       </c>
       <c r="U168" s="48">
-        <f>M168*P168+K168*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V168" s="37" t="n">
+        <f>M168*P168+K168*V168</f>
+        <v/>
+      </c>
+      <c r="V168" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W168" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23193,10 +23694,13 @@
         <v/>
       </c>
       <c r="U169" s="48">
-        <f>M169*P169+K169*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V169" s="37" t="n">
+        <f>M169*P169+K169*V169</f>
+        <v/>
+      </c>
+      <c r="V169" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W169" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23278,10 +23782,13 @@
         <v/>
       </c>
       <c r="U170" s="48">
-        <f>M170*P170+K170*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V170" s="37" t="n">
+        <f>M170*P170+K170*V170</f>
+        <v/>
+      </c>
+      <c r="V170" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W170" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23363,10 +23870,13 @@
         <v/>
       </c>
       <c r="U171" s="48">
-        <f>M171*P171+K171*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V171" s="37" t="n">
+        <f>M171*P171+K171*V171</f>
+        <v/>
+      </c>
+      <c r="V171" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W171" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23448,10 +23958,13 @@
         <v/>
       </c>
       <c r="U172" s="48">
-        <f>M172*P172+K172*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V172" s="37" t="n">
+        <f>M172*P172+K172*V172</f>
+        <v/>
+      </c>
+      <c r="V172" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W172" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23533,10 +24046,13 @@
         <v/>
       </c>
       <c r="U173" s="48">
-        <f>M173*P173+K173*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V173" s="37" t="n">
+        <f>M173*P173+K173*V173</f>
+        <v/>
+      </c>
+      <c r="V173" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W173" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23618,10 +24134,13 @@
         <v/>
       </c>
       <c r="U174" s="48">
-        <f>M174*P174+K174*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V174" s="37" t="n">
+        <f>M174*P174+K174*V174</f>
+        <v/>
+      </c>
+      <c r="V174" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W174" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23703,10 +24222,13 @@
         <v/>
       </c>
       <c r="U175" s="48">
-        <f>M175*P175+K175*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V175" s="37" t="n">
+        <f>M175*P175+K175*V175</f>
+        <v/>
+      </c>
+      <c r="V175" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W175" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23788,10 +24310,13 @@
         <v/>
       </c>
       <c r="U176" s="48">
-        <f>M176*P176+K176*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V176" s="37" t="n">
+        <f>M176*P176+K176*V176</f>
+        <v/>
+      </c>
+      <c r="V176" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W176" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -23873,17 +24398,20 @@
         <v/>
       </c>
       <c r="U177" s="48">
-        <f>M177*P177+K177*'01_Cadrage'!$D$30</f>
-        <v/>
-      </c>
-      <c r="V177" s="37" t="n">
+        <f>M177*P177+K177*V177</f>
+        <v/>
+      </c>
+      <c r="V177" s="47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W177" s="37" t="n">
         <v>2024</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
